--- a/s60_signal/position-01288-601288.xlsx
+++ b/s60_signal/position-01288-601288.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3666" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3681" uniqueCount="455">
   <si>
     <t>trade_time</t>
   </si>
@@ -565,10 +565,10 @@
     <t>2021-07-09</t>
   </si>
   <si>
-    <t>2021-07-15</t>
+    <t>2021-07-22</t>
   </si>
   <si>
-    <t>2021-07-16</t>
+    <t>2021-07-15</t>
   </si>
   <si>
     <t>2017-05-12</t>
@@ -994,6 +994,9 @@
     <t>2021-07-14</t>
   </si>
   <si>
+    <t>2021-07-23</t>
+  </si>
+  <si>
     <t>2021-07-20</t>
   </si>
   <si>
@@ -1374,6 +1377,9 @@
   <si>
     <t>2021-07-08</t>
   </si>
+  <si>
+    <t>2021-07-16</t>
+  </si>
 </sst>
 </file>
 
@@ -1730,7 +1736,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1218"/>
+  <dimension ref="A1:P1223"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1827,7 +1833,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1877,7 +1883,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1927,7 +1933,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1977,7 +1983,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2177,7 +2183,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2227,7 +2233,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2277,7 +2283,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2327,7 +2333,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2377,7 +2383,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2427,7 +2433,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2477,7 +2483,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2527,7 +2533,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2577,7 +2583,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2627,7 +2633,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2677,7 +2683,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2727,7 +2733,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2777,7 +2783,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2827,7 +2833,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -3127,7 +3133,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3177,7 +3183,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3227,7 +3233,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3277,7 +3283,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3327,7 +3333,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3377,7 +3383,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3427,7 +3433,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3777,7 +3783,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3827,7 +3833,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3877,7 +3883,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3927,7 +3933,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3977,7 +3983,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -4027,7 +4033,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4077,7 +4083,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4127,7 +4133,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4177,7 +4183,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4227,7 +4233,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4277,7 +4283,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4327,7 +4333,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4377,7 +4383,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4427,7 +4433,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4477,7 +4483,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4527,7 +4533,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4577,7 +4583,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4627,7 +4633,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4977,7 +4983,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -5027,7 +5033,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -5077,7 +5083,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -5127,7 +5133,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -5177,7 +5183,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5227,7 +5233,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5527,7 +5533,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5577,7 +5583,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5627,7 +5633,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5677,7 +5683,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5727,7 +5733,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5777,7 +5783,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5827,7 +5833,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5877,7 +5883,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5927,7 +5933,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5977,7 +5983,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -6027,7 +6033,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -6077,7 +6083,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -6127,7 +6133,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6177,7 +6183,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6227,7 +6233,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6277,7 +6283,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6327,7 +6333,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6377,7 +6383,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6427,7 +6433,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6477,7 +6483,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6527,7 +6533,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6577,7 +6583,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6627,7 +6633,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6677,7 +6683,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6727,7 +6733,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6777,7 +6783,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6827,7 +6833,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -7277,7 +7283,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7327,7 +7333,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7377,7 +7383,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7427,7 +7433,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7477,7 +7483,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7527,7 +7533,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7577,7 +7583,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7627,7 +7633,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7677,7 +7683,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7727,7 +7733,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7777,7 +7783,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7827,7 +7833,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7877,7 +7883,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7927,7 +7933,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7977,7 +7983,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -8027,7 +8033,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -8077,7 +8083,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -8127,7 +8133,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8177,7 +8183,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8227,7 +8233,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8277,7 +8283,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8327,7 +8333,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8377,7 +8383,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8427,7 +8433,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8477,7 +8483,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8527,7 +8533,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8577,7 +8583,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8627,7 +8633,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8677,7 +8683,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8727,7 +8733,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8777,7 +8783,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -9127,7 +9133,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9177,7 +9183,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9227,7 +9233,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9277,7 +9283,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9327,7 +9333,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9377,7 +9383,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9427,7 +9433,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9477,7 +9483,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9527,7 +9533,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9577,7 +9583,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9777,7 +9783,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9827,7 +9833,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9877,7 +9883,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -10627,7 +10633,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10677,7 +10683,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10727,7 +10733,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10777,7 +10783,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -11077,7 +11083,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -11127,7 +11133,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -11177,7 +11183,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11227,7 +11233,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11277,7 +11283,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11327,7 +11333,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11377,7 +11383,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11427,7 +11433,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11477,7 +11483,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11527,7 +11533,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11577,7 +11583,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11627,7 +11633,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11677,7 +11683,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11727,7 +11733,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11777,7 +11783,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11827,7 +11833,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11877,7 +11883,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11927,7 +11933,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11977,7 +11983,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -12027,7 +12033,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -12077,7 +12083,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -12127,7 +12133,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -12177,7 +12183,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -12227,7 +12233,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12277,7 +12283,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12327,7 +12333,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12377,7 +12383,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12427,7 +12433,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12477,7 +12483,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12527,7 +12533,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12827,7 +12833,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12877,7 +12883,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12927,7 +12933,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12977,7 +12983,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -13027,7 +13033,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -13077,7 +13083,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -13127,7 +13133,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -13177,7 +13183,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -13227,7 +13233,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13277,7 +13283,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13327,7 +13333,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13377,7 +13383,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13427,7 +13433,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13477,7 +13483,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13527,7 +13533,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13577,7 +13583,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13627,7 +13633,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13677,7 +13683,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13727,7 +13733,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13777,7 +13783,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13827,7 +13833,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13877,7 +13883,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13927,7 +13933,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13977,7 +13983,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -14027,7 +14033,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -14077,7 +14083,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -14127,7 +14133,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14177,7 +14183,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -14227,7 +14233,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14577,7 +14583,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14627,7 +14633,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14677,7 +14683,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14727,7 +14733,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14777,7 +14783,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14827,7 +14833,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14877,7 +14883,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14927,7 +14933,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14977,7 +14983,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -15027,7 +15033,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -15077,7 +15083,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -15377,7 +15383,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15427,7 +15433,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15477,7 +15483,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15527,7 +15533,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15577,7 +15583,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15627,7 +15633,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15677,7 +15683,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15727,7 +15733,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15777,7 +15783,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15827,7 +15833,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15877,7 +15883,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15927,7 +15933,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15977,7 +15983,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -16027,7 +16033,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -16077,7 +16083,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -17177,7 +17183,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17227,7 +17233,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17277,7 +17283,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17327,7 +17333,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17377,7 +17383,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17427,7 +17433,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17477,7 +17483,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17527,7 +17533,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17577,7 +17583,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17627,7 +17633,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -20327,7 +20333,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20377,7 +20383,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20427,7 +20433,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20477,7 +20483,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20527,7 +20533,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20577,7 +20583,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20627,7 +20633,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -20677,7 +20683,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20727,7 +20733,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20777,7 +20783,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20827,7 +20833,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20877,7 +20883,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -24177,7 +24183,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24227,7 +24233,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24277,7 +24283,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24327,7 +24333,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24377,7 +24383,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24427,7 +24433,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24477,7 +24483,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -24527,7 +24533,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24577,7 +24583,7 @@
         <v>1</v>
       </c>
       <c r="P457" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="458" spans="1:16">
@@ -24627,7 +24633,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24677,7 +24683,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24727,7 +24733,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24777,7 +24783,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24827,7 +24833,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24877,7 +24883,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24927,7 +24933,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -24977,7 +24983,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -25027,7 +25033,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -25077,7 +25083,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -25127,7 +25133,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -25177,7 +25183,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -25227,7 +25233,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -25277,7 +25283,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -25327,7 +25333,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25377,7 +25383,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25427,7 +25433,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25477,7 +25483,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25527,7 +25533,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25577,7 +25583,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25627,7 +25633,7 @@
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -25677,7 +25683,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -25727,7 +25733,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -25777,7 +25783,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -25827,7 +25833,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -25877,7 +25883,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25927,7 +25933,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25977,7 +25983,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -26027,7 +26033,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -26077,7 +26083,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -26127,7 +26133,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -26177,7 +26183,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26227,7 +26233,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26277,7 +26283,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26327,7 +26333,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26377,7 +26383,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26427,7 +26433,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26477,7 +26483,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26527,7 +26533,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26577,7 +26583,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -26627,7 +26633,7 @@
         <v>1</v>
       </c>
       <c r="P498" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -26677,7 +26683,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26727,7 +26733,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26777,7 +26783,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26827,7 +26833,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26877,7 +26883,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -26927,7 +26933,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -26977,7 +26983,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -27027,7 +27033,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -27077,7 +27083,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -27127,7 +27133,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -27177,7 +27183,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -27227,7 +27233,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -27277,7 +27283,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -27327,7 +27333,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27377,7 +27383,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27427,7 +27433,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27477,7 +27483,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27527,7 +27533,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27577,7 +27583,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -27627,7 +27633,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27677,7 +27683,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27727,7 +27733,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27777,7 +27783,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -27827,7 +27833,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -27877,7 +27883,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -27927,7 +27933,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -27977,7 +27983,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -28027,7 +28033,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -28077,7 +28083,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -28127,7 +28133,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -28177,7 +28183,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -28227,7 +28233,7 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -28277,7 +28283,7 @@
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="532" spans="1:16">
@@ -28327,7 +28333,7 @@
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="533" spans="1:16">
@@ -28377,7 +28383,7 @@
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="534" spans="1:16">
@@ -28427,7 +28433,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -28477,7 +28483,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -28977,7 +28983,7 @@
         <v>1</v>
       </c>
       <c r="P545" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="546" spans="1:16">
@@ -29027,7 +29033,7 @@
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -29077,7 +29083,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -29127,7 +29133,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -29177,7 +29183,7 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -29227,7 +29233,7 @@
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -29277,7 +29283,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -29327,7 +29333,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29377,7 +29383,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29427,7 +29433,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29477,7 +29483,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29527,7 +29533,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -29577,7 +29583,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -29627,7 +29633,7 @@
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -29677,7 +29683,7 @@
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="560" spans="1:16">
@@ -29727,7 +29733,7 @@
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -29777,7 +29783,7 @@
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="562" spans="1:16">
@@ -29827,7 +29833,7 @@
         <v>1</v>
       </c>
       <c r="P562" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="563" spans="1:16">
@@ -29877,7 +29883,7 @@
         <v>1</v>
       </c>
       <c r="P563" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="564" spans="1:16">
@@ -29927,7 +29933,7 @@
         <v>1</v>
       </c>
       <c r="P564" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="565" spans="1:16">
@@ -29977,7 +29983,7 @@
         <v>1</v>
       </c>
       <c r="P565" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="566" spans="1:16">
@@ -30027,7 +30033,7 @@
         <v>1</v>
       </c>
       <c r="P566" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="567" spans="1:16">
@@ -30077,7 +30083,7 @@
         <v>1</v>
       </c>
       <c r="P567" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="568" spans="1:16">
@@ -30127,7 +30133,7 @@
         <v>1</v>
       </c>
       <c r="P568" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="569" spans="1:16">
@@ -30377,7 +30383,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -30427,7 +30433,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -30477,7 +30483,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -30527,7 +30533,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -30577,7 +30583,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -30627,7 +30633,7 @@
         <v>1</v>
       </c>
       <c r="P578" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="579" spans="1:16">
@@ -30677,7 +30683,7 @@
         <v>1</v>
       </c>
       <c r="P579" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="580" spans="1:16">
@@ -30727,7 +30733,7 @@
         <v>1</v>
       </c>
       <c r="P580" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="581" spans="1:16">
@@ -30777,7 +30783,7 @@
         <v>1</v>
       </c>
       <c r="P581" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="582" spans="1:16">
@@ -30827,7 +30833,7 @@
         <v>1</v>
       </c>
       <c r="P582" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="583" spans="1:16">
@@ -31127,7 +31133,7 @@
         <v>1</v>
       </c>
       <c r="P588" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="589" spans="1:16">
@@ -31177,7 +31183,7 @@
         <v>1</v>
       </c>
       <c r="P589" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="590" spans="1:16">
@@ -31227,7 +31233,7 @@
         <v>1</v>
       </c>
       <c r="P590" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="591" spans="1:16">
@@ -31277,7 +31283,7 @@
         <v>1</v>
       </c>
       <c r="P591" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="592" spans="1:16">
@@ -31327,7 +31333,7 @@
         <v>1</v>
       </c>
       <c r="P592" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="593" spans="1:16">
@@ -31377,7 +31383,7 @@
         <v>1</v>
       </c>
       <c r="P593" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="594" spans="1:16">
@@ -31427,7 +31433,7 @@
         <v>1</v>
       </c>
       <c r="P594" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="595" spans="1:16">
@@ -31477,7 +31483,7 @@
         <v>1</v>
       </c>
       <c r="P595" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="596" spans="1:16">
@@ -31527,7 +31533,7 @@
         <v>1</v>
       </c>
       <c r="P596" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="597" spans="1:16">
@@ -31577,7 +31583,7 @@
         <v>1</v>
       </c>
       <c r="P597" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="598" spans="1:16">
@@ -31627,7 +31633,7 @@
         <v>1</v>
       </c>
       <c r="P598" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="599" spans="1:16">
@@ -31677,7 +31683,7 @@
         <v>1</v>
       </c>
       <c r="P599" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="600" spans="1:16">
@@ -31727,7 +31733,7 @@
         <v>1</v>
       </c>
       <c r="P600" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="601" spans="1:16">
@@ -31777,7 +31783,7 @@
         <v>1</v>
       </c>
       <c r="P601" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="602" spans="1:16">
@@ -31827,7 +31833,7 @@
         <v>1</v>
       </c>
       <c r="P602" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="603" spans="1:16">
@@ -31877,7 +31883,7 @@
         <v>1</v>
       </c>
       <c r="P603" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="604" spans="1:16">
@@ -31927,7 +31933,7 @@
         <v>1</v>
       </c>
       <c r="P604" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="605" spans="1:16">
@@ -31977,7 +31983,7 @@
         <v>1</v>
       </c>
       <c r="P605" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="606" spans="1:16">
@@ -32027,7 +32033,7 @@
         <v>1</v>
       </c>
       <c r="P606" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="607" spans="1:16">
@@ -32077,7 +32083,7 @@
         <v>1</v>
       </c>
       <c r="P607" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="608" spans="1:16">
@@ -32127,7 +32133,7 @@
         <v>1</v>
       </c>
       <c r="P608" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="609" spans="1:16">
@@ -32177,7 +32183,7 @@
         <v>1</v>
       </c>
       <c r="P609" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="610" spans="1:16">
@@ -32227,7 +32233,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -32277,7 +32283,7 @@
         <v>1</v>
       </c>
       <c r="P611" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="612" spans="1:16">
@@ -32327,7 +32333,7 @@
         <v>1</v>
       </c>
       <c r="P612" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="613" spans="1:16">
@@ -32377,7 +32383,7 @@
         <v>1</v>
       </c>
       <c r="P613" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="614" spans="1:16">
@@ -32427,7 +32433,7 @@
         <v>1</v>
       </c>
       <c r="P614" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="615" spans="1:16">
@@ -32477,7 +32483,7 @@
         <v>1</v>
       </c>
       <c r="P615" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="616" spans="1:16">
@@ -32527,7 +32533,7 @@
         <v>1</v>
       </c>
       <c r="P616" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="617" spans="1:16">
@@ -32577,7 +32583,7 @@
         <v>1</v>
       </c>
       <c r="P617" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="618" spans="1:16">
@@ -32627,7 +32633,7 @@
         <v>1</v>
       </c>
       <c r="P618" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="619" spans="1:16">
@@ -32677,7 +32683,7 @@
         <v>1</v>
       </c>
       <c r="P619" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="620" spans="1:16">
@@ -32727,7 +32733,7 @@
         <v>1</v>
       </c>
       <c r="P620" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="621" spans="1:16">
@@ -33127,7 +33133,7 @@
         <v>1</v>
       </c>
       <c r="P628" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="629" spans="1:16">
@@ -33177,7 +33183,7 @@
         <v>1</v>
       </c>
       <c r="P629" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="630" spans="1:16">
@@ -33227,7 +33233,7 @@
         <v>1</v>
       </c>
       <c r="P630" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="631" spans="1:16">
@@ -33277,7 +33283,7 @@
         <v>1</v>
       </c>
       <c r="P631" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="632" spans="1:16">
@@ -33327,7 +33333,7 @@
         <v>1</v>
       </c>
       <c r="P632" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -33377,7 +33383,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -33427,7 +33433,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -34127,7 +34133,7 @@
         <v>1</v>
       </c>
       <c r="P648" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="649" spans="1:16">
@@ -34177,7 +34183,7 @@
         <v>1</v>
       </c>
       <c r="P649" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="650" spans="1:16">
@@ -34227,7 +34233,7 @@
         <v>1</v>
       </c>
       <c r="P650" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="651" spans="1:16">
@@ -34277,7 +34283,7 @@
         <v>1</v>
       </c>
       <c r="P651" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="652" spans="1:16">
@@ -34327,7 +34333,7 @@
         <v>1</v>
       </c>
       <c r="P652" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="653" spans="1:16">
@@ -34377,7 +34383,7 @@
         <v>1</v>
       </c>
       <c r="P653" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="654" spans="1:16">
@@ -34427,7 +34433,7 @@
         <v>1</v>
       </c>
       <c r="P654" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="655" spans="1:16">
@@ -35177,7 +35183,7 @@
         <v>1</v>
       </c>
       <c r="P669" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="670" spans="1:16">
@@ -35227,7 +35233,7 @@
         <v>1</v>
       </c>
       <c r="P670" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="671" spans="1:16">
@@ -35277,7 +35283,7 @@
         <v>1</v>
       </c>
       <c r="P671" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="672" spans="1:16">
@@ -35327,7 +35333,7 @@
         <v>1</v>
       </c>
       <c r="P672" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="673" spans="1:16">
@@ -35377,7 +35383,7 @@
         <v>1</v>
       </c>
       <c r="P673" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="674" spans="1:16">
@@ -35427,7 +35433,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -35477,7 +35483,7 @@
         <v>1</v>
       </c>
       <c r="P675" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="676" spans="1:16">
@@ -35527,7 +35533,7 @@
         <v>1</v>
       </c>
       <c r="P676" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="677" spans="1:16">
@@ -35577,7 +35583,7 @@
         <v>1</v>
       </c>
       <c r="P677" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="678" spans="1:16">
@@ -35627,7 +35633,7 @@
         <v>1</v>
       </c>
       <c r="P678" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="679" spans="1:16">
@@ -35677,7 +35683,7 @@
         <v>1</v>
       </c>
       <c r="P679" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="680" spans="1:16">
@@ -35727,7 +35733,7 @@
         <v>1</v>
       </c>
       <c r="P680" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="681" spans="1:16">
@@ -35777,7 +35783,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -35827,7 +35833,7 @@
         <v>1</v>
       </c>
       <c r="P682" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -35877,7 +35883,7 @@
         <v>1</v>
       </c>
       <c r="P683" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="684" spans="1:16">
@@ -36127,7 +36133,7 @@
         <v>1</v>
       </c>
       <c r="P688" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="689" spans="1:16">
@@ -36177,7 +36183,7 @@
         <v>1</v>
       </c>
       <c r="P689" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="690" spans="1:16">
@@ -36227,7 +36233,7 @@
         <v>1</v>
       </c>
       <c r="P690" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="691" spans="1:16">
@@ -36277,7 +36283,7 @@
         <v>1</v>
       </c>
       <c r="P691" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="692" spans="1:16">
@@ -36327,7 +36333,7 @@
         <v>1</v>
       </c>
       <c r="P692" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="693" spans="1:16">
@@ -36377,7 +36383,7 @@
         <v>1</v>
       </c>
       <c r="P693" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -36427,7 +36433,7 @@
         <v>1</v>
       </c>
       <c r="P694" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="695" spans="1:16">
@@ -36477,7 +36483,7 @@
         <v>1</v>
       </c>
       <c r="P695" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="696" spans="1:16">
@@ -36527,7 +36533,7 @@
         <v>1</v>
       </c>
       <c r="P696" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="697" spans="1:16">
@@ -36577,7 +36583,7 @@
         <v>1</v>
       </c>
       <c r="P697" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -36627,7 +36633,7 @@
         <v>1</v>
       </c>
       <c r="P698" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -36677,7 +36683,7 @@
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -36727,7 +36733,7 @@
         <v>1</v>
       </c>
       <c r="P700" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="701" spans="1:16">
@@ -36777,7 +36783,7 @@
         <v>1</v>
       </c>
       <c r="P701" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="702" spans="1:16">
@@ -36827,7 +36833,7 @@
         <v>1</v>
       </c>
       <c r="P702" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="703" spans="1:16">
@@ -38377,7 +38383,7 @@
         <v>1</v>
       </c>
       <c r="P733" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="734" spans="1:16">
@@ -38427,7 +38433,7 @@
         <v>1</v>
       </c>
       <c r="P734" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="735" spans="1:16">
@@ -38477,7 +38483,7 @@
         <v>1</v>
       </c>
       <c r="P735" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="736" spans="1:16">
@@ -38527,7 +38533,7 @@
         <v>1</v>
       </c>
       <c r="P736" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="737" spans="1:16">
@@ -38577,7 +38583,7 @@
         <v>1</v>
       </c>
       <c r="P737" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="738" spans="1:16">
@@ -38877,7 +38883,7 @@
         <v>1</v>
       </c>
       <c r="P743" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="744" spans="1:16">
@@ -38927,7 +38933,7 @@
         <v>1</v>
       </c>
       <c r="P744" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="745" spans="1:16">
@@ -38977,7 +38983,7 @@
         <v>1</v>
       </c>
       <c r="P745" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="746" spans="1:16">
@@ -39027,7 +39033,7 @@
         <v>1</v>
       </c>
       <c r="P746" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="747" spans="1:16">
@@ -39077,7 +39083,7 @@
         <v>1</v>
       </c>
       <c r="P747" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="748" spans="1:16">
@@ -39127,7 +39133,7 @@
         <v>1</v>
       </c>
       <c r="P748" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="749" spans="1:16">
@@ -39177,7 +39183,7 @@
         <v>1</v>
       </c>
       <c r="P749" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="750" spans="1:16">
@@ -39227,7 +39233,7 @@
         <v>1</v>
       </c>
       <c r="P750" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="751" spans="1:16">
@@ -39277,7 +39283,7 @@
         <v>1</v>
       </c>
       <c r="P751" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="752" spans="1:16">
@@ -39327,7 +39333,7 @@
         <v>1</v>
       </c>
       <c r="P752" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="753" spans="1:16">
@@ -39377,7 +39383,7 @@
         <v>1</v>
       </c>
       <c r="P753" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -39427,7 +39433,7 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -39477,7 +39483,7 @@
         <v>1</v>
       </c>
       <c r="P755" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="756" spans="1:16">
@@ -39527,7 +39533,7 @@
         <v>1</v>
       </c>
       <c r="P756" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="757" spans="1:16">
@@ -39577,7 +39583,7 @@
         <v>1</v>
       </c>
       <c r="P757" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="758" spans="1:16">
@@ -39627,7 +39633,7 @@
         <v>1</v>
       </c>
       <c r="P758" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="759" spans="1:16">
@@ -40277,7 +40283,7 @@
         <v>1</v>
       </c>
       <c r="P771" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="772" spans="1:16">
@@ -40327,7 +40333,7 @@
         <v>1</v>
       </c>
       <c r="P772" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="773" spans="1:16">
@@ -40377,7 +40383,7 @@
         <v>1</v>
       </c>
       <c r="P773" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="774" spans="1:16">
@@ -40427,7 +40433,7 @@
         <v>1</v>
       </c>
       <c r="P774" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="775" spans="1:16">
@@ -40477,7 +40483,7 @@
         <v>1</v>
       </c>
       <c r="P775" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="776" spans="1:16">
@@ -40527,7 +40533,7 @@
         <v>1</v>
       </c>
       <c r="P776" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="777" spans="1:16">
@@ -40577,7 +40583,7 @@
         <v>1</v>
       </c>
       <c r="P777" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="778" spans="1:16">
@@ -40627,7 +40633,7 @@
         <v>1</v>
       </c>
       <c r="P778" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="779" spans="1:16">
@@ -40677,7 +40683,7 @@
         <v>1</v>
       </c>
       <c r="P779" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="780" spans="1:16">
@@ -40727,7 +40733,7 @@
         <v>1</v>
       </c>
       <c r="P780" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="781" spans="1:16">
@@ -40777,7 +40783,7 @@
         <v>1</v>
       </c>
       <c r="P781" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="782" spans="1:16">
@@ -40827,7 +40833,7 @@
         <v>1</v>
       </c>
       <c r="P782" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="783" spans="1:16">
@@ -41977,7 +41983,7 @@
         <v>1</v>
       </c>
       <c r="P805" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="806" spans="1:16">
@@ -42027,7 +42033,7 @@
         <v>1</v>
       </c>
       <c r="P806" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="807" spans="1:16">
@@ -42077,7 +42083,7 @@
         <v>1</v>
       </c>
       <c r="P807" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="808" spans="1:16">
@@ -42127,7 +42133,7 @@
         <v>1</v>
       </c>
       <c r="P808" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="809" spans="1:16">
@@ -42177,7 +42183,7 @@
         <v>1</v>
       </c>
       <c r="P809" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="810" spans="1:16">
@@ -42227,7 +42233,7 @@
         <v>1</v>
       </c>
       <c r="P810" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="811" spans="1:16">
@@ -42277,7 +42283,7 @@
         <v>1</v>
       </c>
       <c r="P811" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="812" spans="1:16">
@@ -42327,7 +42333,7 @@
         <v>1</v>
       </c>
       <c r="P812" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="813" spans="1:16">
@@ -42377,7 +42383,7 @@
         <v>1</v>
       </c>
       <c r="P813" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="814" spans="1:16">
@@ -42427,7 +42433,7 @@
         <v>1</v>
       </c>
       <c r="P814" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="815" spans="1:16">
@@ -42477,7 +42483,7 @@
         <v>1</v>
       </c>
       <c r="P815" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="816" spans="1:16">
@@ -42527,7 +42533,7 @@
         <v>1</v>
       </c>
       <c r="P816" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="817" spans="1:16">
@@ -42577,7 +42583,7 @@
         <v>1</v>
       </c>
       <c r="P817" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="818" spans="1:16">
@@ -43727,7 +43733,7 @@
         <v>1</v>
       </c>
       <c r="P840" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="841" spans="1:16">
@@ -43827,7 +43833,7 @@
         <v>1</v>
       </c>
       <c r="P842" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="843" spans="1:16">
@@ -43877,7 +43883,7 @@
         <v>1</v>
       </c>
       <c r="P843" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="844" spans="1:16">
@@ -43977,7 +43983,7 @@
         <v>1</v>
       </c>
       <c r="P845" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="846" spans="1:16">
@@ -44077,7 +44083,7 @@
         <v>1</v>
       </c>
       <c r="P847" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="848" spans="1:16">
@@ -44127,7 +44133,7 @@
         <v>1</v>
       </c>
       <c r="P848" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="849" spans="1:16">
@@ -44977,7 +44983,7 @@
         <v>1</v>
       </c>
       <c r="P865" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="866" spans="1:16">
@@ -45027,7 +45033,7 @@
         <v>1</v>
       </c>
       <c r="P866" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="867" spans="1:16">
@@ -45077,7 +45083,7 @@
         <v>1</v>
       </c>
       <c r="P867" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="868" spans="1:16">
@@ -45127,7 +45133,7 @@
         <v>1</v>
       </c>
       <c r="P868" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="869" spans="1:16">
@@ -45177,7 +45183,7 @@
         <v>1</v>
       </c>
       <c r="P869" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="870" spans="1:16">
@@ -45227,7 +45233,7 @@
         <v>1</v>
       </c>
       <c r="P870" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="871" spans="1:16">
@@ -45277,7 +45283,7 @@
         <v>1</v>
       </c>
       <c r="P871" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="872" spans="1:16">
@@ -45327,7 +45333,7 @@
         <v>1</v>
       </c>
       <c r="P872" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="873" spans="1:16">
@@ -45377,7 +45383,7 @@
         <v>1</v>
       </c>
       <c r="P873" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="874" spans="1:16">
@@ -45427,7 +45433,7 @@
         <v>1</v>
       </c>
       <c r="P874" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="875" spans="1:16">
@@ -45477,7 +45483,7 @@
         <v>1</v>
       </c>
       <c r="P875" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="876" spans="1:16">
@@ -45527,7 +45533,7 @@
         <v>1</v>
       </c>
       <c r="P876" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="877" spans="1:16">
@@ -45577,7 +45583,7 @@
         <v>1</v>
       </c>
       <c r="P877" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="878" spans="1:16">
@@ -45627,7 +45633,7 @@
         <v>1</v>
       </c>
       <c r="P878" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="879" spans="1:16">
@@ -45927,7 +45933,7 @@
         <v>1</v>
       </c>
       <c r="P884" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="885" spans="1:16">
@@ -45977,7 +45983,7 @@
         <v>1</v>
       </c>
       <c r="P885" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="886" spans="1:16">
@@ -46027,7 +46033,7 @@
         <v>1</v>
       </c>
       <c r="P886" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="887" spans="1:16">
@@ -46077,7 +46083,7 @@
         <v>1</v>
       </c>
       <c r="P887" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="888" spans="1:16">
@@ -46127,7 +46133,7 @@
         <v>1</v>
       </c>
       <c r="P888" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="889" spans="1:16">
@@ -46177,7 +46183,7 @@
         <v>1</v>
       </c>
       <c r="P889" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="890" spans="1:16">
@@ -46227,7 +46233,7 @@
         <v>1</v>
       </c>
       <c r="P890" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="891" spans="1:16">
@@ -46277,7 +46283,7 @@
         <v>1</v>
       </c>
       <c r="P891" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="892" spans="1:16">
@@ -46327,7 +46333,7 @@
         <v>1</v>
       </c>
       <c r="P892" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="893" spans="1:16">
@@ -46377,7 +46383,7 @@
         <v>1</v>
       </c>
       <c r="P893" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="894" spans="1:16">
@@ -46677,7 +46683,7 @@
         <v>1</v>
       </c>
       <c r="P899" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="900" spans="1:16">
@@ -46727,7 +46733,7 @@
         <v>1</v>
       </c>
       <c r="P900" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="901" spans="1:16">
@@ -46777,7 +46783,7 @@
         <v>1</v>
       </c>
       <c r="P901" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="902" spans="1:16">
@@ -46827,7 +46833,7 @@
         <v>1</v>
       </c>
       <c r="P902" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="903" spans="1:16">
@@ -46877,7 +46883,7 @@
         <v>1</v>
       </c>
       <c r="P903" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="904" spans="1:16">
@@ -48477,7 +48483,7 @@
         <v>1</v>
       </c>
       <c r="P935" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="936" spans="1:16">
@@ -48527,7 +48533,7 @@
         <v>1</v>
       </c>
       <c r="P936" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="937" spans="1:16">
@@ -48577,7 +48583,7 @@
         <v>1</v>
       </c>
       <c r="P937" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="938" spans="1:16">
@@ -48627,7 +48633,7 @@
         <v>1</v>
       </c>
       <c r="P938" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="939" spans="1:16">
@@ -50827,7 +50833,7 @@
         <v>1</v>
       </c>
       <c r="P982" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="983" spans="1:16">
@@ -50877,7 +50883,7 @@
         <v>1</v>
       </c>
       <c r="P983" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="984" spans="1:16">
@@ -50927,7 +50933,7 @@
         <v>1</v>
       </c>
       <c r="P984" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="985" spans="1:16">
@@ -50977,7 +50983,7 @@
         <v>1</v>
       </c>
       <c r="P985" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="986" spans="1:16">
@@ -51027,7 +51033,7 @@
         <v>1</v>
       </c>
       <c r="P986" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="987" spans="1:16">
@@ -51077,7 +51083,7 @@
         <v>1</v>
       </c>
       <c r="P987" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="988" spans="1:16">
@@ -51127,7 +51133,7 @@
         <v>1</v>
       </c>
       <c r="P988" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="989" spans="1:16">
@@ -51177,7 +51183,7 @@
         <v>1</v>
       </c>
       <c r="P989" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="990" spans="1:16">
@@ -51227,7 +51233,7 @@
         <v>1</v>
       </c>
       <c r="P990" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="991" spans="1:16">
@@ -51277,7 +51283,7 @@
         <v>1</v>
       </c>
       <c r="P991" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="992" spans="1:16">
@@ -51327,7 +51333,7 @@
         <v>1</v>
       </c>
       <c r="P992" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="993" spans="1:16">
@@ -51377,7 +51383,7 @@
         <v>1</v>
       </c>
       <c r="P993" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="994" spans="1:16">
@@ -51427,7 +51433,7 @@
         <v>1</v>
       </c>
       <c r="P994" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="995" spans="1:16">
@@ -51477,7 +51483,7 @@
         <v>1</v>
       </c>
       <c r="P995" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="996" spans="1:16">
@@ -51527,7 +51533,7 @@
         <v>1</v>
       </c>
       <c r="P996" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="997" spans="1:16">
@@ -51827,7 +51833,7 @@
         <v>1</v>
       </c>
       <c r="P1002" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="1003" spans="1:16">
@@ -51877,7 +51883,7 @@
         <v>1</v>
       </c>
       <c r="P1003" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="1004" spans="1:16">
@@ -51927,7 +51933,7 @@
         <v>1</v>
       </c>
       <c r="P1004" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="1005" spans="1:16">
@@ -51977,7 +51983,7 @@
         <v>1</v>
       </c>
       <c r="P1005" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="1006" spans="1:16">
@@ -52027,7 +52033,7 @@
         <v>1</v>
       </c>
       <c r="P1006" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="1007" spans="1:16">
@@ -52677,7 +52683,7 @@
         <v>1</v>
       </c>
       <c r="P1019" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="1020" spans="1:16">
@@ -52727,7 +52733,7 @@
         <v>1</v>
       </c>
       <c r="P1020" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="1021" spans="1:16">
@@ -52777,7 +52783,7 @@
         <v>1</v>
       </c>
       <c r="P1021" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="1022" spans="1:16">
@@ -52827,7 +52833,7 @@
         <v>1</v>
       </c>
       <c r="P1022" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="1023" spans="1:16">
@@ -52877,7 +52883,7 @@
         <v>1</v>
       </c>
       <c r="P1023" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="1024" spans="1:16">
@@ -52927,7 +52933,7 @@
         <v>1</v>
       </c>
       <c r="P1024" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="1025" spans="1:16">
@@ -52977,7 +52983,7 @@
         <v>1</v>
       </c>
       <c r="P1025" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="1026" spans="1:16">
@@ -53027,7 +53033,7 @@
         <v>1</v>
       </c>
       <c r="P1026" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="1027" spans="1:16">
@@ -53077,7 +53083,7 @@
         <v>1</v>
       </c>
       <c r="P1027" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="1028" spans="1:16">
@@ -53127,7 +53133,7 @@
         <v>1</v>
       </c>
       <c r="P1028" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="1029" spans="1:16">
@@ -53177,7 +53183,7 @@
         <v>1</v>
       </c>
       <c r="P1029" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="1030" spans="1:16">
@@ -53227,7 +53233,7 @@
         <v>1</v>
       </c>
       <c r="P1030" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="1031" spans="1:16">
@@ -53277,7 +53283,7 @@
         <v>1</v>
       </c>
       <c r="P1031" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="1032" spans="1:16">
@@ -53327,7 +53333,7 @@
         <v>1</v>
       </c>
       <c r="P1032" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="1033" spans="1:16">
@@ -53377,7 +53383,7 @@
         <v>1</v>
       </c>
       <c r="P1033" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="1034" spans="1:16">
@@ -53427,7 +53433,7 @@
         <v>1</v>
       </c>
       <c r="P1034" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="1035" spans="1:16">
@@ -53477,7 +53483,7 @@
         <v>1</v>
       </c>
       <c r="P1035" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="1036" spans="1:16">
@@ -53527,7 +53533,7 @@
         <v>1</v>
       </c>
       <c r="P1036" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="1037" spans="1:16">
@@ -53577,7 +53583,7 @@
         <v>1</v>
       </c>
       <c r="P1037" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="1038" spans="1:16">
@@ -53627,7 +53633,7 @@
         <v>1</v>
       </c>
       <c r="P1038" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="1039" spans="1:16">
@@ -54427,7 +54433,7 @@
         <v>1</v>
       </c>
       <c r="P1054" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="1055" spans="1:16">
@@ -54477,7 +54483,7 @@
         <v>1</v>
       </c>
       <c r="P1055" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="1056" spans="1:16">
@@ -54527,7 +54533,7 @@
         <v>1</v>
       </c>
       <c r="P1056" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="1057" spans="1:16">
@@ -54577,7 +54583,7 @@
         <v>1</v>
       </c>
       <c r="P1057" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="1058" spans="1:16">
@@ -54627,7 +54633,7 @@
         <v>1</v>
       </c>
       <c r="P1058" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="1059" spans="1:16">
@@ -54677,7 +54683,7 @@
         <v>1</v>
       </c>
       <c r="P1059" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="1060" spans="1:16">
@@ -54727,7 +54733,7 @@
         <v>1</v>
       </c>
       <c r="P1060" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="1061" spans="1:16">
@@ -54777,7 +54783,7 @@
         <v>1</v>
       </c>
       <c r="P1061" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="1062" spans="1:16">
@@ -54827,7 +54833,7 @@
         <v>1</v>
       </c>
       <c r="P1062" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="1063" spans="1:16">
@@ -54877,7 +54883,7 @@
         <v>1</v>
       </c>
       <c r="P1063" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="1064" spans="1:16">
@@ -54927,7 +54933,7 @@
         <v>1</v>
       </c>
       <c r="P1064" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="1065" spans="1:16">
@@ -54977,7 +54983,7 @@
         <v>1</v>
       </c>
       <c r="P1065" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="1066" spans="1:16">
@@ -55027,7 +55033,7 @@
         <v>1</v>
       </c>
       <c r="P1066" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="1067" spans="1:16">
@@ -55077,7 +55083,7 @@
         <v>1</v>
       </c>
       <c r="P1067" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="1068" spans="1:16">
@@ -55127,7 +55133,7 @@
         <v>1</v>
       </c>
       <c r="P1068" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="1069" spans="1:16">
@@ -55177,7 +55183,7 @@
         <v>1</v>
       </c>
       <c r="P1069" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="1070" spans="1:16">
@@ -55227,7 +55233,7 @@
         <v>1</v>
       </c>
       <c r="P1070" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="1071" spans="1:16">
@@ -55277,7 +55283,7 @@
         <v>1</v>
       </c>
       <c r="P1071" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="1072" spans="1:16">
@@ -55327,7 +55333,7 @@
         <v>1</v>
       </c>
       <c r="P1072" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="1073" spans="1:16">
@@ -55377,7 +55383,7 @@
         <v>1</v>
       </c>
       <c r="P1073" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="1074" spans="1:16">
@@ -55427,7 +55433,7 @@
         <v>1</v>
       </c>
       <c r="P1074" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="1075" spans="1:16">
@@ -55477,7 +55483,7 @@
         <v>1</v>
       </c>
       <c r="P1075" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="1076" spans="1:16">
@@ -55527,7 +55533,7 @@
         <v>1</v>
       </c>
       <c r="P1076" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="1077" spans="1:16">
@@ -55927,7 +55933,7 @@
         <v>1</v>
       </c>
       <c r="P1084" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="1085" spans="1:16">
@@ -55977,7 +55983,7 @@
         <v>1</v>
       </c>
       <c r="P1085" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="1086" spans="1:16">
@@ -56027,7 +56033,7 @@
         <v>1</v>
       </c>
       <c r="P1086" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="1087" spans="1:16">
@@ -56077,7 +56083,7 @@
         <v>1</v>
       </c>
       <c r="P1087" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="1088" spans="1:16">
@@ -56127,7 +56133,7 @@
         <v>1</v>
       </c>
       <c r="P1088" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="1089" spans="1:16">
@@ -56177,7 +56183,7 @@
         <v>1</v>
       </c>
       <c r="P1089" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="1090" spans="1:16">
@@ -56227,7 +56233,7 @@
         <v>1</v>
       </c>
       <c r="P1090" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="1091" spans="1:16">
@@ -56277,7 +56283,7 @@
         <v>1</v>
       </c>
       <c r="P1091" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="1092" spans="1:16">
@@ -56327,7 +56333,7 @@
         <v>1</v>
       </c>
       <c r="P1092" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="1093" spans="1:16">
@@ -56377,7 +56383,7 @@
         <v>1</v>
       </c>
       <c r="P1093" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="1094" spans="1:16">
@@ -56427,7 +56433,7 @@
         <v>1</v>
       </c>
       <c r="P1094" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="1095" spans="1:16">
@@ -56477,7 +56483,7 @@
         <v>1</v>
       </c>
       <c r="P1095" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="1096" spans="1:16">
@@ -56527,7 +56533,7 @@
         <v>1</v>
       </c>
       <c r="P1096" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="1097" spans="1:16">
@@ -56577,7 +56583,7 @@
         <v>1</v>
       </c>
       <c r="P1097" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="1098" spans="1:16">
@@ -60827,7 +60833,7 @@
         <v>1</v>
       </c>
       <c r="P1182" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="1183" spans="1:16">
@@ -60877,7 +60883,7 @@
         <v>1</v>
       </c>
       <c r="P1183" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="1184" spans="1:16">
@@ -60927,7 +60933,7 @@
         <v>1</v>
       </c>
       <c r="P1184" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="1185" spans="1:16">
@@ -60977,7 +60983,7 @@
         <v>1</v>
       </c>
       <c r="P1185" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="1186" spans="1:16">
@@ -61027,7 +61033,7 @@
         <v>1</v>
       </c>
       <c r="P1186" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="1187" spans="1:16">
@@ -61077,7 +61083,7 @@
         <v>1</v>
       </c>
       <c r="P1187" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="1188" spans="1:16">
@@ -61127,7 +61133,7 @@
         <v>1</v>
       </c>
       <c r="P1188" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="1189" spans="1:16">
@@ -61177,7 +61183,7 @@
         <v>1</v>
       </c>
       <c r="P1189" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="1190" spans="1:16">
@@ -61927,7 +61933,7 @@
         <v>1</v>
       </c>
       <c r="P1204" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="1205" spans="1:16">
@@ -61977,7 +61983,7 @@
         <v>1</v>
       </c>
       <c r="P1205" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="1206" spans="1:16">
@@ -62027,7 +62033,7 @@
         <v>1</v>
       </c>
       <c r="P1206" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="1207" spans="1:16">
@@ -62077,7 +62083,7 @@
         <v>1</v>
       </c>
       <c r="P1207" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="1208" spans="1:16">
@@ -62127,7 +62133,7 @@
         <v>1</v>
       </c>
       <c r="P1208" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="1209" spans="1:16">
@@ -62177,7 +62183,7 @@
         <v>1</v>
       </c>
       <c r="P1209" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="1210" spans="1:16">
@@ -62227,7 +62233,7 @@
         <v>1</v>
       </c>
       <c r="P1210" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="1211" spans="1:16">
@@ -62277,7 +62283,7 @@
         <v>1</v>
       </c>
       <c r="P1211" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="1212" spans="1:16">
@@ -62377,7 +62383,7 @@
         <v>1</v>
       </c>
       <c r="P1213" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="1214" spans="1:16">
@@ -62427,7 +62433,7 @@
         <v>1</v>
       </c>
       <c r="P1214" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="1215" spans="1:16">
@@ -62477,7 +62483,7 @@
         <v>1</v>
       </c>
       <c r="P1215" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="1216" spans="1:16">
@@ -62488,40 +62494,40 @@
         <v>183</v>
       </c>
       <c r="C1216">
-        <v>1.923641660546712</v>
+        <v>1.951755497771238</v>
       </c>
       <c r="D1216" t="s">
         <v>326</v>
       </c>
       <c r="E1216">
-        <v>1.943722972849945</v>
+        <v>1.937739235310592</v>
       </c>
       <c r="F1216">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1216">
-        <v>0.004076358339453288</v>
+        <v>0.004048244502228762</v>
       </c>
       <c r="H1216">
-        <v>0.004056277027150055</v>
+        <v>0.004042260764689409</v>
       </c>
       <c r="I1216">
-        <v>0.02008131230323307</v>
+        <v>0.01401626246064658</v>
       </c>
       <c r="J1216">
         <v>0.4016262460646597</v>
       </c>
       <c r="K1216">
-        <v>2.68</v>
+        <v>2.61</v>
       </c>
       <c r="L1216">
         <v>3</v>
       </c>
       <c r="M1216">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="N1216">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="O1216">
         <v>1</v>
@@ -62535,13 +62541,13 @@
         <v>0</v>
       </c>
       <c r="B1217" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C1217">
         <v>1.874172526137948</v>
       </c>
       <c r="D1217" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E1217">
         <v>1.895176770053285</v>
@@ -62582,52 +62588,302 @@
     </row>
     <row r="1218" spans="1:16">
       <c r="A1218" s="1">
+        <v>1</v>
+      </c>
+      <c r="B1218" t="s">
+        <v>183</v>
+      </c>
+      <c r="C1218">
+        <v>1.90357846761942</v>
+      </c>
+      <c r="D1218" t="s">
+        <v>326</v>
+      </c>
+      <c r="E1218">
+        <v>1.889377618836352</v>
+      </c>
+      <c r="F1218">
+        <v>-1</v>
+      </c>
+      <c r="G1218">
+        <v>0.00409642153238058</v>
+      </c>
+      <c r="H1218">
+        <v>0.004090622381163648</v>
+      </c>
+      <c r="I1218">
+        <v>0.01420084878306715</v>
+      </c>
+      <c r="J1218">
+        <v>0.4200848783067358</v>
+      </c>
+      <c r="K1218">
+        <v>2.61</v>
+      </c>
+      <c r="L1218">
+        <v>3</v>
+      </c>
+      <c r="M1218">
+        <v>2.62</v>
+      </c>
+      <c r="N1218">
+        <v>2.99</v>
+      </c>
+      <c r="O1218">
+        <v>1</v>
+      </c>
+      <c r="P1218" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:16">
+      <c r="A1219" s="1">
         <v>0</v>
       </c>
-      <c r="B1218" t="s">
+      <c r="B1219" t="s">
         <v>184</v>
       </c>
-      <c r="C1218">
-        <v>1.818814899187029</v>
-      </c>
-      <c r="D1218" t="s">
-        <v>327</v>
-      </c>
-      <c r="E1218">
+      <c r="C1219">
+        <v>1.824428438135294</v>
+      </c>
+      <c r="D1219" t="s">
+        <v>328</v>
+      </c>
+      <c r="E1219">
         <v>1.837587821290496</v>
       </c>
-      <c r="F1218">
-        <v>1</v>
-      </c>
-      <c r="G1218">
-        <v>0.004161185100812972</v>
-      </c>
-      <c r="H1218">
+      <c r="F1219">
+        <v>1</v>
+      </c>
+      <c r="G1219">
+        <v>0.004175571561864705</v>
+      </c>
+      <c r="H1219">
         <v>0.004162412178709504</v>
       </c>
-      <c r="I1218">
-        <v>0.01877292210346759</v>
-      </c>
-      <c r="J1218">
+      <c r="I1219">
+        <v>0.01315938315520193</v>
+      </c>
+      <c r="J1219">
         <v>0.4386461051733976</v>
       </c>
-      <c r="K1218">
-        <v>2.67</v>
-      </c>
-      <c r="L1218">
+      <c r="K1219">
+        <v>2.68</v>
+      </c>
+      <c r="L1219">
+        <v>3</v>
+      </c>
+      <c r="M1219">
+        <v>2.65</v>
+      </c>
+      <c r="N1219">
+        <v>3</v>
+      </c>
+      <c r="O1219">
+        <v>1</v>
+      </c>
+      <c r="P1219" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:16">
+      <c r="A1220" s="1">
+        <v>1</v>
+      </c>
+      <c r="B1220" t="s">
+        <v>183</v>
+      </c>
+      <c r="C1220">
+        <v>1.855133665497432</v>
+      </c>
+      <c r="D1220" t="s">
+        <v>326</v>
+      </c>
+      <c r="E1220">
+        <v>1.840747204445699</v>
+      </c>
+      <c r="F1220">
+        <v>-1</v>
+      </c>
+      <c r="G1220">
+        <v>0.004144866334502568</v>
+      </c>
+      <c r="H1220">
+        <v>0.004139252795554303</v>
+      </c>
+      <c r="I1220">
+        <v>0.01438646105173391</v>
+      </c>
+      <c r="J1220">
+        <v>0.4386461051733976</v>
+      </c>
+      <c r="K1220">
+        <v>2.61</v>
+      </c>
+      <c r="L1220">
+        <v>3</v>
+      </c>
+      <c r="M1220">
+        <v>2.62</v>
+      </c>
+      <c r="N1220">
         <v>2.99</v>
       </c>
-      <c r="M1218">
-        <v>2.65</v>
-      </c>
-      <c r="N1218">
+      <c r="O1220">
+        <v>1</v>
+      </c>
+      <c r="P1220" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:16">
+      <c r="A1221" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1221" t="s">
+        <v>183</v>
+      </c>
+      <c r="C1221">
+        <v>1.799225846496912</v>
+      </c>
+      <c r="D1221" t="s">
+        <v>326</v>
+      </c>
+      <c r="E1221">
+        <v>1.784625179242111</v>
+      </c>
+      <c r="F1221">
+        <v>-1</v>
+      </c>
+      <c r="G1221">
+        <v>0.004200774153503088</v>
+      </c>
+      <c r="H1221">
+        <v>0.00419537482075789</v>
+      </c>
+      <c r="I1221">
+        <v>0.01460066725480114</v>
+      </c>
+      <c r="J1221">
+        <v>0.4600667254801102</v>
+      </c>
+      <c r="K1221">
+        <v>2.61</v>
+      </c>
+      <c r="L1221">
         <v>3</v>
       </c>
-      <c r="O1218">
-        <v>1</v>
-      </c>
-      <c r="P1218" t="s">
-        <v>325</v>
+      <c r="M1221">
+        <v>2.62</v>
+      </c>
+      <c r="N1221">
+        <v>2.99</v>
+      </c>
+      <c r="O1221">
+        <v>1</v>
+      </c>
+      <c r="P1221" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="1222" spans="1:16">
+      <c r="A1222" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1222" t="s">
+        <v>183</v>
+      </c>
+      <c r="C1222">
+        <v>1.757120068971974</v>
+      </c>
+      <c r="D1222" t="s">
+        <v>326</v>
+      </c>
+      <c r="E1222">
+        <v>1.74235807689907</v>
+      </c>
+      <c r="F1222">
+        <v>-1</v>
+      </c>
+      <c r="G1222">
+        <v>0.004242879931028026</v>
+      </c>
+      <c r="H1222">
+        <v>0.004237641923100931</v>
+      </c>
+      <c r="I1222">
+        <v>0.0147619920729043</v>
+      </c>
+      <c r="J1222">
+        <v>0.4761992072904313</v>
+      </c>
+      <c r="K1222">
+        <v>2.61</v>
+      </c>
+      <c r="L1222">
+        <v>3</v>
+      </c>
+      <c r="M1222">
+        <v>2.62</v>
+      </c>
+      <c r="N1222">
+        <v>2.99</v>
+      </c>
+      <c r="O1222">
+        <v>1</v>
+      </c>
+      <c r="P1222" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:16">
+      <c r="A1223" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1223" t="s">
+        <v>183</v>
+      </c>
+      <c r="C1223">
+        <v>1.720910516107593</v>
+      </c>
+      <c r="D1223" t="s">
+        <v>326</v>
+      </c>
+      <c r="E1223">
+        <v>1.706009790115668</v>
+      </c>
+      <c r="F1223">
+        <v>-1</v>
+      </c>
+      <c r="G1223">
+        <v>0.004279089483892407</v>
+      </c>
+      <c r="H1223">
+        <v>0.004273990209884331</v>
+      </c>
+      <c r="I1223">
+        <v>0.01490072599192471</v>
+      </c>
+      <c r="J1223">
+        <v>0.4900725991924931</v>
+      </c>
+      <c r="K1223">
+        <v>2.61</v>
+      </c>
+      <c r="L1223">
+        <v>3</v>
+      </c>
+      <c r="M1223">
+        <v>2.62</v>
+      </c>
+      <c r="N1223">
+        <v>2.99</v>
+      </c>
+      <c r="O1223">
+        <v>1</v>
+      </c>
+      <c r="P1223" t="s">
+        <v>328</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01288-601288.xlsx
+++ b/s60_signal/position-01288-601288.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3753" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3756" uniqueCount="468">
   <si>
     <t>trade_time</t>
   </si>
@@ -562,9 +562,6 @@
     <t>2021-07-05</t>
   </si>
   <si>
-    <t>2021-07-09</t>
-  </si>
-  <si>
     <t>2021-07-30</t>
   </si>
   <si>
@@ -577,13 +574,16 @@
     <t>2021-07-20</t>
   </si>
   <si>
+    <t>2021-08-09</t>
+  </si>
+  <si>
     <t>2021-07-19</t>
   </si>
   <si>
-    <t>2021-08-09</t>
+    <t>2021-08-05</t>
   </si>
   <si>
-    <t>2021-08-05</t>
+    <t>2021-08-11</t>
   </si>
   <si>
     <t>2017-05-12</t>
@@ -1006,13 +1006,10 @@
     <t>2021-07-13</t>
   </si>
   <si>
-    <t>2021-07-16</t>
+    <t>2021-07-27</t>
   </si>
   <si>
-    <t>2021-08-11</t>
-  </si>
-  <si>
-    <t>2021-07-27</t>
+    <t>2021-08-12</t>
   </si>
   <si>
     <t>2021-07-28</t>
@@ -1399,10 +1396,16 @@
     <t>2021-07-08</t>
   </si>
   <si>
+    <t>2021-07-09</t>
+  </si>
+  <si>
     <t>2021-07-14</t>
   </si>
   <si>
     <t>2021-07-15</t>
+  </si>
+  <si>
+    <t>2021-07-16</t>
   </si>
   <si>
     <t>2021-07-21</t>
@@ -1412,6 +1415,9 @@
   </si>
   <si>
     <t>2021-07-26</t>
+  </si>
+  <si>
+    <t>2021-08-10</t>
   </si>
 </sst>
 </file>
@@ -1769,7 +1775,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1247"/>
+  <dimension ref="A1:P1248"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1866,7 +1872,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1916,7 +1922,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1966,7 +1972,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2016,7 +2022,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2216,7 +2222,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2266,7 +2272,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2316,7 +2322,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2366,7 +2372,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2416,7 +2422,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2466,7 +2472,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2516,7 +2522,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2566,7 +2572,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2616,7 +2622,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2666,7 +2672,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2716,7 +2722,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2766,7 +2772,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2816,7 +2822,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2866,7 +2872,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -3166,7 +3172,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3216,7 +3222,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3266,7 +3272,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3316,7 +3322,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3366,7 +3372,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3416,7 +3422,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3466,7 +3472,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3816,7 +3822,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3866,7 +3872,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3916,7 +3922,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3966,7 +3972,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -4016,7 +4022,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -4066,7 +4072,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4116,7 +4122,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4166,7 +4172,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4216,7 +4222,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4266,7 +4272,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4316,7 +4322,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4366,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4416,7 +4422,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4466,7 +4472,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4516,7 +4522,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4566,7 +4572,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4616,7 +4622,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4666,7 +4672,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -5016,7 +5022,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -5066,7 +5072,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -5116,7 +5122,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -5166,7 +5172,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -5216,7 +5222,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5266,7 +5272,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5566,7 +5572,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5616,7 +5622,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5666,7 +5672,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5716,7 +5722,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5766,7 +5772,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5816,7 +5822,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5866,7 +5872,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5916,7 +5922,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5966,7 +5972,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -6016,7 +6022,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -6066,7 +6072,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -6116,7 +6122,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -6166,7 +6172,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6216,7 +6222,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6266,7 +6272,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6316,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6366,7 +6372,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6416,7 +6422,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6466,7 +6472,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6516,7 +6522,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6566,7 +6572,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6616,7 +6622,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6666,7 +6672,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6716,7 +6722,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6766,7 +6772,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6816,7 +6822,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6866,7 +6872,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -7316,7 +7322,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7366,7 +7372,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7416,7 +7422,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7466,7 +7472,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7516,7 +7522,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7566,7 +7572,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7616,7 +7622,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7666,7 +7672,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7716,7 +7722,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7766,7 +7772,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7816,7 +7822,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7866,7 +7872,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7916,7 +7922,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7966,7 +7972,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -8016,7 +8022,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -8066,7 +8072,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -8116,7 +8122,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -8166,7 +8172,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8216,7 +8222,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8266,7 +8272,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8316,7 +8322,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8366,7 +8372,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8416,7 +8422,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8466,7 +8472,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8516,7 +8522,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8566,7 +8572,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8616,7 +8622,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8666,7 +8672,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8716,7 +8722,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8766,7 +8772,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8816,7 +8822,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -9166,7 +9172,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9216,7 +9222,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9266,7 +9272,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9316,7 +9322,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9366,7 +9372,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9416,7 +9422,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9466,7 +9472,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9516,7 +9522,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9566,7 +9572,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9616,7 +9622,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9816,7 +9822,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9866,7 +9872,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9916,7 +9922,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -10666,7 +10672,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10716,7 +10722,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10766,7 +10772,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10816,7 +10822,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -11116,7 +11122,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -11166,7 +11172,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -11216,7 +11222,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11266,7 +11272,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11316,7 +11322,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11366,7 +11372,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11416,7 +11422,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11466,7 +11472,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11516,7 +11522,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11566,7 +11572,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11616,7 +11622,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11666,7 +11672,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11716,7 +11722,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11766,7 +11772,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11816,7 +11822,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11866,7 +11872,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11916,7 +11922,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11966,7 +11972,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -12016,7 +12022,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -12066,7 +12072,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -12116,7 +12122,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -12166,7 +12172,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -12216,7 +12222,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -12266,7 +12272,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12316,7 +12322,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12366,7 +12372,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12416,7 +12422,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12466,7 +12472,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12516,7 +12522,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12566,7 +12572,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12866,7 +12872,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12916,7 +12922,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12966,7 +12972,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -13016,7 +13022,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -13066,7 +13072,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -13116,7 +13122,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -13166,7 +13172,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -13216,7 +13222,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -13266,7 +13272,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13316,7 +13322,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13366,7 +13372,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13416,7 +13422,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13466,7 +13472,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13516,7 +13522,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13566,7 +13572,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13616,7 +13622,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13666,7 +13672,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13716,7 +13722,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13766,7 +13772,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13816,7 +13822,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13866,7 +13872,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13916,7 +13922,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13966,7 +13972,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -14016,7 +14022,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -14066,7 +14072,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -14116,7 +14122,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -14166,7 +14172,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14216,7 +14222,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -14266,7 +14272,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14616,7 +14622,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14666,7 +14672,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14716,7 +14722,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14766,7 +14772,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14816,7 +14822,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14866,7 +14872,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14916,7 +14922,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14966,7 +14972,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -15016,7 +15022,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -15066,7 +15072,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -15116,7 +15122,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -15416,7 +15422,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15466,7 +15472,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15516,7 +15522,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15566,7 +15572,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15616,7 +15622,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15666,7 +15672,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15716,7 +15722,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15766,7 +15772,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15816,7 +15822,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15866,7 +15872,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15916,7 +15922,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15966,7 +15972,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -16016,7 +16022,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -16066,7 +16072,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -16116,7 +16122,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -17216,7 +17222,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17266,7 +17272,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17316,7 +17322,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17366,7 +17372,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17416,7 +17422,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17466,7 +17472,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17516,7 +17522,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17566,7 +17572,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17616,7 +17622,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17666,7 +17672,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -20366,7 +20372,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20416,7 +20422,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20466,7 +20472,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20516,7 +20522,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20566,7 +20572,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20616,7 +20622,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20666,7 +20672,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -20716,7 +20722,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20766,7 +20772,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20816,7 +20822,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20866,7 +20872,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20916,7 +20922,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -24216,7 +24222,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24266,7 +24272,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24316,7 +24322,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24366,7 +24372,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24416,7 +24422,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24466,7 +24472,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24516,7 +24522,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -24566,7 +24572,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24616,7 +24622,7 @@
         <v>1</v>
       </c>
       <c r="P457" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="458" spans="1:16">
@@ -24666,7 +24672,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24716,7 +24722,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24766,7 +24772,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24816,7 +24822,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24866,7 +24872,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24916,7 +24922,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24966,7 +24972,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -25016,7 +25022,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -25066,7 +25072,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -25116,7 +25122,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -25166,7 +25172,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -25216,7 +25222,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -25266,7 +25272,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -25316,7 +25322,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -25366,7 +25372,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25416,7 +25422,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25466,7 +25472,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25516,7 +25522,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25566,7 +25572,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25616,7 +25622,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25666,7 +25672,7 @@
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -25716,7 +25722,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -25766,7 +25772,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -25816,7 +25822,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -25866,7 +25872,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -25916,7 +25922,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25966,7 +25972,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -26016,7 +26022,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -26066,7 +26072,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -26116,7 +26122,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -26166,7 +26172,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -26216,7 +26222,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26266,7 +26272,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26316,7 +26322,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26366,7 +26372,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26416,7 +26422,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26466,7 +26472,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26516,7 +26522,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26566,7 +26572,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26616,7 +26622,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -26666,7 +26672,7 @@
         <v>1</v>
       </c>
       <c r="P498" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -26716,7 +26722,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26766,7 +26772,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26816,7 +26822,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26866,7 +26872,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26916,7 +26922,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -26966,7 +26972,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -27016,7 +27022,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -27066,7 +27072,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -27116,7 +27122,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -27166,7 +27172,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -27216,7 +27222,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -27266,7 +27272,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -27316,7 +27322,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -27366,7 +27372,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27416,7 +27422,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27466,7 +27472,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27516,7 +27522,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27566,7 +27572,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27616,7 +27622,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -27666,7 +27672,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27716,7 +27722,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27766,7 +27772,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27816,7 +27822,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -27866,7 +27872,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -27916,7 +27922,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -27966,7 +27972,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -28016,7 +28022,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -28066,7 +28072,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -28116,7 +28122,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -28166,7 +28172,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -28216,7 +28222,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -28266,7 +28272,7 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -28316,7 +28322,7 @@
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="532" spans="1:16">
@@ -28366,7 +28372,7 @@
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="533" spans="1:16">
@@ -28416,7 +28422,7 @@
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="534" spans="1:16">
@@ -28466,7 +28472,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -28516,7 +28522,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -29016,7 +29022,7 @@
         <v>1</v>
       </c>
       <c r="P545" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="546" spans="1:16">
@@ -29066,7 +29072,7 @@
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -29116,7 +29122,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -29166,7 +29172,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -29216,7 +29222,7 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -29266,7 +29272,7 @@
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -29316,7 +29322,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -29366,7 +29372,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29416,7 +29422,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29466,7 +29472,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29516,7 +29522,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29566,7 +29572,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -29616,7 +29622,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -29666,7 +29672,7 @@
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -29716,7 +29722,7 @@
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="560" spans="1:16">
@@ -29766,7 +29772,7 @@
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -29816,7 +29822,7 @@
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="562" spans="1:16">
@@ -29866,7 +29872,7 @@
         <v>1</v>
       </c>
       <c r="P562" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="563" spans="1:16">
@@ -29916,7 +29922,7 @@
         <v>1</v>
       </c>
       <c r="P563" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="564" spans="1:16">
@@ -29966,7 +29972,7 @@
         <v>1</v>
       </c>
       <c r="P564" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="565" spans="1:16">
@@ -30016,7 +30022,7 @@
         <v>1</v>
       </c>
       <c r="P565" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="566" spans="1:16">
@@ -30066,7 +30072,7 @@
         <v>1</v>
       </c>
       <c r="P566" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="567" spans="1:16">
@@ -30116,7 +30122,7 @@
         <v>1</v>
       </c>
       <c r="P567" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="568" spans="1:16">
@@ -30166,7 +30172,7 @@
         <v>1</v>
       </c>
       <c r="P568" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="569" spans="1:16">
@@ -30416,7 +30422,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -30466,7 +30472,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -30516,7 +30522,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -30566,7 +30572,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -30616,7 +30622,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -30666,7 +30672,7 @@
         <v>1</v>
       </c>
       <c r="P578" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="579" spans="1:16">
@@ -30716,7 +30722,7 @@
         <v>1</v>
       </c>
       <c r="P579" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="580" spans="1:16">
@@ -30766,7 +30772,7 @@
         <v>1</v>
       </c>
       <c r="P580" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="581" spans="1:16">
@@ -30816,7 +30822,7 @@
         <v>1</v>
       </c>
       <c r="P581" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="582" spans="1:16">
@@ -30866,7 +30872,7 @@
         <v>1</v>
       </c>
       <c r="P582" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="583" spans="1:16">
@@ -31166,7 +31172,7 @@
         <v>1</v>
       </c>
       <c r="P588" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="589" spans="1:16">
@@ -31216,7 +31222,7 @@
         <v>1</v>
       </c>
       <c r="P589" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="590" spans="1:16">
@@ -31266,7 +31272,7 @@
         <v>1</v>
       </c>
       <c r="P590" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="591" spans="1:16">
@@ -31316,7 +31322,7 @@
         <v>1</v>
       </c>
       <c r="P591" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="592" spans="1:16">
@@ -31366,7 +31372,7 @@
         <v>1</v>
       </c>
       <c r="P592" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="593" spans="1:16">
@@ -31416,7 +31422,7 @@
         <v>1</v>
       </c>
       <c r="P593" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="594" spans="1:16">
@@ -31466,7 +31472,7 @@
         <v>1</v>
       </c>
       <c r="P594" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="595" spans="1:16">
@@ -31516,7 +31522,7 @@
         <v>1</v>
       </c>
       <c r="P595" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="596" spans="1:16">
@@ -31566,7 +31572,7 @@
         <v>1</v>
       </c>
       <c r="P596" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="597" spans="1:16">
@@ -31616,7 +31622,7 @@
         <v>1</v>
       </c>
       <c r="P597" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="598" spans="1:16">
@@ -31666,7 +31672,7 @@
         <v>1</v>
       </c>
       <c r="P598" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="599" spans="1:16">
@@ -31716,7 +31722,7 @@
         <v>1</v>
       </c>
       <c r="P599" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="600" spans="1:16">
@@ -31766,7 +31772,7 @@
         <v>1</v>
       </c>
       <c r="P600" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="601" spans="1:16">
@@ -31816,7 +31822,7 @@
         <v>1</v>
       </c>
       <c r="P601" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="602" spans="1:16">
@@ -31866,7 +31872,7 @@
         <v>1</v>
       </c>
       <c r="P602" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="603" spans="1:16">
@@ -31916,7 +31922,7 @@
         <v>1</v>
       </c>
       <c r="P603" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="604" spans="1:16">
@@ -31966,7 +31972,7 @@
         <v>1</v>
       </c>
       <c r="P604" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="605" spans="1:16">
@@ -32016,7 +32022,7 @@
         <v>1</v>
       </c>
       <c r="P605" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="606" spans="1:16">
@@ -32066,7 +32072,7 @@
         <v>1</v>
       </c>
       <c r="P606" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="607" spans="1:16">
@@ -32116,7 +32122,7 @@
         <v>1</v>
       </c>
       <c r="P607" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="608" spans="1:16">
@@ -32166,7 +32172,7 @@
         <v>1</v>
       </c>
       <c r="P608" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="609" spans="1:16">
@@ -32216,7 +32222,7 @@
         <v>1</v>
       </c>
       <c r="P609" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="610" spans="1:16">
@@ -32266,7 +32272,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -32316,7 +32322,7 @@
         <v>1</v>
       </c>
       <c r="P611" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="612" spans="1:16">
@@ -32366,7 +32372,7 @@
         <v>1</v>
       </c>
       <c r="P612" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="613" spans="1:16">
@@ -32416,7 +32422,7 @@
         <v>1</v>
       </c>
       <c r="P613" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="614" spans="1:16">
@@ -32466,7 +32472,7 @@
         <v>1</v>
       </c>
       <c r="P614" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="615" spans="1:16">
@@ -32516,7 +32522,7 @@
         <v>1</v>
       </c>
       <c r="P615" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="616" spans="1:16">
@@ -32566,7 +32572,7 @@
         <v>1</v>
       </c>
       <c r="P616" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="617" spans="1:16">
@@ -32616,7 +32622,7 @@
         <v>1</v>
       </c>
       <c r="P617" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="618" spans="1:16">
@@ -32666,7 +32672,7 @@
         <v>1</v>
       </c>
       <c r="P618" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="619" spans="1:16">
@@ -32716,7 +32722,7 @@
         <v>1</v>
       </c>
       <c r="P619" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="620" spans="1:16">
@@ -32766,7 +32772,7 @@
         <v>1</v>
       </c>
       <c r="P620" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="621" spans="1:16">
@@ -33166,7 +33172,7 @@
         <v>1</v>
       </c>
       <c r="P628" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="629" spans="1:16">
@@ -33216,7 +33222,7 @@
         <v>1</v>
       </c>
       <c r="P629" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="630" spans="1:16">
@@ -33266,7 +33272,7 @@
         <v>1</v>
       </c>
       <c r="P630" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="631" spans="1:16">
@@ -33316,7 +33322,7 @@
         <v>1</v>
       </c>
       <c r="P631" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="632" spans="1:16">
@@ -33366,7 +33372,7 @@
         <v>1</v>
       </c>
       <c r="P632" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -33416,7 +33422,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -33466,7 +33472,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -34166,7 +34172,7 @@
         <v>1</v>
       </c>
       <c r="P648" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="649" spans="1:16">
@@ -34216,7 +34222,7 @@
         <v>1</v>
       </c>
       <c r="P649" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="650" spans="1:16">
@@ -34266,7 +34272,7 @@
         <v>1</v>
       </c>
       <c r="P650" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="651" spans="1:16">
@@ -34316,7 +34322,7 @@
         <v>1</v>
       </c>
       <c r="P651" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="652" spans="1:16">
@@ -34366,7 +34372,7 @@
         <v>1</v>
       </c>
       <c r="P652" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="653" spans="1:16">
@@ -34416,7 +34422,7 @@
         <v>1</v>
       </c>
       <c r="P653" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="654" spans="1:16">
@@ -34466,7 +34472,7 @@
         <v>1</v>
       </c>
       <c r="P654" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="655" spans="1:16">
@@ -35216,7 +35222,7 @@
         <v>1</v>
       </c>
       <c r="P669" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="670" spans="1:16">
@@ -35266,7 +35272,7 @@
         <v>1</v>
       </c>
       <c r="P670" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="671" spans="1:16">
@@ -35316,7 +35322,7 @@
         <v>1</v>
       </c>
       <c r="P671" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="672" spans="1:16">
@@ -35366,7 +35372,7 @@
         <v>1</v>
       </c>
       <c r="P672" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="673" spans="1:16">
@@ -35416,7 +35422,7 @@
         <v>1</v>
       </c>
       <c r="P673" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="674" spans="1:16">
@@ -35466,7 +35472,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -35516,7 +35522,7 @@
         <v>1</v>
       </c>
       <c r="P675" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="676" spans="1:16">
@@ -35566,7 +35572,7 @@
         <v>1</v>
       </c>
       <c r="P676" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="677" spans="1:16">
@@ -35616,7 +35622,7 @@
         <v>1</v>
       </c>
       <c r="P677" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="678" spans="1:16">
@@ -35666,7 +35672,7 @@
         <v>1</v>
       </c>
       <c r="P678" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="679" spans="1:16">
@@ -35716,7 +35722,7 @@
         <v>1</v>
       </c>
       <c r="P679" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="680" spans="1:16">
@@ -35766,7 +35772,7 @@
         <v>1</v>
       </c>
       <c r="P680" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="681" spans="1:16">
@@ -35816,7 +35822,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -35866,7 +35872,7 @@
         <v>1</v>
       </c>
       <c r="P682" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -35916,7 +35922,7 @@
         <v>1</v>
       </c>
       <c r="P683" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="684" spans="1:16">
@@ -36166,7 +36172,7 @@
         <v>1</v>
       </c>
       <c r="P688" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="689" spans="1:16">
@@ -36216,7 +36222,7 @@
         <v>1</v>
       </c>
       <c r="P689" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="690" spans="1:16">
@@ -36266,7 +36272,7 @@
         <v>1</v>
       </c>
       <c r="P690" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="691" spans="1:16">
@@ -36316,7 +36322,7 @@
         <v>1</v>
       </c>
       <c r="P691" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="692" spans="1:16">
@@ -36366,7 +36372,7 @@
         <v>1</v>
       </c>
       <c r="P692" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="693" spans="1:16">
@@ -36416,7 +36422,7 @@
         <v>1</v>
       </c>
       <c r="P693" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -36466,7 +36472,7 @@
         <v>1</v>
       </c>
       <c r="P694" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="695" spans="1:16">
@@ -36516,7 +36522,7 @@
         <v>1</v>
       </c>
       <c r="P695" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="696" spans="1:16">
@@ -36566,7 +36572,7 @@
         <v>1</v>
       </c>
       <c r="P696" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="697" spans="1:16">
@@ -36616,7 +36622,7 @@
         <v>1</v>
       </c>
       <c r="P697" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -36666,7 +36672,7 @@
         <v>1</v>
       </c>
       <c r="P698" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -36716,7 +36722,7 @@
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -36766,7 +36772,7 @@
         <v>1</v>
       </c>
       <c r="P700" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="701" spans="1:16">
@@ -36816,7 +36822,7 @@
         <v>1</v>
       </c>
       <c r="P701" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="702" spans="1:16">
@@ -36866,7 +36872,7 @@
         <v>1</v>
       </c>
       <c r="P702" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="703" spans="1:16">
@@ -38416,7 +38422,7 @@
         <v>1</v>
       </c>
       <c r="P733" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="734" spans="1:16">
@@ -38466,7 +38472,7 @@
         <v>1</v>
       </c>
       <c r="P734" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="735" spans="1:16">
@@ -38516,7 +38522,7 @@
         <v>1</v>
       </c>
       <c r="P735" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="736" spans="1:16">
@@ -38566,7 +38572,7 @@
         <v>1</v>
       </c>
       <c r="P736" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="737" spans="1:16">
@@ -38616,7 +38622,7 @@
         <v>1</v>
       </c>
       <c r="P737" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="738" spans="1:16">
@@ -38916,7 +38922,7 @@
         <v>1</v>
       </c>
       <c r="P743" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="744" spans="1:16">
@@ -38966,7 +38972,7 @@
         <v>1</v>
       </c>
       <c r="P744" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="745" spans="1:16">
@@ -39016,7 +39022,7 @@
         <v>1</v>
       </c>
       <c r="P745" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="746" spans="1:16">
@@ -39066,7 +39072,7 @@
         <v>1</v>
       </c>
       <c r="P746" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="747" spans="1:16">
@@ -39116,7 +39122,7 @@
         <v>1</v>
       </c>
       <c r="P747" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="748" spans="1:16">
@@ -39166,7 +39172,7 @@
         <v>1</v>
       </c>
       <c r="P748" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="749" spans="1:16">
@@ -39216,7 +39222,7 @@
         <v>1</v>
       </c>
       <c r="P749" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="750" spans="1:16">
@@ -39266,7 +39272,7 @@
         <v>1</v>
       </c>
       <c r="P750" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="751" spans="1:16">
@@ -39316,7 +39322,7 @@
         <v>1</v>
       </c>
       <c r="P751" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="752" spans="1:16">
@@ -39366,7 +39372,7 @@
         <v>1</v>
       </c>
       <c r="P752" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="753" spans="1:16">
@@ -39416,7 +39422,7 @@
         <v>1</v>
       </c>
       <c r="P753" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -39466,7 +39472,7 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -39516,7 +39522,7 @@
         <v>1</v>
       </c>
       <c r="P755" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="756" spans="1:16">
@@ -39566,7 +39572,7 @@
         <v>1</v>
       </c>
       <c r="P756" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="757" spans="1:16">
@@ -39616,7 +39622,7 @@
         <v>1</v>
       </c>
       <c r="P757" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="758" spans="1:16">
@@ -39666,7 +39672,7 @@
         <v>1</v>
       </c>
       <c r="P758" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="759" spans="1:16">
@@ -40316,7 +40322,7 @@
         <v>1</v>
       </c>
       <c r="P771" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="772" spans="1:16">
@@ -40366,7 +40372,7 @@
         <v>1</v>
       </c>
       <c r="P772" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="773" spans="1:16">
@@ -40416,7 +40422,7 @@
         <v>1</v>
       </c>
       <c r="P773" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="774" spans="1:16">
@@ -40466,7 +40472,7 @@
         <v>1</v>
       </c>
       <c r="P774" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="775" spans="1:16">
@@ -40516,7 +40522,7 @@
         <v>1</v>
       </c>
       <c r="P775" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="776" spans="1:16">
@@ -40566,7 +40572,7 @@
         <v>1</v>
       </c>
       <c r="P776" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="777" spans="1:16">
@@ -40616,7 +40622,7 @@
         <v>1</v>
       </c>
       <c r="P777" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="778" spans="1:16">
@@ -40666,7 +40672,7 @@
         <v>1</v>
       </c>
       <c r="P778" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="779" spans="1:16">
@@ -40716,7 +40722,7 @@
         <v>1</v>
       </c>
       <c r="P779" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="780" spans="1:16">
@@ -40766,7 +40772,7 @@
         <v>1</v>
       </c>
       <c r="P780" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="781" spans="1:16">
@@ -40816,7 +40822,7 @@
         <v>1</v>
       </c>
       <c r="P781" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="782" spans="1:16">
@@ -40866,7 +40872,7 @@
         <v>1</v>
       </c>
       <c r="P782" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="783" spans="1:16">
@@ -42016,7 +42022,7 @@
         <v>1</v>
       </c>
       <c r="P805" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="806" spans="1:16">
@@ -42066,7 +42072,7 @@
         <v>1</v>
       </c>
       <c r="P806" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="807" spans="1:16">
@@ -42116,7 +42122,7 @@
         <v>1</v>
       </c>
       <c r="P807" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="808" spans="1:16">
@@ -42166,7 +42172,7 @@
         <v>1</v>
       </c>
       <c r="P808" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="809" spans="1:16">
@@ -42216,7 +42222,7 @@
         <v>1</v>
       </c>
       <c r="P809" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="810" spans="1:16">
@@ -42266,7 +42272,7 @@
         <v>1</v>
       </c>
       <c r="P810" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="811" spans="1:16">
@@ -42316,7 +42322,7 @@
         <v>1</v>
       </c>
       <c r="P811" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="812" spans="1:16">
@@ -42366,7 +42372,7 @@
         <v>1</v>
       </c>
       <c r="P812" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="813" spans="1:16">
@@ -42416,7 +42422,7 @@
         <v>1</v>
       </c>
       <c r="P813" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="814" spans="1:16">
@@ -42466,7 +42472,7 @@
         <v>1</v>
       </c>
       <c r="P814" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="815" spans="1:16">
@@ -42516,7 +42522,7 @@
         <v>1</v>
       </c>
       <c r="P815" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="816" spans="1:16">
@@ -42566,7 +42572,7 @@
         <v>1</v>
       </c>
       <c r="P816" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="817" spans="1:16">
@@ -42616,7 +42622,7 @@
         <v>1</v>
       </c>
       <c r="P817" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="818" spans="1:16">
@@ -43766,7 +43772,7 @@
         <v>1</v>
       </c>
       <c r="P840" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="841" spans="1:16">
@@ -43866,7 +43872,7 @@
         <v>1</v>
       </c>
       <c r="P842" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="843" spans="1:16">
@@ -43916,7 +43922,7 @@
         <v>1</v>
       </c>
       <c r="P843" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="844" spans="1:16">
@@ -44016,7 +44022,7 @@
         <v>1</v>
       </c>
       <c r="P845" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="846" spans="1:16">
@@ -44116,7 +44122,7 @@
         <v>1</v>
       </c>
       <c r="P847" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="848" spans="1:16">
@@ -44166,7 +44172,7 @@
         <v>1</v>
       </c>
       <c r="P848" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="849" spans="1:16">
@@ -45016,7 +45022,7 @@
         <v>1</v>
       </c>
       <c r="P865" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="866" spans="1:16">
@@ -45066,7 +45072,7 @@
         <v>1</v>
       </c>
       <c r="P866" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="867" spans="1:16">
@@ -45116,7 +45122,7 @@
         <v>1</v>
       </c>
       <c r="P867" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="868" spans="1:16">
@@ -45166,7 +45172,7 @@
         <v>1</v>
       </c>
       <c r="P868" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="869" spans="1:16">
@@ -45216,7 +45222,7 @@
         <v>1</v>
       </c>
       <c r="P869" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="870" spans="1:16">
@@ -45266,7 +45272,7 @@
         <v>1</v>
       </c>
       <c r="P870" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="871" spans="1:16">
@@ -45316,7 +45322,7 @@
         <v>1</v>
       </c>
       <c r="P871" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="872" spans="1:16">
@@ -45366,7 +45372,7 @@
         <v>1</v>
       </c>
       <c r="P872" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="873" spans="1:16">
@@ -45416,7 +45422,7 @@
         <v>1</v>
       </c>
       <c r="P873" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="874" spans="1:16">
@@ -45466,7 +45472,7 @@
         <v>1</v>
       </c>
       <c r="P874" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="875" spans="1:16">
@@ -45516,7 +45522,7 @@
         <v>1</v>
       </c>
       <c r="P875" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="876" spans="1:16">
@@ -45566,7 +45572,7 @@
         <v>1</v>
       </c>
       <c r="P876" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="877" spans="1:16">
@@ -45616,7 +45622,7 @@
         <v>1</v>
       </c>
       <c r="P877" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="878" spans="1:16">
@@ -45666,7 +45672,7 @@
         <v>1</v>
       </c>
       <c r="P878" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="879" spans="1:16">
@@ -45966,7 +45972,7 @@
         <v>1</v>
       </c>
       <c r="P884" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="885" spans="1:16">
@@ -46016,7 +46022,7 @@
         <v>1</v>
       </c>
       <c r="P885" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="886" spans="1:16">
@@ -46066,7 +46072,7 @@
         <v>1</v>
       </c>
       <c r="P886" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="887" spans="1:16">
@@ -46116,7 +46122,7 @@
         <v>1</v>
       </c>
       <c r="P887" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="888" spans="1:16">
@@ -46166,7 +46172,7 @@
         <v>1</v>
       </c>
       <c r="P888" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="889" spans="1:16">
@@ -46216,7 +46222,7 @@
         <v>1</v>
       </c>
       <c r="P889" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="890" spans="1:16">
@@ -46266,7 +46272,7 @@
         <v>1</v>
       </c>
       <c r="P890" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="891" spans="1:16">
@@ -46316,7 +46322,7 @@
         <v>1</v>
       </c>
       <c r="P891" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="892" spans="1:16">
@@ -46366,7 +46372,7 @@
         <v>1</v>
       </c>
       <c r="P892" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="893" spans="1:16">
@@ -46416,7 +46422,7 @@
         <v>1</v>
       </c>
       <c r="P893" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="894" spans="1:16">
@@ -46716,7 +46722,7 @@
         <v>1</v>
       </c>
       <c r="P899" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="900" spans="1:16">
@@ -46766,7 +46772,7 @@
         <v>1</v>
       </c>
       <c r="P900" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="901" spans="1:16">
@@ -46816,7 +46822,7 @@
         <v>1</v>
       </c>
       <c r="P901" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="902" spans="1:16">
@@ -46866,7 +46872,7 @@
         <v>1</v>
       </c>
       <c r="P902" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="903" spans="1:16">
@@ -46916,7 +46922,7 @@
         <v>1</v>
       </c>
       <c r="P903" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="904" spans="1:16">
@@ -48516,7 +48522,7 @@
         <v>1</v>
       </c>
       <c r="P935" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="936" spans="1:16">
@@ -48566,7 +48572,7 @@
         <v>1</v>
       </c>
       <c r="P936" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="937" spans="1:16">
@@ -48616,7 +48622,7 @@
         <v>1</v>
       </c>
       <c r="P937" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="938" spans="1:16">
@@ -48666,7 +48672,7 @@
         <v>1</v>
       </c>
       <c r="P938" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="939" spans="1:16">
@@ -50866,7 +50872,7 @@
         <v>1</v>
       </c>
       <c r="P982" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="983" spans="1:16">
@@ -50916,7 +50922,7 @@
         <v>1</v>
       </c>
       <c r="P983" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="984" spans="1:16">
@@ -50966,7 +50972,7 @@
         <v>1</v>
       </c>
       <c r="P984" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="985" spans="1:16">
@@ -51016,7 +51022,7 @@
         <v>1</v>
       </c>
       <c r="P985" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="986" spans="1:16">
@@ -51066,7 +51072,7 @@
         <v>1</v>
       </c>
       <c r="P986" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="987" spans="1:16">
@@ -51116,7 +51122,7 @@
         <v>1</v>
       </c>
       <c r="P987" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="988" spans="1:16">
@@ -51166,7 +51172,7 @@
         <v>1</v>
       </c>
       <c r="P988" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="989" spans="1:16">
@@ -51216,7 +51222,7 @@
         <v>1</v>
       </c>
       <c r="P989" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="990" spans="1:16">
@@ -51266,7 +51272,7 @@
         <v>1</v>
       </c>
       <c r="P990" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="991" spans="1:16">
@@ -51316,7 +51322,7 @@
         <v>1</v>
       </c>
       <c r="P991" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="992" spans="1:16">
@@ -51366,7 +51372,7 @@
         <v>1</v>
       </c>
       <c r="P992" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="993" spans="1:16">
@@ -51416,7 +51422,7 @@
         <v>1</v>
       </c>
       <c r="P993" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="994" spans="1:16">
@@ -51466,7 +51472,7 @@
         <v>1</v>
       </c>
       <c r="P994" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="995" spans="1:16">
@@ -51516,7 +51522,7 @@
         <v>1</v>
       </c>
       <c r="P995" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="996" spans="1:16">
@@ -51566,7 +51572,7 @@
         <v>1</v>
       </c>
       <c r="P996" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="997" spans="1:16">
@@ -51866,7 +51872,7 @@
         <v>1</v>
       </c>
       <c r="P1002" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="1003" spans="1:16">
@@ -51916,7 +51922,7 @@
         <v>1</v>
       </c>
       <c r="P1003" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="1004" spans="1:16">
@@ -51966,7 +51972,7 @@
         <v>1</v>
       </c>
       <c r="P1004" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="1005" spans="1:16">
@@ -52016,7 +52022,7 @@
         <v>1</v>
       </c>
       <c r="P1005" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="1006" spans="1:16">
@@ -52066,7 +52072,7 @@
         <v>1</v>
       </c>
       <c r="P1006" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="1007" spans="1:16">
@@ -52716,7 +52722,7 @@
         <v>1</v>
       </c>
       <c r="P1019" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="1020" spans="1:16">
@@ -52766,7 +52772,7 @@
         <v>1</v>
       </c>
       <c r="P1020" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="1021" spans="1:16">
@@ -52816,7 +52822,7 @@
         <v>1</v>
       </c>
       <c r="P1021" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="1022" spans="1:16">
@@ -52866,7 +52872,7 @@
         <v>1</v>
       </c>
       <c r="P1022" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="1023" spans="1:16">
@@ -52916,7 +52922,7 @@
         <v>1</v>
       </c>
       <c r="P1023" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="1024" spans="1:16">
@@ -52966,7 +52972,7 @@
         <v>1</v>
       </c>
       <c r="P1024" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="1025" spans="1:16">
@@ -53016,7 +53022,7 @@
         <v>1</v>
       </c>
       <c r="P1025" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="1026" spans="1:16">
@@ -53066,7 +53072,7 @@
         <v>1</v>
       </c>
       <c r="P1026" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="1027" spans="1:16">
@@ -53116,7 +53122,7 @@
         <v>1</v>
       </c>
       <c r="P1027" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="1028" spans="1:16">
@@ -53166,7 +53172,7 @@
         <v>1</v>
       </c>
       <c r="P1028" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="1029" spans="1:16">
@@ -53216,7 +53222,7 @@
         <v>1</v>
       </c>
       <c r="P1029" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="1030" spans="1:16">
@@ -53266,7 +53272,7 @@
         <v>1</v>
       </c>
       <c r="P1030" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="1031" spans="1:16">
@@ -53316,7 +53322,7 @@
         <v>1</v>
       </c>
       <c r="P1031" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="1032" spans="1:16">
@@ -53366,7 +53372,7 @@
         <v>1</v>
       </c>
       <c r="P1032" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="1033" spans="1:16">
@@ -53416,7 +53422,7 @@
         <v>1</v>
       </c>
       <c r="P1033" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="1034" spans="1:16">
@@ -53466,7 +53472,7 @@
         <v>1</v>
       </c>
       <c r="P1034" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="1035" spans="1:16">
@@ -53516,7 +53522,7 @@
         <v>1</v>
       </c>
       <c r="P1035" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="1036" spans="1:16">
@@ -53566,7 +53572,7 @@
         <v>1</v>
       </c>
       <c r="P1036" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="1037" spans="1:16">
@@ -53616,7 +53622,7 @@
         <v>1</v>
       </c>
       <c r="P1037" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="1038" spans="1:16">
@@ -53666,7 +53672,7 @@
         <v>1</v>
       </c>
       <c r="P1038" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="1039" spans="1:16">
@@ -54466,7 +54472,7 @@
         <v>1</v>
       </c>
       <c r="P1054" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="1055" spans="1:16">
@@ -54516,7 +54522,7 @@
         <v>1</v>
       </c>
       <c r="P1055" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="1056" spans="1:16">
@@ -54566,7 +54572,7 @@
         <v>1</v>
       </c>
       <c r="P1056" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="1057" spans="1:16">
@@ -54616,7 +54622,7 @@
         <v>1</v>
       </c>
       <c r="P1057" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="1058" spans="1:16">
@@ -54666,7 +54672,7 @@
         <v>1</v>
       </c>
       <c r="P1058" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="1059" spans="1:16">
@@ -54716,7 +54722,7 @@
         <v>1</v>
       </c>
       <c r="P1059" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="1060" spans="1:16">
@@ -54766,7 +54772,7 @@
         <v>1</v>
       </c>
       <c r="P1060" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="1061" spans="1:16">
@@ -54816,7 +54822,7 @@
         <v>1</v>
       </c>
       <c r="P1061" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="1062" spans="1:16">
@@ -54866,7 +54872,7 @@
         <v>1</v>
       </c>
       <c r="P1062" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="1063" spans="1:16">
@@ -54916,7 +54922,7 @@
         <v>1</v>
       </c>
       <c r="P1063" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="1064" spans="1:16">
@@ -54966,7 +54972,7 @@
         <v>1</v>
       </c>
       <c r="P1064" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="1065" spans="1:16">
@@ -55016,7 +55022,7 @@
         <v>1</v>
       </c>
       <c r="P1065" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="1066" spans="1:16">
@@ -55066,7 +55072,7 @@
         <v>1</v>
       </c>
       <c r="P1066" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="1067" spans="1:16">
@@ -55116,7 +55122,7 @@
         <v>1</v>
       </c>
       <c r="P1067" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="1068" spans="1:16">
@@ -55166,7 +55172,7 @@
         <v>1</v>
       </c>
       <c r="P1068" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="1069" spans="1:16">
@@ -55216,7 +55222,7 @@
         <v>1</v>
       </c>
       <c r="P1069" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="1070" spans="1:16">
@@ -55266,7 +55272,7 @@
         <v>1</v>
       </c>
       <c r="P1070" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="1071" spans="1:16">
@@ -55316,7 +55322,7 @@
         <v>1</v>
       </c>
       <c r="P1071" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="1072" spans="1:16">
@@ -55366,7 +55372,7 @@
         <v>1</v>
       </c>
       <c r="P1072" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="1073" spans="1:16">
@@ -55416,7 +55422,7 @@
         <v>1</v>
       </c>
       <c r="P1073" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="1074" spans="1:16">
@@ -55466,7 +55472,7 @@
         <v>1</v>
       </c>
       <c r="P1074" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="1075" spans="1:16">
@@ -55516,7 +55522,7 @@
         <v>1</v>
       </c>
       <c r="P1075" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="1076" spans="1:16">
@@ -55566,7 +55572,7 @@
         <v>1</v>
       </c>
       <c r="P1076" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="1077" spans="1:16">
@@ -55966,7 +55972,7 @@
         <v>1</v>
       </c>
       <c r="P1084" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="1085" spans="1:16">
@@ -56016,7 +56022,7 @@
         <v>1</v>
       </c>
       <c r="P1085" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="1086" spans="1:16">
@@ -56066,7 +56072,7 @@
         <v>1</v>
       </c>
       <c r="P1086" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="1087" spans="1:16">
@@ -56116,7 +56122,7 @@
         <v>1</v>
       </c>
       <c r="P1087" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="1088" spans="1:16">
@@ -56166,7 +56172,7 @@
         <v>1</v>
       </c>
       <c r="P1088" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="1089" spans="1:16">
@@ -56216,7 +56222,7 @@
         <v>1</v>
       </c>
       <c r="P1089" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="1090" spans="1:16">
@@ -56266,7 +56272,7 @@
         <v>1</v>
       </c>
       <c r="P1090" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="1091" spans="1:16">
@@ -56316,7 +56322,7 @@
         <v>1</v>
       </c>
       <c r="P1091" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="1092" spans="1:16">
@@ -56366,7 +56372,7 @@
         <v>1</v>
       </c>
       <c r="P1092" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="1093" spans="1:16">
@@ -56416,7 +56422,7 @@
         <v>1</v>
       </c>
       <c r="P1093" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="1094" spans="1:16">
@@ -56466,7 +56472,7 @@
         <v>1</v>
       </c>
       <c r="P1094" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="1095" spans="1:16">
@@ -56516,7 +56522,7 @@
         <v>1</v>
       </c>
       <c r="P1095" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="1096" spans="1:16">
@@ -56566,7 +56572,7 @@
         <v>1</v>
       </c>
       <c r="P1096" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="1097" spans="1:16">
@@ -56616,7 +56622,7 @@
         <v>1</v>
       </c>
       <c r="P1097" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="1098" spans="1:16">
@@ -60866,7 +60872,7 @@
         <v>1</v>
       </c>
       <c r="P1182" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="1183" spans="1:16">
@@ -60916,7 +60922,7 @@
         <v>1</v>
       </c>
       <c r="P1183" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="1184" spans="1:16">
@@ -60966,7 +60972,7 @@
         <v>1</v>
       </c>
       <c r="P1184" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="1185" spans="1:16">
@@ -61016,7 +61022,7 @@
         <v>1</v>
       </c>
       <c r="P1185" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="1186" spans="1:16">
@@ -61066,7 +61072,7 @@
         <v>1</v>
       </c>
       <c r="P1186" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="1187" spans="1:16">
@@ -61116,7 +61122,7 @@
         <v>1</v>
       </c>
       <c r="P1187" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="1188" spans="1:16">
@@ -61166,7 +61172,7 @@
         <v>1</v>
       </c>
       <c r="P1188" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="1189" spans="1:16">
@@ -61216,7 +61222,7 @@
         <v>1</v>
       </c>
       <c r="P1189" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="1190" spans="1:16">
@@ -61966,7 +61972,7 @@
         <v>1</v>
       </c>
       <c r="P1204" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="1205" spans="1:16">
@@ -62016,7 +62022,7 @@
         <v>1</v>
       </c>
       <c r="P1205" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="1206" spans="1:16">
@@ -62066,7 +62072,7 @@
         <v>1</v>
       </c>
       <c r="P1206" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="1207" spans="1:16">
@@ -62116,7 +62122,7 @@
         <v>1</v>
       </c>
       <c r="P1207" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="1208" spans="1:16">
@@ -62166,7 +62172,7 @@
         <v>1</v>
       </c>
       <c r="P1208" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="1209" spans="1:16">
@@ -62216,7 +62222,7 @@
         <v>1</v>
       </c>
       <c r="P1209" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="1210" spans="1:16">
@@ -62233,7 +62239,7 @@
         <v>330</v>
       </c>
       <c r="E1210">
-        <v>2.105009406823479</v>
+        <v>2.09821140739365</v>
       </c>
       <c r="F1210">
         <v>-1</v>
@@ -62242,10 +62248,10 @@
         <v>0.003928305164686547</v>
       </c>
       <c r="H1210">
-        <v>0.003874990593176522</v>
+        <v>0.00382178859260635</v>
       </c>
       <c r="I1210">
-        <v>0.04668542848997514</v>
+        <v>0.05348342791980443</v>
       </c>
       <c r="J1210">
         <v>0.3314571510024426</v>
@@ -62257,16 +62263,16 @@
         <v>3.04</v>
       </c>
       <c r="M1210">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="N1210">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="O1210">
         <v>1</v>
       </c>
       <c r="P1210" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="1211" spans="1:16">
@@ -62277,46 +62283,46 @@
         <v>182</v>
       </c>
       <c r="C1211">
-        <v>2.151638549843527</v>
+        <v>2.071525978903674</v>
       </c>
       <c r="D1211" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E1211">
-        <v>2.105009406823479</v>
+        <v>2.074896835883625</v>
       </c>
       <c r="F1211">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1211">
-        <v>0.003908361450156472</v>
+        <v>0.003788474021096327</v>
       </c>
       <c r="H1211">
-        <v>0.003874990593176522</v>
+        <v>0.003805103164116375</v>
       </c>
       <c r="I1211">
-        <v>0.0466291430200485</v>
+        <v>0.003370856979950876</v>
       </c>
       <c r="J1211">
         <v>0.3314571510024426</v>
       </c>
       <c r="K1211">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="L1211">
-        <v>3.03</v>
+        <v>2.93</v>
       </c>
       <c r="M1211">
-        <v>2.67</v>
+        <v>2.61</v>
       </c>
       <c r="N1211">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="O1211">
         <v>1</v>
       </c>
       <c r="P1211" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="1212" spans="1:16">
@@ -62327,78 +62333,78 @@
         <v>183</v>
       </c>
       <c r="C1212">
-        <v>2.071525978903674</v>
+        <v>2.048267692863576</v>
       </c>
       <c r="D1212" t="s">
         <v>331</v>
       </c>
       <c r="E1212">
-        <v>2.078267692863576</v>
+        <v>2.074896835883625</v>
       </c>
       <c r="F1212">
         <v>1</v>
       </c>
       <c r="G1212">
-        <v>0.003788474021096327</v>
+        <v>0.003791732307136424</v>
       </c>
       <c r="H1212">
-        <v>0.003821732307136424</v>
+        <v>0.003805103164116375</v>
       </c>
       <c r="I1212">
-        <v>0.006741713959902196</v>
+        <v>0.02662914302004893</v>
       </c>
       <c r="J1212">
         <v>0.3314571510024426</v>
       </c>
       <c r="K1212">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="L1212">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="M1212">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="N1212">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="O1212">
         <v>1</v>
       </c>
       <c r="P1212" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="1213" spans="1:16">
       <c r="A1213" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1213" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C1213">
-        <v>2.048267692863576</v>
+        <v>2.022204053708345</v>
       </c>
       <c r="D1213" t="s">
         <v>331</v>
       </c>
       <c r="E1213">
-        <v>2.078267692863576</v>
+        <v>2.049031399307522</v>
       </c>
       <c r="F1213">
         <v>1</v>
       </c>
       <c r="G1213">
-        <v>0.003791732307136424</v>
+        <v>0.003817795946291655</v>
       </c>
       <c r="H1213">
-        <v>0.003821732307136424</v>
+        <v>0.003830968600692479</v>
       </c>
       <c r="I1213">
-        <v>0.03000000000000025</v>
+        <v>0.02682734559917632</v>
       </c>
       <c r="J1213">
-        <v>0.3314571510024426</v>
+        <v>0.3413672799588041</v>
       </c>
       <c r="K1213">
         <v>2.63</v>
@@ -62407,16 +62413,16 @@
         <v>2.92</v>
       </c>
       <c r="M1213">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="N1213">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="O1213">
         <v>1</v>
       </c>
       <c r="P1213" t="s">
-        <v>457</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1214" spans="1:16">
@@ -62424,49 +62430,49 @@
         <v>0</v>
       </c>
       <c r="B1214" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C1214">
-        <v>2.125376708109169</v>
+        <v>2.084873479736085</v>
       </c>
       <c r="D1214" t="s">
         <v>330</v>
       </c>
       <c r="E1214">
-        <v>2.078549362509993</v>
+        <v>2.048379711614491</v>
       </c>
       <c r="F1214">
         <v>-1</v>
       </c>
       <c r="G1214">
-        <v>0.003934623291890831</v>
+        <v>0.003915126520263916</v>
       </c>
       <c r="H1214">
-        <v>0.003901450637490007</v>
+        <v>0.00387162028838551</v>
       </c>
       <c r="I1214">
-        <v>0.0468273455991759</v>
+        <v>0.03649376812159399</v>
       </c>
       <c r="J1214">
-        <v>0.3413672799588041</v>
+        <v>0.3506231878405806</v>
       </c>
       <c r="K1214">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
       <c r="L1214">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="M1214">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="N1214">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="O1214">
         <v>1</v>
       </c>
       <c r="P1214" t="s">
-        <v>181</v>
+        <v>457</v>
       </c>
     </row>
     <row r="1215" spans="1:16">
@@ -62474,31 +62480,31 @@
         <v>1</v>
       </c>
       <c r="B1215" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C1215">
-        <v>2.022204053708345</v>
+        <v>1.997861015979273</v>
       </c>
       <c r="D1215" t="s">
         <v>331</v>
       </c>
       <c r="E1215">
-        <v>2.052204053708345</v>
+        <v>2.024873479736085</v>
       </c>
       <c r="F1215">
         <v>1</v>
       </c>
       <c r="G1215">
-        <v>0.003817795946291655</v>
+        <v>0.003842138984020727</v>
       </c>
       <c r="H1215">
-        <v>0.003847795946291655</v>
+        <v>0.003855126520263915</v>
       </c>
       <c r="I1215">
-        <v>0.03000000000000025</v>
+        <v>0.02701246375681166</v>
       </c>
       <c r="J1215">
-        <v>0.3413672799588041</v>
+        <v>0.3506231878405806</v>
       </c>
       <c r="K1215">
         <v>2.63</v>
@@ -62507,16 +62513,16 @@
         <v>2.92</v>
       </c>
       <c r="M1215">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="N1215">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="O1215">
         <v>1</v>
       </c>
       <c r="P1215" t="s">
-        <v>181</v>
+        <v>457</v>
       </c>
     </row>
     <row r="1216" spans="1:16">
@@ -62527,40 +62533,40 @@
         <v>184</v>
       </c>
       <c r="C1216">
-        <v>1.997861015979273</v>
+        <v>2.059438228380508</v>
       </c>
       <c r="D1216" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E1216">
-        <v>2.027861015979273</v>
+        <v>2.023041913329242</v>
       </c>
       <c r="F1216">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1216">
-        <v>0.003842138984020727</v>
+        <v>0.003940561771619492</v>
       </c>
       <c r="H1216">
-        <v>0.003872138984020727</v>
+        <v>0.003896958086670759</v>
       </c>
       <c r="I1216">
-        <v>0.03000000000000025</v>
+        <v>0.03639631505126628</v>
       </c>
       <c r="J1216">
-        <v>0.3506231878405806</v>
+        <v>0.3603684948733686</v>
       </c>
       <c r="K1216">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="L1216">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="M1216">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="N1216">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="O1216">
         <v>1</v>
@@ -62571,96 +62577,96 @@
     </row>
     <row r="1217" spans="1:16">
       <c r="A1217" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1217" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C1217">
-        <v>2.059438228380508</v>
+        <v>1.97223085848304</v>
       </c>
       <c r="D1217" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E1217">
-        <v>2.023041913329242</v>
+        <v>1.999438228380508</v>
       </c>
       <c r="F1217">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1217">
-        <v>0.003940561771619492</v>
+        <v>0.00386776914151696</v>
       </c>
       <c r="H1217">
-        <v>0.003896958086670759</v>
+        <v>0.003880561771619492</v>
       </c>
       <c r="I1217">
-        <v>0.03639631505126628</v>
+        <v>0.02720736989746753</v>
       </c>
       <c r="J1217">
         <v>0.3603684948733686</v>
       </c>
       <c r="K1217">
+        <v>2.63</v>
+      </c>
+      <c r="L1217">
+        <v>2.92</v>
+      </c>
+      <c r="M1217">
         <v>2.61</v>
       </c>
-      <c r="L1217">
-        <v>3</v>
-      </c>
-      <c r="M1217">
-        <v>2.6</v>
-      </c>
       <c r="N1217">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="O1217">
         <v>1</v>
       </c>
       <c r="P1217" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="1218" spans="1:16">
       <c r="A1218" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1218" t="s">
         <v>184</v>
       </c>
       <c r="C1218">
-        <v>1.97223085848304</v>
+        <v>2.026571566955544</v>
       </c>
       <c r="D1218" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E1218">
-        <v>2.002230858483041</v>
+        <v>1.989112345246391</v>
       </c>
       <c r="F1218">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1218">
-        <v>0.00386776914151696</v>
+        <v>0.003973428433044456</v>
       </c>
       <c r="H1218">
-        <v>0.00389776914151696</v>
+        <v>0.003950887654753609</v>
       </c>
       <c r="I1218">
-        <v>0.03000000000000025</v>
+        <v>0.03745922170915295</v>
       </c>
       <c r="J1218">
-        <v>0.3603684948733686</v>
+        <v>0.3729610854576461</v>
       </c>
       <c r="K1218">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="L1218">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="M1218">
         <v>2.63</v>
       </c>
       <c r="N1218">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="O1218">
         <v>1</v>
@@ -62671,93 +62677,93 @@
     </row>
     <row r="1219" spans="1:16">
       <c r="A1219" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1219" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C1219">
-        <v>2.026571566955544</v>
+        <v>1.939112345246391</v>
       </c>
       <c r="D1219" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E1219">
-        <v>1.99030117781012</v>
+        <v>1.966571566955544</v>
       </c>
       <c r="F1219">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1219">
-        <v>0.003973428433044456</v>
+        <v>0.003900887654753609</v>
       </c>
       <c r="H1219">
-        <v>0.00392969882218988</v>
+        <v>0.003913428433044456</v>
       </c>
       <c r="I1219">
-        <v>0.03627038914542391</v>
+        <v>0.02745922170915316</v>
       </c>
       <c r="J1219">
         <v>0.3729610854576461</v>
       </c>
       <c r="K1219">
+        <v>2.63</v>
+      </c>
+      <c r="L1219">
+        <v>2.92</v>
+      </c>
+      <c r="M1219">
         <v>2.61</v>
       </c>
-      <c r="L1219">
-        <v>3</v>
-      </c>
-      <c r="M1219">
-        <v>2.6</v>
-      </c>
       <c r="N1219">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="O1219">
         <v>1</v>
       </c>
       <c r="P1219" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="1220" spans="1:16">
       <c r="A1220" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1220" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C1220">
-        <v>1.939112345246391</v>
+        <v>1.980696042050148</v>
       </c>
       <c r="D1220" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E1220">
-        <v>1.969112345246391</v>
+        <v>1.938447402947106</v>
       </c>
       <c r="F1220">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1220">
-        <v>0.003900887654753609</v>
+        <v>0.004019303957949851</v>
       </c>
       <c r="H1220">
-        <v>0.003930887654753609</v>
+        <v>0.003961552597052894</v>
       </c>
       <c r="I1220">
-        <v>0.03000000000000025</v>
+        <v>0.04224863910304277</v>
       </c>
       <c r="J1220">
-        <v>0.3729610854576461</v>
+        <v>0.3875680448478523</v>
       </c>
       <c r="K1220">
         <v>2.63</v>
       </c>
       <c r="L1220">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="M1220">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="N1220">
         <v>2.95</v>
@@ -62771,10 +62777,10 @@
     </row>
     <row r="1221" spans="1:16">
       <c r="A1221" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1221" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C1221">
         <v>1.988447402947106</v>
@@ -62783,7 +62789,7 @@
         <v>333</v>
       </c>
       <c r="E1221">
-        <v>1.950696042050149</v>
+        <v>1.938447402947106</v>
       </c>
       <c r="F1221">
         <v>-1</v>
@@ -62792,10 +62798,10 @@
         <v>0.004011552597052894</v>
       </c>
       <c r="H1221">
-        <v>0.003989303957949852</v>
+        <v>0.003961552597052894</v>
       </c>
       <c r="I1221">
-        <v>0.03775136089695685</v>
+        <v>0.04999999999999982</v>
       </c>
       <c r="J1221">
         <v>0.3875680448478523</v>
@@ -62807,24 +62813,24 @@
         <v>3</v>
       </c>
       <c r="M1221">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="N1221">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="O1221">
         <v>1</v>
       </c>
       <c r="P1221" t="s">
-        <v>182</v>
+        <v>460</v>
       </c>
     </row>
     <row r="1222" spans="1:16">
       <c r="A1222" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1222" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C1222">
         <v>1.900696042050148</v>
@@ -62833,7 +62839,7 @@
         <v>331</v>
       </c>
       <c r="E1222">
-        <v>1.930696042050149</v>
+        <v>1.928447402947105</v>
       </c>
       <c r="F1222">
         <v>1</v>
@@ -62842,10 +62848,10 @@
         <v>0.003939303957949852</v>
       </c>
       <c r="H1222">
-        <v>0.003969303957949852</v>
+        <v>0.003951552597052895</v>
       </c>
       <c r="I1222">
-        <v>0.03000000000000025</v>
+        <v>0.02775136089695707</v>
       </c>
       <c r="J1222">
         <v>0.3875680448478523</v>
@@ -62857,16 +62863,16 @@
         <v>2.92</v>
       </c>
       <c r="M1222">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="N1222">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="O1222">
         <v>1</v>
       </c>
       <c r="P1222" t="s">
-        <v>182</v>
+        <v>460</v>
       </c>
     </row>
     <row r="1223" spans="1:16">
@@ -62874,13 +62880,13 @@
         <v>0</v>
       </c>
       <c r="B1223" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C1223">
         <v>1.943722972849945</v>
       </c>
       <c r="D1223" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E1223">
         <v>1.901755497771239</v>
@@ -62924,7 +62930,7 @@
         <v>1</v>
       </c>
       <c r="B1224" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C1224">
         <v>1.863722972849945</v>
@@ -62933,7 +62939,7 @@
         <v>331</v>
       </c>
       <c r="E1224">
-        <v>1.893722972849945</v>
+        <v>1.891755497771238</v>
       </c>
       <c r="F1224">
         <v>1</v>
@@ -62942,10 +62948,10 @@
         <v>0.003976277027150055</v>
       </c>
       <c r="H1224">
-        <v>0.004006277027150056</v>
+        <v>0.003988244502228761</v>
       </c>
       <c r="I1224">
-        <v>0.03000000000000025</v>
+        <v>0.02803252492129338</v>
       </c>
       <c r="J1224">
         <v>0.4016262460646597</v>
@@ -62957,10 +62963,10 @@
         <v>2.92</v>
       </c>
       <c r="M1224">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="N1224">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="O1224">
         <v>1</v>
@@ -62974,13 +62980,13 @@
         <v>0</v>
       </c>
       <c r="B1225" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C1225">
         <v>1.895176770053285</v>
       </c>
       <c r="D1225" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E1225">
         <v>1.85357846761942</v>
@@ -63024,7 +63030,7 @@
         <v>1</v>
       </c>
       <c r="B1226" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C1226">
         <v>1.815176770053285</v>
@@ -63033,7 +63039,7 @@
         <v>331</v>
       </c>
       <c r="E1226">
-        <v>1.845176770053285</v>
+        <v>1.84357846761942</v>
       </c>
       <c r="F1226">
         <v>1</v>
@@ -63042,10 +63048,10 @@
         <v>0.004024823229946716</v>
       </c>
       <c r="H1226">
-        <v>0.004054823229946715</v>
+        <v>0.004036421532380581</v>
       </c>
       <c r="I1226">
-        <v>0.03000000000000025</v>
+        <v>0.02840169756613475</v>
       </c>
       <c r="J1226">
         <v>0.4200848783067358</v>
@@ -63057,10 +63063,10 @@
         <v>2.92</v>
       </c>
       <c r="M1226">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="N1226">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="O1226">
         <v>1</v>
@@ -63071,93 +63077,93 @@
     </row>
     <row r="1227" spans="1:16">
       <c r="A1227" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1227" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C1227">
-        <v>1.837587821290496</v>
+        <v>1.831980165185554</v>
       </c>
       <c r="D1227" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="E1227">
-        <v>1.805133665497433</v>
+        <v>1.84357846761942</v>
       </c>
       <c r="F1227">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1227">
-        <v>0.004162412178709504</v>
+        <v>0.004008019834814446</v>
       </c>
       <c r="H1227">
-        <v>0.004094866334502568</v>
+        <v>0.004036421532380581</v>
       </c>
       <c r="I1227">
-        <v>0.03245415579306377</v>
+        <v>0.01159830243386528</v>
       </c>
       <c r="J1227">
-        <v>0.4386461051733976</v>
+        <v>0.4200848783067358</v>
       </c>
       <c r="K1227">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="L1227">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="M1227">
         <v>2.61</v>
       </c>
       <c r="N1227">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="O1227">
         <v>1</v>
       </c>
       <c r="P1227" t="s">
-        <v>461</v>
+        <v>329</v>
       </c>
     </row>
     <row r="1228" spans="1:16">
       <c r="A1228" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1228" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C1228">
-        <v>1.766360743393964</v>
+        <v>1.837587821290496</v>
       </c>
       <c r="D1228" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E1228">
-        <v>1.796360743393965</v>
+        <v>1.805133665497433</v>
       </c>
       <c r="F1228">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1228">
-        <v>0.004073639256606036</v>
+        <v>0.004162412178709504</v>
       </c>
       <c r="H1228">
-        <v>0.004103639256606035</v>
+        <v>0.004094866334502568</v>
       </c>
       <c r="I1228">
-        <v>0.03000000000000025</v>
+        <v>0.03245415579306377</v>
       </c>
       <c r="J1228">
         <v>0.4386461051733976</v>
       </c>
       <c r="K1228">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="L1228">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="M1228">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="N1228">
         <v>2.95</v>
@@ -63171,46 +63177,46 @@
     </row>
     <row r="1229" spans="1:16">
       <c r="A1229" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1229" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C1229">
-        <v>1.7839065876009</v>
+        <v>1.766360743393964</v>
       </c>
       <c r="D1229" t="s">
         <v>331</v>
       </c>
       <c r="E1229">
-        <v>1.796360743393965</v>
+        <v>1.795133665497432</v>
       </c>
       <c r="F1229">
         <v>1</v>
       </c>
       <c r="G1229">
-        <v>0.004056093412399099</v>
+        <v>0.004073639256606036</v>
       </c>
       <c r="H1229">
-        <v>0.004103639256606035</v>
+        <v>0.004084866334502568</v>
       </c>
       <c r="I1229">
-        <v>0.01245415579306441</v>
+        <v>0.02877292210346805</v>
       </c>
       <c r="J1229">
         <v>0.4386461051733976</v>
       </c>
       <c r="K1229">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="L1229">
         <v>2.92</v>
       </c>
       <c r="M1229">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="N1229">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="O1229">
         <v>1</v>
@@ -63221,93 +63227,93 @@
     </row>
     <row r="1230" spans="1:16">
       <c r="A1230" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1230" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C1230">
-        <v>1.780823177477708</v>
+        <v>1.7839065876009</v>
       </c>
       <c r="D1230" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="E1230">
-        <v>1.749225846496913</v>
+        <v>1.795133665497432</v>
       </c>
       <c r="F1230">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1230">
-        <v>0.004219176822522292</v>
+        <v>0.004056093412399099</v>
       </c>
       <c r="H1230">
-        <v>0.004150774153503088</v>
+        <v>0.004084866334502568</v>
       </c>
       <c r="I1230">
-        <v>0.03159733098079531</v>
+        <v>0.01122707789653221</v>
       </c>
       <c r="J1230">
-        <v>0.4600667254801102</v>
+        <v>0.4386461051733976</v>
       </c>
       <c r="K1230">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="L1230">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="M1230">
         <v>2.61</v>
       </c>
       <c r="N1230">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="O1230">
         <v>1</v>
       </c>
       <c r="P1230" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="1231" spans="1:16">
       <c r="A1231" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1231" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C1231">
-        <v>1.71002451198731</v>
+        <v>1.780823177477708</v>
       </c>
       <c r="D1231" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E1231">
-        <v>1.74002451198731</v>
+        <v>1.749225846496913</v>
       </c>
       <c r="F1231">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1231">
-        <v>0.004129975488012689</v>
+        <v>0.004219176822522292</v>
       </c>
       <c r="H1231">
-        <v>0.00415997548801269</v>
+        <v>0.004150774153503088</v>
       </c>
       <c r="I1231">
-        <v>0.03000000000000025</v>
+        <v>0.03159733098079531</v>
       </c>
       <c r="J1231">
         <v>0.4600667254801102</v>
       </c>
       <c r="K1231">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="L1231">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="M1231">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="N1231">
         <v>2.95</v>
@@ -63321,93 +63327,93 @@
     </row>
     <row r="1232" spans="1:16">
       <c r="A1232" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1232" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C1232">
-        <v>1.738072100680357</v>
+        <v>1.71002451198731</v>
       </c>
       <c r="D1232" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="E1232">
-        <v>1.707120068971975</v>
+        <v>1.739225846496912</v>
       </c>
       <c r="F1232">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1232">
-        <v>0.004261927899319643</v>
+        <v>0.004129975488012689</v>
       </c>
       <c r="H1232">
-        <v>0.004192879931028026</v>
+        <v>0.004140774153503088</v>
       </c>
       <c r="I1232">
-        <v>0.03095203170838245</v>
+        <v>0.02920133450960227</v>
       </c>
       <c r="J1232">
-        <v>0.4761992072904313</v>
+        <v>0.4600667254801102</v>
       </c>
       <c r="K1232">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="L1232">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="M1232">
         <v>2.61</v>
       </c>
       <c r="N1232">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="O1232">
         <v>1</v>
       </c>
       <c r="P1232" t="s">
-        <v>330</v>
+        <v>462</v>
       </c>
     </row>
     <row r="1233" spans="1:16">
       <c r="A1233" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1233" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C1233">
-        <v>1.667596084826166</v>
+        <v>1.738072100680357</v>
       </c>
       <c r="D1233" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E1233">
-        <v>1.697596084826166</v>
+        <v>1.707120068971975</v>
       </c>
       <c r="F1233">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1233">
-        <v>0.004172403915173835</v>
+        <v>0.004261927899319643</v>
       </c>
       <c r="H1233">
-        <v>0.004202403915173834</v>
+        <v>0.004192879931028026</v>
       </c>
       <c r="I1233">
-        <v>0.03000000000000025</v>
+        <v>0.03095203170838245</v>
       </c>
       <c r="J1233">
         <v>0.4761992072904313</v>
       </c>
       <c r="K1233">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="L1233">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="M1233">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="N1233">
         <v>2.95</v>
@@ -63416,65 +63422,65 @@
         <v>1</v>
       </c>
       <c r="P1233" t="s">
-        <v>330</v>
+        <v>463</v>
       </c>
     </row>
     <row r="1234" spans="1:16">
       <c r="A1234" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1234" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C1234">
-        <v>1.711109064123743</v>
+        <v>1.667596084826166</v>
       </c>
       <c r="D1234" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="E1234">
-        <v>1.670910516107593</v>
+        <v>1.697120068971974</v>
       </c>
       <c r="F1234">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1234">
-        <v>0.004288890935876257</v>
+        <v>0.004172403915173835</v>
       </c>
       <c r="H1234">
-        <v>0.004229089483892407</v>
+        <v>0.004182879931028026</v>
       </c>
       <c r="I1234">
-        <v>0.04019854801614997</v>
+        <v>0.02952398414580859</v>
       </c>
       <c r="J1234">
-        <v>0.4900725991924931</v>
+        <v>0.4761992072904313</v>
       </c>
       <c r="K1234">
         <v>2.63</v>
       </c>
       <c r="L1234">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="M1234">
         <v>2.61</v>
       </c>
       <c r="N1234">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="O1234">
         <v>1</v>
       </c>
       <c r="P1234" t="s">
-        <v>187</v>
+        <v>463</v>
       </c>
     </row>
     <row r="1235" spans="1:16">
       <c r="A1235" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1235" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C1235">
         <v>1.631109064123743</v>
@@ -63483,7 +63489,7 @@
         <v>331</v>
       </c>
       <c r="E1235">
-        <v>1.661109064123743</v>
+        <v>1.660910516107593</v>
       </c>
       <c r="F1235">
         <v>1</v>
@@ -63492,10 +63498,10 @@
         <v>0.004208890935876257</v>
       </c>
       <c r="H1235">
-        <v>0.004238890935876257</v>
+        <v>0.004219089483892408</v>
       </c>
       <c r="I1235">
-        <v>0.03000000000000025</v>
+        <v>0.02980145198384987</v>
       </c>
       <c r="J1235">
         <v>0.4900725991924931</v>
@@ -63507,10 +63513,10 @@
         <v>2.92</v>
       </c>
       <c r="M1235">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="N1235">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="O1235">
         <v>1</v>
@@ -63524,7 +63530,7 @@
         <v>0</v>
       </c>
       <c r="B1236" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C1236">
         <v>1.596583044051827</v>
@@ -63533,7 +63539,7 @@
         <v>331</v>
       </c>
       <c r="E1236">
-        <v>1.626583044051827</v>
+        <v>1.626647051321395</v>
       </c>
       <c r="F1236">
         <v>1</v>
@@ -63542,10 +63548,10 @@
         <v>0.004243416955948173</v>
       </c>
       <c r="H1236">
-        <v>0.004273416955948173</v>
+        <v>0.004253352948678605</v>
       </c>
       <c r="I1236">
-        <v>0.03000000000000025</v>
+        <v>0.03006400726956793</v>
       </c>
       <c r="J1236">
         <v>0.5032003634783927</v>
@@ -63557,16 +63563,16 @@
         <v>2.92</v>
       </c>
       <c r="M1236">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="N1236">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="O1236">
         <v>1</v>
       </c>
       <c r="P1236" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1237" spans="1:16">
@@ -63574,7 +63580,7 @@
         <v>0</v>
       </c>
       <c r="B1237" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C1237">
         <v>1.575343698422129</v>
@@ -63583,7 +63589,7 @@
         <v>331</v>
       </c>
       <c r="E1237">
-        <v>1.60534369842213</v>
+        <v>1.605569221628045</v>
       </c>
       <c r="F1237">
         <v>1</v>
@@ -63592,10 +63598,10 @@
         <v>0.004264656301577871</v>
       </c>
       <c r="H1237">
-        <v>0.004294656301577871</v>
+        <v>0.004274430778371956</v>
       </c>
       <c r="I1237">
-        <v>0.03000000000000025</v>
+        <v>0.03022552320591543</v>
       </c>
       <c r="J1237">
         <v>0.5112761602957683</v>
@@ -63607,16 +63613,16 @@
         <v>2.92</v>
       </c>
       <c r="M1237">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="N1237">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="O1237">
         <v>1</v>
       </c>
       <c r="P1237" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="1238" spans="1:16">
@@ -63624,7 +63630,7 @@
         <v>1</v>
       </c>
       <c r="B1238" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C1238">
         <v>1.586020268039876</v>
@@ -63633,7 +63639,7 @@
         <v>331</v>
       </c>
       <c r="E1238">
-        <v>1.60534369842213</v>
+        <v>1.605569221628045</v>
       </c>
       <c r="F1238">
         <v>1</v>
@@ -63642,10 +63648,10 @@
         <v>0.004213979731960125</v>
       </c>
       <c r="H1238">
-        <v>0.004294656301577871</v>
+        <v>0.004274430778371956</v>
       </c>
       <c r="I1238">
-        <v>0.01932343038225404</v>
+        <v>0.01954895358816922</v>
       </c>
       <c r="J1238">
         <v>0.5112761602957683</v>
@@ -63657,16 +63663,16 @@
         <v>2.9</v>
       </c>
       <c r="M1238">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="N1238">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="O1238">
         <v>1</v>
       </c>
       <c r="P1238" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="1239" spans="1:16">
@@ -63674,7 +63680,7 @@
         <v>0</v>
       </c>
       <c r="B1239" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C1239">
         <v>1.558285979436833</v>
@@ -63683,7 +63689,7 @@
         <v>331</v>
       </c>
       <c r="E1239">
-        <v>1.588285979436833</v>
+        <v>1.588641219136933</v>
       </c>
       <c r="F1239">
         <v>1</v>
@@ -63692,10 +63698,10 @@
         <v>0.004281714020563167</v>
       </c>
       <c r="H1239">
-        <v>0.004311714020563168</v>
+        <v>0.004291358780863067</v>
       </c>
       <c r="I1239">
-        <v>0.03000000000000025</v>
+        <v>0.03035523970010012</v>
       </c>
       <c r="J1239">
         <v>0.5177619850050065</v>
@@ -63707,16 +63713,16 @@
         <v>2.92</v>
       </c>
       <c r="M1239">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="N1239">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="O1239">
         <v>1</v>
       </c>
       <c r="P1239" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1240" spans="1:16">
@@ -63724,7 +63730,7 @@
         <v>1</v>
       </c>
       <c r="B1240" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C1240">
         <v>1.569351698537133</v>
@@ -63733,7 +63739,7 @@
         <v>331</v>
       </c>
       <c r="E1240">
-        <v>1.588285979436833</v>
+        <v>1.588641219136933</v>
       </c>
       <c r="F1240">
         <v>1</v>
@@ -63742,10 +63748,10 @@
         <v>0.004230648301462867</v>
       </c>
       <c r="H1240">
-        <v>0.004311714020563168</v>
+        <v>0.004291358780863067</v>
       </c>
       <c r="I1240">
-        <v>0.01893428089969973</v>
+        <v>0.0192895205997996</v>
       </c>
       <c r="J1240">
         <v>0.5177619850050065</v>
@@ -63757,16 +63763,16 @@
         <v>2.9</v>
       </c>
       <c r="M1240">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="N1240">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="O1240">
         <v>1</v>
       </c>
       <c r="P1240" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1241" spans="1:16">
@@ -63774,7 +63780,7 @@
         <v>0</v>
       </c>
       <c r="B1241" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C1241">
         <v>1.540926184059721</v>
@@ -63783,7 +63789,7 @@
         <v>331</v>
       </c>
       <c r="E1241">
-        <v>1.570926184059722</v>
+        <v>1.571413437412879</v>
       </c>
       <c r="F1241">
         <v>1</v>
@@ -63792,10 +63798,10 @@
         <v>0.004299073815940278</v>
       </c>
       <c r="H1241">
-        <v>0.004329073815940279</v>
+        <v>0.00430858656258712</v>
       </c>
       <c r="I1241">
-        <v>0.03000000000000025</v>
+        <v>0.03048725335315816</v>
       </c>
       <c r="J1241">
         <v>0.5243626676579006</v>
@@ -63807,16 +63813,16 @@
         <v>2.92</v>
       </c>
       <c r="M1241">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="N1241">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="O1241">
         <v>1</v>
       </c>
       <c r="P1241" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="1242" spans="1:16">
@@ -63824,7 +63830,7 @@
         <v>1</v>
       </c>
       <c r="B1242" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C1242">
         <v>1.552387944119195</v>
@@ -63833,7 +63839,7 @@
         <v>331</v>
       </c>
       <c r="E1242">
-        <v>1.570926184059722</v>
+        <v>1.571413437412879</v>
       </c>
       <c r="F1242">
         <v>1</v>
@@ -63842,10 +63848,10 @@
         <v>0.004247612055880804</v>
       </c>
       <c r="H1242">
-        <v>0.004329073815940279</v>
+        <v>0.00430858656258712</v>
       </c>
       <c r="I1242">
-        <v>0.01853823994052606</v>
+        <v>0.01902549329368397</v>
       </c>
       <c r="J1242">
         <v>0.5243626676579006</v>
@@ -63857,16 +63863,16 @@
         <v>2.9</v>
       </c>
       <c r="M1242">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="N1242">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="O1242">
         <v>1</v>
       </c>
       <c r="P1242" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="1243" spans="1:16">
@@ -63874,7 +63880,7 @@
         <v>0</v>
       </c>
       <c r="B1243" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C1243">
         <v>1.523625633709941</v>
@@ -63883,7 +63889,7 @@
         <v>331</v>
       </c>
       <c r="E1243">
-        <v>1.553625633709941</v>
+        <v>1.554244450183629</v>
       </c>
       <c r="F1243">
         <v>1</v>
@@ -63892,10 +63898,10 @@
         <v>0.004316374366290059</v>
       </c>
       <c r="H1243">
-        <v>0.00434637436629006</v>
+        <v>0.004325755549816371</v>
       </c>
       <c r="I1243">
-        <v>0.03000000000000025</v>
+        <v>0.03061881647368869</v>
       </c>
       <c r="J1243">
         <v>0.5309408236844333</v>
@@ -63907,16 +63913,16 @@
         <v>2.92</v>
       </c>
       <c r="M1243">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="N1243">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="O1243">
         <v>1</v>
       </c>
       <c r="P1243" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="1244" spans="1:16">
@@ -63924,7 +63930,7 @@
         <v>1</v>
       </c>
       <c r="B1244" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C1244">
         <v>1.535482083131007</v>
@@ -63933,7 +63939,7 @@
         <v>331</v>
       </c>
       <c r="E1244">
-        <v>1.553625633709941</v>
+        <v>1.554244450183629</v>
       </c>
       <c r="F1244">
         <v>1</v>
@@ -63942,10 +63948,10 @@
         <v>0.004264517916868993</v>
       </c>
       <c r="H1244">
-        <v>0.00434637436629006</v>
+        <v>0.004325755549816371</v>
       </c>
       <c r="I1244">
-        <v>0.01814355057893424</v>
+        <v>0.01876236705262269</v>
       </c>
       <c r="J1244">
         <v>0.5309408236844333</v>
@@ -63957,16 +63963,16 @@
         <v>2.9</v>
       </c>
       <c r="M1244">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="N1244">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="O1244">
         <v>1</v>
       </c>
       <c r="P1244" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="1245" spans="1:16">
@@ -63974,13 +63980,13 @@
         <v>0</v>
       </c>
       <c r="B1245" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C1245">
         <v>1.520319515886164</v>
       </c>
       <c r="D1245" t="s">
-        <v>331</v>
+        <v>189</v>
       </c>
       <c r="E1245">
         <v>1.538109076568332</v>
@@ -64016,7 +64022,7 @@
         <v>1</v>
       </c>
       <c r="P1245" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="1246" spans="1:16">
@@ -64024,13 +64030,13 @@
         <v>0</v>
       </c>
       <c r="B1246" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C1246">
         <v>1.50458822952096</v>
       </c>
       <c r="D1246" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E1246">
         <v>1.520017847304926</v>
@@ -64066,7 +64072,7 @@
         <v>1</v>
       </c>
       <c r="P1246" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="1247" spans="1:16">
@@ -64074,13 +64080,13 @@
         <v>0</v>
       </c>
       <c r="B1247" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C1247">
         <v>1.485291405699136</v>
       </c>
       <c r="D1247" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E1247">
         <v>1.500796108400696</v>
@@ -64116,7 +64122,57 @@
         <v>1</v>
       </c>
       <c r="P1247" t="s">
-        <v>334</v>
+        <v>333</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:16">
+      <c r="A1248" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1248" t="s">
+        <v>189</v>
+      </c>
+      <c r="C1248">
+        <v>1.338592496196642</v>
+      </c>
+      <c r="D1248" t="s">
+        <v>331</v>
+      </c>
+      <c r="E1248">
+        <v>1.340846545655222</v>
+      </c>
+      <c r="F1248">
+        <v>1</v>
+      </c>
+      <c r="G1248">
+        <v>0.004561407503803359</v>
+      </c>
+      <c r="H1248">
+        <v>0.004539153454344778</v>
+      </c>
+      <c r="I1248">
+        <v>0.002254049458580543</v>
+      </c>
+      <c r="J1248">
+        <v>0.6127024729290337</v>
+      </c>
+      <c r="K1248">
+        <v>2.63</v>
+      </c>
+      <c r="L1248">
+        <v>2.95</v>
+      </c>
+      <c r="M1248">
+        <v>2.61</v>
+      </c>
+      <c r="N1248">
+        <v>2.94</v>
+      </c>
+      <c r="O1248">
+        <v>1</v>
+      </c>
+      <c r="P1248" t="s">
+        <v>467</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01288-601288.xlsx
+++ b/s60_signal/position-01288-601288.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3756" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3765" uniqueCount="470">
   <si>
     <t>trade_time</t>
   </si>
@@ -562,10 +562,10 @@
     <t>2021-07-05</t>
   </si>
   <si>
-    <t>2021-07-30</t>
+    <t>2021-08-03</t>
   </si>
   <si>
-    <t>2021-08-03</t>
+    <t>2021-08-13</t>
   </si>
   <si>
     <t>2021-07-22</t>
@@ -583,7 +583,7 @@
     <t>2021-08-05</t>
   </si>
   <si>
-    <t>2021-08-11</t>
+    <t>2021-08-12</t>
   </si>
   <si>
     <t>2017-05-12</t>
@@ -1009,13 +1009,13 @@
     <t>2021-07-27</t>
   </si>
   <si>
-    <t>2021-08-12</t>
-  </si>
-  <si>
-    <t>2021-07-28</t>
+    <t>2021-08-16</t>
   </si>
   <si>
     <t>2021-07-29</t>
+  </si>
+  <si>
+    <t>2021-08-11</t>
   </si>
   <si>
     <t>2021-08-06</t>
@@ -1417,7 +1417,13 @@
     <t>2021-07-26</t>
   </si>
   <si>
-    <t>2021-08-10</t>
+    <t>2021-07-28</t>
+  </si>
+  <si>
+    <t>2021-07-30</t>
+  </si>
+  <si>
+    <t>2021-08-04</t>
   </si>
 </sst>
 </file>
@@ -1775,7 +1781,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1248"/>
+  <dimension ref="A1:P1251"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -62283,40 +62289,40 @@
         <v>182</v>
       </c>
       <c r="C1211">
-        <v>2.071525978903674</v>
+        <v>2.048267692863576</v>
       </c>
       <c r="D1211" t="s">
         <v>331</v>
       </c>
       <c r="E1211">
-        <v>2.074896835883625</v>
+        <v>2.061582264373601</v>
       </c>
       <c r="F1211">
         <v>1</v>
       </c>
       <c r="G1211">
-        <v>0.003788474021096327</v>
+        <v>0.003791732307136424</v>
       </c>
       <c r="H1211">
-        <v>0.003805103164116375</v>
+        <v>0.0037984177356264</v>
       </c>
       <c r="I1211">
-        <v>0.003370856979950876</v>
+        <v>0.01331457151002491</v>
       </c>
       <c r="J1211">
         <v>0.3314571510024426</v>
       </c>
       <c r="K1211">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="L1211">
+        <v>2.92</v>
+      </c>
+      <c r="M1211">
+        <v>2.62</v>
+      </c>
+      <c r="N1211">
         <v>2.93</v>
-      </c>
-      <c r="M1211">
-        <v>2.61</v>
-      </c>
-      <c r="N1211">
-        <v>2.94</v>
       </c>
       <c r="O1211">
         <v>1</v>
@@ -62333,40 +62339,40 @@
         <v>183</v>
       </c>
       <c r="C1212">
-        <v>2.048267692863576</v>
+        <v>2.068211407393649</v>
       </c>
       <c r="D1212" t="s">
         <v>331</v>
       </c>
       <c r="E1212">
-        <v>2.074896835883625</v>
+        <v>2.061582264373601</v>
       </c>
       <c r="F1212">
         <v>1</v>
       </c>
       <c r="G1212">
-        <v>0.003791732307136424</v>
+        <v>0.003791788592606351</v>
       </c>
       <c r="H1212">
-        <v>0.003805103164116375</v>
+        <v>0.0037984177356264</v>
       </c>
       <c r="I1212">
-        <v>0.02662914302004893</v>
+        <v>-0.006629143020048467</v>
       </c>
       <c r="J1212">
         <v>0.3314571510024426</v>
       </c>
       <c r="K1212">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="L1212">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="M1212">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="N1212">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="O1212">
         <v>1</v>
@@ -62380,43 +62386,43 @@
         <v>0</v>
       </c>
       <c r="B1213" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C1213">
-        <v>2.022204053708345</v>
+        <v>2.109031399307522</v>
       </c>
       <c r="D1213" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E1213">
-        <v>2.049031399307522</v>
+        <v>2.072445072107109</v>
       </c>
       <c r="F1213">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1213">
-        <v>0.003817795946291655</v>
+        <v>0.003890968600692479</v>
       </c>
       <c r="H1213">
-        <v>0.003830968600692479</v>
+        <v>0.003847554927892891</v>
       </c>
       <c r="I1213">
-        <v>0.02682734559917632</v>
+        <v>0.03658632720041233</v>
       </c>
       <c r="J1213">
         <v>0.3413672799588041</v>
       </c>
       <c r="K1213">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="L1213">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="M1213">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="N1213">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="O1213">
         <v>1</v>
@@ -62427,96 +62433,96 @@
     </row>
     <row r="1214" spans="1:16">
       <c r="A1214" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1214" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C1214">
-        <v>2.084873479736085</v>
+        <v>2.022204053708345</v>
       </c>
       <c r="D1214" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E1214">
-        <v>2.048379711614491</v>
+        <v>2.035617726507934</v>
       </c>
       <c r="F1214">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1214">
-        <v>0.003915126520263916</v>
+        <v>0.003817795946291655</v>
       </c>
       <c r="H1214">
-        <v>0.00387162028838551</v>
+        <v>0.003824382273492067</v>
       </c>
       <c r="I1214">
-        <v>0.03649376812159399</v>
+        <v>0.01341367279958838</v>
       </c>
       <c r="J1214">
-        <v>0.3506231878405806</v>
+        <v>0.3413672799588041</v>
       </c>
       <c r="K1214">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="L1214">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="M1214">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="N1214">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="O1214">
         <v>1</v>
       </c>
       <c r="P1214" t="s">
-        <v>457</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1215" spans="1:16">
       <c r="A1215" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1215" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C1215">
-        <v>1.997861015979273</v>
+        <v>2.084873479736085</v>
       </c>
       <c r="D1215" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E1215">
-        <v>2.024873479736085</v>
+        <v>2.048379711614491</v>
       </c>
       <c r="F1215">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1215">
-        <v>0.003842138984020727</v>
+        <v>0.003915126520263916</v>
       </c>
       <c r="H1215">
-        <v>0.003855126520263915</v>
+        <v>0.00387162028838551</v>
       </c>
       <c r="I1215">
-        <v>0.02701246375681166</v>
+        <v>0.03649376812159399</v>
       </c>
       <c r="J1215">
         <v>0.3506231878405806</v>
       </c>
       <c r="K1215">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="L1215">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="M1215">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="N1215">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="O1215">
         <v>1</v>
@@ -62527,96 +62533,96 @@
     </row>
     <row r="1216" spans="1:16">
       <c r="A1216" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1216" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C1216">
-        <v>2.059438228380508</v>
+        <v>1.997861015979273</v>
       </c>
       <c r="D1216" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E1216">
-        <v>2.023041913329242</v>
+        <v>2.011367247857679</v>
       </c>
       <c r="F1216">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1216">
-        <v>0.003940561771619492</v>
+        <v>0.003842138984020727</v>
       </c>
       <c r="H1216">
-        <v>0.003896958086670759</v>
+        <v>0.003848632752142321</v>
       </c>
       <c r="I1216">
-        <v>0.03639631505126628</v>
+        <v>0.01350623187840627</v>
       </c>
       <c r="J1216">
-        <v>0.3603684948733686</v>
+        <v>0.3506231878405806</v>
       </c>
       <c r="K1216">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="L1216">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="M1216">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="N1216">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="O1216">
         <v>1</v>
       </c>
       <c r="P1216" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="1217" spans="1:16">
       <c r="A1217" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1217" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C1217">
-        <v>1.97223085848304</v>
+        <v>2.059438228380508</v>
       </c>
       <c r="D1217" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E1217">
-        <v>1.999438228380508</v>
+        <v>2.009438228380508</v>
       </c>
       <c r="F1217">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1217">
-        <v>0.00386776914151696</v>
+        <v>0.003940561771619492</v>
       </c>
       <c r="H1217">
-        <v>0.003880561771619492</v>
+        <v>0.003890561771619492</v>
       </c>
       <c r="I1217">
-        <v>0.02720736989746753</v>
+        <v>0.04999999999999982</v>
       </c>
       <c r="J1217">
         <v>0.3603684948733686</v>
       </c>
       <c r="K1217">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="L1217">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="M1217">
         <v>2.61</v>
       </c>
       <c r="N1217">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="O1217">
         <v>1</v>
@@ -62627,81 +62633,81 @@
     </row>
     <row r="1218" spans="1:16">
       <c r="A1218" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1218" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C1218">
-        <v>2.026571566955544</v>
+        <v>1.97223085848304</v>
       </c>
       <c r="D1218" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E1218">
-        <v>1.989112345246391</v>
+        <v>1.985834543431774</v>
       </c>
       <c r="F1218">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1218">
-        <v>0.003973428433044456</v>
+        <v>0.00386776914151696</v>
       </c>
       <c r="H1218">
-        <v>0.003950887654753609</v>
+        <v>0.003874165456568226</v>
       </c>
       <c r="I1218">
-        <v>0.03745922170915295</v>
+        <v>0.01360368494873399</v>
       </c>
       <c r="J1218">
-        <v>0.3729610854576461</v>
+        <v>0.3603684948733686</v>
       </c>
       <c r="K1218">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="L1218">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="M1218">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="N1218">
-        <v>2.97</v>
+        <v>2.93</v>
       </c>
       <c r="O1218">
         <v>1</v>
       </c>
       <c r="P1218" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="1219" spans="1:16">
       <c r="A1219" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1219" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C1219">
-        <v>1.939112345246391</v>
+        <v>2.019112345246391</v>
       </c>
       <c r="D1219" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E1219">
-        <v>1.966571566955544</v>
+        <v>1.976571566955544</v>
       </c>
       <c r="F1219">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1219">
-        <v>0.003900887654753609</v>
+        <v>0.00398088765475361</v>
       </c>
       <c r="H1219">
-        <v>0.003913428433044456</v>
+        <v>0.003923428433044457</v>
       </c>
       <c r="I1219">
-        <v>0.02745922170915316</v>
+        <v>0.04254077829084668</v>
       </c>
       <c r="J1219">
         <v>0.3729610854576461</v>
@@ -62710,13 +62716,13 @@
         <v>2.63</v>
       </c>
       <c r="L1219">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="M1219">
         <v>2.61</v>
       </c>
       <c r="N1219">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="O1219">
         <v>1</v>
@@ -62727,37 +62733,37 @@
     </row>
     <row r="1220" spans="1:16">
       <c r="A1220" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1220" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C1220">
-        <v>1.980696042050148</v>
+        <v>2.026571566955544</v>
       </c>
       <c r="D1220" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E1220">
-        <v>1.938447402947106</v>
+        <v>1.976571566955544</v>
       </c>
       <c r="F1220">
         <v>-1</v>
       </c>
       <c r="G1220">
-        <v>0.004019303957949851</v>
+        <v>0.003973428433044456</v>
       </c>
       <c r="H1220">
-        <v>0.003961552597052894</v>
+        <v>0.003923428433044457</v>
       </c>
       <c r="I1220">
-        <v>0.04224863910304277</v>
+        <v>0.04999999999999982</v>
       </c>
       <c r="J1220">
-        <v>0.3875680448478523</v>
+        <v>0.3729610854576461</v>
       </c>
       <c r="K1220">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="L1220">
         <v>3</v>
@@ -62772,86 +62778,86 @@
         <v>1</v>
       </c>
       <c r="P1220" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="1221" spans="1:16">
       <c r="A1221" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1221" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C1221">
-        <v>1.988447402947106</v>
+        <v>1.939112345246391</v>
       </c>
       <c r="D1221" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E1221">
-        <v>1.938447402947106</v>
+        <v>1.952841956100968</v>
       </c>
       <c r="F1221">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1221">
-        <v>0.004011552597052894</v>
+        <v>0.003900887654753609</v>
       </c>
       <c r="H1221">
-        <v>0.003961552597052894</v>
+        <v>0.003907158043899033</v>
       </c>
       <c r="I1221">
-        <v>0.04999999999999982</v>
+        <v>0.0137296108545768</v>
       </c>
       <c r="J1221">
-        <v>0.3875680448478523</v>
+        <v>0.3729610854576461</v>
       </c>
       <c r="K1221">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="L1221">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="M1221">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="N1221">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="O1221">
         <v>1</v>
       </c>
       <c r="P1221" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="1222" spans="1:16">
       <c r="A1222" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1222" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C1222">
-        <v>1.900696042050148</v>
+        <v>1.980696042050148</v>
       </c>
       <c r="D1222" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E1222">
-        <v>1.928447402947105</v>
+        <v>1.938447402947106</v>
       </c>
       <c r="F1222">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1222">
-        <v>0.003939303957949852</v>
+        <v>0.004019303957949851</v>
       </c>
       <c r="H1222">
-        <v>0.003951552597052895</v>
+        <v>0.003961552597052894</v>
       </c>
       <c r="I1222">
-        <v>0.02775136089695707</v>
+        <v>0.04224863910304277</v>
       </c>
       <c r="J1222">
         <v>0.3875680448478523</v>
@@ -62860,13 +62866,13 @@
         <v>2.63</v>
       </c>
       <c r="L1222">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="M1222">
         <v>2.61</v>
       </c>
       <c r="N1222">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="O1222">
         <v>1</v>
@@ -62877,81 +62883,81 @@
     </row>
     <row r="1223" spans="1:16">
       <c r="A1223" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1223" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C1223">
-        <v>1.943722972849945</v>
+        <v>1.900696042050148</v>
       </c>
       <c r="D1223" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E1223">
-        <v>1.901755497771239</v>
+        <v>1.914571722498627</v>
       </c>
       <c r="F1223">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1223">
-        <v>0.004056277027150055</v>
+        <v>0.003939303957949852</v>
       </c>
       <c r="H1223">
-        <v>0.003998244502228762</v>
+        <v>0.003945428277501373</v>
       </c>
       <c r="I1223">
-        <v>0.04196747507870646</v>
+        <v>0.01387568044847876</v>
       </c>
       <c r="J1223">
-        <v>0.4016262460646597</v>
+        <v>0.3875680448478523</v>
       </c>
       <c r="K1223">
         <v>2.63</v>
       </c>
       <c r="L1223">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="M1223">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="N1223">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="O1223">
         <v>1</v>
       </c>
       <c r="P1223" t="s">
-        <v>328</v>
+        <v>460</v>
       </c>
     </row>
     <row r="1224" spans="1:16">
       <c r="A1224" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1224" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C1224">
-        <v>1.863722972849945</v>
+        <v>1.943722972849945</v>
       </c>
       <c r="D1224" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E1224">
-        <v>1.891755497771238</v>
+        <v>1.901755497771239</v>
       </c>
       <c r="F1224">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1224">
-        <v>0.003976277027150055</v>
+        <v>0.004056277027150055</v>
       </c>
       <c r="H1224">
-        <v>0.003988244502228761</v>
+        <v>0.003998244502228762</v>
       </c>
       <c r="I1224">
-        <v>0.02803252492129338</v>
+        <v>0.04196747507870646</v>
       </c>
       <c r="J1224">
         <v>0.4016262460646597</v>
@@ -62960,13 +62966,13 @@
         <v>2.63</v>
       </c>
       <c r="L1224">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="M1224">
         <v>2.61</v>
       </c>
       <c r="N1224">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="O1224">
         <v>1</v>
@@ -62977,146 +62983,146 @@
     </row>
     <row r="1225" spans="1:16">
       <c r="A1225" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1225" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C1225">
-        <v>1.895176770053285</v>
+        <v>1.863722972849945</v>
       </c>
       <c r="D1225" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E1225">
-        <v>1.85357846761942</v>
+        <v>1.877739235310592</v>
       </c>
       <c r="F1225">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1225">
-        <v>0.004104823229946716</v>
+        <v>0.003976277027150055</v>
       </c>
       <c r="H1225">
-        <v>0.004046421532380581</v>
+        <v>0.003982260764689409</v>
       </c>
       <c r="I1225">
-        <v>0.04159830243386509</v>
+        <v>0.0140162624606468</v>
       </c>
       <c r="J1225">
-        <v>0.4200848783067358</v>
+        <v>0.4016262460646597</v>
       </c>
       <c r="K1225">
         <v>2.63</v>
       </c>
       <c r="L1225">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="M1225">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="N1225">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="O1225">
         <v>1</v>
       </c>
       <c r="P1225" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="1226" spans="1:16">
       <c r="A1226" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1226" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C1226">
-        <v>1.815176770053285</v>
+        <v>1.879788022692531</v>
       </c>
       <c r="D1226" t="s">
         <v>331</v>
       </c>
       <c r="E1226">
-        <v>1.84357846761942</v>
+        <v>1.877739235310592</v>
       </c>
       <c r="F1226">
         <v>1</v>
       </c>
       <c r="G1226">
-        <v>0.004024823229946716</v>
+        <v>0.003960211977307468</v>
       </c>
       <c r="H1226">
-        <v>0.004036421532380581</v>
+        <v>0.003982260764689409</v>
       </c>
       <c r="I1226">
-        <v>0.02840169756613475</v>
+        <v>-0.002048787381939698</v>
       </c>
       <c r="J1226">
-        <v>0.4200848783067358</v>
+        <v>0.4016262460646597</v>
       </c>
       <c r="K1226">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="L1226">
         <v>2.92</v>
       </c>
       <c r="M1226">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="N1226">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="O1226">
         <v>1</v>
       </c>
       <c r="P1226" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="1227" spans="1:16">
       <c r="A1227" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1227" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C1227">
-        <v>1.831980165185554</v>
+        <v>1.88677507248715</v>
       </c>
       <c r="D1227" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E1227">
-        <v>1.84357846761942</v>
+        <v>1.85357846761942</v>
       </c>
       <c r="F1227">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1227">
-        <v>0.004008019834814446</v>
+        <v>0.00411322492751285</v>
       </c>
       <c r="H1227">
-        <v>0.004036421532380581</v>
+        <v>0.004046421532380581</v>
       </c>
       <c r="I1227">
-        <v>0.01159830243386528</v>
+        <v>0.03319660486773035</v>
       </c>
       <c r="J1227">
         <v>0.4200848783067358</v>
       </c>
       <c r="K1227">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="L1227">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="M1227">
         <v>2.61</v>
       </c>
       <c r="N1227">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="O1227">
         <v>1</v>
@@ -63127,146 +63133,146 @@
     </row>
     <row r="1228" spans="1:16">
       <c r="A1228" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1228" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C1228">
-        <v>1.837587821290496</v>
+        <v>1.815176770053285</v>
       </c>
       <c r="D1228" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E1228">
-        <v>1.805133665497433</v>
+        <v>1.829377618836352</v>
       </c>
       <c r="F1228">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1228">
-        <v>0.004162412178709504</v>
+        <v>0.004024823229946716</v>
       </c>
       <c r="H1228">
-        <v>0.004094866334502568</v>
+        <v>0.004030622381163648</v>
       </c>
       <c r="I1228">
-        <v>0.03245415579306377</v>
+        <v>0.0142008487830676</v>
       </c>
       <c r="J1228">
-        <v>0.4386461051733976</v>
+        <v>0.4200848783067358</v>
       </c>
       <c r="K1228">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="L1228">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="M1228">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="N1228">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="O1228">
         <v>1</v>
       </c>
       <c r="P1228" t="s">
-        <v>461</v>
+        <v>329</v>
       </c>
     </row>
     <row r="1229" spans="1:16">
       <c r="A1229" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1229" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C1229">
-        <v>1.766360743393964</v>
+        <v>1.831980165185554</v>
       </c>
       <c r="D1229" t="s">
         <v>331</v>
       </c>
       <c r="E1229">
-        <v>1.795133665497432</v>
+        <v>1.829377618836352</v>
       </c>
       <c r="F1229">
         <v>1</v>
       </c>
       <c r="G1229">
-        <v>0.004073639256606036</v>
+        <v>0.004008019834814446</v>
       </c>
       <c r="H1229">
-        <v>0.004084866334502568</v>
+        <v>0.004030622381163648</v>
       </c>
       <c r="I1229">
-        <v>0.02877292210346805</v>
+        <v>-0.002602546349201873</v>
       </c>
       <c r="J1229">
-        <v>0.4386461051733976</v>
+        <v>0.4200848783067358</v>
       </c>
       <c r="K1229">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="L1229">
         <v>2.92</v>
       </c>
       <c r="M1229">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="N1229">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="O1229">
         <v>1</v>
       </c>
       <c r="P1229" t="s">
-        <v>461</v>
+        <v>329</v>
       </c>
     </row>
     <row r="1230" spans="1:16">
       <c r="A1230" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1230" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C1230">
-        <v>1.7839065876009</v>
+        <v>1.837587821290496</v>
       </c>
       <c r="D1230" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E1230">
-        <v>1.795133665497432</v>
+        <v>1.805133665497433</v>
       </c>
       <c r="F1230">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1230">
-        <v>0.004056093412399099</v>
+        <v>0.004162412178709504</v>
       </c>
       <c r="H1230">
-        <v>0.004084866334502568</v>
+        <v>0.004094866334502568</v>
       </c>
       <c r="I1230">
-        <v>0.01122707789653221</v>
+        <v>0.03245415579306377</v>
       </c>
       <c r="J1230">
         <v>0.4386461051733976</v>
       </c>
       <c r="K1230">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="L1230">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="M1230">
         <v>2.61</v>
       </c>
       <c r="N1230">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="O1230">
         <v>1</v>
@@ -63277,96 +63283,96 @@
     </row>
     <row r="1231" spans="1:16">
       <c r="A1231" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1231" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C1231">
-        <v>1.780823177477708</v>
+        <v>1.766360743393964</v>
       </c>
       <c r="D1231" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E1231">
-        <v>1.749225846496913</v>
+        <v>1.780747204445698</v>
       </c>
       <c r="F1231">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1231">
-        <v>0.004219176822522292</v>
+        <v>0.004073639256606036</v>
       </c>
       <c r="H1231">
-        <v>0.004150774153503088</v>
+        <v>0.004079252795554302</v>
       </c>
       <c r="I1231">
-        <v>0.03159733098079531</v>
+        <v>0.01438646105173413</v>
       </c>
       <c r="J1231">
-        <v>0.4600667254801102</v>
+        <v>0.4386461051733976</v>
       </c>
       <c r="K1231">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="L1231">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="M1231">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="N1231">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="O1231">
         <v>1</v>
       </c>
       <c r="P1231" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="1232" spans="1:16">
       <c r="A1232" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1232" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C1232">
-        <v>1.71002451198731</v>
+        <v>1.780823177477708</v>
       </c>
       <c r="D1232" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E1232">
-        <v>1.739225846496912</v>
+        <v>1.749225846496913</v>
       </c>
       <c r="F1232">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1232">
-        <v>0.004129975488012689</v>
+        <v>0.004219176822522292</v>
       </c>
       <c r="H1232">
-        <v>0.004140774153503088</v>
+        <v>0.004150774153503088</v>
       </c>
       <c r="I1232">
-        <v>0.02920133450960227</v>
+        <v>0.03159733098079531</v>
       </c>
       <c r="J1232">
         <v>0.4600667254801102</v>
       </c>
       <c r="K1232">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="L1232">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="M1232">
         <v>2.61</v>
       </c>
       <c r="N1232">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="O1232">
         <v>1</v>
@@ -63377,96 +63383,96 @@
     </row>
     <row r="1233" spans="1:16">
       <c r="A1233" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1233" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C1233">
-        <v>1.738072100680357</v>
+        <v>1.71002451198731</v>
       </c>
       <c r="D1233" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E1233">
-        <v>1.707120068971975</v>
+        <v>1.724625179242111</v>
       </c>
       <c r="F1233">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1233">
-        <v>0.004261927899319643</v>
+        <v>0.004129975488012689</v>
       </c>
       <c r="H1233">
-        <v>0.004192879931028026</v>
+        <v>0.004135374820757889</v>
       </c>
       <c r="I1233">
-        <v>0.03095203170838245</v>
+        <v>0.01460066725480114</v>
       </c>
       <c r="J1233">
-        <v>0.4761992072904313</v>
+        <v>0.4600667254801102</v>
       </c>
       <c r="K1233">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="L1233">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="M1233">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="N1233">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="O1233">
         <v>1</v>
       </c>
       <c r="P1233" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="1234" spans="1:16">
       <c r="A1234" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1234" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C1234">
-        <v>1.667596084826166</v>
+        <v>1.738072100680357</v>
       </c>
       <c r="D1234" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E1234">
-        <v>1.697120068971974</v>
+        <v>1.707120068971975</v>
       </c>
       <c r="F1234">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1234">
-        <v>0.004172403915173835</v>
+        <v>0.004261927899319643</v>
       </c>
       <c r="H1234">
-        <v>0.004182879931028026</v>
+        <v>0.004192879931028026</v>
       </c>
       <c r="I1234">
-        <v>0.02952398414580859</v>
+        <v>0.03095203170838245</v>
       </c>
       <c r="J1234">
         <v>0.4761992072904313</v>
       </c>
       <c r="K1234">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="L1234">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="M1234">
         <v>2.61</v>
       </c>
       <c r="N1234">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="O1234">
         <v>1</v>
@@ -63477,34 +63483,34 @@
     </row>
     <row r="1235" spans="1:16">
       <c r="A1235" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1235" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C1235">
-        <v>1.631109064123743</v>
+        <v>1.667596084826166</v>
       </c>
       <c r="D1235" t="s">
         <v>331</v>
       </c>
       <c r="E1235">
-        <v>1.660910516107593</v>
+        <v>1.68235807689907</v>
       </c>
       <c r="F1235">
         <v>1</v>
       </c>
       <c r="G1235">
-        <v>0.004208890935876257</v>
+        <v>0.004172403915173835</v>
       </c>
       <c r="H1235">
-        <v>0.004219089483892408</v>
+        <v>0.00417764192310093</v>
       </c>
       <c r="I1235">
-        <v>0.02980145198384987</v>
+        <v>0.0147619920729043</v>
       </c>
       <c r="J1235">
-        <v>0.4900725991924931</v>
+        <v>0.4761992072904313</v>
       </c>
       <c r="K1235">
         <v>2.63</v>
@@ -63513,16 +63519,16 @@
         <v>2.92</v>
       </c>
       <c r="M1235">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="N1235">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="O1235">
         <v>1</v>
       </c>
       <c r="P1235" t="s">
-        <v>187</v>
+        <v>463</v>
       </c>
     </row>
     <row r="1236" spans="1:16">
@@ -63530,31 +63536,31 @@
         <v>0</v>
       </c>
       <c r="B1236" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C1236">
-        <v>1.596583044051827</v>
+        <v>1.631109064123743</v>
       </c>
       <c r="D1236" t="s">
         <v>331</v>
       </c>
       <c r="E1236">
-        <v>1.626647051321395</v>
+        <v>1.646009790115668</v>
       </c>
       <c r="F1236">
         <v>1</v>
       </c>
       <c r="G1236">
-        <v>0.004243416955948173</v>
+        <v>0.004208890935876257</v>
       </c>
       <c r="H1236">
-        <v>0.004253352948678605</v>
+        <v>0.004213990209884332</v>
       </c>
       <c r="I1236">
-        <v>0.03006400726956793</v>
+        <v>0.01490072599192516</v>
       </c>
       <c r="J1236">
-        <v>0.5032003634783927</v>
+        <v>0.4900725991924931</v>
       </c>
       <c r="K1236">
         <v>2.63</v>
@@ -63563,16 +63569,16 @@
         <v>2.92</v>
       </c>
       <c r="M1236">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="N1236">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="O1236">
         <v>1</v>
       </c>
       <c r="P1236" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="1237" spans="1:16">
@@ -63580,31 +63586,31 @@
         <v>0</v>
       </c>
       <c r="B1237" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C1237">
-        <v>1.575343698422129</v>
+        <v>1.596583044051827</v>
       </c>
       <c r="D1237" t="s">
         <v>331</v>
       </c>
       <c r="E1237">
-        <v>1.605569221628045</v>
+        <v>1.611615047686611</v>
       </c>
       <c r="F1237">
         <v>1</v>
       </c>
       <c r="G1237">
-        <v>0.004264656301577871</v>
+        <v>0.004243416955948173</v>
       </c>
       <c r="H1237">
-        <v>0.004274430778371956</v>
+        <v>0.004248384952313389</v>
       </c>
       <c r="I1237">
-        <v>0.03022552320591543</v>
+        <v>0.01503200363478419</v>
       </c>
       <c r="J1237">
-        <v>0.5112761602957683</v>
+        <v>0.5032003634783927</v>
       </c>
       <c r="K1237">
         <v>2.63</v>
@@ -63613,16 +63619,16 @@
         <v>2.92</v>
       </c>
       <c r="M1237">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="N1237">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="O1237">
         <v>1</v>
       </c>
       <c r="P1237" t="s">
-        <v>464</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1238" spans="1:16">
@@ -63633,28 +63639,28 @@
         <v>188</v>
       </c>
       <c r="C1238">
-        <v>1.586020268039876</v>
+        <v>1.606775065860531</v>
       </c>
       <c r="D1238" t="s">
         <v>331</v>
       </c>
       <c r="E1238">
-        <v>1.605569221628045</v>
+        <v>1.611615047686611</v>
       </c>
       <c r="F1238">
         <v>1</v>
       </c>
       <c r="G1238">
-        <v>0.004213979731960125</v>
+        <v>0.004193224934139469</v>
       </c>
       <c r="H1238">
-        <v>0.004274430778371956</v>
+        <v>0.004248384952313389</v>
       </c>
       <c r="I1238">
-        <v>0.01954895358816922</v>
+        <v>0.004839981826080697</v>
       </c>
       <c r="J1238">
-        <v>0.5112761602957683</v>
+        <v>0.5032003634783927</v>
       </c>
       <c r="K1238">
         <v>2.57</v>
@@ -63663,16 +63669,16 @@
         <v>2.9</v>
       </c>
       <c r="M1238">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="N1238">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="O1238">
         <v>1</v>
       </c>
       <c r="P1238" t="s">
-        <v>464</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1239" spans="1:16">
@@ -63680,31 +63686,31 @@
         <v>0</v>
       </c>
       <c r="B1239" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C1239">
-        <v>1.558285979436833</v>
+        <v>1.575343698422129</v>
       </c>
       <c r="D1239" t="s">
         <v>331</v>
       </c>
       <c r="E1239">
-        <v>1.588641219136933</v>
+        <v>1.590456460025087</v>
       </c>
       <c r="F1239">
         <v>1</v>
       </c>
       <c r="G1239">
-        <v>0.004281714020563167</v>
+        <v>0.004264656301577871</v>
       </c>
       <c r="H1239">
-        <v>0.004291358780863067</v>
+        <v>0.004269543539974914</v>
       </c>
       <c r="I1239">
-        <v>0.03035523970010012</v>
+        <v>0.01511276160295782</v>
       </c>
       <c r="J1239">
-        <v>0.5177619850050065</v>
+        <v>0.5112761602957683</v>
       </c>
       <c r="K1239">
         <v>2.63</v>
@@ -63713,16 +63719,16 @@
         <v>2.92</v>
       </c>
       <c r="M1239">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="N1239">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="O1239">
         <v>1</v>
       </c>
       <c r="P1239" t="s">
-        <v>184</v>
+        <v>464</v>
       </c>
     </row>
     <row r="1240" spans="1:16">
@@ -63733,28 +63739,28 @@
         <v>188</v>
       </c>
       <c r="C1240">
-        <v>1.569351698537133</v>
+        <v>1.586020268039876</v>
       </c>
       <c r="D1240" t="s">
         <v>331</v>
       </c>
       <c r="E1240">
-        <v>1.588641219136933</v>
+        <v>1.590456460025087</v>
       </c>
       <c r="F1240">
         <v>1</v>
       </c>
       <c r="G1240">
-        <v>0.004230648301462867</v>
+        <v>0.004213979731960125</v>
       </c>
       <c r="H1240">
-        <v>0.004291358780863067</v>
+        <v>0.004269543539974914</v>
       </c>
       <c r="I1240">
-        <v>0.0192895205997996</v>
+        <v>0.004436191985211613</v>
       </c>
       <c r="J1240">
-        <v>0.5177619850050065</v>
+        <v>0.5112761602957683</v>
       </c>
       <c r="K1240">
         <v>2.57</v>
@@ -63763,16 +63769,16 @@
         <v>2.9</v>
       </c>
       <c r="M1240">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="N1240">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="O1240">
         <v>1</v>
       </c>
       <c r="P1240" t="s">
-        <v>184</v>
+        <v>464</v>
       </c>
     </row>
     <row r="1241" spans="1:16">
@@ -63780,31 +63786,31 @@
         <v>0</v>
       </c>
       <c r="B1241" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C1241">
-        <v>1.540926184059721</v>
+        <v>1.558285979436833</v>
       </c>
       <c r="D1241" t="s">
         <v>331</v>
       </c>
       <c r="E1241">
-        <v>1.571413437412879</v>
+        <v>1.573463599286883</v>
       </c>
       <c r="F1241">
         <v>1</v>
       </c>
       <c r="G1241">
-        <v>0.004299073815940278</v>
+        <v>0.004281714020563167</v>
       </c>
       <c r="H1241">
-        <v>0.00430858656258712</v>
+        <v>0.004286536400713118</v>
       </c>
       <c r="I1241">
-        <v>0.03048725335315816</v>
+        <v>0.01517761985005017</v>
       </c>
       <c r="J1241">
-        <v>0.5243626676579006</v>
+        <v>0.5177619850050065</v>
       </c>
       <c r="K1241">
         <v>2.63</v>
@@ -63813,16 +63819,16 @@
         <v>2.92</v>
       </c>
       <c r="M1241">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="N1241">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="O1241">
         <v>1</v>
       </c>
       <c r="P1241" t="s">
-        <v>465</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1242" spans="1:16">
@@ -63833,28 +63839,28 @@
         <v>188</v>
       </c>
       <c r="C1242">
-        <v>1.552387944119195</v>
+        <v>1.569351698537133</v>
       </c>
       <c r="D1242" t="s">
         <v>331</v>
       </c>
       <c r="E1242">
-        <v>1.571413437412879</v>
+        <v>1.573463599286883</v>
       </c>
       <c r="F1242">
         <v>1</v>
       </c>
       <c r="G1242">
-        <v>0.004247612055880804</v>
+        <v>0.004230648301462867</v>
       </c>
       <c r="H1242">
-        <v>0.00430858656258712</v>
+        <v>0.004286536400713118</v>
       </c>
       <c r="I1242">
-        <v>0.01902549329368397</v>
+        <v>0.004111900749749653</v>
       </c>
       <c r="J1242">
-        <v>0.5243626676579006</v>
+        <v>0.5177619850050065</v>
       </c>
       <c r="K1242">
         <v>2.57</v>
@@ -63863,16 +63869,16 @@
         <v>2.9</v>
       </c>
       <c r="M1242">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="N1242">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="O1242">
         <v>1</v>
       </c>
       <c r="P1242" t="s">
-        <v>465</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1243" spans="1:16">
@@ -63880,31 +63886,31 @@
         <v>0</v>
       </c>
       <c r="B1243" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C1243">
-        <v>1.523625633709941</v>
+        <v>1.540926184059721</v>
       </c>
       <c r="D1243" t="s">
         <v>331</v>
       </c>
       <c r="E1243">
-        <v>1.554244450183629</v>
+        <v>1.5561698107363</v>
       </c>
       <c r="F1243">
         <v>1</v>
       </c>
       <c r="G1243">
-        <v>0.004316374366290059</v>
+        <v>0.004299073815940278</v>
       </c>
       <c r="H1243">
-        <v>0.004325755549816371</v>
+        <v>0.004303830189263699</v>
       </c>
       <c r="I1243">
-        <v>0.03061881647368869</v>
+        <v>0.01524362667657919</v>
       </c>
       <c r="J1243">
-        <v>0.5309408236844333</v>
+        <v>0.5243626676579006</v>
       </c>
       <c r="K1243">
         <v>2.63</v>
@@ -63913,16 +63919,16 @@
         <v>2.92</v>
       </c>
       <c r="M1243">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="N1243">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="O1243">
         <v>1</v>
       </c>
       <c r="P1243" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="1244" spans="1:16">
@@ -63933,28 +63939,28 @@
         <v>188</v>
       </c>
       <c r="C1244">
-        <v>1.535482083131007</v>
+        <v>1.552387944119195</v>
       </c>
       <c r="D1244" t="s">
         <v>331</v>
       </c>
       <c r="E1244">
-        <v>1.554244450183629</v>
+        <v>1.5561698107363</v>
       </c>
       <c r="F1244">
         <v>1</v>
       </c>
       <c r="G1244">
-        <v>0.004264517916868993</v>
+        <v>0.004247612055880804</v>
       </c>
       <c r="H1244">
-        <v>0.004325755549816371</v>
+        <v>0.004303830189263699</v>
       </c>
       <c r="I1244">
-        <v>0.01876236705262269</v>
+        <v>0.003781866617105001</v>
       </c>
       <c r="J1244">
-        <v>0.5309408236844333</v>
+        <v>0.5243626676579006</v>
       </c>
       <c r="K1244">
         <v>2.57</v>
@@ -63963,16 +63969,16 @@
         <v>2.9</v>
       </c>
       <c r="M1244">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="N1244">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="O1244">
         <v>1</v>
       </c>
       <c r="P1244" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="1245" spans="1:16">
@@ -63983,28 +63989,28 @@
         <v>188</v>
       </c>
       <c r="C1245">
-        <v>1.520319515886164</v>
+        <v>1.535482083131007</v>
       </c>
       <c r="D1245" t="s">
         <v>189</v>
       </c>
       <c r="E1245">
-        <v>1.538109076568332</v>
+        <v>1.554244450183629</v>
       </c>
       <c r="F1245">
         <v>1</v>
       </c>
       <c r="G1245">
-        <v>0.004279680484113835</v>
+        <v>0.004264517916868993</v>
       </c>
       <c r="H1245">
-        <v>0.004361890923431668</v>
+        <v>0.004325755549816371</v>
       </c>
       <c r="I1245">
-        <v>0.01778956068216764</v>
+        <v>0.01876236705262269</v>
       </c>
       <c r="J1245">
-        <v>0.5368406552972123</v>
+        <v>0.5309408236844333</v>
       </c>
       <c r="K1245">
         <v>2.57</v>
@@ -64013,16 +64019,16 @@
         <v>2.9</v>
       </c>
       <c r="M1245">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="N1245">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="O1245">
         <v>1</v>
       </c>
       <c r="P1245" t="s">
-        <v>330</v>
+        <v>466</v>
       </c>
     </row>
     <row r="1246" spans="1:16">
@@ -64033,28 +64039,28 @@
         <v>188</v>
       </c>
       <c r="C1246">
-        <v>1.50458822952096</v>
+        <v>1.520319515886164</v>
       </c>
       <c r="D1246" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E1246">
-        <v>1.520017847304926</v>
+        <v>1.538109076568332</v>
       </c>
       <c r="F1246">
         <v>1</v>
       </c>
       <c r="G1246">
-        <v>0.00429541177047904</v>
+        <v>0.004279680484113835</v>
       </c>
       <c r="H1246">
-        <v>0.004299982152695074</v>
+        <v>0.004361890923431668</v>
       </c>
       <c r="I1246">
-        <v>0.01542961778396523</v>
+        <v>0.01778956068216764</v>
       </c>
       <c r="J1246">
-        <v>0.5429617783965135</v>
+        <v>0.5368406552972123</v>
       </c>
       <c r="K1246">
         <v>2.57</v>
@@ -64063,16 +64069,16 @@
         <v>2.9</v>
       </c>
       <c r="M1246">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="N1246">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="O1246">
         <v>1</v>
       </c>
       <c r="P1246" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="1247" spans="1:16">
@@ -64083,28 +64089,28 @@
         <v>188</v>
       </c>
       <c r="C1247">
-        <v>1.485291405699136</v>
+        <v>1.50458822952096</v>
       </c>
       <c r="D1247" t="s">
         <v>334</v>
       </c>
       <c r="E1247">
-        <v>1.500796108400696</v>
+        <v>1.520017847304926</v>
       </c>
       <c r="F1247">
         <v>1</v>
       </c>
       <c r="G1247">
-        <v>0.004314708594300864</v>
+        <v>0.00429541177047904</v>
       </c>
       <c r="H1247">
-        <v>0.004319203891599305</v>
+        <v>0.004299982152695074</v>
       </c>
       <c r="I1247">
-        <v>0.01550470270156001</v>
+        <v>0.01542961778396523</v>
       </c>
       <c r="J1247">
-        <v>0.5504702701559784</v>
+        <v>0.5429617783965135</v>
       </c>
       <c r="K1247">
         <v>2.57</v>
@@ -64122,7 +64128,7 @@
         <v>1</v>
       </c>
       <c r="P1247" t="s">
-        <v>333</v>
+        <v>467</v>
       </c>
     </row>
     <row r="1248" spans="1:16">
@@ -64130,49 +64136,199 @@
         <v>0</v>
       </c>
       <c r="B1248" t="s">
+        <v>188</v>
+      </c>
+      <c r="C1248">
+        <v>1.485291405699136</v>
+      </c>
+      <c r="D1248" t="s">
+        <v>334</v>
+      </c>
+      <c r="E1248">
+        <v>1.500796108400696</v>
+      </c>
+      <c r="F1248">
+        <v>1</v>
+      </c>
+      <c r="G1248">
+        <v>0.004314708594300864</v>
+      </c>
+      <c r="H1248">
+        <v>0.004319203891599305</v>
+      </c>
+      <c r="I1248">
+        <v>0.01550470270156001</v>
+      </c>
+      <c r="J1248">
+        <v>0.5504702701559784</v>
+      </c>
+      <c r="K1248">
+        <v>2.57</v>
+      </c>
+      <c r="L1248">
+        <v>2.9</v>
+      </c>
+      <c r="M1248">
+        <v>2.56</v>
+      </c>
+      <c r="N1248">
+        <v>2.91</v>
+      </c>
+      <c r="O1248">
+        <v>1</v>
+      </c>
+      <c r="P1248" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:16">
+      <c r="A1249" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1249" t="s">
+        <v>188</v>
+      </c>
+      <c r="C1249">
+        <v>1.46240311169745</v>
+      </c>
+      <c r="D1249" t="s">
+        <v>334</v>
+      </c>
+      <c r="E1249">
+        <v>1.477996873908744</v>
+      </c>
+      <c r="F1249">
+        <v>1</v>
+      </c>
+      <c r="G1249">
+        <v>0.00433759688830255</v>
+      </c>
+      <c r="H1249">
+        <v>0.004342003126091256</v>
+      </c>
+      <c r="I1249">
+        <v>0.01559376221129405</v>
+      </c>
+      <c r="J1249">
+        <v>0.5593762211293968</v>
+      </c>
+      <c r="K1249">
+        <v>2.57</v>
+      </c>
+      <c r="L1249">
+        <v>2.9</v>
+      </c>
+      <c r="M1249">
+        <v>2.56</v>
+      </c>
+      <c r="N1249">
+        <v>2.91</v>
+      </c>
+      <c r="O1249">
+        <v>1</v>
+      </c>
+      <c r="P1249" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:16">
+      <c r="A1250" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1250" t="s">
         <v>189</v>
       </c>
-      <c r="C1248">
-        <v>1.338592496196642</v>
-      </c>
-      <c r="D1248" t="s">
+      <c r="C1250">
+        <v>1.428791673251903</v>
+      </c>
+      <c r="D1250" t="s">
         <v>331</v>
       </c>
-      <c r="E1248">
-        <v>1.340846545655222</v>
-      </c>
-      <c r="F1248">
-        <v>1</v>
-      </c>
-      <c r="G1248">
-        <v>0.004561407503803359</v>
-      </c>
-      <c r="H1248">
-        <v>0.004539153454344778</v>
-      </c>
-      <c r="I1248">
-        <v>0.002254049458580543</v>
-      </c>
-      <c r="J1248">
-        <v>0.6127024729290337</v>
-      </c>
-      <c r="K1248">
-        <v>2.63</v>
-      </c>
-      <c r="L1248">
-        <v>2.95</v>
-      </c>
-      <c r="M1248">
+      <c r="E1250">
+        <v>1.413001603034477</v>
+      </c>
+      <c r="F1250">
+        <v>-1</v>
+      </c>
+      <c r="G1250">
+        <v>0.004451208326748097</v>
+      </c>
+      <c r="H1250">
+        <v>0.004446998396965524</v>
+      </c>
+      <c r="I1250">
+        <v>0.01579007021742562</v>
+      </c>
+      <c r="J1250">
+        <v>0.579007021742566</v>
+      </c>
+      <c r="K1250">
         <v>2.61</v>
       </c>
-      <c r="N1248">
+      <c r="L1250">
         <v>2.94</v>
       </c>
-      <c r="O1248">
-        <v>1</v>
-      </c>
-      <c r="P1248" t="s">
-        <v>467</v>
+      <c r="M1250">
+        <v>2.62</v>
+      </c>
+      <c r="N1250">
+        <v>2.93</v>
+      </c>
+      <c r="O1250">
+        <v>1</v>
+      </c>
+      <c r="P1250" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:16">
+      <c r="A1251" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1251" t="s">
+        <v>189</v>
+      </c>
+      <c r="C1251">
+        <v>1.410645585279646</v>
+      </c>
+      <c r="D1251" t="s">
+        <v>331</v>
+      </c>
+      <c r="E1251">
+        <v>1.394785989820947</v>
+      </c>
+      <c r="F1251">
+        <v>-1</v>
+      </c>
+      <c r="G1251">
+        <v>0.004469354414720354</v>
+      </c>
+      <c r="H1251">
+        <v>0.004465214010179054</v>
+      </c>
+      <c r="I1251">
+        <v>0.01585959545869864</v>
+      </c>
+      <c r="J1251">
+        <v>0.5859595458698675</v>
+      </c>
+      <c r="K1251">
+        <v>2.61</v>
+      </c>
+      <c r="L1251">
+        <v>2.94</v>
+      </c>
+      <c r="M1251">
+        <v>2.62</v>
+      </c>
+      <c r="N1251">
+        <v>2.93</v>
+      </c>
+      <c r="O1251">
+        <v>1</v>
+      </c>
+      <c r="P1251" t="s">
+        <v>469</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01288-601288.xlsx
+++ b/s60_signal/position-01288-601288.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3885" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3879" uniqueCount="475">
   <si>
     <t>trade_time</t>
   </si>
@@ -571,10 +571,10 @@
     <t>2021-07-20</t>
   </si>
   <si>
-    <t>2021-07-19</t>
+    <t>2021-08-09</t>
   </si>
   <si>
-    <t>2021-08-09</t>
+    <t>2021-07-19</t>
   </si>
   <si>
     <t>2021-08-20</t>
@@ -1012,7 +1012,7 @@
     <t>2021-08-18</t>
   </si>
   <si>
-    <t>2021-08-24</t>
+    <t>2021-08-25</t>
   </si>
   <si>
     <t>2021-08-11</t>
@@ -1796,7 +1796,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1291"/>
+  <dimension ref="A1:P1289"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -62407,10 +62407,10 @@
         <v>2.109031399307522</v>
       </c>
       <c r="D1213" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E1213">
-        <v>2.072445072107109</v>
+        <v>2.059031399307522</v>
       </c>
       <c r="F1213">
         <v>-1</v>
@@ -62419,10 +62419,10 @@
         <v>0.003890968600692479</v>
       </c>
       <c r="H1213">
-        <v>0.003847554927892891</v>
+        <v>0.003840968600692479</v>
       </c>
       <c r="I1213">
-        <v>0.03658632720041233</v>
+        <v>0.04999999999999982</v>
       </c>
       <c r="J1213">
         <v>0.3413672799588041</v>
@@ -62434,10 +62434,10 @@
         <v>3</v>
       </c>
       <c r="M1213">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="N1213">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="O1213">
         <v>1</v>
@@ -63151,10 +63151,10 @@
         <v>2</v>
       </c>
       <c r="B1228" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C1228">
-        <v>1.914571722498627</v>
+        <v>1.916198763844063</v>
       </c>
       <c r="D1228" t="s">
         <v>187</v>
@@ -63166,22 +63166,22 @@
         <v>1</v>
       </c>
       <c r="G1228">
-        <v>0.003945428277501373</v>
+        <v>0.003923801236155938</v>
       </c>
       <c r="H1228">
         <v>0.003963801236155938</v>
       </c>
       <c r="I1228">
-        <v>0.04162704134543538</v>
+        <v>0.04000000000000004</v>
       </c>
       <c r="J1228">
         <v>0.3875680448478523</v>
       </c>
       <c r="K1228">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="L1228">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="M1228">
         <v>2.59</v>
@@ -63198,96 +63198,96 @@
     </row>
     <row r="1229" spans="1:16">
       <c r="A1229" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1229" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C1229">
-        <v>1.935690447928652</v>
+        <v>1.914571722498627</v>
       </c>
       <c r="D1229" t="s">
-        <v>330</v>
+        <v>187</v>
       </c>
       <c r="E1229">
-        <v>1.901755497771239</v>
+        <v>1.956198763844063</v>
       </c>
       <c r="F1229">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1229">
-        <v>0.004064309552071348</v>
+        <v>0.003945428277501373</v>
       </c>
       <c r="H1229">
-        <v>0.003998244502228762</v>
+        <v>0.003963801236155938</v>
       </c>
       <c r="I1229">
-        <v>0.03393495015741332</v>
+        <v>0.04162704134543538</v>
       </c>
       <c r="J1229">
-        <v>0.4016262460646597</v>
+        <v>0.3875680448478523</v>
       </c>
       <c r="K1229">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="L1229">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="M1229">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="N1229">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="O1229">
         <v>1</v>
       </c>
       <c r="P1229" t="s">
-        <v>327</v>
+        <v>461</v>
       </c>
     </row>
     <row r="1230" spans="1:16">
       <c r="A1230" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1230" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C1230">
-        <v>1.863722972849945</v>
+        <v>1.935690447928652</v>
       </c>
       <c r="D1230" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E1230">
-        <v>1.907739235310592</v>
+        <v>1.901755497771239</v>
       </c>
       <c r="F1230">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1230">
-        <v>0.003976277027150055</v>
+        <v>0.004064309552071348</v>
       </c>
       <c r="H1230">
-        <v>0.004012260764689408</v>
+        <v>0.003998244502228762</v>
       </c>
       <c r="I1230">
-        <v>0.0440162624606466</v>
+        <v>0.03393495015741332</v>
       </c>
       <c r="J1230">
         <v>0.4016262460646597</v>
       </c>
       <c r="K1230">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="L1230">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="M1230">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="N1230">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="O1230">
         <v>1</v>
@@ -63298,13 +63298,13 @@
     </row>
     <row r="1231" spans="1:16">
       <c r="A1231" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1231" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C1231">
-        <v>1.879788022692531</v>
+        <v>1.863722972849945</v>
       </c>
       <c r="D1231" t="s">
         <v>331</v>
@@ -63316,19 +63316,19 @@
         <v>1</v>
       </c>
       <c r="G1231">
-        <v>0.003960211977307468</v>
+        <v>0.003976277027150055</v>
       </c>
       <c r="H1231">
         <v>0.004012260764689408</v>
       </c>
       <c r="I1231">
-        <v>0.02795121261806011</v>
+        <v>0.0440162624606466</v>
       </c>
       <c r="J1231">
         <v>0.4016262460646597</v>
       </c>
       <c r="K1231">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="L1231">
         <v>2.92</v>
@@ -63348,13 +63348,13 @@
     </row>
     <row r="1232" spans="1:16">
       <c r="A1232" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1232" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C1232">
-        <v>1.877739235310592</v>
+        <v>1.879788022692531</v>
       </c>
       <c r="D1232" t="s">
         <v>331</v>
@@ -63366,22 +63366,22 @@
         <v>1</v>
       </c>
       <c r="G1232">
-        <v>0.003982260764689409</v>
+        <v>0.003960211977307468</v>
       </c>
       <c r="H1232">
         <v>0.004012260764689408</v>
       </c>
       <c r="I1232">
-        <v>0.0299999999999998</v>
+        <v>0.02795121261806011</v>
       </c>
       <c r="J1232">
         <v>0.4016262460646597</v>
       </c>
       <c r="K1232">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="L1232">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="M1232">
         <v>2.62</v>
@@ -63398,96 +63398,96 @@
     </row>
     <row r="1233" spans="1:16">
       <c r="A1233" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1233" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C1233">
-        <v>1.88677507248715</v>
+        <v>1.877739235310592</v>
       </c>
       <c r="D1233" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E1233">
-        <v>1.85357846761942</v>
+        <v>1.907739235310592</v>
       </c>
       <c r="F1233">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1233">
-        <v>0.00411322492751285</v>
+        <v>0.003982260764689409</v>
       </c>
       <c r="H1233">
-        <v>0.004046421532380581</v>
+        <v>0.004012260764689408</v>
       </c>
       <c r="I1233">
-        <v>0.03319660486773035</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="J1233">
-        <v>0.4200848783067358</v>
+        <v>0.4016262460646597</v>
       </c>
       <c r="K1233">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="L1233">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="M1233">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="N1233">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="O1233">
         <v>1</v>
       </c>
       <c r="P1233" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="1234" spans="1:16">
       <c r="A1234" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1234" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C1234">
-        <v>1.815176770053285</v>
+        <v>1.88677507248715</v>
       </c>
       <c r="D1234" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E1234">
-        <v>1.859377618836352</v>
+        <v>1.85357846761942</v>
       </c>
       <c r="F1234">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1234">
-        <v>0.004024823229946716</v>
+        <v>0.00411322492751285</v>
       </c>
       <c r="H1234">
-        <v>0.004060622381163647</v>
+        <v>0.004046421532380581</v>
       </c>
       <c r="I1234">
-        <v>0.0442008487830674</v>
+        <v>0.03319660486773035</v>
       </c>
       <c r="J1234">
         <v>0.4200848783067358</v>
       </c>
       <c r="K1234">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="L1234">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="M1234">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="N1234">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="O1234">
         <v>1</v>
@@ -63498,13 +63498,13 @@
     </row>
     <row r="1235" spans="1:16">
       <c r="A1235" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1235" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C1235">
-        <v>1.831980165185554</v>
+        <v>1.815176770053285</v>
       </c>
       <c r="D1235" t="s">
         <v>331</v>
@@ -63516,19 +63516,19 @@
         <v>1</v>
       </c>
       <c r="G1235">
-        <v>0.004008019834814446</v>
+        <v>0.004024823229946716</v>
       </c>
       <c r="H1235">
         <v>0.004060622381163647</v>
       </c>
       <c r="I1235">
-        <v>0.02739745365079793</v>
+        <v>0.0442008487830674</v>
       </c>
       <c r="J1235">
         <v>0.4200848783067358</v>
       </c>
       <c r="K1235">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="L1235">
         <v>2.92</v>
@@ -63548,13 +63548,13 @@
     </row>
     <row r="1236" spans="1:16">
       <c r="A1236" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1236" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C1236">
-        <v>1.829377618836352</v>
+        <v>1.831980165185554</v>
       </c>
       <c r="D1236" t="s">
         <v>331</v>
@@ -63566,22 +63566,22 @@
         <v>1</v>
       </c>
       <c r="G1236">
-        <v>0.004030622381163648</v>
+        <v>0.004008019834814446</v>
       </c>
       <c r="H1236">
         <v>0.004060622381163647</v>
       </c>
       <c r="I1236">
-        <v>0.0299999999999998</v>
+        <v>0.02739745365079793</v>
       </c>
       <c r="J1236">
         <v>0.4200848783067358</v>
       </c>
       <c r="K1236">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="L1236">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="M1236">
         <v>2.62</v>
@@ -63598,96 +63598,96 @@
     </row>
     <row r="1237" spans="1:16">
       <c r="A1237" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1237" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C1237">
-        <v>1.837587821290496</v>
+        <v>1.829377618836352</v>
       </c>
       <c r="D1237" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E1237">
-        <v>1.805133665497433</v>
+        <v>1.859377618836352</v>
       </c>
       <c r="F1237">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1237">
-        <v>0.004162412178709504</v>
+        <v>0.004030622381163648</v>
       </c>
       <c r="H1237">
-        <v>0.004094866334502568</v>
+        <v>0.004060622381163647</v>
       </c>
       <c r="I1237">
-        <v>0.03245415579306377</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="J1237">
-        <v>0.4386461051733976</v>
+        <v>0.4200848783067358</v>
       </c>
       <c r="K1237">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="L1237">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="M1237">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="N1237">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="O1237">
         <v>1</v>
       </c>
       <c r="P1237" t="s">
-        <v>462</v>
+        <v>328</v>
       </c>
     </row>
     <row r="1238" spans="1:16">
       <c r="A1238" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1238" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C1238">
-        <v>1.766360743393964</v>
+        <v>1.837587821290496</v>
       </c>
       <c r="D1238" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E1238">
-        <v>1.810747204445698</v>
+        <v>1.805133665497433</v>
       </c>
       <c r="F1238">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1238">
-        <v>0.004073639256606036</v>
+        <v>0.004162412178709504</v>
       </c>
       <c r="H1238">
-        <v>0.004109252795554301</v>
+        <v>0.004094866334502568</v>
       </c>
       <c r="I1238">
-        <v>0.04438646105173394</v>
+        <v>0.03245415579306377</v>
       </c>
       <c r="J1238">
         <v>0.4386461051733976</v>
       </c>
       <c r="K1238">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="L1238">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="M1238">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="N1238">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="O1238">
         <v>1</v>
@@ -63698,13 +63698,13 @@
     </row>
     <row r="1239" spans="1:16">
       <c r="A1239" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1239" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C1239">
-        <v>1.7839065876009</v>
+        <v>1.766360743393964</v>
       </c>
       <c r="D1239" t="s">
         <v>331</v>
@@ -63716,19 +63716,19 @@
         <v>1</v>
       </c>
       <c r="G1239">
-        <v>0.004056093412399099</v>
+        <v>0.004073639256606036</v>
       </c>
       <c r="H1239">
         <v>0.004109252795554301</v>
       </c>
       <c r="I1239">
-        <v>0.0268406168447981</v>
+        <v>0.04438646105173394</v>
       </c>
       <c r="J1239">
         <v>0.4386461051733976</v>
       </c>
       <c r="K1239">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="L1239">
         <v>2.92</v>
@@ -63748,13 +63748,13 @@
     </row>
     <row r="1240" spans="1:16">
       <c r="A1240" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1240" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C1240">
-        <v>1.780747204445698</v>
+        <v>1.7839065876009</v>
       </c>
       <c r="D1240" t="s">
         <v>331</v>
@@ -63766,22 +63766,22 @@
         <v>1</v>
       </c>
       <c r="G1240">
-        <v>0.004079252795554302</v>
+        <v>0.004056093412399099</v>
       </c>
       <c r="H1240">
         <v>0.004109252795554301</v>
       </c>
       <c r="I1240">
-        <v>0.0299999999999998</v>
+        <v>0.0268406168447981</v>
       </c>
       <c r="J1240">
         <v>0.4386461051733976</v>
       </c>
       <c r="K1240">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="L1240">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="M1240">
         <v>2.62</v>
@@ -63798,96 +63798,96 @@
     </row>
     <row r="1241" spans="1:16">
       <c r="A1241" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1241" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C1241">
-        <v>1.780823177477708</v>
+        <v>1.780747204445698</v>
       </c>
       <c r="D1241" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E1241">
-        <v>1.749225846496913</v>
+        <v>1.810747204445698</v>
       </c>
       <c r="F1241">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1241">
-        <v>0.004219176822522292</v>
+        <v>0.004079252795554302</v>
       </c>
       <c r="H1241">
-        <v>0.004150774153503088</v>
+        <v>0.004109252795554301</v>
       </c>
       <c r="I1241">
-        <v>0.03159733098079531</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="J1241">
-        <v>0.4600667254801102</v>
+        <v>0.4386461051733976</v>
       </c>
       <c r="K1241">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="L1241">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="M1241">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="N1241">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="O1241">
         <v>1</v>
       </c>
       <c r="P1241" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="1242" spans="1:16">
       <c r="A1242" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1242" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C1242">
-        <v>1.71002451198731</v>
+        <v>1.780823177477708</v>
       </c>
       <c r="D1242" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E1242">
-        <v>1.754625179242111</v>
+        <v>1.749225846496913</v>
       </c>
       <c r="F1242">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1242">
-        <v>0.004129975488012689</v>
+        <v>0.004219176822522292</v>
       </c>
       <c r="H1242">
-        <v>0.004165374820757889</v>
+        <v>0.004150774153503088</v>
       </c>
       <c r="I1242">
-        <v>0.04460066725480094</v>
+        <v>0.03159733098079531</v>
       </c>
       <c r="J1242">
         <v>0.4600667254801102</v>
       </c>
       <c r="K1242">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="L1242">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="M1242">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="N1242">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="O1242">
         <v>1</v>
@@ -63898,13 +63898,13 @@
     </row>
     <row r="1243" spans="1:16">
       <c r="A1243" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1243" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C1243">
-        <v>1.724625179242111</v>
+        <v>1.71002451198731</v>
       </c>
       <c r="D1243" t="s">
         <v>331</v>
@@ -63916,22 +63916,22 @@
         <v>1</v>
       </c>
       <c r="G1243">
-        <v>0.004135374820757889</v>
+        <v>0.004129975488012689</v>
       </c>
       <c r="H1243">
         <v>0.004165374820757889</v>
       </c>
       <c r="I1243">
-        <v>0.0299999999999998</v>
+        <v>0.04460066725480094</v>
       </c>
       <c r="J1243">
         <v>0.4600667254801102</v>
       </c>
       <c r="K1243">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="L1243">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="M1243">
         <v>2.62</v>
@@ -63948,96 +63948,96 @@
     </row>
     <row r="1244" spans="1:16">
       <c r="A1244" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1244" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C1244">
-        <v>1.738072100680357</v>
+        <v>1.724625179242111</v>
       </c>
       <c r="D1244" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E1244">
-        <v>1.707120068971975</v>
+        <v>1.754625179242111</v>
       </c>
       <c r="F1244">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1244">
-        <v>0.004261927899319643</v>
+        <v>0.004135374820757889</v>
       </c>
       <c r="H1244">
-        <v>0.004192879931028026</v>
+        <v>0.004165374820757889</v>
       </c>
       <c r="I1244">
-        <v>0.03095203170838245</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="J1244">
-        <v>0.4761992072904313</v>
+        <v>0.4600667254801102</v>
       </c>
       <c r="K1244">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="L1244">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="M1244">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="N1244">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="O1244">
         <v>1</v>
       </c>
       <c r="P1244" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="1245" spans="1:16">
       <c r="A1245" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1245" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C1245">
-        <v>1.667596084826166</v>
+        <v>1.738072100680357</v>
       </c>
       <c r="D1245" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E1245">
-        <v>1.71235807689907</v>
+        <v>1.707120068971975</v>
       </c>
       <c r="F1245">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1245">
-        <v>0.004172403915173835</v>
+        <v>0.004261927899319643</v>
       </c>
       <c r="H1245">
-        <v>0.00420764192310093</v>
+        <v>0.004192879931028026</v>
       </c>
       <c r="I1245">
-        <v>0.0447619920729041</v>
+        <v>0.03095203170838245</v>
       </c>
       <c r="J1245">
         <v>0.4761992072904313</v>
       </c>
       <c r="K1245">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="L1245">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="M1245">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="N1245">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="O1245">
         <v>1</v>
@@ -64048,13 +64048,13 @@
     </row>
     <row r="1246" spans="1:16">
       <c r="A1246" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1246" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C1246">
-        <v>1.68235807689907</v>
+        <v>1.667596084826166</v>
       </c>
       <c r="D1246" t="s">
         <v>331</v>
@@ -64066,22 +64066,22 @@
         <v>1</v>
       </c>
       <c r="G1246">
-        <v>0.00417764192310093</v>
+        <v>0.004172403915173835</v>
       </c>
       <c r="H1246">
         <v>0.00420764192310093</v>
       </c>
       <c r="I1246">
-        <v>0.0299999999999998</v>
+        <v>0.0447619920729041</v>
       </c>
       <c r="J1246">
         <v>0.4761992072904313</v>
       </c>
       <c r="K1246">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="L1246">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="M1246">
         <v>2.62</v>
@@ -64098,40 +64098,40 @@
     </row>
     <row r="1247" spans="1:16">
       <c r="A1247" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1247" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C1247">
-        <v>1.631109064123743</v>
+        <v>1.68235807689907</v>
       </c>
       <c r="D1247" t="s">
         <v>331</v>
       </c>
       <c r="E1247">
-        <v>1.676009790115668</v>
+        <v>1.71235807689907</v>
       </c>
       <c r="F1247">
         <v>1</v>
       </c>
       <c r="G1247">
-        <v>0.004208890935876257</v>
+        <v>0.00417764192310093</v>
       </c>
       <c r="H1247">
-        <v>0.004243990209884333</v>
+        <v>0.00420764192310093</v>
       </c>
       <c r="I1247">
-        <v>0.04490072599192496</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="J1247">
-        <v>0.4900725991924931</v>
+        <v>0.4761992072904313</v>
       </c>
       <c r="K1247">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="L1247">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="M1247">
         <v>2.62</v>
@@ -64143,18 +64143,18 @@
         <v>1</v>
       </c>
       <c r="P1247" t="s">
-        <v>185</v>
+        <v>464</v>
       </c>
     </row>
     <row r="1248" spans="1:16">
       <c r="A1248" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1248" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C1248">
-        <v>1.646009790115668</v>
+        <v>1.631109064123743</v>
       </c>
       <c r="D1248" t="s">
         <v>331</v>
@@ -64166,22 +64166,22 @@
         <v>1</v>
       </c>
       <c r="G1248">
-        <v>0.004213990209884332</v>
+        <v>0.004208890935876257</v>
       </c>
       <c r="H1248">
         <v>0.004243990209884333</v>
       </c>
       <c r="I1248">
-        <v>0.0299999999999998</v>
+        <v>0.04490072599192496</v>
       </c>
       <c r="J1248">
         <v>0.4900725991924931</v>
       </c>
       <c r="K1248">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="L1248">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="M1248">
         <v>2.62</v>
@@ -64193,45 +64193,45 @@
         <v>1</v>
       </c>
       <c r="P1248" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="1249" spans="1:16">
       <c r="A1249" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1249" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C1249">
-        <v>1.596583044051827</v>
+        <v>1.646009790115668</v>
       </c>
       <c r="D1249" t="s">
         <v>331</v>
       </c>
       <c r="E1249">
-        <v>1.641615047686611</v>
+        <v>1.676009790115668</v>
       </c>
       <c r="F1249">
         <v>1</v>
       </c>
       <c r="G1249">
-        <v>0.004243416955948173</v>
+        <v>0.004213990209884332</v>
       </c>
       <c r="H1249">
-        <v>0.004278384952313389</v>
+        <v>0.004243990209884333</v>
       </c>
       <c r="I1249">
-        <v>0.04503200363478399</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="J1249">
-        <v>0.5032003634783927</v>
+        <v>0.4900725991924931</v>
       </c>
       <c r="K1249">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="L1249">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="M1249">
         <v>2.62</v>
@@ -64243,18 +64243,18 @@
         <v>1</v>
       </c>
       <c r="P1249" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="1250" spans="1:16">
       <c r="A1250" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1250" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C1250">
-        <v>1.611615047686611</v>
+        <v>1.596583044051827</v>
       </c>
       <c r="D1250" t="s">
         <v>331</v>
@@ -64266,22 +64266,22 @@
         <v>1</v>
       </c>
       <c r="G1250">
-        <v>0.004248384952313389</v>
+        <v>0.004243416955948173</v>
       </c>
       <c r="H1250">
         <v>0.004278384952313389</v>
       </c>
       <c r="I1250">
-        <v>0.0299999999999998</v>
+        <v>0.04503200363478399</v>
       </c>
       <c r="J1250">
         <v>0.5032003634783927</v>
       </c>
       <c r="K1250">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="L1250">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="M1250">
         <v>2.62</v>
@@ -64298,40 +64298,40 @@
     </row>
     <row r="1251" spans="1:16">
       <c r="A1251" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1251" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C1251">
-        <v>1.575343698422129</v>
+        <v>1.611615047686611</v>
       </c>
       <c r="D1251" t="s">
         <v>331</v>
       </c>
       <c r="E1251">
-        <v>1.620456460025087</v>
+        <v>1.641615047686611</v>
       </c>
       <c r="F1251">
         <v>1</v>
       </c>
       <c r="G1251">
-        <v>0.004264656301577871</v>
+        <v>0.004248384952313389</v>
       </c>
       <c r="H1251">
-        <v>0.004299543539974913</v>
+        <v>0.004278384952313389</v>
       </c>
       <c r="I1251">
-        <v>0.04511276160295763</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="J1251">
-        <v>0.5112761602957683</v>
+        <v>0.5032003634783927</v>
       </c>
       <c r="K1251">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="L1251">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="M1251">
         <v>2.62</v>
@@ -64343,18 +64343,18 @@
         <v>1</v>
       </c>
       <c r="P1251" t="s">
-        <v>465</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1252" spans="1:16">
       <c r="A1252" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1252" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C1252">
-        <v>1.590456460025087</v>
+        <v>1.575343698422129</v>
       </c>
       <c r="D1252" t="s">
         <v>331</v>
@@ -64366,22 +64366,22 @@
         <v>1</v>
       </c>
       <c r="G1252">
-        <v>0.004269543539974914</v>
+        <v>0.004264656301577871</v>
       </c>
       <c r="H1252">
         <v>0.004299543539974913</v>
       </c>
       <c r="I1252">
-        <v>0.0299999999999998</v>
+        <v>0.04511276160295763</v>
       </c>
       <c r="J1252">
         <v>0.5112761602957683</v>
       </c>
       <c r="K1252">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="L1252">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="M1252">
         <v>2.62</v>
@@ -64398,40 +64398,40 @@
     </row>
     <row r="1253" spans="1:16">
       <c r="A1253" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1253" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C1253">
-        <v>1.558285979436833</v>
+        <v>1.590456460025087</v>
       </c>
       <c r="D1253" t="s">
         <v>331</v>
       </c>
       <c r="E1253">
-        <v>1.603463599286883</v>
+        <v>1.620456460025087</v>
       </c>
       <c r="F1253">
         <v>1</v>
       </c>
       <c r="G1253">
-        <v>0.004281714020563167</v>
+        <v>0.004269543539974914</v>
       </c>
       <c r="H1253">
-        <v>0.004316536400713117</v>
+        <v>0.004299543539974913</v>
       </c>
       <c r="I1253">
-        <v>0.04517761985004998</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="J1253">
-        <v>0.5177619850050065</v>
+        <v>0.5112761602957683</v>
       </c>
       <c r="K1253">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="L1253">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="M1253">
         <v>2.62</v>
@@ -64443,18 +64443,18 @@
         <v>1</v>
       </c>
       <c r="P1253" t="s">
-        <v>181</v>
+        <v>465</v>
       </c>
     </row>
     <row r="1254" spans="1:16">
       <c r="A1254" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1254" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C1254">
-        <v>1.573463599286883</v>
+        <v>1.558285979436833</v>
       </c>
       <c r="D1254" t="s">
         <v>331</v>
@@ -64466,22 +64466,22 @@
         <v>1</v>
       </c>
       <c r="G1254">
-        <v>0.004286536400713118</v>
+        <v>0.004281714020563167</v>
       </c>
       <c r="H1254">
         <v>0.004316536400713117</v>
       </c>
       <c r="I1254">
-        <v>0.0299999999999998</v>
+        <v>0.04517761985004998</v>
       </c>
       <c r="J1254">
         <v>0.5177619850050065</v>
       </c>
       <c r="K1254">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="L1254">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="M1254">
         <v>2.62</v>
@@ -64498,40 +64498,40 @@
     </row>
     <row r="1255" spans="1:16">
       <c r="A1255" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1255" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C1255">
-        <v>1.540926184059721</v>
+        <v>1.573463599286883</v>
       </c>
       <c r="D1255" t="s">
         <v>331</v>
       </c>
       <c r="E1255">
-        <v>1.5861698107363</v>
+        <v>1.603463599286883</v>
       </c>
       <c r="F1255">
         <v>1</v>
       </c>
       <c r="G1255">
-        <v>0.004299073815940278</v>
+        <v>0.004286536400713118</v>
       </c>
       <c r="H1255">
-        <v>0.0043338301892637</v>
+        <v>0.004316536400713117</v>
       </c>
       <c r="I1255">
-        <v>0.045243626676579</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="J1255">
-        <v>0.5243626676579006</v>
+        <v>0.5177619850050065</v>
       </c>
       <c r="K1255">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="L1255">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="M1255">
         <v>2.62</v>
@@ -64543,18 +64543,18 @@
         <v>1</v>
       </c>
       <c r="P1255" t="s">
-        <v>466</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1256" spans="1:16">
       <c r="A1256" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1256" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C1256">
-        <v>1.5561698107363</v>
+        <v>1.540926184059721</v>
       </c>
       <c r="D1256" t="s">
         <v>331</v>
@@ -64566,22 +64566,22 @@
         <v>1</v>
       </c>
       <c r="G1256">
-        <v>0.004303830189263699</v>
+        <v>0.004299073815940278</v>
       </c>
       <c r="H1256">
         <v>0.0043338301892637</v>
       </c>
       <c r="I1256">
-        <v>0.0299999999999998</v>
+        <v>0.045243626676579</v>
       </c>
       <c r="J1256">
         <v>0.5243626676579006</v>
       </c>
       <c r="K1256">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="L1256">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="M1256">
         <v>2.62</v>
@@ -64598,46 +64598,46 @@
     </row>
     <row r="1257" spans="1:16">
       <c r="A1257" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1257" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C1257">
-        <v>1.601900690766037</v>
+        <v>1.5561698107363</v>
       </c>
       <c r="D1257" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E1257">
-        <v>1.576657064089458</v>
+        <v>1.5861698107363</v>
       </c>
       <c r="F1257">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1257">
-        <v>0.004318099309233963</v>
+        <v>0.004303830189263699</v>
       </c>
       <c r="H1257">
-        <v>0.004303342935910542</v>
+        <v>0.0043338301892637</v>
       </c>
       <c r="I1257">
-        <v>0.0252436266765792</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="J1257">
         <v>0.5243626676579006</v>
       </c>
       <c r="K1257">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="L1257">
+        <v>2.93</v>
+      </c>
+      <c r="M1257">
+        <v>2.62</v>
+      </c>
+      <c r="N1257">
         <v>2.96</v>
-      </c>
-      <c r="M1257">
-        <v>2.6</v>
-      </c>
-      <c r="N1257">
-        <v>2.94</v>
       </c>
       <c r="O1257">
         <v>1</v>
@@ -64648,63 +64648,63 @@
     </row>
     <row r="1258" spans="1:16">
       <c r="A1258" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1258" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C1258">
-        <v>1.523625633709941</v>
+        <v>1.601900690766037</v>
       </c>
       <c r="D1258" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E1258">
-        <v>1.568935041946785</v>
+        <v>1.566657064089458</v>
       </c>
       <c r="F1258">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1258">
-        <v>0.004316374366290059</v>
+        <v>0.004318099309233963</v>
       </c>
       <c r="H1258">
-        <v>0.004351064958053216</v>
+        <v>0.004293342935910542</v>
       </c>
       <c r="I1258">
-        <v>0.04530940823684415</v>
+        <v>0.03524362667657899</v>
       </c>
       <c r="J1258">
-        <v>0.5309408236844333</v>
+        <v>0.5243626676579006</v>
       </c>
       <c r="K1258">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="L1258">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="M1258">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="N1258">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="O1258">
         <v>1</v>
       </c>
       <c r="P1258" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="1259" spans="1:16">
       <c r="A1259" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1259" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C1259">
-        <v>1.538935041946785</v>
+        <v>1.523625633709941</v>
       </c>
       <c r="D1259" t="s">
         <v>331</v>
@@ -64716,22 +64716,22 @@
         <v>1</v>
       </c>
       <c r="G1259">
-        <v>0.004321064958053215</v>
+        <v>0.004316374366290059</v>
       </c>
       <c r="H1259">
         <v>0.004351064958053216</v>
       </c>
       <c r="I1259">
-        <v>0.0299999999999998</v>
+        <v>0.04530940823684415</v>
       </c>
       <c r="J1259">
         <v>0.5309408236844333</v>
       </c>
       <c r="K1259">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="L1259">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="M1259">
         <v>2.62</v>
@@ -64748,46 +64748,46 @@
     </row>
     <row r="1260" spans="1:16">
       <c r="A1260" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1260" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C1260">
-        <v>1.584863266657318</v>
+        <v>1.538935041946785</v>
       </c>
       <c r="D1260" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E1260">
-        <v>1.559553858420473</v>
+        <v>1.568935041946785</v>
       </c>
       <c r="F1260">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1260">
-        <v>0.004335136733342682</v>
+        <v>0.004321064958053215</v>
       </c>
       <c r="H1260">
-        <v>0.004320446141579526</v>
+        <v>0.004351064958053216</v>
       </c>
       <c r="I1260">
-        <v>0.02530940823684458</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="J1260">
         <v>0.5309408236844333</v>
       </c>
       <c r="K1260">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="L1260">
+        <v>2.93</v>
+      </c>
+      <c r="M1260">
+        <v>2.62</v>
+      </c>
+      <c r="N1260">
         <v>2.96</v>
-      </c>
-      <c r="M1260">
-        <v>2.6</v>
-      </c>
-      <c r="N1260">
-        <v>2.94</v>
       </c>
       <c r="O1260">
         <v>1</v>
@@ -64798,63 +64798,63 @@
     </row>
     <row r="1261" spans="1:16">
       <c r="A1261" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1261" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C1261">
-        <v>1.508109076568332</v>
+        <v>1.584863266657318</v>
       </c>
       <c r="D1261" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E1261">
-        <v>1.553477483121304</v>
+        <v>1.549553858420474</v>
       </c>
       <c r="F1261">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1261">
-        <v>0.004331890923431669</v>
+        <v>0.004335136733342682</v>
       </c>
       <c r="H1261">
-        <v>0.004366522516878696</v>
+        <v>0.004310446141579527</v>
       </c>
       <c r="I1261">
-        <v>0.04536840655297203</v>
+        <v>0.03530940823684436</v>
       </c>
       <c r="J1261">
-        <v>0.5368406552972123</v>
+        <v>0.5309408236844333</v>
       </c>
       <c r="K1261">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="L1261">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="M1261">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="N1261">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="O1261">
         <v>1</v>
       </c>
       <c r="P1261" t="s">
-        <v>329</v>
+        <v>467</v>
       </c>
     </row>
     <row r="1262" spans="1:16">
       <c r="A1262" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1262" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C1262">
-        <v>1.523477483121304</v>
+        <v>1.508109076568332</v>
       </c>
       <c r="D1262" t="s">
         <v>331</v>
@@ -64866,22 +64866,22 @@
         <v>1</v>
       </c>
       <c r="G1262">
-        <v>0.004336522516878697</v>
+        <v>0.004331890923431669</v>
       </c>
       <c r="H1262">
         <v>0.004366522516878696</v>
       </c>
       <c r="I1262">
-        <v>0.0299999999999998</v>
+        <v>0.04536840655297203</v>
       </c>
       <c r="J1262">
         <v>0.5368406552972123</v>
       </c>
       <c r="K1262">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="L1262">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="M1262">
         <v>2.62</v>
@@ -64898,46 +64898,46 @@
     </row>
     <row r="1263" spans="1:16">
       <c r="A1263" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1263" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C1263">
-        <v>1.56958270278022</v>
+        <v>1.523477483121304</v>
       </c>
       <c r="D1263" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E1263">
-        <v>1.544214296227248</v>
+        <v>1.553477483121304</v>
       </c>
       <c r="F1263">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1263">
-        <v>0.00435041729721978</v>
+        <v>0.004336522516878697</v>
       </c>
       <c r="H1263">
-        <v>0.004335785703772752</v>
+        <v>0.004366522516878696</v>
       </c>
       <c r="I1263">
-        <v>0.02536840655297223</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="J1263">
         <v>0.5368406552972123</v>
       </c>
       <c r="K1263">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="L1263">
+        <v>2.93</v>
+      </c>
+      <c r="M1263">
+        <v>2.62</v>
+      </c>
+      <c r="N1263">
         <v>2.96</v>
-      </c>
-      <c r="M1263">
-        <v>2.6</v>
-      </c>
-      <c r="N1263">
-        <v>2.94</v>
       </c>
       <c r="O1263">
         <v>1</v>
@@ -64948,96 +64948,96 @@
     </row>
     <row r="1264" spans="1:16">
       <c r="A1264" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1264" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C1264">
-        <v>1.507440140601135</v>
+        <v>1.56958270278022</v>
       </c>
       <c r="D1264" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E1264">
-        <v>1.537440140601135</v>
+        <v>1.534214296227248</v>
       </c>
       <c r="F1264">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1264">
-        <v>0.004352559859398865</v>
+        <v>0.00435041729721978</v>
       </c>
       <c r="H1264">
-        <v>0.004382559859398866</v>
+        <v>0.004325785703772752</v>
       </c>
       <c r="I1264">
-        <v>0.0299999999999998</v>
+        <v>0.03536840655297202</v>
       </c>
       <c r="J1264">
-        <v>0.5429617783965135</v>
+        <v>0.5368406552972123</v>
       </c>
       <c r="K1264">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="L1264">
+        <v>2.96</v>
+      </c>
+      <c r="M1264">
+        <v>2.6</v>
+      </c>
+      <c r="N1264">
         <v>2.93</v>
       </c>
-      <c r="M1264">
-        <v>2.62</v>
-      </c>
-      <c r="N1264">
-        <v>2.96</v>
-      </c>
       <c r="O1264">
         <v>1</v>
       </c>
       <c r="P1264" t="s">
-        <v>468</v>
+        <v>329</v>
       </c>
     </row>
     <row r="1265" spans="1:16">
       <c r="A1265" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1265" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C1265">
-        <v>1.55372899395303</v>
+        <v>1.507440140601135</v>
       </c>
       <c r="D1265" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E1265">
-        <v>1.528299376169065</v>
+        <v>1.537440140601135</v>
       </c>
       <c r="F1265">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1265">
-        <v>0.004366271006046971</v>
+        <v>0.004352559859398865</v>
       </c>
       <c r="H1265">
-        <v>0.004351700623830935</v>
+        <v>0.004382559859398866</v>
       </c>
       <c r="I1265">
-        <v>0.02542961778396524</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="J1265">
         <v>0.5429617783965135</v>
       </c>
       <c r="K1265">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="L1265">
+        <v>2.93</v>
+      </c>
+      <c r="M1265">
+        <v>2.62</v>
+      </c>
+      <c r="N1265">
         <v>2.96</v>
-      </c>
-      <c r="M1265">
-        <v>2.6</v>
-      </c>
-      <c r="N1265">
-        <v>2.94</v>
       </c>
       <c r="O1265">
         <v>1</v>
@@ -65048,57 +65048,57 @@
     </row>
     <row r="1266" spans="1:16">
       <c r="A1266" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1266" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C1266">
-        <v>1.485291405699136</v>
+        <v>1.55372899395303</v>
       </c>
       <c r="D1266" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E1266">
-        <v>1.502263189489777</v>
+        <v>1.518299376169065</v>
       </c>
       <c r="F1266">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1266">
-        <v>0.004314708594300864</v>
+        <v>0.004366271006046971</v>
       </c>
       <c r="H1266">
-        <v>0.004397736810510223</v>
+        <v>0.004341700623830935</v>
       </c>
       <c r="I1266">
-        <v>0.01697178379064157</v>
+        <v>0.03542961778396503</v>
       </c>
       <c r="J1266">
-        <v>0.5504702701559784</v>
+        <v>0.5429617783965135</v>
       </c>
       <c r="K1266">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="L1266">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="M1266">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="N1266">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="O1266">
         <v>1</v>
       </c>
       <c r="P1266" t="s">
-        <v>330</v>
+        <v>468</v>
       </c>
     </row>
     <row r="1267" spans="1:16">
       <c r="A1267" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1267" t="s">
         <v>183</v>
@@ -65148,7 +65148,7 @@
     </row>
     <row r="1268" spans="1:16">
       <c r="A1268" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1268" t="s">
         <v>187</v>
@@ -65160,7 +65160,7 @@
         <v>332</v>
       </c>
       <c r="E1268">
-        <v>1.508777297594456</v>
+        <v>1.498777297594456</v>
       </c>
       <c r="F1268">
         <v>-1</v>
@@ -65169,10 +65169,10 @@
         <v>0.004385717999703984</v>
       </c>
       <c r="H1268">
-        <v>0.004371222702405544</v>
+        <v>0.004361222702405544</v>
       </c>
       <c r="I1268">
-        <v>0.02550470270156002</v>
+        <v>0.03550470270155981</v>
       </c>
       <c r="J1268">
         <v>0.5504702701559784</v>
@@ -65187,7 +65187,7 @@
         <v>2.6</v>
       </c>
       <c r="N1268">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="O1268">
         <v>1</v>
@@ -65310,7 +65310,7 @@
         <v>332</v>
       </c>
       <c r="E1271">
-        <v>1.485621825063568</v>
+        <v>1.475621825063568</v>
       </c>
       <c r="F1271">
         <v>-1</v>
@@ -65319,10 +65319,10 @@
         <v>0.004408784412725138</v>
       </c>
       <c r="H1271">
-        <v>0.004394378174936432</v>
+        <v>0.004384378174936431</v>
       </c>
       <c r="I1271">
-        <v>0.02559376221129428</v>
+        <v>0.03559376221129407</v>
       </c>
       <c r="J1271">
         <v>0.5593762211293968</v>
@@ -65337,7 +65337,7 @@
         <v>2.6</v>
       </c>
       <c r="N1271">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="O1271">
         <v>1</v>
@@ -65460,7 +65460,7 @@
         <v>332</v>
       </c>
       <c r="E1274">
-        <v>1.462949275647666</v>
+        <v>1.452949275647666</v>
       </c>
       <c r="F1274">
         <v>-1</v>
@@ -65469,10 +65469,10 @@
         <v>0.004431369760027902</v>
       </c>
       <c r="H1274">
-        <v>0.004417050724352335</v>
+        <v>0.004407050724352334</v>
       </c>
       <c r="I1274">
-        <v>0.02568096432443223</v>
+        <v>0.03568096432443202</v>
       </c>
       <c r="J1274">
         <v>0.5680964324432053</v>
@@ -65487,7 +65487,7 @@
         <v>2.6</v>
       </c>
       <c r="N1274">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="O1274">
         <v>1</v>
@@ -65560,7 +65560,7 @@
         <v>332</v>
       </c>
       <c r="E1276">
-        <v>1.434581743469328</v>
+        <v>1.424581743469328</v>
       </c>
       <c r="F1276">
         <v>-1</v>
@@ -65569,10 +65569,10 @@
         <v>0.004459628186313246</v>
       </c>
       <c r="H1276">
-        <v>0.004445418256530671</v>
+        <v>0.004435418256530672</v>
       </c>
       <c r="I1276">
-        <v>0.02579007021742585</v>
+        <v>0.03579007021742564</v>
       </c>
       <c r="J1276">
         <v>0.579007021742566</v>
@@ -65587,7 +65587,7 @@
         <v>2.6</v>
       </c>
       <c r="N1276">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="O1276">
         <v>1</v>
@@ -65648,52 +65648,52 @@
     </row>
     <row r="1278" spans="1:16">
       <c r="A1278" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1278" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C1278">
-        <v>1.442364776197043</v>
+        <v>1.375586295079521</v>
       </c>
       <c r="D1278" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E1278">
-        <v>1.416505180738344</v>
+        <v>1.405586295079521</v>
       </c>
       <c r="F1278">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1278">
-        <v>0.004477635223802957</v>
+        <v>0.004484413704920479</v>
       </c>
       <c r="H1278">
-        <v>0.004463494819261656</v>
+        <v>0.004514413704920479</v>
       </c>
       <c r="I1278">
-        <v>0.02585959545869887</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="J1278">
-        <v>0.5859595458698675</v>
+        <v>0.5932876736337707</v>
       </c>
       <c r="K1278">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="L1278">
+        <v>2.93</v>
+      </c>
+      <c r="M1278">
+        <v>2.62</v>
+      </c>
+      <c r="N1278">
         <v>2.96</v>
       </c>
-      <c r="M1278">
-        <v>2.6</v>
-      </c>
-      <c r="N1278">
-        <v>2.94</v>
-      </c>
       <c r="O1278">
         <v>1</v>
       </c>
       <c r="P1278" t="s">
-        <v>471</v>
+        <v>188</v>
       </c>
     </row>
     <row r="1279" spans="1:16">
@@ -65704,28 +65704,28 @@
         <v>183</v>
       </c>
       <c r="C1279">
-        <v>1.375586295079521</v>
+        <v>1.354610467845981</v>
       </c>
       <c r="D1279" t="s">
         <v>331</v>
       </c>
       <c r="E1279">
-        <v>1.405586295079521</v>
+        <v>1.384610467845981</v>
       </c>
       <c r="F1279">
         <v>1</v>
       </c>
       <c r="G1279">
-        <v>0.004484413704920479</v>
+        <v>0.00450538953215402</v>
       </c>
       <c r="H1279">
-        <v>0.004514413704920479</v>
+        <v>0.004535389532154019</v>
       </c>
       <c r="I1279">
         <v>0.0299999999999998</v>
       </c>
       <c r="J1279">
-        <v>0.5932876736337707</v>
+        <v>0.6012937145626027</v>
       </c>
       <c r="K1279">
         <v>2.62</v>
@@ -65743,606 +65743,506 @@
         <v>1</v>
       </c>
       <c r="P1279" t="s">
-        <v>188</v>
+        <v>334</v>
       </c>
     </row>
     <row r="1280" spans="1:16">
       <c r="A1280" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1280" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C1280">
-        <v>1.423384925288534</v>
+        <v>1.339075752139688</v>
       </c>
       <c r="D1280" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E1280">
-        <v>1.397452048552196</v>
+        <v>1.369075752139688</v>
       </c>
       <c r="F1280">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1280">
-        <v>0.004496615074711466</v>
+        <v>0.004520924247860313</v>
       </c>
       <c r="H1280">
-        <v>0.004482547951447803</v>
+        <v>0.004550924247860312</v>
       </c>
       <c r="I1280">
-        <v>0.02593287673633782</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="J1280">
-        <v>0.5932876736337707</v>
+        <v>0.6072229953665313</v>
       </c>
       <c r="K1280">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="L1280">
+        <v>2.93</v>
+      </c>
+      <c r="M1280">
+        <v>2.62</v>
+      </c>
+      <c r="N1280">
         <v>2.96</v>
       </c>
-      <c r="M1280">
-        <v>2.6</v>
-      </c>
-      <c r="N1280">
-        <v>2.94</v>
-      </c>
       <c r="O1280">
         <v>1</v>
       </c>
       <c r="P1280" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1281" spans="1:16">
       <c r="A1281" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1281" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C1281">
-        <v>1.354610467845981</v>
+        <v>1.387292442000684</v>
       </c>
       <c r="D1281" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E1281">
-        <v>1.384610467845981</v>
+        <v>1.351220212047019</v>
       </c>
       <c r="F1281">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1281">
-        <v>0.00450538953215402</v>
+        <v>0.004532707557999316</v>
       </c>
       <c r="H1281">
-        <v>0.004535389532154019</v>
+        <v>0.004508779787952982</v>
       </c>
       <c r="I1281">
-        <v>0.0299999999999998</v>
+        <v>0.0360722299536651</v>
       </c>
       <c r="J1281">
-        <v>0.6012937145626027</v>
+        <v>0.6072229953665313</v>
       </c>
       <c r="K1281">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="L1281">
+        <v>2.96</v>
+      </c>
+      <c r="M1281">
+        <v>2.6</v>
+      </c>
+      <c r="N1281">
         <v>2.93</v>
       </c>
-      <c r="M1281">
-        <v>2.62</v>
-      </c>
-      <c r="N1281">
-        <v>2.96</v>
-      </c>
       <c r="O1281">
         <v>1</v>
       </c>
       <c r="P1281" t="s">
-        <v>334</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1282" spans="1:16">
       <c r="A1282" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1282" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C1282">
-        <v>1.402649279282859</v>
+        <v>1.324719520925932</v>
       </c>
       <c r="D1282" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E1282">
-        <v>1.376636342137233</v>
+        <v>1.354719520925932</v>
       </c>
       <c r="F1282">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1282">
-        <v>0.00451735072071714</v>
+        <v>0.004535280479074069</v>
       </c>
       <c r="H1282">
-        <v>0.004503363657862768</v>
+        <v>0.004565280479074068</v>
       </c>
       <c r="I1282">
-        <v>0.02601293714562636</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="J1282">
-        <v>0.6012937145626027</v>
+        <v>0.6127024729290337</v>
       </c>
       <c r="K1282">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="L1282">
+        <v>2.93</v>
+      </c>
+      <c r="M1282">
+        <v>2.62</v>
+      </c>
+      <c r="N1282">
         <v>2.96</v>
       </c>
-      <c r="M1282">
-        <v>2.6</v>
-      </c>
-      <c r="N1282">
-        <v>2.94</v>
-      </c>
       <c r="O1282">
         <v>1</v>
       </c>
       <c r="P1282" t="s">
-        <v>334</v>
+        <v>472</v>
       </c>
     </row>
     <row r="1283" spans="1:16">
       <c r="A1283" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1283" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C1283">
-        <v>1.339075752139688</v>
+        <v>1.373100595113803</v>
       </c>
       <c r="D1283" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E1283">
-        <v>1.369075752139688</v>
+        <v>1.336973570384512</v>
       </c>
       <c r="F1283">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1283">
-        <v>0.004520924247860313</v>
+        <v>0.004546899404886198</v>
       </c>
       <c r="H1283">
-        <v>0.004550924247860312</v>
+        <v>0.004523026429615488</v>
       </c>
       <c r="I1283">
-        <v>0.0299999999999998</v>
+        <v>0.03612702472929041</v>
       </c>
       <c r="J1283">
-        <v>0.6072229953665313</v>
+        <v>0.6127024729290337</v>
       </c>
       <c r="K1283">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="L1283">
+        <v>2.96</v>
+      </c>
+      <c r="M1283">
+        <v>2.6</v>
+      </c>
+      <c r="N1283">
         <v>2.93</v>
       </c>
-      <c r="M1283">
-        <v>2.62</v>
-      </c>
-      <c r="N1283">
-        <v>2.96</v>
-      </c>
       <c r="O1283">
         <v>1</v>
       </c>
       <c r="P1283" t="s">
-        <v>186</v>
+        <v>472</v>
       </c>
     </row>
     <row r="1284" spans="1:16">
       <c r="A1284" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1284" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C1284">
-        <v>1.387292442000684</v>
+        <v>1.313106945179855</v>
       </c>
       <c r="D1284" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E1284">
-        <v>1.361220212047018</v>
+        <v>1.343106945179855</v>
       </c>
       <c r="F1284">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1284">
-        <v>0.004532707557999316</v>
+        <v>0.004546893054820146</v>
       </c>
       <c r="H1284">
-        <v>0.004518779787952981</v>
+        <v>0.004576893054820145</v>
       </c>
       <c r="I1284">
-        <v>0.02607222995366532</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="J1284">
-        <v>0.6072229953665313</v>
+        <v>0.6171347537481471</v>
       </c>
       <c r="K1284">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="L1284">
+        <v>2.93</v>
+      </c>
+      <c r="M1284">
+        <v>2.62</v>
+      </c>
+      <c r="N1284">
         <v>2.96</v>
       </c>
-      <c r="M1284">
-        <v>2.6</v>
-      </c>
-      <c r="N1284">
-        <v>2.94</v>
-      </c>
       <c r="O1284">
         <v>1</v>
       </c>
       <c r="P1284" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
     </row>
     <row r="1285" spans="1:16">
       <c r="A1285" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1285" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C1285">
-        <v>1.324719520925932</v>
+        <v>1.361620987792299</v>
       </c>
       <c r="D1285" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E1285">
-        <v>1.354719520925932</v>
+        <v>1.325449640254818</v>
       </c>
       <c r="F1285">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1285">
-        <v>0.004535280479074069</v>
+        <v>0.004558379012207701</v>
       </c>
       <c r="H1285">
-        <v>0.004565280479074068</v>
+        <v>0.004534550359745182</v>
       </c>
       <c r="I1285">
-        <v>0.0299999999999998</v>
+        <v>0.03617134753748141</v>
       </c>
       <c r="J1285">
-        <v>0.6127024729290337</v>
+        <v>0.6171347537481471</v>
       </c>
       <c r="K1285">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="L1285">
+        <v>2.96</v>
+      </c>
+      <c r="M1285">
+        <v>2.6</v>
+      </c>
+      <c r="N1285">
         <v>2.93</v>
       </c>
-      <c r="M1285">
-        <v>2.62</v>
-      </c>
-      <c r="N1285">
-        <v>2.96</v>
-      </c>
       <c r="O1285">
         <v>1</v>
       </c>
       <c r="P1285" t="s">
-        <v>472</v>
+        <v>333</v>
       </c>
     </row>
     <row r="1286" spans="1:16">
       <c r="A1286" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1286" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C1286">
-        <v>1.373100595113803</v>
+        <v>1.303704050944863</v>
       </c>
       <c r="D1286" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E1286">
-        <v>1.346973570384512</v>
+        <v>1.333704050944863</v>
       </c>
       <c r="F1286">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1286">
-        <v>0.004546899404886198</v>
+        <v>0.004556295949055138</v>
       </c>
       <c r="H1286">
-        <v>0.004533026429615488</v>
+        <v>0.004586295949055136</v>
       </c>
       <c r="I1286">
-        <v>0.02612702472929063</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="J1286">
-        <v>0.6127024729290337</v>
+        <v>0.6207236446775332</v>
       </c>
       <c r="K1286">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="L1286">
+        <v>2.93</v>
+      </c>
+      <c r="M1286">
+        <v>2.62</v>
+      </c>
+      <c r="N1286">
         <v>2.96</v>
       </c>
-      <c r="M1286">
-        <v>2.6</v>
-      </c>
-      <c r="N1286">
-        <v>2.94</v>
-      </c>
       <c r="O1286">
         <v>1</v>
       </c>
       <c r="P1286" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="1287" spans="1:16">
       <c r="A1287" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1287" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C1287">
-        <v>1.313106945179855</v>
+        <v>1.352325760285189</v>
       </c>
       <c r="D1287" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E1287">
-        <v>1.343106945179855</v>
+        <v>1.316118523838414</v>
       </c>
       <c r="F1287">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1287">
-        <v>0.004546893054820146</v>
+        <v>0.004567674239714811</v>
       </c>
       <c r="H1287">
-        <v>0.004576893054820145</v>
+        <v>0.004543881476161586</v>
       </c>
       <c r="I1287">
-        <v>0.0299999999999998</v>
+        <v>0.03620723644677537</v>
       </c>
       <c r="J1287">
-        <v>0.6171347537481471</v>
+        <v>0.6207236446775332</v>
       </c>
       <c r="K1287">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="L1287">
+        <v>2.96</v>
+      </c>
+      <c r="M1287">
+        <v>2.6</v>
+      </c>
+      <c r="N1287">
         <v>2.93</v>
       </c>
-      <c r="M1287">
-        <v>2.62</v>
-      </c>
-      <c r="N1287">
-        <v>2.96</v>
-      </c>
       <c r="O1287">
         <v>1</v>
       </c>
       <c r="P1287" t="s">
-        <v>333</v>
+        <v>473</v>
       </c>
     </row>
     <row r="1288" spans="1:16">
       <c r="A1288" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1288" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C1288">
-        <v>1.361620987792299</v>
+        <v>1.294319282110393</v>
       </c>
       <c r="D1288" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E1288">
-        <v>1.335449640254817</v>
+        <v>1.324319282110392</v>
       </c>
       <c r="F1288">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1288">
-        <v>0.004558379012207701</v>
+        <v>0.004565680717889608</v>
       </c>
       <c r="H1288">
-        <v>0.004544550359745182</v>
+        <v>0.004595680717889608</v>
       </c>
       <c r="I1288">
-        <v>0.02617134753748163</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="J1288">
-        <v>0.6171347537481471</v>
+        <v>0.6243056175151174</v>
       </c>
       <c r="K1288">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="L1288">
+        <v>2.93</v>
+      </c>
+      <c r="M1288">
+        <v>2.62</v>
+      </c>
+      <c r="N1288">
         <v>2.96</v>
       </c>
-      <c r="M1288">
-        <v>2.6</v>
-      </c>
-      <c r="N1288">
-        <v>2.94</v>
-      </c>
       <c r="O1288">
         <v>1</v>
       </c>
       <c r="P1288" t="s">
-        <v>333</v>
+        <v>474</v>
       </c>
     </row>
     <row r="1289" spans="1:16">
       <c r="A1289" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1289" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C1289">
-        <v>1.303704050944863</v>
+        <v>1.343048450635846</v>
       </c>
       <c r="D1289" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E1289">
-        <v>1.333704050944863</v>
+        <v>1.306805394460695</v>
       </c>
       <c r="F1289">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1289">
-        <v>0.004556295949055138</v>
+        <v>0.004576951549364153</v>
       </c>
       <c r="H1289">
-        <v>0.004586295949055136</v>
+        <v>0.004553194605539305</v>
       </c>
       <c r="I1289">
-        <v>0.0299999999999998</v>
+        <v>0.036243056175151</v>
       </c>
       <c r="J1289">
-        <v>0.6207236446775332</v>
+        <v>0.6243056175151174</v>
       </c>
       <c r="K1289">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="L1289">
+        <v>2.96</v>
+      </c>
+      <c r="M1289">
+        <v>2.6</v>
+      </c>
+      <c r="N1289">
         <v>2.93</v>
       </c>
-      <c r="M1289">
-        <v>2.62</v>
-      </c>
-      <c r="N1289">
-        <v>2.96</v>
-      </c>
       <c r="O1289">
         <v>1</v>
       </c>
       <c r="P1289" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="1290" spans="1:16">
-      <c r="A1290" s="1">
-        <v>1</v>
-      </c>
-      <c r="B1290" t="s">
-        <v>187</v>
-      </c>
-      <c r="C1290">
-        <v>1.352325760285189</v>
-      </c>
-      <c r="D1290" t="s">
-        <v>332</v>
-      </c>
-      <c r="E1290">
-        <v>1.326118523838414</v>
-      </c>
-      <c r="F1290">
-        <v>-1</v>
-      </c>
-      <c r="G1290">
-        <v>0.004567674239714811</v>
-      </c>
-      <c r="H1290">
-        <v>0.004553881476161586</v>
-      </c>
-      <c r="I1290">
-        <v>0.02620723644677558</v>
-      </c>
-      <c r="J1290">
-        <v>0.6207236446775332</v>
-      </c>
-      <c r="K1290">
-        <v>2.59</v>
-      </c>
-      <c r="L1290">
-        <v>2.96</v>
-      </c>
-      <c r="M1290">
-        <v>2.6</v>
-      </c>
-      <c r="N1290">
-        <v>2.94</v>
-      </c>
-      <c r="O1290">
-        <v>1</v>
-      </c>
-      <c r="P1290" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="1291" spans="1:16">
-      <c r="A1291" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1291" t="s">
-        <v>183</v>
-      </c>
-      <c r="C1291">
-        <v>1.294319282110393</v>
-      </c>
-      <c r="D1291" t="s">
-        <v>331</v>
-      </c>
-      <c r="E1291">
-        <v>1.324319282110392</v>
-      </c>
-      <c r="F1291">
-        <v>1</v>
-      </c>
-      <c r="G1291">
-        <v>0.004565680717889608</v>
-      </c>
-      <c r="H1291">
-        <v>0.004595680717889608</v>
-      </c>
-      <c r="I1291">
-        <v>0.0299999999999998</v>
-      </c>
-      <c r="J1291">
-        <v>0.6243056175151174</v>
-      </c>
-      <c r="K1291">
-        <v>2.62</v>
-      </c>
-      <c r="L1291">
-        <v>2.93</v>
-      </c>
-      <c r="M1291">
-        <v>2.62</v>
-      </c>
-      <c r="N1291">
-        <v>2.96</v>
-      </c>
-      <c r="O1291">
-        <v>1</v>
-      </c>
-      <c r="P1291" t="s">
         <v>474</v>
       </c>
     </row>

--- a/s60_signal/position-01288-601288.xlsx
+++ b/s60_signal/position-01288-601288.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3879" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3864" uniqueCount="475">
   <si>
     <t>trade_time</t>
   </si>
@@ -571,16 +571,16 @@
     <t>2021-07-20</t>
   </si>
   <si>
+    <t>2021-07-19</t>
+  </si>
+  <si>
     <t>2021-08-09</t>
   </si>
   <si>
-    <t>2021-07-19</t>
+    <t>2021-08-05</t>
   </si>
   <si>
     <t>2021-08-20</t>
-  </si>
-  <si>
-    <t>2021-08-05</t>
   </si>
   <si>
     <t>2017-05-12</t>
@@ -1003,13 +1003,13 @@
     <t>2021-07-13</t>
   </si>
   <si>
-    <t>2021-07-27</t>
-  </si>
-  <si>
     <t>2021-07-29</t>
   </si>
   <si>
     <t>2021-08-18</t>
+  </si>
+  <si>
+    <t>2021-07-30</t>
   </si>
   <si>
     <t>2021-08-25</t>
@@ -1420,10 +1420,10 @@
     <t>2021-07-26</t>
   </si>
   <si>
-    <t>2021-07-28</t>
+    <t>2021-07-27</t>
   </si>
   <si>
-    <t>2021-07-30</t>
+    <t>2021-07-28</t>
   </si>
   <si>
     <t>2021-08-02</t>
@@ -1796,7 +1796,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1289"/>
+  <dimension ref="A1:P1284"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -62260,7 +62260,7 @@
         <v>329</v>
       </c>
       <c r="E1210">
-        <v>2.09821140739365</v>
+        <v>2.084896835883625</v>
       </c>
       <c r="F1210">
         <v>-1</v>
@@ -62269,10 +62269,10 @@
         <v>0.003865103164116375</v>
       </c>
       <c r="H1210">
-        <v>0.00382178859260635</v>
+        <v>0.003815103164116375</v>
       </c>
       <c r="I1210">
-        <v>0.03668542848997536</v>
+        <v>0.04999999999999982</v>
       </c>
       <c r="J1210">
         <v>0.3314571510024426</v>
@@ -62284,10 +62284,10 @@
         <v>3</v>
       </c>
       <c r="M1210">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="N1210">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="O1210">
         <v>1</v>
@@ -62307,7 +62307,7 @@
         <v>2.048267692863576</v>
       </c>
       <c r="D1211" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E1211">
         <v>2.101525978903674</v>
@@ -62357,7 +62357,7 @@
         <v>2.061582264373601</v>
       </c>
       <c r="D1212" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E1212">
         <v>2.101525978903674</v>
@@ -62407,7 +62407,7 @@
         <v>2.109031399307522</v>
       </c>
       <c r="D1213" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E1213">
         <v>2.059031399307522</v>
@@ -62457,7 +62457,7 @@
         <v>2.022204053708345</v>
       </c>
       <c r="D1214" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E1214">
         <v>2.075858744906697</v>
@@ -62507,7 +62507,7 @@
         <v>2.035617726507934</v>
       </c>
       <c r="D1215" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E1215">
         <v>2.075858744906697</v>
@@ -62557,7 +62557,7 @@
         <v>2.077861015979273</v>
       </c>
       <c r="D1216" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E1216">
         <v>2.034873479736085</v>
@@ -62607,7 +62607,7 @@
         <v>2.084873479736085</v>
       </c>
       <c r="D1217" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E1217">
         <v>2.034873479736085</v>
@@ -62657,7 +62657,7 @@
         <v>1.997861015979273</v>
       </c>
       <c r="D1218" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E1218">
         <v>2.051885943492896</v>
@@ -62707,7 +62707,7 @@
         <v>2.011367247857679</v>
       </c>
       <c r="D1219" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E1219">
         <v>2.051885943492896</v>
@@ -62757,7 +62757,7 @@
         <v>2.05223085848304</v>
       </c>
       <c r="D1220" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E1220">
         <v>2.009438228380508</v>
@@ -62807,7 +62807,7 @@
         <v>1.97223085848304</v>
       </c>
       <c r="D1221" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E1221">
         <v>2.026645598277975</v>
@@ -62857,7 +62857,7 @@
         <v>1.985834543431774</v>
       </c>
       <c r="D1222" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E1222">
         <v>2.026645598277975</v>
@@ -62907,7 +62907,7 @@
         <v>2.019112345246391</v>
       </c>
       <c r="D1223" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E1223">
         <v>1.976571566955544</v>
@@ -62957,7 +62957,7 @@
         <v>1.939112345246391</v>
       </c>
       <c r="D1224" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E1224">
         <v>1.994030788664697</v>
@@ -63007,7 +63007,7 @@
         <v>1.952841956100968</v>
       </c>
       <c r="D1225" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E1225">
         <v>1.994030788664697</v>
@@ -63051,13 +63051,13 @@
         <v>0</v>
       </c>
       <c r="B1226" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C1226">
-        <v>1.980696042050148</v>
+        <v>1.972944681153191</v>
       </c>
       <c r="D1226" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E1226">
         <v>1.938447402947106</v>
@@ -63066,19 +63066,19 @@
         <v>-1</v>
       </c>
       <c r="G1226">
-        <v>0.004019303957949851</v>
+        <v>0.004027055318846808</v>
       </c>
       <c r="H1226">
         <v>0.003961552597052894</v>
       </c>
       <c r="I1226">
-        <v>0.04224863910304277</v>
+        <v>0.03449727820608572</v>
       </c>
       <c r="J1226">
         <v>0.3875680448478523</v>
       </c>
       <c r="K1226">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="L1226">
         <v>3</v>
@@ -63107,10 +63107,10 @@
         <v>1.900696042050148</v>
       </c>
       <c r="D1227" t="s">
-        <v>187</v>
+        <v>330</v>
       </c>
       <c r="E1227">
-        <v>1.956198763844063</v>
+        <v>1.944571722498627</v>
       </c>
       <c r="F1227">
         <v>1</v>
@@ -63119,10 +63119,10 @@
         <v>0.003939303957949852</v>
       </c>
       <c r="H1227">
-        <v>0.003963801236155938</v>
+        <v>0.003975428277501373</v>
       </c>
       <c r="I1227">
-        <v>0.05550272179391413</v>
+        <v>0.04387568044847856</v>
       </c>
       <c r="J1227">
         <v>0.3875680448478523</v>
@@ -63134,7 +63134,7 @@
         <v>2.92</v>
       </c>
       <c r="M1227">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="N1227">
         <v>2.96</v>
@@ -63151,16 +63151,16 @@
         <v>2</v>
       </c>
       <c r="B1228" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C1228">
         <v>1.916198763844063</v>
       </c>
       <c r="D1228" t="s">
-        <v>187</v>
+        <v>330</v>
       </c>
       <c r="E1228">
-        <v>1.956198763844063</v>
+        <v>1.944571722498627</v>
       </c>
       <c r="F1228">
         <v>1</v>
@@ -63169,10 +63169,10 @@
         <v>0.003923801236155938</v>
       </c>
       <c r="H1228">
-        <v>0.003963801236155938</v>
+        <v>0.003975428277501373</v>
       </c>
       <c r="I1228">
-        <v>0.04000000000000004</v>
+        <v>0.02837295865456446</v>
       </c>
       <c r="J1228">
         <v>0.3875680448478523</v>
@@ -63184,7 +63184,7 @@
         <v>2.92</v>
       </c>
       <c r="M1228">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="N1228">
         <v>2.96</v>
@@ -63207,10 +63207,10 @@
         <v>1.914571722498627</v>
       </c>
       <c r="D1229" t="s">
-        <v>187</v>
+        <v>330</v>
       </c>
       <c r="E1229">
-        <v>1.956198763844063</v>
+        <v>1.944571722498627</v>
       </c>
       <c r="F1229">
         <v>1</v>
@@ -63219,10 +63219,10 @@
         <v>0.003945428277501373</v>
       </c>
       <c r="H1229">
-        <v>0.003963801236155938</v>
+        <v>0.003975428277501373</v>
       </c>
       <c r="I1229">
-        <v>0.04162704134543538</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="J1229">
         <v>0.3875680448478523</v>
@@ -63234,7 +63234,7 @@
         <v>2.93</v>
       </c>
       <c r="M1229">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="N1229">
         <v>2.96</v>
@@ -63251,13 +63251,13 @@
         <v>0</v>
       </c>
       <c r="B1230" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C1230">
         <v>1.935690447928652</v>
       </c>
       <c r="D1230" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E1230">
         <v>1.901755497771239</v>
@@ -63307,7 +63307,7 @@
         <v>1.863722972849945</v>
       </c>
       <c r="D1231" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E1231">
         <v>1.907739235310592</v>
@@ -63351,13 +63351,13 @@
         <v>2</v>
       </c>
       <c r="B1232" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C1232">
         <v>1.879788022692531</v>
       </c>
       <c r="D1232" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E1232">
         <v>1.907739235310592</v>
@@ -63407,7 +63407,7 @@
         <v>1.877739235310592</v>
       </c>
       <c r="D1233" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E1233">
         <v>1.907739235310592</v>
@@ -63451,13 +63451,13 @@
         <v>0</v>
       </c>
       <c r="B1234" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C1234">
         <v>1.88677507248715</v>
       </c>
       <c r="D1234" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E1234">
         <v>1.85357846761942</v>
@@ -63507,7 +63507,7 @@
         <v>1.815176770053285</v>
       </c>
       <c r="D1235" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E1235">
         <v>1.859377618836352</v>
@@ -63551,13 +63551,13 @@
         <v>2</v>
       </c>
       <c r="B1236" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C1236">
-        <v>1.831980165185554</v>
+        <v>1.829377618836352</v>
       </c>
       <c r="D1236" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E1236">
         <v>1.859377618836352</v>
@@ -63566,22 +63566,22 @@
         <v>1</v>
       </c>
       <c r="G1236">
-        <v>0.004008019834814446</v>
+        <v>0.004030622381163648</v>
       </c>
       <c r="H1236">
         <v>0.004060622381163647</v>
       </c>
       <c r="I1236">
-        <v>0.02739745365079793</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="J1236">
         <v>0.4200848783067358</v>
       </c>
       <c r="K1236">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="L1236">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="M1236">
         <v>2.62</v>
@@ -63598,96 +63598,96 @@
     </row>
     <row r="1237" spans="1:16">
       <c r="A1237" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1237" t="s">
+        <v>185</v>
+      </c>
+      <c r="C1237">
+        <v>1.837587821290496</v>
+      </c>
+      <c r="D1237" t="s">
+        <v>329</v>
+      </c>
+      <c r="E1237">
+        <v>1.805133665497433</v>
+      </c>
+      <c r="F1237">
+        <v>-1</v>
+      </c>
+      <c r="G1237">
+        <v>0.004162412178709504</v>
+      </c>
+      <c r="H1237">
+        <v>0.004094866334502568</v>
+      </c>
+      <c r="I1237">
+        <v>0.03245415579306377</v>
+      </c>
+      <c r="J1237">
+        <v>0.4386461051733976</v>
+      </c>
+      <c r="K1237">
+        <v>2.65</v>
+      </c>
+      <c r="L1237">
         <v>3</v>
       </c>
-      <c r="B1237" t="s">
-        <v>183</v>
-      </c>
-      <c r="C1237">
-        <v>1.829377618836352</v>
-      </c>
-      <c r="D1237" t="s">
-        <v>331</v>
-      </c>
-      <c r="E1237">
-        <v>1.859377618836352</v>
-      </c>
-      <c r="F1237">
-        <v>1</v>
-      </c>
-      <c r="G1237">
-        <v>0.004030622381163648</v>
-      </c>
-      <c r="H1237">
-        <v>0.004060622381163647</v>
-      </c>
-      <c r="I1237">
-        <v>0.0299999999999998</v>
-      </c>
-      <c r="J1237">
-        <v>0.4200848783067358</v>
-      </c>
-      <c r="K1237">
-        <v>2.62</v>
-      </c>
-      <c r="L1237">
-        <v>2.93</v>
-      </c>
       <c r="M1237">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="N1237">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="O1237">
         <v>1</v>
       </c>
       <c r="P1237" t="s">
-        <v>328</v>
+        <v>462</v>
       </c>
     </row>
     <row r="1238" spans="1:16">
       <c r="A1238" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1238" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C1238">
-        <v>1.837587821290496</v>
+        <v>1.766360743393964</v>
       </c>
       <c r="D1238" t="s">
         <v>330</v>
       </c>
       <c r="E1238">
-        <v>1.805133665497433</v>
+        <v>1.810747204445698</v>
       </c>
       <c r="F1238">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1238">
-        <v>0.004162412178709504</v>
+        <v>0.004073639256606036</v>
       </c>
       <c r="H1238">
-        <v>0.004094866334502568</v>
+        <v>0.004109252795554301</v>
       </c>
       <c r="I1238">
-        <v>0.03245415579306377</v>
+        <v>0.04438646105173394</v>
       </c>
       <c r="J1238">
         <v>0.4386461051733976</v>
       </c>
       <c r="K1238">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="L1238">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="M1238">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="N1238">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="O1238">
         <v>1</v>
@@ -63698,16 +63698,16 @@
     </row>
     <row r="1239" spans="1:16">
       <c r="A1239" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1239" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C1239">
-        <v>1.766360743393964</v>
+        <v>1.780747204445698</v>
       </c>
       <c r="D1239" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E1239">
         <v>1.810747204445698</v>
@@ -63716,22 +63716,22 @@
         <v>1</v>
       </c>
       <c r="G1239">
-        <v>0.004073639256606036</v>
+        <v>0.004079252795554302</v>
       </c>
       <c r="H1239">
         <v>0.004109252795554301</v>
       </c>
       <c r="I1239">
-        <v>0.04438646105173394</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="J1239">
         <v>0.4386461051733976</v>
       </c>
       <c r="K1239">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="L1239">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="M1239">
         <v>2.62</v>
@@ -63748,90 +63748,90 @@
     </row>
     <row r="1240" spans="1:16">
       <c r="A1240" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1240" t="s">
         <v>185</v>
       </c>
       <c r="C1240">
-        <v>1.7839065876009</v>
+        <v>1.780823177477708</v>
       </c>
       <c r="D1240" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E1240">
-        <v>1.810747204445698</v>
+        <v>1.749225846496913</v>
       </c>
       <c r="F1240">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1240">
-        <v>0.004056093412399099</v>
+        <v>0.004219176822522292</v>
       </c>
       <c r="H1240">
-        <v>0.004109252795554301</v>
+        <v>0.004150774153503088</v>
       </c>
       <c r="I1240">
-        <v>0.0268406168447981</v>
+        <v>0.03159733098079531</v>
       </c>
       <c r="J1240">
-        <v>0.4386461051733976</v>
+        <v>0.4600667254801102</v>
       </c>
       <c r="K1240">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="L1240">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="M1240">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="N1240">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="O1240">
         <v>1</v>
       </c>
       <c r="P1240" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="1241" spans="1:16">
       <c r="A1241" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1241" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C1241">
-        <v>1.780747204445698</v>
+        <v>1.71002451198731</v>
       </c>
       <c r="D1241" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E1241">
-        <v>1.810747204445698</v>
+        <v>1.754625179242111</v>
       </c>
       <c r="F1241">
         <v>1</v>
       </c>
       <c r="G1241">
-        <v>0.004079252795554302</v>
+        <v>0.004129975488012689</v>
       </c>
       <c r="H1241">
-        <v>0.004109252795554301</v>
+        <v>0.004165374820757889</v>
       </c>
       <c r="I1241">
-        <v>0.0299999999999998</v>
+        <v>0.04460066725480094</v>
       </c>
       <c r="J1241">
-        <v>0.4386461051733976</v>
+        <v>0.4600667254801102</v>
       </c>
       <c r="K1241">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="L1241">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="M1241">
         <v>2.62</v>
@@ -63843,51 +63843,51 @@
         <v>1</v>
       </c>
       <c r="P1241" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="1242" spans="1:16">
       <c r="A1242" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1242" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C1242">
-        <v>1.780823177477708</v>
+        <v>1.724625179242111</v>
       </c>
       <c r="D1242" t="s">
         <v>330</v>
       </c>
       <c r="E1242">
-        <v>1.749225846496913</v>
+        <v>1.754625179242111</v>
       </c>
       <c r="F1242">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1242">
-        <v>0.004219176822522292</v>
+        <v>0.004135374820757889</v>
       </c>
       <c r="H1242">
-        <v>0.004150774153503088</v>
+        <v>0.004165374820757889</v>
       </c>
       <c r="I1242">
-        <v>0.03159733098079531</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="J1242">
         <v>0.4600667254801102</v>
       </c>
       <c r="K1242">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="L1242">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="M1242">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="N1242">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="O1242">
         <v>1</v>
@@ -63898,90 +63898,90 @@
     </row>
     <row r="1243" spans="1:16">
       <c r="A1243" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1243" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C1243">
-        <v>1.71002451198731</v>
+        <v>1.738072100680357</v>
       </c>
       <c r="D1243" t="s">
         <v>331</v>
       </c>
       <c r="E1243">
-        <v>1.754625179242111</v>
+        <v>1.696644053117783</v>
       </c>
       <c r="F1243">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1243">
-        <v>0.004129975488012689</v>
+        <v>0.004261927899319643</v>
       </c>
       <c r="H1243">
-        <v>0.004165374820757889</v>
+        <v>0.004163355946882217</v>
       </c>
       <c r="I1243">
-        <v>0.04460066725480094</v>
+        <v>0.0414280475625739</v>
       </c>
       <c r="J1243">
-        <v>0.4600667254801102</v>
+        <v>0.4761992072904313</v>
       </c>
       <c r="K1243">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="L1243">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="M1243">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="N1243">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="O1243">
         <v>1</v>
       </c>
       <c r="P1243" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="1244" spans="1:16">
       <c r="A1244" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1244" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C1244">
-        <v>1.724625179242111</v>
+        <v>1.667596084826166</v>
       </c>
       <c r="D1244" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E1244">
-        <v>1.754625179242111</v>
+        <v>1.71235807689907</v>
       </c>
       <c r="F1244">
         <v>1</v>
       </c>
       <c r="G1244">
-        <v>0.004135374820757889</v>
+        <v>0.004172403915173835</v>
       </c>
       <c r="H1244">
-        <v>0.004165374820757889</v>
+        <v>0.00420764192310093</v>
       </c>
       <c r="I1244">
-        <v>0.0299999999999998</v>
+        <v>0.0447619920729041</v>
       </c>
       <c r="J1244">
-        <v>0.4600667254801102</v>
+        <v>0.4761992072904313</v>
       </c>
       <c r="K1244">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="L1244">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="M1244">
         <v>2.62</v>
@@ -63993,51 +63993,51 @@
         <v>1</v>
       </c>
       <c r="P1244" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="1245" spans="1:16">
       <c r="A1245" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1245" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C1245">
-        <v>1.738072100680357</v>
+        <v>1.68235807689907</v>
       </c>
       <c r="D1245" t="s">
         <v>330</v>
       </c>
       <c r="E1245">
-        <v>1.707120068971975</v>
+        <v>1.71235807689907</v>
       </c>
       <c r="F1245">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1245">
-        <v>0.004261927899319643</v>
+        <v>0.00417764192310093</v>
       </c>
       <c r="H1245">
-        <v>0.004192879931028026</v>
+        <v>0.00420764192310093</v>
       </c>
       <c r="I1245">
-        <v>0.03095203170838245</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="J1245">
         <v>0.4761992072904313</v>
       </c>
       <c r="K1245">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="L1245">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="M1245">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="N1245">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="O1245">
         <v>1</v>
@@ -64048,34 +64048,34 @@
     </row>
     <row r="1246" spans="1:16">
       <c r="A1246" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1246" t="s">
         <v>182</v>
       </c>
       <c r="C1246">
-        <v>1.667596084826166</v>
+        <v>1.631109064123743</v>
       </c>
       <c r="D1246" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E1246">
-        <v>1.71235807689907</v>
+        <v>1.676009790115668</v>
       </c>
       <c r="F1246">
         <v>1</v>
       </c>
       <c r="G1246">
-        <v>0.004172403915173835</v>
+        <v>0.004208890935876257</v>
       </c>
       <c r="H1246">
-        <v>0.00420764192310093</v>
+        <v>0.004243990209884333</v>
       </c>
       <c r="I1246">
-        <v>0.0447619920729041</v>
+        <v>0.04490072599192496</v>
       </c>
       <c r="J1246">
-        <v>0.4761992072904313</v>
+        <v>0.4900725991924931</v>
       </c>
       <c r="K1246">
         <v>2.63</v>
@@ -64093,39 +64093,39 @@
         <v>1</v>
       </c>
       <c r="P1246" t="s">
-        <v>464</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1247" spans="1:16">
       <c r="A1247" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1247" t="s">
         <v>183</v>
       </c>
       <c r="C1247">
-        <v>1.68235807689907</v>
+        <v>1.646009790115668</v>
       </c>
       <c r="D1247" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E1247">
-        <v>1.71235807689907</v>
+        <v>1.676009790115668</v>
       </c>
       <c r="F1247">
         <v>1</v>
       </c>
       <c r="G1247">
-        <v>0.00417764192310093</v>
+        <v>0.004213990209884332</v>
       </c>
       <c r="H1247">
-        <v>0.00420764192310093</v>
+        <v>0.004243990209884333</v>
       </c>
       <c r="I1247">
         <v>0.0299999999999998</v>
       </c>
       <c r="J1247">
-        <v>0.4761992072904313</v>
+        <v>0.4900725991924931</v>
       </c>
       <c r="K1247">
         <v>2.62</v>
@@ -64143,7 +64143,7 @@
         <v>1</v>
       </c>
       <c r="P1247" t="s">
-        <v>464</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1248" spans="1:16">
@@ -64154,28 +64154,28 @@
         <v>182</v>
       </c>
       <c r="C1248">
-        <v>1.631109064123743</v>
+        <v>1.596583044051827</v>
       </c>
       <c r="D1248" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E1248">
-        <v>1.676009790115668</v>
+        <v>1.641615047686611</v>
       </c>
       <c r="F1248">
         <v>1</v>
       </c>
       <c r="G1248">
-        <v>0.004208890935876257</v>
+        <v>0.004243416955948173</v>
       </c>
       <c r="H1248">
-        <v>0.004243990209884333</v>
+        <v>0.004278384952313389</v>
       </c>
       <c r="I1248">
-        <v>0.04490072599192496</v>
+        <v>0.04503200363478399</v>
       </c>
       <c r="J1248">
-        <v>0.4900725991924931</v>
+        <v>0.5032003634783927</v>
       </c>
       <c r="K1248">
         <v>2.63</v>
@@ -64193,7 +64193,7 @@
         <v>1</v>
       </c>
       <c r="P1248" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1249" spans="1:16">
@@ -64204,28 +64204,28 @@
         <v>183</v>
       </c>
       <c r="C1249">
-        <v>1.646009790115668</v>
+        <v>1.611615047686611</v>
       </c>
       <c r="D1249" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E1249">
-        <v>1.676009790115668</v>
+        <v>1.641615047686611</v>
       </c>
       <c r="F1249">
         <v>1</v>
       </c>
       <c r="G1249">
-        <v>0.004213990209884332</v>
+        <v>0.004248384952313389</v>
       </c>
       <c r="H1249">
-        <v>0.004243990209884333</v>
+        <v>0.004278384952313389</v>
       </c>
       <c r="I1249">
         <v>0.0299999999999998</v>
       </c>
       <c r="J1249">
-        <v>0.4900725991924931</v>
+        <v>0.5032003634783927</v>
       </c>
       <c r="K1249">
         <v>2.62</v>
@@ -64243,7 +64243,7 @@
         <v>1</v>
       </c>
       <c r="P1249" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1250" spans="1:16">
@@ -64254,28 +64254,28 @@
         <v>182</v>
       </c>
       <c r="C1250">
-        <v>1.596583044051827</v>
+        <v>1.575343698422129</v>
       </c>
       <c r="D1250" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E1250">
-        <v>1.641615047686611</v>
+        <v>1.620456460025087</v>
       </c>
       <c r="F1250">
         <v>1</v>
       </c>
       <c r="G1250">
-        <v>0.004243416955948173</v>
+        <v>0.004264656301577871</v>
       </c>
       <c r="H1250">
-        <v>0.004278384952313389</v>
+        <v>0.004299543539974913</v>
       </c>
       <c r="I1250">
-        <v>0.04503200363478399</v>
+        <v>0.04511276160295763</v>
       </c>
       <c r="J1250">
-        <v>0.5032003634783927</v>
+        <v>0.5112761602957683</v>
       </c>
       <c r="K1250">
         <v>2.63</v>
@@ -64293,7 +64293,7 @@
         <v>1</v>
       </c>
       <c r="P1250" t="s">
-        <v>184</v>
+        <v>465</v>
       </c>
     </row>
     <row r="1251" spans="1:16">
@@ -64304,28 +64304,28 @@
         <v>183</v>
       </c>
       <c r="C1251">
-        <v>1.611615047686611</v>
+        <v>1.590456460025087</v>
       </c>
       <c r="D1251" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E1251">
-        <v>1.641615047686611</v>
+        <v>1.620456460025087</v>
       </c>
       <c r="F1251">
         <v>1</v>
       </c>
       <c r="G1251">
-        <v>0.004248384952313389</v>
+        <v>0.004269543539974914</v>
       </c>
       <c r="H1251">
-        <v>0.004278384952313389</v>
+        <v>0.004299543539974913</v>
       </c>
       <c r="I1251">
         <v>0.0299999999999998</v>
       </c>
       <c r="J1251">
-        <v>0.5032003634783927</v>
+        <v>0.5112761602957683</v>
       </c>
       <c r="K1251">
         <v>2.62</v>
@@ -64343,7 +64343,7 @@
         <v>1</v>
       </c>
       <c r="P1251" t="s">
-        <v>184</v>
+        <v>465</v>
       </c>
     </row>
     <row r="1252" spans="1:16">
@@ -64354,28 +64354,28 @@
         <v>182</v>
       </c>
       <c r="C1252">
-        <v>1.575343698422129</v>
+        <v>1.558285979436833</v>
       </c>
       <c r="D1252" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E1252">
-        <v>1.620456460025087</v>
+        <v>1.603463599286883</v>
       </c>
       <c r="F1252">
         <v>1</v>
       </c>
       <c r="G1252">
-        <v>0.004264656301577871</v>
+        <v>0.004281714020563167</v>
       </c>
       <c r="H1252">
-        <v>0.004299543539974913</v>
+        <v>0.004316536400713117</v>
       </c>
       <c r="I1252">
-        <v>0.04511276160295763</v>
+        <v>0.04517761985004998</v>
       </c>
       <c r="J1252">
-        <v>0.5112761602957683</v>
+        <v>0.5177619850050065</v>
       </c>
       <c r="K1252">
         <v>2.63</v>
@@ -64393,7 +64393,7 @@
         <v>1</v>
       </c>
       <c r="P1252" t="s">
-        <v>465</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1253" spans="1:16">
@@ -64401,37 +64401,37 @@
         <v>1</v>
       </c>
       <c r="B1253" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C1253">
-        <v>1.590456460025087</v>
+        <v>1.569351698537133</v>
       </c>
       <c r="D1253" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E1253">
-        <v>1.620456460025087</v>
+        <v>1.603463599286883</v>
       </c>
       <c r="F1253">
         <v>1</v>
       </c>
       <c r="G1253">
-        <v>0.004269543539974914</v>
+        <v>0.004230648301462867</v>
       </c>
       <c r="H1253">
-        <v>0.004299543539974913</v>
+        <v>0.004316536400713117</v>
       </c>
       <c r="I1253">
-        <v>0.0299999999999998</v>
+        <v>0.03411190074974946</v>
       </c>
       <c r="J1253">
-        <v>0.5112761602957683</v>
+        <v>0.5177619850050065</v>
       </c>
       <c r="K1253">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="L1253">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="M1253">
         <v>2.62</v>
@@ -64443,7 +64443,7 @@
         <v>1</v>
       </c>
       <c r="P1253" t="s">
-        <v>465</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1254" spans="1:16">
@@ -64454,28 +64454,28 @@
         <v>182</v>
       </c>
       <c r="C1254">
-        <v>1.558285979436833</v>
+        <v>1.540926184059721</v>
       </c>
       <c r="D1254" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E1254">
-        <v>1.603463599286883</v>
+        <v>1.5861698107363</v>
       </c>
       <c r="F1254">
         <v>1</v>
       </c>
       <c r="G1254">
-        <v>0.004281714020563167</v>
+        <v>0.004299073815940278</v>
       </c>
       <c r="H1254">
-        <v>0.004316536400713117</v>
+        <v>0.0043338301892637</v>
       </c>
       <c r="I1254">
-        <v>0.04517761985004998</v>
+        <v>0.045243626676579</v>
       </c>
       <c r="J1254">
-        <v>0.5177619850050065</v>
+        <v>0.5243626676579006</v>
       </c>
       <c r="K1254">
         <v>2.63</v>
@@ -64493,7 +64493,7 @@
         <v>1</v>
       </c>
       <c r="P1254" t="s">
-        <v>181</v>
+        <v>466</v>
       </c>
     </row>
     <row r="1255" spans="1:16">
@@ -64504,28 +64504,28 @@
         <v>183</v>
       </c>
       <c r="C1255">
-        <v>1.573463599286883</v>
+        <v>1.5561698107363</v>
       </c>
       <c r="D1255" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E1255">
-        <v>1.603463599286883</v>
+        <v>1.5861698107363</v>
       </c>
       <c r="F1255">
         <v>1</v>
       </c>
       <c r="G1255">
-        <v>0.004286536400713118</v>
+        <v>0.004303830189263699</v>
       </c>
       <c r="H1255">
-        <v>0.004316536400713117</v>
+        <v>0.0043338301892637</v>
       </c>
       <c r="I1255">
         <v>0.0299999999999998</v>
       </c>
       <c r="J1255">
-        <v>0.5177619850050065</v>
+        <v>0.5243626676579006</v>
       </c>
       <c r="K1255">
         <v>2.62</v>
@@ -64543,51 +64543,51 @@
         <v>1</v>
       </c>
       <c r="P1255" t="s">
-        <v>181</v>
+        <v>466</v>
       </c>
     </row>
     <row r="1256" spans="1:16">
       <c r="A1256" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1256" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="C1256">
-        <v>1.540926184059721</v>
+        <v>1.601900690766037</v>
       </c>
       <c r="D1256" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E1256">
-        <v>1.5861698107363</v>
+        <v>1.566657064089458</v>
       </c>
       <c r="F1256">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1256">
-        <v>0.004299073815940278</v>
+        <v>0.004318099309233963</v>
       </c>
       <c r="H1256">
-        <v>0.0043338301892637</v>
+        <v>0.004293342935910542</v>
       </c>
       <c r="I1256">
-        <v>0.045243626676579</v>
+        <v>0.03524362667657899</v>
       </c>
       <c r="J1256">
         <v>0.5243626676579006</v>
       </c>
       <c r="K1256">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="L1256">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="M1256">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="N1256">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="O1256">
         <v>1</v>
@@ -64598,40 +64598,40 @@
     </row>
     <row r="1257" spans="1:16">
       <c r="A1257" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1257" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C1257">
-        <v>1.5561698107363</v>
+        <v>1.523625633709941</v>
       </c>
       <c r="D1257" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E1257">
-        <v>1.5861698107363</v>
+        <v>1.568935041946785</v>
       </c>
       <c r="F1257">
         <v>1</v>
       </c>
       <c r="G1257">
-        <v>0.004303830189263699</v>
+        <v>0.004316374366290059</v>
       </c>
       <c r="H1257">
-        <v>0.0043338301892637</v>
+        <v>0.004351064958053216</v>
       </c>
       <c r="I1257">
-        <v>0.0299999999999998</v>
+        <v>0.04530940823684415</v>
       </c>
       <c r="J1257">
-        <v>0.5243626676579006</v>
+        <v>0.5309408236844333</v>
       </c>
       <c r="K1257">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="L1257">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="M1257">
         <v>2.62</v>
@@ -64643,101 +64643,101 @@
         <v>1</v>
       </c>
       <c r="P1257" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="1258" spans="1:16">
       <c r="A1258" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1258" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C1258">
-        <v>1.601900690766037</v>
+        <v>1.538935041946785</v>
       </c>
       <c r="D1258" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E1258">
-        <v>1.566657064089458</v>
+        <v>1.568935041946785</v>
       </c>
       <c r="F1258">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1258">
-        <v>0.004318099309233963</v>
+        <v>0.004321064958053215</v>
       </c>
       <c r="H1258">
-        <v>0.004293342935910542</v>
+        <v>0.004351064958053216</v>
       </c>
       <c r="I1258">
-        <v>0.03524362667657899</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="J1258">
-        <v>0.5243626676579006</v>
+        <v>0.5309408236844333</v>
       </c>
       <c r="K1258">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="L1258">
+        <v>2.93</v>
+      </c>
+      <c r="M1258">
+        <v>2.62</v>
+      </c>
+      <c r="N1258">
         <v>2.96</v>
       </c>
-      <c r="M1258">
-        <v>2.6</v>
-      </c>
-      <c r="N1258">
-        <v>2.93</v>
-      </c>
       <c r="O1258">
         <v>1</v>
       </c>
       <c r="P1258" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="1259" spans="1:16">
       <c r="A1259" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1259" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="C1259">
-        <v>1.523625633709941</v>
+        <v>1.584863266657318</v>
       </c>
       <c r="D1259" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E1259">
-        <v>1.568935041946785</v>
+        <v>1.549553858420474</v>
       </c>
       <c r="F1259">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1259">
-        <v>0.004316374366290059</v>
+        <v>0.004335136733342682</v>
       </c>
       <c r="H1259">
-        <v>0.004351064958053216</v>
+        <v>0.004310446141579527</v>
       </c>
       <c r="I1259">
-        <v>0.04530940823684415</v>
+        <v>0.03530940823684436</v>
       </c>
       <c r="J1259">
         <v>0.5309408236844333</v>
       </c>
       <c r="K1259">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="L1259">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="M1259">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="N1259">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="O1259">
         <v>1</v>
@@ -64748,40 +64748,40 @@
     </row>
     <row r="1260" spans="1:16">
       <c r="A1260" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1260" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C1260">
-        <v>1.538935041946785</v>
+        <v>1.508109076568332</v>
       </c>
       <c r="D1260" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E1260">
-        <v>1.568935041946785</v>
+        <v>1.553477483121304</v>
       </c>
       <c r="F1260">
         <v>1</v>
       </c>
       <c r="G1260">
-        <v>0.004321064958053215</v>
+        <v>0.004331890923431669</v>
       </c>
       <c r="H1260">
-        <v>0.004351064958053216</v>
+        <v>0.004366522516878696</v>
       </c>
       <c r="I1260">
-        <v>0.0299999999999998</v>
+        <v>0.04536840655297203</v>
       </c>
       <c r="J1260">
-        <v>0.5309408236844333</v>
+        <v>0.5368406552972123</v>
       </c>
       <c r="K1260">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="L1260">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="M1260">
         <v>2.62</v>
@@ -64793,139 +64793,139 @@
         <v>1</v>
       </c>
       <c r="P1260" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="1261" spans="1:16">
       <c r="A1261" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1261" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C1261">
-        <v>1.584863266657318</v>
+        <v>1.523477483121304</v>
       </c>
       <c r="D1261" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E1261">
-        <v>1.549553858420474</v>
+        <v>1.553477483121304</v>
       </c>
       <c r="F1261">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1261">
-        <v>0.004335136733342682</v>
+        <v>0.004336522516878697</v>
       </c>
       <c r="H1261">
-        <v>0.004310446141579527</v>
+        <v>0.004366522516878696</v>
       </c>
       <c r="I1261">
-        <v>0.03530940823684436</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="J1261">
-        <v>0.5309408236844333</v>
+        <v>0.5368406552972123</v>
       </c>
       <c r="K1261">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="L1261">
+        <v>2.93</v>
+      </c>
+      <c r="M1261">
+        <v>2.62</v>
+      </c>
+      <c r="N1261">
         <v>2.96</v>
       </c>
-      <c r="M1261">
-        <v>2.6</v>
-      </c>
-      <c r="N1261">
-        <v>2.93</v>
-      </c>
       <c r="O1261">
         <v>1</v>
       </c>
       <c r="P1261" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="1262" spans="1:16">
       <c r="A1262" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1262" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="C1262">
-        <v>1.508109076568332</v>
+        <v>1.56958270278022</v>
       </c>
       <c r="D1262" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E1262">
-        <v>1.553477483121304</v>
+        <v>1.534214296227248</v>
       </c>
       <c r="F1262">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1262">
-        <v>0.004331890923431669</v>
+        <v>0.00435041729721978</v>
       </c>
       <c r="H1262">
-        <v>0.004366522516878696</v>
+        <v>0.004325785703772752</v>
       </c>
       <c r="I1262">
-        <v>0.04536840655297203</v>
+        <v>0.03536840655297202</v>
       </c>
       <c r="J1262">
         <v>0.5368406552972123</v>
       </c>
       <c r="K1262">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="L1262">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="M1262">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="N1262">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="O1262">
         <v>1</v>
       </c>
       <c r="P1262" t="s">
-        <v>329</v>
+        <v>468</v>
       </c>
     </row>
     <row r="1263" spans="1:16">
       <c r="A1263" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1263" t="s">
         <v>183</v>
       </c>
       <c r="C1263">
-        <v>1.523477483121304</v>
+        <v>1.507440140601135</v>
       </c>
       <c r="D1263" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E1263">
-        <v>1.553477483121304</v>
+        <v>1.537440140601135</v>
       </c>
       <c r="F1263">
         <v>1</v>
       </c>
       <c r="G1263">
-        <v>0.004336522516878697</v>
+        <v>0.004352559859398865</v>
       </c>
       <c r="H1263">
-        <v>0.004366522516878696</v>
+        <v>0.004382559859398866</v>
       </c>
       <c r="I1263">
         <v>0.0299999999999998</v>
       </c>
       <c r="J1263">
-        <v>0.5368406552972123</v>
+        <v>0.5429617783965135</v>
       </c>
       <c r="K1263">
         <v>2.62</v>
@@ -64943,39 +64943,39 @@
         <v>1</v>
       </c>
       <c r="P1263" t="s">
-        <v>329</v>
+        <v>469</v>
       </c>
     </row>
     <row r="1264" spans="1:16">
       <c r="A1264" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1264" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C1264">
-        <v>1.56958270278022</v>
+        <v>1.55372899395303</v>
       </c>
       <c r="D1264" t="s">
         <v>332</v>
       </c>
       <c r="E1264">
-        <v>1.534214296227248</v>
+        <v>1.518299376169065</v>
       </c>
       <c r="F1264">
         <v>-1</v>
       </c>
       <c r="G1264">
-        <v>0.00435041729721978</v>
+        <v>0.004366271006046971</v>
       </c>
       <c r="H1264">
-        <v>0.004325785703772752</v>
+        <v>0.004341700623830935</v>
       </c>
       <c r="I1264">
-        <v>0.03536840655297202</v>
+        <v>0.03542961778396503</v>
       </c>
       <c r="J1264">
-        <v>0.5368406552972123</v>
+        <v>0.5429617783965135</v>
       </c>
       <c r="K1264">
         <v>2.59</v>
@@ -64993,7 +64993,7 @@
         <v>1</v>
       </c>
       <c r="P1264" t="s">
-        <v>329</v>
+        <v>469</v>
       </c>
     </row>
     <row r="1265" spans="1:16">
@@ -65001,49 +65001,49 @@
         <v>0</v>
       </c>
       <c r="B1265" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C1265">
-        <v>1.507440140601135</v>
+        <v>1.485291405699136</v>
       </c>
       <c r="D1265" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E1265">
-        <v>1.537440140601135</v>
+        <v>1.502263189489777</v>
       </c>
       <c r="F1265">
         <v>1</v>
       </c>
       <c r="G1265">
-        <v>0.004352559859398865</v>
+        <v>0.004314708594300864</v>
       </c>
       <c r="H1265">
-        <v>0.004382559859398866</v>
+        <v>0.004397736810510223</v>
       </c>
       <c r="I1265">
-        <v>0.0299999999999998</v>
+        <v>0.01697178379064157</v>
       </c>
       <c r="J1265">
-        <v>0.5429617783965135</v>
+        <v>0.5504702701559784</v>
       </c>
       <c r="K1265">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="L1265">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="M1265">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="N1265">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="O1265">
         <v>1</v>
       </c>
       <c r="P1265" t="s">
-        <v>468</v>
+        <v>329</v>
       </c>
     </row>
     <row r="1266" spans="1:16">
@@ -65051,49 +65051,49 @@
         <v>1</v>
       </c>
       <c r="B1266" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C1266">
-        <v>1.55372899395303</v>
+        <v>1.487767892191337</v>
       </c>
       <c r="D1266" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E1266">
-        <v>1.518299376169065</v>
+        <v>1.517767892191336</v>
       </c>
       <c r="F1266">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1266">
-        <v>0.004366271006046971</v>
+        <v>0.004372232107808664</v>
       </c>
       <c r="H1266">
-        <v>0.004341700623830935</v>
+        <v>0.004402232107808663</v>
       </c>
       <c r="I1266">
-        <v>0.03542961778396503</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="J1266">
-        <v>0.5429617783965135</v>
+        <v>0.5504702701559784</v>
       </c>
       <c r="K1266">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="L1266">
+        <v>2.93</v>
+      </c>
+      <c r="M1266">
+        <v>2.62</v>
+      </c>
+      <c r="N1266">
         <v>2.96</v>
       </c>
-      <c r="M1266">
-        <v>2.6</v>
-      </c>
-      <c r="N1266">
-        <v>2.93</v>
-      </c>
       <c r="O1266">
         <v>1</v>
       </c>
       <c r="P1266" t="s">
-        <v>468</v>
+        <v>329</v>
       </c>
     </row>
     <row r="1267" spans="1:16">
@@ -65101,49 +65101,49 @@
         <v>0</v>
       </c>
       <c r="B1267" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C1267">
-        <v>1.487767892191337</v>
+        <v>1.46240311169745</v>
       </c>
       <c r="D1267" t="s">
+        <v>334</v>
+      </c>
+      <c r="E1267">
+        <v>1.477996873908744</v>
+      </c>
+      <c r="F1267">
+        <v>1</v>
+      </c>
+      <c r="G1267">
+        <v>0.00433759688830255</v>
+      </c>
+      <c r="H1267">
+        <v>0.004342003126091256</v>
+      </c>
+      <c r="I1267">
+        <v>0.01559376221129405</v>
+      </c>
+      <c r="J1267">
+        <v>0.5593762211293968</v>
+      </c>
+      <c r="K1267">
+        <v>2.57</v>
+      </c>
+      <c r="L1267">
+        <v>2.9</v>
+      </c>
+      <c r="M1267">
+        <v>2.56</v>
+      </c>
+      <c r="N1267">
+        <v>2.91</v>
+      </c>
+      <c r="O1267">
+        <v>1</v>
+      </c>
+      <c r="P1267" t="s">
         <v>331</v>
-      </c>
-      <c r="E1267">
-        <v>1.517767892191336</v>
-      </c>
-      <c r="F1267">
-        <v>1</v>
-      </c>
-      <c r="G1267">
-        <v>0.004372232107808664</v>
-      </c>
-      <c r="H1267">
-        <v>0.004402232107808663</v>
-      </c>
-      <c r="I1267">
-        <v>0.0299999999999998</v>
-      </c>
-      <c r="J1267">
-        <v>0.5504702701559784</v>
-      </c>
-      <c r="K1267">
-        <v>2.62</v>
-      </c>
-      <c r="L1267">
-        <v>2.93</v>
-      </c>
-      <c r="M1267">
-        <v>2.62</v>
-      </c>
-      <c r="N1267">
-        <v>2.96</v>
-      </c>
-      <c r="O1267">
-        <v>1</v>
-      </c>
-      <c r="P1267" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="1268" spans="1:16">
@@ -65151,49 +65151,49 @@
         <v>1</v>
       </c>
       <c r="B1268" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C1268">
-        <v>1.534282000296016</v>
+        <v>1.464434300640981</v>
       </c>
       <c r="D1268" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E1268">
-        <v>1.498777297594456</v>
+        <v>1.49443430064098</v>
       </c>
       <c r="F1268">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1268">
-        <v>0.004385717999703984</v>
+        <v>0.00439556569935902</v>
       </c>
       <c r="H1268">
-        <v>0.004361222702405544</v>
+        <v>0.00442556569935902</v>
       </c>
       <c r="I1268">
-        <v>0.03550470270155981</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="J1268">
-        <v>0.5504702701559784</v>
+        <v>0.5593762211293968</v>
       </c>
       <c r="K1268">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="L1268">
+        <v>2.93</v>
+      </c>
+      <c r="M1268">
+        <v>2.62</v>
+      </c>
+      <c r="N1268">
         <v>2.96</v>
       </c>
-      <c r="M1268">
-        <v>2.6</v>
-      </c>
-      <c r="N1268">
-        <v>2.93</v>
-      </c>
       <c r="O1268">
         <v>1</v>
       </c>
       <c r="P1268" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="1269" spans="1:16">
@@ -65201,31 +65201,31 @@
         <v>0</v>
       </c>
       <c r="B1269" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C1269">
-        <v>1.46240311169745</v>
+        <v>1.439992168620962</v>
       </c>
       <c r="D1269" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E1269">
-        <v>1.478840538429687</v>
+        <v>1.455673132945394</v>
       </c>
       <c r="F1269">
         <v>1</v>
       </c>
       <c r="G1269">
-        <v>0.00433759688830255</v>
+        <v>0.004360007831379038</v>
       </c>
       <c r="H1269">
-        <v>0.004421159461570314</v>
+        <v>0.004364326867054606</v>
       </c>
       <c r="I1269">
-        <v>0.01643742673223647</v>
+        <v>0.015680964324432</v>
       </c>
       <c r="J1269">
-        <v>0.5593762211293968</v>
+        <v>0.5680964324432053</v>
       </c>
       <c r="K1269">
         <v>2.57</v>
@@ -65234,98 +65234,98 @@
         <v>2.9</v>
       </c>
       <c r="M1269">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="N1269">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="O1269">
         <v>1</v>
       </c>
       <c r="P1269" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="1270" spans="1:16">
       <c r="A1270" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1270" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C1270">
-        <v>1.464434300640981</v>
+        <v>1.411951954121605</v>
       </c>
       <c r="D1270" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="E1270">
-        <v>1.49443430064098</v>
+        <v>1.427742024339031</v>
       </c>
       <c r="F1270">
         <v>1</v>
       </c>
       <c r="G1270">
-        <v>0.00439556569935902</v>
+        <v>0.004388048045878395</v>
       </c>
       <c r="H1270">
-        <v>0.00442556569935902</v>
+        <v>0.00439225797566097</v>
       </c>
       <c r="I1270">
-        <v>0.0299999999999998</v>
+        <v>0.01579007021742584</v>
       </c>
       <c r="J1270">
-        <v>0.5593762211293968</v>
+        <v>0.579007021742566</v>
       </c>
       <c r="K1270">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="L1270">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="M1270">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="N1270">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="O1270">
         <v>1</v>
       </c>
       <c r="P1270" t="s">
-        <v>469</v>
+        <v>182</v>
       </c>
     </row>
     <row r="1271" spans="1:16">
       <c r="A1271" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1271" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C1271">
-        <v>1.511215587274862</v>
+        <v>1.460371813686754</v>
       </c>
       <c r="D1271" t="s">
         <v>332</v>
       </c>
       <c r="E1271">
-        <v>1.475621825063568</v>
+        <v>1.424581743469328</v>
       </c>
       <c r="F1271">
         <v>-1</v>
       </c>
       <c r="G1271">
-        <v>0.004408784412725138</v>
+        <v>0.004459628186313246</v>
       </c>
       <c r="H1271">
-        <v>0.004384378174936431</v>
+        <v>0.004435418256530672</v>
       </c>
       <c r="I1271">
-        <v>0.03559376221129407</v>
+        <v>0.03579007021742564</v>
       </c>
       <c r="J1271">
-        <v>0.5593762211293968</v>
+        <v>0.579007021742566</v>
       </c>
       <c r="K1271">
         <v>2.59</v>
@@ -65343,7 +65343,7 @@
         <v>1</v>
       </c>
       <c r="P1271" t="s">
-        <v>469</v>
+        <v>182</v>
       </c>
     </row>
     <row r="1272" spans="1:16">
@@ -65351,81 +65351,81 @@
         <v>0</v>
       </c>
       <c r="B1272" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C1272">
-        <v>1.439992168620962</v>
+        <v>1.394785989820947</v>
       </c>
       <c r="D1272" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="E1272">
-        <v>1.455673132945394</v>
+        <v>1.424785989820947</v>
       </c>
       <c r="F1272">
         <v>1</v>
       </c>
       <c r="G1272">
-        <v>0.004360007831379038</v>
+        <v>0.004465214010179054</v>
       </c>
       <c r="H1272">
-        <v>0.004364326867054606</v>
+        <v>0.004495214010179053</v>
       </c>
       <c r="I1272">
-        <v>0.015680964324432</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="J1272">
-        <v>0.5680964324432053</v>
+        <v>0.5859595458698675</v>
       </c>
       <c r="K1272">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="L1272">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="M1272">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="N1272">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="O1272">
         <v>1</v>
       </c>
       <c r="P1272" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="1273" spans="1:16">
       <c r="A1273" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1273" t="s">
         <v>183</v>
       </c>
       <c r="C1273">
-        <v>1.441587346998802</v>
+        <v>1.375586295079521</v>
       </c>
       <c r="D1273" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E1273">
-        <v>1.471587346998802</v>
+        <v>1.405586295079521</v>
       </c>
       <c r="F1273">
         <v>1</v>
       </c>
       <c r="G1273">
-        <v>0.004418412653001198</v>
+        <v>0.004484413704920479</v>
       </c>
       <c r="H1273">
-        <v>0.004448412653001197</v>
+        <v>0.004514413704920479</v>
       </c>
       <c r="I1273">
         <v>0.0299999999999998</v>
       </c>
       <c r="J1273">
-        <v>0.5680964324432053</v>
+        <v>0.5932876736337707</v>
       </c>
       <c r="K1273">
         <v>2.62</v>
@@ -65443,57 +65443,57 @@
         <v>1</v>
       </c>
       <c r="P1273" t="s">
-        <v>470</v>
+        <v>187</v>
       </c>
     </row>
     <row r="1274" spans="1:16">
       <c r="A1274" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1274" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C1274">
-        <v>1.488630239972098</v>
+        <v>1.354610467845981</v>
       </c>
       <c r="D1274" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E1274">
-        <v>1.452949275647666</v>
+        <v>1.384610467845981</v>
       </c>
       <c r="F1274">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1274">
-        <v>0.004431369760027902</v>
+        <v>0.00450538953215402</v>
       </c>
       <c r="H1274">
-        <v>0.004407050724352334</v>
+        <v>0.004535389532154019</v>
       </c>
       <c r="I1274">
-        <v>0.03568096432443202</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="J1274">
-        <v>0.5680964324432053</v>
+        <v>0.6012937145626027</v>
       </c>
       <c r="K1274">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="L1274">
+        <v>2.93</v>
+      </c>
+      <c r="M1274">
+        <v>2.62</v>
+      </c>
+      <c r="N1274">
         <v>2.96</v>
       </c>
-      <c r="M1274">
-        <v>2.6</v>
-      </c>
-      <c r="N1274">
-        <v>2.93</v>
-      </c>
       <c r="O1274">
         <v>1</v>
       </c>
       <c r="P1274" t="s">
-        <v>470</v>
+        <v>334</v>
       </c>
     </row>
     <row r="1275" spans="1:16">
@@ -65501,149 +65501,149 @@
         <v>0</v>
       </c>
       <c r="B1275" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C1275">
-        <v>1.411951954121605</v>
+        <v>1.339075752139688</v>
       </c>
       <c r="D1275" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="E1275">
-        <v>1.427742024339031</v>
+        <v>1.369075752139688</v>
       </c>
       <c r="F1275">
         <v>1</v>
       </c>
       <c r="G1275">
-        <v>0.004388048045878395</v>
+        <v>0.004520924247860313</v>
       </c>
       <c r="H1275">
-        <v>0.00439225797566097</v>
+        <v>0.004550924247860312</v>
       </c>
       <c r="I1275">
-        <v>0.01579007021742584</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="J1275">
-        <v>0.579007021742566</v>
+        <v>0.6072229953665313</v>
       </c>
       <c r="K1275">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="L1275">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="M1275">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="N1275">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="O1275">
         <v>1</v>
       </c>
       <c r="P1275" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="1276" spans="1:16">
       <c r="A1276" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1276" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C1276">
-        <v>1.460371813686754</v>
+        <v>1.324719520925932</v>
       </c>
       <c r="D1276" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E1276">
-        <v>1.424581743469328</v>
+        <v>1.354719520925932</v>
       </c>
       <c r="F1276">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1276">
-        <v>0.004459628186313246</v>
+        <v>0.004535280479074069</v>
       </c>
       <c r="H1276">
-        <v>0.004435418256530672</v>
+        <v>0.004565280479074068</v>
       </c>
       <c r="I1276">
-        <v>0.03579007021742564</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="J1276">
-        <v>0.579007021742566</v>
+        <v>0.6127024729290337</v>
       </c>
       <c r="K1276">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="L1276">
+        <v>2.93</v>
+      </c>
+      <c r="M1276">
+        <v>2.62</v>
+      </c>
+      <c r="N1276">
         <v>2.96</v>
       </c>
-      <c r="M1276">
-        <v>2.6</v>
-      </c>
-      <c r="N1276">
-        <v>2.93</v>
-      </c>
       <c r="O1276">
         <v>1</v>
       </c>
       <c r="P1276" t="s">
-        <v>182</v>
+        <v>472</v>
       </c>
     </row>
     <row r="1277" spans="1:16">
       <c r="A1277" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1277" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="C1277">
-        <v>1.394785989820947</v>
+        <v>1.373100595113803</v>
       </c>
       <c r="D1277" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E1277">
-        <v>1.424785989820947</v>
+        <v>1.336973570384512</v>
       </c>
       <c r="F1277">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1277">
-        <v>0.004465214010179054</v>
+        <v>0.004546899404886198</v>
       </c>
       <c r="H1277">
-        <v>0.004495214010179053</v>
+        <v>0.004523026429615488</v>
       </c>
       <c r="I1277">
-        <v>0.0299999999999998</v>
+        <v>0.03612702472929041</v>
       </c>
       <c r="J1277">
-        <v>0.5859595458698675</v>
+        <v>0.6127024729290337</v>
       </c>
       <c r="K1277">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="L1277">
+        <v>2.96</v>
+      </c>
+      <c r="M1277">
+        <v>2.6</v>
+      </c>
+      <c r="N1277">
         <v>2.93</v>
       </c>
-      <c r="M1277">
-        <v>2.62</v>
-      </c>
-      <c r="N1277">
-        <v>2.96</v>
-      </c>
       <c r="O1277">
         <v>1</v>
       </c>
       <c r="P1277" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="1278" spans="1:16">
@@ -65654,28 +65654,28 @@
         <v>183</v>
       </c>
       <c r="C1278">
-        <v>1.375586295079521</v>
+        <v>1.313106945179855</v>
       </c>
       <c r="D1278" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E1278">
-        <v>1.405586295079521</v>
+        <v>1.343106945179855</v>
       </c>
       <c r="F1278">
         <v>1</v>
       </c>
       <c r="G1278">
-        <v>0.004484413704920479</v>
+        <v>0.004546893054820146</v>
       </c>
       <c r="H1278">
-        <v>0.004514413704920479</v>
+        <v>0.004576893054820145</v>
       </c>
       <c r="I1278">
         <v>0.0299999999999998</v>
       </c>
       <c r="J1278">
-        <v>0.5932876736337707</v>
+        <v>0.6171347537481471</v>
       </c>
       <c r="K1278">
         <v>2.62</v>
@@ -65693,57 +65693,57 @@
         <v>1</v>
       </c>
       <c r="P1278" t="s">
-        <v>188</v>
+        <v>333</v>
       </c>
     </row>
     <row r="1279" spans="1:16">
       <c r="A1279" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1279" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="C1279">
-        <v>1.354610467845981</v>
+        <v>1.361620987792299</v>
       </c>
       <c r="D1279" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E1279">
-        <v>1.384610467845981</v>
+        <v>1.325449640254818</v>
       </c>
       <c r="F1279">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1279">
-        <v>0.00450538953215402</v>
+        <v>0.004558379012207701</v>
       </c>
       <c r="H1279">
-        <v>0.004535389532154019</v>
+        <v>0.004534550359745182</v>
       </c>
       <c r="I1279">
-        <v>0.0299999999999998</v>
+        <v>0.03617134753748141</v>
       </c>
       <c r="J1279">
-        <v>0.6012937145626027</v>
+        <v>0.6171347537481471</v>
       </c>
       <c r="K1279">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="L1279">
+        <v>2.96</v>
+      </c>
+      <c r="M1279">
+        <v>2.6</v>
+      </c>
+      <c r="N1279">
         <v>2.93</v>
       </c>
-      <c r="M1279">
-        <v>2.62</v>
-      </c>
-      <c r="N1279">
-        <v>2.96</v>
-      </c>
       <c r="O1279">
         <v>1</v>
       </c>
       <c r="P1279" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="1280" spans="1:16">
@@ -65754,28 +65754,28 @@
         <v>183</v>
       </c>
       <c r="C1280">
-        <v>1.339075752139688</v>
+        <v>1.303704050944863</v>
       </c>
       <c r="D1280" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E1280">
-        <v>1.369075752139688</v>
+        <v>1.333704050944863</v>
       </c>
       <c r="F1280">
         <v>1</v>
       </c>
       <c r="G1280">
-        <v>0.004520924247860313</v>
+        <v>0.004556295949055138</v>
       </c>
       <c r="H1280">
-        <v>0.004550924247860312</v>
+        <v>0.004586295949055136</v>
       </c>
       <c r="I1280">
         <v>0.0299999999999998</v>
       </c>
       <c r="J1280">
-        <v>0.6072229953665313</v>
+        <v>0.6207236446775332</v>
       </c>
       <c r="K1280">
         <v>2.62</v>
@@ -65793,7 +65793,7 @@
         <v>1</v>
       </c>
       <c r="P1280" t="s">
-        <v>185</v>
+        <v>473</v>
       </c>
     </row>
     <row r="1281" spans="1:16">
@@ -65801,31 +65801,31 @@
         <v>1</v>
       </c>
       <c r="B1281" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C1281">
-        <v>1.387292442000684</v>
+        <v>1.352325760285189</v>
       </c>
       <c r="D1281" t="s">
         <v>332</v>
       </c>
       <c r="E1281">
-        <v>1.351220212047019</v>
+        <v>1.316118523838414</v>
       </c>
       <c r="F1281">
         <v>-1</v>
       </c>
       <c r="G1281">
-        <v>0.004532707557999316</v>
+        <v>0.004567674239714811</v>
       </c>
       <c r="H1281">
-        <v>0.004508779787952982</v>
+        <v>0.004543881476161586</v>
       </c>
       <c r="I1281">
-        <v>0.0360722299536651</v>
+        <v>0.03620723644677537</v>
       </c>
       <c r="J1281">
-        <v>0.6072229953665313</v>
+        <v>0.6207236446775332</v>
       </c>
       <c r="K1281">
         <v>2.59</v>
@@ -65843,7 +65843,7 @@
         <v>1</v>
       </c>
       <c r="P1281" t="s">
-        <v>185</v>
+        <v>473</v>
       </c>
     </row>
     <row r="1282" spans="1:16">
@@ -65854,28 +65854,28 @@
         <v>183</v>
       </c>
       <c r="C1282">
-        <v>1.324719520925932</v>
+        <v>1.294319282110393</v>
       </c>
       <c r="D1282" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E1282">
-        <v>1.354719520925932</v>
+        <v>1.324319282110392</v>
       </c>
       <c r="F1282">
         <v>1</v>
       </c>
       <c r="G1282">
-        <v>0.004535280479074069</v>
+        <v>0.004565680717889608</v>
       </c>
       <c r="H1282">
-        <v>0.004565280479074068</v>
+        <v>0.004595680717889608</v>
       </c>
       <c r="I1282">
         <v>0.0299999999999998</v>
       </c>
       <c r="J1282">
-        <v>0.6127024729290337</v>
+        <v>0.6243056175151174</v>
       </c>
       <c r="K1282">
         <v>2.62</v>
@@ -65893,7 +65893,7 @@
         <v>1</v>
       </c>
       <c r="P1282" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="1283" spans="1:16">
@@ -65901,31 +65901,31 @@
         <v>1</v>
       </c>
       <c r="B1283" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C1283">
-        <v>1.373100595113803</v>
+        <v>1.343048450635846</v>
       </c>
       <c r="D1283" t="s">
         <v>332</v>
       </c>
       <c r="E1283">
-        <v>1.336973570384512</v>
+        <v>1.306805394460695</v>
       </c>
       <c r="F1283">
         <v>-1</v>
       </c>
       <c r="G1283">
-        <v>0.004546899404886198</v>
+        <v>0.004576951549364153</v>
       </c>
       <c r="H1283">
-        <v>0.004523026429615488</v>
+        <v>0.004553194605539305</v>
       </c>
       <c r="I1283">
-        <v>0.03612702472929041</v>
+        <v>0.036243056175151</v>
       </c>
       <c r="J1283">
-        <v>0.6127024729290337</v>
+        <v>0.6243056175151174</v>
       </c>
       <c r="K1283">
         <v>2.59</v>
@@ -65943,7 +65943,7 @@
         <v>1</v>
       </c>
       <c r="P1283" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="1284" spans="1:16">
@@ -65951,299 +65951,49 @@
         <v>0</v>
       </c>
       <c r="B1284" t="s">
+        <v>188</v>
+      </c>
+      <c r="C1284">
+        <v>1.333264016795541</v>
+      </c>
+      <c r="D1284" t="s">
+        <v>332</v>
+      </c>
+      <c r="E1284">
+        <v>1.296983182883554</v>
+      </c>
+      <c r="F1284">
+        <v>-1</v>
+      </c>
+      <c r="G1284">
+        <v>0.004586735983204459</v>
+      </c>
+      <c r="H1284">
+        <v>0.004563016817116446</v>
+      </c>
+      <c r="I1284">
+        <v>0.03628083391198622</v>
+      </c>
+      <c r="J1284">
+        <v>0.628083391198633</v>
+      </c>
+      <c r="K1284">
+        <v>2.59</v>
+      </c>
+      <c r="L1284">
+        <v>2.96</v>
+      </c>
+      <c r="M1284">
+        <v>2.6</v>
+      </c>
+      <c r="N1284">
+        <v>2.93</v>
+      </c>
+      <c r="O1284">
+        <v>1</v>
+      </c>
+      <c r="P1284" t="s">
         <v>183</v>
-      </c>
-      <c r="C1284">
-        <v>1.313106945179855</v>
-      </c>
-      <c r="D1284" t="s">
-        <v>331</v>
-      </c>
-      <c r="E1284">
-        <v>1.343106945179855</v>
-      </c>
-      <c r="F1284">
-        <v>1</v>
-      </c>
-      <c r="G1284">
-        <v>0.004546893054820146</v>
-      </c>
-      <c r="H1284">
-        <v>0.004576893054820145</v>
-      </c>
-      <c r="I1284">
-        <v>0.0299999999999998</v>
-      </c>
-      <c r="J1284">
-        <v>0.6171347537481471</v>
-      </c>
-      <c r="K1284">
-        <v>2.62</v>
-      </c>
-      <c r="L1284">
-        <v>2.93</v>
-      </c>
-      <c r="M1284">
-        <v>2.62</v>
-      </c>
-      <c r="N1284">
-        <v>2.96</v>
-      </c>
-      <c r="O1284">
-        <v>1</v>
-      </c>
-      <c r="P1284" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="1285" spans="1:16">
-      <c r="A1285" s="1">
-        <v>1</v>
-      </c>
-      <c r="B1285" t="s">
-        <v>187</v>
-      </c>
-      <c r="C1285">
-        <v>1.361620987792299</v>
-      </c>
-      <c r="D1285" t="s">
-        <v>332</v>
-      </c>
-      <c r="E1285">
-        <v>1.325449640254818</v>
-      </c>
-      <c r="F1285">
-        <v>-1</v>
-      </c>
-      <c r="G1285">
-        <v>0.004558379012207701</v>
-      </c>
-      <c r="H1285">
-        <v>0.004534550359745182</v>
-      </c>
-      <c r="I1285">
-        <v>0.03617134753748141</v>
-      </c>
-      <c r="J1285">
-        <v>0.6171347537481471</v>
-      </c>
-      <c r="K1285">
-        <v>2.59</v>
-      </c>
-      <c r="L1285">
-        <v>2.96</v>
-      </c>
-      <c r="M1285">
-        <v>2.6</v>
-      </c>
-      <c r="N1285">
-        <v>2.93</v>
-      </c>
-      <c r="O1285">
-        <v>1</v>
-      </c>
-      <c r="P1285" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="1286" spans="1:16">
-      <c r="A1286" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1286" t="s">
-        <v>183</v>
-      </c>
-      <c r="C1286">
-        <v>1.303704050944863</v>
-      </c>
-      <c r="D1286" t="s">
-        <v>331</v>
-      </c>
-      <c r="E1286">
-        <v>1.333704050944863</v>
-      </c>
-      <c r="F1286">
-        <v>1</v>
-      </c>
-      <c r="G1286">
-        <v>0.004556295949055138</v>
-      </c>
-      <c r="H1286">
-        <v>0.004586295949055136</v>
-      </c>
-      <c r="I1286">
-        <v>0.0299999999999998</v>
-      </c>
-      <c r="J1286">
-        <v>0.6207236446775332</v>
-      </c>
-      <c r="K1286">
-        <v>2.62</v>
-      </c>
-      <c r="L1286">
-        <v>2.93</v>
-      </c>
-      <c r="M1286">
-        <v>2.62</v>
-      </c>
-      <c r="N1286">
-        <v>2.96</v>
-      </c>
-      <c r="O1286">
-        <v>1</v>
-      </c>
-      <c r="P1286" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="1287" spans="1:16">
-      <c r="A1287" s="1">
-        <v>1</v>
-      </c>
-      <c r="B1287" t="s">
-        <v>187</v>
-      </c>
-      <c r="C1287">
-        <v>1.352325760285189</v>
-      </c>
-      <c r="D1287" t="s">
-        <v>332</v>
-      </c>
-      <c r="E1287">
-        <v>1.316118523838414</v>
-      </c>
-      <c r="F1287">
-        <v>-1</v>
-      </c>
-      <c r="G1287">
-        <v>0.004567674239714811</v>
-      </c>
-      <c r="H1287">
-        <v>0.004543881476161586</v>
-      </c>
-      <c r="I1287">
-        <v>0.03620723644677537</v>
-      </c>
-      <c r="J1287">
-        <v>0.6207236446775332</v>
-      </c>
-      <c r="K1287">
-        <v>2.59</v>
-      </c>
-      <c r="L1287">
-        <v>2.96</v>
-      </c>
-      <c r="M1287">
-        <v>2.6</v>
-      </c>
-      <c r="N1287">
-        <v>2.93</v>
-      </c>
-      <c r="O1287">
-        <v>1</v>
-      </c>
-      <c r="P1287" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="1288" spans="1:16">
-      <c r="A1288" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1288" t="s">
-        <v>183</v>
-      </c>
-      <c r="C1288">
-        <v>1.294319282110393</v>
-      </c>
-      <c r="D1288" t="s">
-        <v>331</v>
-      </c>
-      <c r="E1288">
-        <v>1.324319282110392</v>
-      </c>
-      <c r="F1288">
-        <v>1</v>
-      </c>
-      <c r="G1288">
-        <v>0.004565680717889608</v>
-      </c>
-      <c r="H1288">
-        <v>0.004595680717889608</v>
-      </c>
-      <c r="I1288">
-        <v>0.0299999999999998</v>
-      </c>
-      <c r="J1288">
-        <v>0.6243056175151174</v>
-      </c>
-      <c r="K1288">
-        <v>2.62</v>
-      </c>
-      <c r="L1288">
-        <v>2.93</v>
-      </c>
-      <c r="M1288">
-        <v>2.62</v>
-      </c>
-      <c r="N1288">
-        <v>2.96</v>
-      </c>
-      <c r="O1288">
-        <v>1</v>
-      </c>
-      <c r="P1288" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="1289" spans="1:16">
-      <c r="A1289" s="1">
-        <v>1</v>
-      </c>
-      <c r="B1289" t="s">
-        <v>187</v>
-      </c>
-      <c r="C1289">
-        <v>1.343048450635846</v>
-      </c>
-      <c r="D1289" t="s">
-        <v>332</v>
-      </c>
-      <c r="E1289">
-        <v>1.306805394460695</v>
-      </c>
-      <c r="F1289">
-        <v>-1</v>
-      </c>
-      <c r="G1289">
-        <v>0.004576951549364153</v>
-      </c>
-      <c r="H1289">
-        <v>0.004553194605539305</v>
-      </c>
-      <c r="I1289">
-        <v>0.036243056175151</v>
-      </c>
-      <c r="J1289">
-        <v>0.6243056175151174</v>
-      </c>
-      <c r="K1289">
-        <v>2.59</v>
-      </c>
-      <c r="L1289">
-        <v>2.96</v>
-      </c>
-      <c r="M1289">
-        <v>2.6</v>
-      </c>
-      <c r="N1289">
-        <v>2.93</v>
-      </c>
-      <c r="O1289">
-        <v>1</v>
-      </c>
-      <c r="P1289" t="s">
-        <v>474</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01288-601288.xlsx
+++ b/s60_signal/position-01288-601288.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4485" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4485" uniqueCount="501">
   <si>
     <t>trade_time</t>
   </si>
@@ -607,10 +607,10 @@
     <t>2021-09-09</t>
   </si>
   <si>
-    <t>2021-09-02</t>
+    <t>2021-09-24</t>
   </si>
   <si>
-    <t>2021-09-24</t>
+    <t>2021-09-28</t>
   </si>
   <si>
     <t>2017-05-12</t>
@@ -1042,7 +1042,7 @@
     <t>2021-08-18</t>
   </si>
   <si>
-    <t>2021-09-28</t>
+    <t>2021-09-29</t>
   </si>
   <si>
     <t>2021-08-25</t>
@@ -1501,6 +1501,9 @@
     <t>2021-08-27</t>
   </si>
   <si>
+    <t>2021-09-02</t>
+  </si>
+  <si>
     <t>2021-09-06</t>
   </si>
   <si>
@@ -63126,10 +63129,10 @@
         <v>4</v>
       </c>
       <c r="B1226" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C1226">
-        <v>2.082798697195215</v>
+        <v>2.073836088465649</v>
       </c>
       <c r="D1226" t="s">
         <v>195</v>
@@ -63141,22 +63144,22 @@
         <v>-1</v>
       </c>
       <c r="G1226">
-        <v>0.003997201302804785</v>
+        <v>0.003946163911534351</v>
       </c>
       <c r="H1226">
         <v>0.003947201302804786</v>
       </c>
       <c r="I1226">
-        <v>0.04999999999999982</v>
+        <v>0.04103739127043449</v>
       </c>
       <c r="J1226">
         <v>0.3506231878405806</v>
       </c>
       <c r="K1226">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="L1226">
-        <v>3.04</v>
+        <v>3.01</v>
       </c>
       <c r="M1226">
         <v>2.73</v>
@@ -63173,81 +63176,81 @@
     </row>
     <row r="1227" spans="1:16">
       <c r="A1227" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B1227" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C1227">
-        <v>2.05223085848304</v>
+        <v>2.082798697195215</v>
       </c>
       <c r="D1227" t="s">
-        <v>339</v>
+        <v>195</v>
       </c>
       <c r="E1227">
-        <v>2.009438228380508</v>
+        <v>2.032798697195215</v>
       </c>
       <c r="F1227">
         <v>-1</v>
       </c>
       <c r="G1227">
-        <v>0.00394776914151696</v>
+        <v>0.003997201302804785</v>
       </c>
       <c r="H1227">
-        <v>0.003890561771619492</v>
+        <v>0.003947201302804786</v>
       </c>
       <c r="I1227">
-        <v>0.04279263010253231</v>
+        <v>0.04999999999999982</v>
       </c>
       <c r="J1227">
-        <v>0.3603684948733686</v>
+        <v>0.3506231878405806</v>
       </c>
       <c r="K1227">
-        <v>2.63</v>
+        <v>2.73</v>
       </c>
       <c r="L1227">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="M1227">
-        <v>2.61</v>
+        <v>2.73</v>
       </c>
       <c r="N1227">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="O1227">
         <v>1</v>
       </c>
       <c r="P1227" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="1228" spans="1:16">
       <c r="A1228" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1228" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C1228">
-        <v>1.97223085848304</v>
+        <v>2.05223085848304</v>
       </c>
       <c r="D1228" t="s">
-        <v>193</v>
+        <v>339</v>
       </c>
       <c r="E1228">
-        <v>2.026645598277975</v>
+        <v>2.009438228380508</v>
       </c>
       <c r="F1228">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1228">
-        <v>0.00386776914151696</v>
+        <v>0.00394776914151696</v>
       </c>
       <c r="H1228">
-        <v>0.003893354401722025</v>
+        <v>0.003890561771619492</v>
       </c>
       <c r="I1228">
-        <v>0.05441473979493461</v>
+        <v>0.04279263010253231</v>
       </c>
       <c r="J1228">
         <v>0.3603684948733686</v>
@@ -63256,13 +63259,13 @@
         <v>2.63</v>
       </c>
       <c r="L1228">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="M1228">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="N1228">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="O1228">
         <v>1</v>
@@ -63273,13 +63276,13 @@
     </row>
     <row r="1229" spans="1:16">
       <c r="A1229" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1229" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C1229">
-        <v>1.985834543431774</v>
+        <v>1.97223085848304</v>
       </c>
       <c r="D1229" t="s">
         <v>193</v>
@@ -63291,22 +63294,22 @@
         <v>1</v>
       </c>
       <c r="G1229">
-        <v>0.003874165456568226</v>
+        <v>0.00386776914151696</v>
       </c>
       <c r="H1229">
         <v>0.003893354401722025</v>
       </c>
       <c r="I1229">
-        <v>0.04081105484620062</v>
+        <v>0.05441473979493461</v>
       </c>
       <c r="J1229">
         <v>0.3603684948733686</v>
       </c>
       <c r="K1229">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="L1229">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="M1229">
         <v>2.59</v>
@@ -63323,43 +63326,43 @@
     </row>
     <row r="1230" spans="1:16">
       <c r="A1230" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1230" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C1230">
-        <v>1.983041913329241</v>
+        <v>1.985834543431774</v>
       </c>
       <c r="D1230" t="s">
-        <v>340</v>
+        <v>193</v>
       </c>
       <c r="E1230">
-        <v>2.019438228380508</v>
+        <v>2.026645598277975</v>
       </c>
       <c r="F1230">
         <v>1</v>
       </c>
       <c r="G1230">
-        <v>0.003856958086670758</v>
+        <v>0.003874165456568226</v>
       </c>
       <c r="H1230">
-        <v>0.003900561771619492</v>
+        <v>0.003893354401722025</v>
       </c>
       <c r="I1230">
-        <v>0.0363963150512665</v>
+        <v>0.04081105484620062</v>
       </c>
       <c r="J1230">
         <v>0.3603684948733686</v>
       </c>
       <c r="K1230">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="L1230">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="M1230">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="N1230">
         <v>2.96</v>
@@ -63373,46 +63376,46 @@
     </row>
     <row r="1231" spans="1:16">
       <c r="A1231" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1231" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C1231">
-        <v>2.047816118688106</v>
+        <v>1.983041913329241</v>
       </c>
       <c r="D1231" t="s">
-        <v>195</v>
+        <v>340</v>
       </c>
       <c r="E1231">
-        <v>2.006194008995704</v>
+        <v>2.019438228380508</v>
       </c>
       <c r="F1231">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1231">
-        <v>0.003972183881311894</v>
+        <v>0.003856958086670758</v>
       </c>
       <c r="H1231">
-        <v>0.003973805991004296</v>
+        <v>0.003900561771619492</v>
       </c>
       <c r="I1231">
-        <v>0.04162210969240165</v>
+        <v>0.0363963150512665</v>
       </c>
       <c r="J1231">
         <v>0.3603684948733686</v>
       </c>
       <c r="K1231">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="L1231">
-        <v>3.01</v>
+        <v>2.92</v>
       </c>
       <c r="M1231">
-        <v>2.73</v>
+        <v>2.61</v>
       </c>
       <c r="N1231">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="O1231">
         <v>1</v>
@@ -63423,13 +63426,13 @@
     </row>
     <row r="1232" spans="1:16">
       <c r="A1232" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1232" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C1232">
-        <v>2.056194008995704</v>
+        <v>2.047816118688106</v>
       </c>
       <c r="D1232" t="s">
         <v>195</v>
@@ -63441,22 +63444,22 @@
         <v>-1</v>
       </c>
       <c r="G1232">
-        <v>0.004023805991004297</v>
+        <v>0.003972183881311894</v>
       </c>
       <c r="H1232">
         <v>0.003973805991004296</v>
       </c>
       <c r="I1232">
-        <v>0.04999999999999982</v>
+        <v>0.04162210969240165</v>
       </c>
       <c r="J1232">
         <v>0.3603684948733686</v>
       </c>
       <c r="K1232">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="L1232">
-        <v>3.04</v>
+        <v>3.01</v>
       </c>
       <c r="M1232">
         <v>2.73</v>
@@ -63473,96 +63476,96 @@
     </row>
     <row r="1233" spans="1:16">
       <c r="A1233" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B1233" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C1233">
-        <v>2.019112345246391</v>
+        <v>2.056194008995704</v>
       </c>
       <c r="D1233" t="s">
-        <v>339</v>
+        <v>195</v>
       </c>
       <c r="E1233">
-        <v>1.976571566955544</v>
+        <v>2.006194008995704</v>
       </c>
       <c r="F1233">
         <v>-1</v>
       </c>
       <c r="G1233">
-        <v>0.00398088765475361</v>
+        <v>0.004023805991004297</v>
       </c>
       <c r="H1233">
-        <v>0.003923428433044457</v>
+        <v>0.003973805991004296</v>
       </c>
       <c r="I1233">
-        <v>0.04254077829084668</v>
+        <v>0.04999999999999982</v>
       </c>
       <c r="J1233">
-        <v>0.3729610854576461</v>
+        <v>0.3603684948733686</v>
       </c>
       <c r="K1233">
-        <v>2.63</v>
+        <v>2.73</v>
       </c>
       <c r="L1233">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="M1233">
-        <v>2.61</v>
+        <v>2.73</v>
       </c>
       <c r="N1233">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="O1233">
         <v>1</v>
       </c>
       <c r="P1233" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="1234" spans="1:16">
       <c r="A1234" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1234" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="C1234">
-        <v>1.939112345246391</v>
+        <v>2.011653123537238</v>
       </c>
       <c r="D1234" t="s">
-        <v>193</v>
+        <v>339</v>
       </c>
       <c r="E1234">
-        <v>1.994030788664697</v>
+        <v>1.976571566955544</v>
       </c>
       <c r="F1234">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1234">
-        <v>0.003900887654753609</v>
+        <v>0.003988346876462762</v>
       </c>
       <c r="H1234">
-        <v>0.003925969211335303</v>
+        <v>0.003923428433044457</v>
       </c>
       <c r="I1234">
-        <v>0.05491844341830587</v>
+        <v>0.03508155658169398</v>
       </c>
       <c r="J1234">
         <v>0.3729610854576461</v>
       </c>
       <c r="K1234">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="L1234">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="M1234">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="N1234">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="O1234">
         <v>1</v>
@@ -63573,13 +63576,13 @@
     </row>
     <row r="1235" spans="1:16">
       <c r="A1235" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1235" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C1235">
-        <v>1.952841956100968</v>
+        <v>1.939112345246391</v>
       </c>
       <c r="D1235" t="s">
         <v>193</v>
@@ -63591,22 +63594,22 @@
         <v>1</v>
       </c>
       <c r="G1235">
-        <v>0.003907158043899033</v>
+        <v>0.003900887654753609</v>
       </c>
       <c r="H1235">
         <v>0.003925969211335303</v>
       </c>
       <c r="I1235">
-        <v>0.04118883256372907</v>
+        <v>0.05491844341830587</v>
       </c>
       <c r="J1235">
         <v>0.3729610854576461</v>
       </c>
       <c r="K1235">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="L1235">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="M1235">
         <v>2.59</v>
@@ -63623,43 +63626,43 @@
     </row>
     <row r="1236" spans="1:16">
       <c r="A1236" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1236" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C1236">
-        <v>1.95030117781012</v>
+        <v>1.952841956100968</v>
       </c>
       <c r="D1236" t="s">
-        <v>340</v>
+        <v>193</v>
       </c>
       <c r="E1236">
-        <v>1.986571566955544</v>
+        <v>1.994030788664697</v>
       </c>
       <c r="F1236">
         <v>1</v>
       </c>
       <c r="G1236">
-        <v>0.00388969882218988</v>
+        <v>0.003907158043899033</v>
       </c>
       <c r="H1236">
-        <v>0.003933428433044456</v>
+        <v>0.003925969211335303</v>
       </c>
       <c r="I1236">
-        <v>0.03627038914542391</v>
+        <v>0.04118883256372907</v>
       </c>
       <c r="J1236">
         <v>0.3729610854576461</v>
       </c>
       <c r="K1236">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="L1236">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="M1236">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="N1236">
         <v>2.96</v>
@@ -63673,46 +63676,46 @@
     </row>
     <row r="1237" spans="1:16">
       <c r="A1237" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1237" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C1237">
-        <v>2.014193901828085</v>
+        <v>1.95030117781012</v>
       </c>
       <c r="D1237" t="s">
-        <v>195</v>
+        <v>340</v>
       </c>
       <c r="E1237">
-        <v>1.971816236700626</v>
+        <v>1.986571566955544</v>
       </c>
       <c r="F1237">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1237">
-        <v>0.004005806098171915</v>
+        <v>0.00388969882218988</v>
       </c>
       <c r="H1237">
-        <v>0.004008183763299374</v>
+        <v>0.003933428433044456</v>
       </c>
       <c r="I1237">
-        <v>0.04237766512745833</v>
+        <v>0.03627038914542391</v>
       </c>
       <c r="J1237">
         <v>0.3729610854576461</v>
       </c>
       <c r="K1237">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="L1237">
-        <v>3.01</v>
+        <v>2.92</v>
       </c>
       <c r="M1237">
-        <v>2.73</v>
+        <v>2.61</v>
       </c>
       <c r="N1237">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="O1237">
         <v>1</v>
@@ -63723,13 +63726,13 @@
     </row>
     <row r="1238" spans="1:16">
       <c r="A1238" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1238" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C1238">
-        <v>2.021816236700626</v>
+        <v>2.014193901828085</v>
       </c>
       <c r="D1238" t="s">
         <v>195</v>
@@ -63741,22 +63744,22 @@
         <v>-1</v>
       </c>
       <c r="G1238">
-        <v>0.004058183763299373</v>
+        <v>0.004005806098171915</v>
       </c>
       <c r="H1238">
         <v>0.004008183763299374</v>
       </c>
       <c r="I1238">
-        <v>0.05000000000000004</v>
+        <v>0.04237766512745833</v>
       </c>
       <c r="J1238">
         <v>0.3729610854576461</v>
       </c>
       <c r="K1238">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="L1238">
-        <v>3.04</v>
+        <v>3.01</v>
       </c>
       <c r="M1238">
         <v>2.73</v>
@@ -63773,96 +63776,96 @@
     </row>
     <row r="1239" spans="1:16">
       <c r="A1239" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B1239" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C1239">
-        <v>1.972944681153191</v>
+        <v>2.021816236700626</v>
       </c>
       <c r="D1239" t="s">
-        <v>339</v>
+        <v>195</v>
       </c>
       <c r="E1239">
-        <v>1.938447402947106</v>
+        <v>1.971816236700626</v>
       </c>
       <c r="F1239">
         <v>-1</v>
       </c>
       <c r="G1239">
-        <v>0.004027055318846808</v>
+        <v>0.004058183763299373</v>
       </c>
       <c r="H1239">
-        <v>0.003961552597052894</v>
+        <v>0.004008183763299374</v>
       </c>
       <c r="I1239">
-        <v>0.03449727820608572</v>
+        <v>0.05000000000000004</v>
       </c>
       <c r="J1239">
-        <v>0.3875680448478523</v>
+        <v>0.3729610854576461</v>
       </c>
       <c r="K1239">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="L1239">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="M1239">
-        <v>2.61</v>
+        <v>2.73</v>
       </c>
       <c r="N1239">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="O1239">
         <v>1</v>
       </c>
       <c r="P1239" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="1240" spans="1:16">
       <c r="A1240" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1240" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="C1240">
-        <v>1.900696042050148</v>
+        <v>1.972944681153191</v>
       </c>
       <c r="D1240" t="s">
-        <v>193</v>
+        <v>339</v>
       </c>
       <c r="E1240">
-        <v>1.956198763844063</v>
+        <v>1.938447402947106</v>
       </c>
       <c r="F1240">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1240">
-        <v>0.003939303957949852</v>
+        <v>0.004027055318846808</v>
       </c>
       <c r="H1240">
-        <v>0.003963801236155938</v>
+        <v>0.003961552597052894</v>
       </c>
       <c r="I1240">
-        <v>0.05550272179391413</v>
+        <v>0.03449727820608572</v>
       </c>
       <c r="J1240">
         <v>0.3875680448478523</v>
       </c>
       <c r="K1240">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="L1240">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="M1240">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="N1240">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="O1240">
         <v>1</v>
@@ -63873,13 +63876,13 @@
     </row>
     <row r="1241" spans="1:16">
       <c r="A1241" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1241" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C1241">
-        <v>1.914571722498627</v>
+        <v>1.900696042050148</v>
       </c>
       <c r="D1241" t="s">
         <v>193</v>
@@ -63891,22 +63894,22 @@
         <v>1</v>
       </c>
       <c r="G1241">
-        <v>0.003945428277501373</v>
+        <v>0.003939303957949852</v>
       </c>
       <c r="H1241">
         <v>0.003963801236155938</v>
       </c>
       <c r="I1241">
-        <v>0.04162704134543538</v>
+        <v>0.05550272179391413</v>
       </c>
       <c r="J1241">
         <v>0.3875680448478523</v>
       </c>
       <c r="K1241">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="L1241">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="M1241">
         <v>2.59</v>
@@ -63923,43 +63926,43 @@
     </row>
     <row r="1242" spans="1:16">
       <c r="A1242" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1242" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C1242">
-        <v>1.912323083395584</v>
+        <v>1.914571722498627</v>
       </c>
       <c r="D1242" t="s">
-        <v>340</v>
+        <v>193</v>
       </c>
       <c r="E1242">
-        <v>1.948447402947106</v>
+        <v>1.956198763844063</v>
       </c>
       <c r="F1242">
         <v>1</v>
       </c>
       <c r="G1242">
-        <v>0.003927676916604416</v>
+        <v>0.003945428277501373</v>
       </c>
       <c r="H1242">
-        <v>0.003971552597052895</v>
+        <v>0.003963801236155938</v>
       </c>
       <c r="I1242">
-        <v>0.03612431955152151</v>
+        <v>0.04162704134543538</v>
       </c>
       <c r="J1242">
         <v>0.3875680448478523</v>
       </c>
       <c r="K1242">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="L1242">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="M1242">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="N1242">
         <v>2.96</v>
@@ -63973,46 +63976,46 @@
     </row>
     <row r="1243" spans="1:16">
       <c r="A1243" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1243" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C1243">
-        <v>1.975193320256234</v>
+        <v>1.912323083395584</v>
       </c>
       <c r="D1243" t="s">
-        <v>195</v>
+        <v>340</v>
       </c>
       <c r="E1243">
-        <v>1.931939237565363</v>
+        <v>1.948447402947106</v>
       </c>
       <c r="F1243">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1243">
-        <v>0.004044806679743765</v>
+        <v>0.003927676916604416</v>
       </c>
       <c r="H1243">
-        <v>0.004048060762434637</v>
+        <v>0.003971552597052895</v>
       </c>
       <c r="I1243">
-        <v>0.04325408269087072</v>
+        <v>0.03612431955152151</v>
       </c>
       <c r="J1243">
         <v>0.3875680448478523</v>
       </c>
       <c r="K1243">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="L1243">
-        <v>3.01</v>
+        <v>2.92</v>
       </c>
       <c r="M1243">
-        <v>2.73</v>
+        <v>2.61</v>
       </c>
       <c r="N1243">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="O1243">
         <v>1</v>
@@ -64023,13 +64026,13 @@
     </row>
     <row r="1244" spans="1:16">
       <c r="A1244" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1244" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C1244">
-        <v>1.981939237565363</v>
+        <v>1.975193320256234</v>
       </c>
       <c r="D1244" t="s">
         <v>195</v>
@@ -64041,22 +64044,22 @@
         <v>-1</v>
       </c>
       <c r="G1244">
-        <v>0.004098060762434637</v>
+        <v>0.004044806679743765</v>
       </c>
       <c r="H1244">
         <v>0.004048060762434637</v>
       </c>
       <c r="I1244">
-        <v>0.04999999999999982</v>
+        <v>0.04325408269087072</v>
       </c>
       <c r="J1244">
         <v>0.3875680448478523</v>
       </c>
       <c r="K1244">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="L1244">
-        <v>3.04</v>
+        <v>3.01</v>
       </c>
       <c r="M1244">
         <v>2.73</v>
@@ -64073,96 +64076,96 @@
     </row>
     <row r="1245" spans="1:16">
       <c r="A1245" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B1245" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C1245">
-        <v>1.935690447928652</v>
+        <v>1.981939237565363</v>
       </c>
       <c r="D1245" t="s">
-        <v>339</v>
+        <v>195</v>
       </c>
       <c r="E1245">
-        <v>1.901755497771239</v>
+        <v>1.931939237565363</v>
       </c>
       <c r="F1245">
         <v>-1</v>
       </c>
       <c r="G1245">
-        <v>0.004064309552071348</v>
+        <v>0.004098060762434637</v>
       </c>
       <c r="H1245">
-        <v>0.003998244502228762</v>
+        <v>0.004048060762434637</v>
       </c>
       <c r="I1245">
-        <v>0.03393495015741332</v>
+        <v>0.04999999999999982</v>
       </c>
       <c r="J1245">
-        <v>0.4016262460646597</v>
+        <v>0.3875680448478523</v>
       </c>
       <c r="K1245">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="L1245">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="M1245">
-        <v>2.61</v>
+        <v>2.73</v>
       </c>
       <c r="N1245">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="O1245">
         <v>1</v>
       </c>
       <c r="P1245" t="s">
-        <v>337</v>
+        <v>473</v>
       </c>
     </row>
     <row r="1246" spans="1:16">
       <c r="A1246" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1246" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="C1246">
-        <v>1.863722972849945</v>
+        <v>1.935690447928652</v>
       </c>
       <c r="D1246" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E1246">
-        <v>1.907739235310592</v>
+        <v>1.901755497771239</v>
       </c>
       <c r="F1246">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1246">
-        <v>0.003976277027150055</v>
+        <v>0.004064309552071348</v>
       </c>
       <c r="H1246">
-        <v>0.004012260764689408</v>
+        <v>0.003998244502228762</v>
       </c>
       <c r="I1246">
-        <v>0.0440162624606466</v>
+        <v>0.03393495015741332</v>
       </c>
       <c r="J1246">
         <v>0.4016262460646597</v>
       </c>
       <c r="K1246">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="L1246">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="M1246">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="N1246">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="O1246">
         <v>1</v>
@@ -64173,13 +64176,13 @@
     </row>
     <row r="1247" spans="1:16">
       <c r="A1247" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1247" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C1247">
-        <v>1.877739235310592</v>
+        <v>1.863722972849945</v>
       </c>
       <c r="D1247" t="s">
         <v>341</v>
@@ -64191,22 +64194,22 @@
         <v>1</v>
       </c>
       <c r="G1247">
-        <v>0.003982260764689409</v>
+        <v>0.003976277027150055</v>
       </c>
       <c r="H1247">
         <v>0.004012260764689408</v>
       </c>
       <c r="I1247">
-        <v>0.0299999999999998</v>
+        <v>0.0440162624606466</v>
       </c>
       <c r="J1247">
         <v>0.4016262460646597</v>
       </c>
       <c r="K1247">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="L1247">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="M1247">
         <v>2.62</v>
@@ -64223,43 +64226,43 @@
     </row>
     <row r="1248" spans="1:16">
       <c r="A1248" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1248" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C1248">
-        <v>1.875771760231885</v>
+        <v>1.877739235310592</v>
       </c>
       <c r="D1248" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E1248">
-        <v>1.911755497771238</v>
+        <v>1.907739235310592</v>
       </c>
       <c r="F1248">
         <v>1</v>
       </c>
       <c r="G1248">
-        <v>0.003964228239768115</v>
+        <v>0.003982260764689409</v>
       </c>
       <c r="H1248">
-        <v>0.004008244502228761</v>
+        <v>0.004012260764689408</v>
       </c>
       <c r="I1248">
-        <v>0.03598373753935369</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="J1248">
         <v>0.4016262460646597</v>
       </c>
       <c r="K1248">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="L1248">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="M1248">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="N1248">
         <v>2.96</v>
@@ -64273,46 +64276,46 @@
     </row>
     <row r="1249" spans="1:16">
       <c r="A1249" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1249" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C1249">
-        <v>1.937657923007359</v>
+        <v>1.875771760231885</v>
       </c>
       <c r="D1249" t="s">
-        <v>195</v>
+        <v>340</v>
       </c>
       <c r="E1249">
-        <v>1.893560348243479</v>
+        <v>1.911755497771238</v>
       </c>
       <c r="F1249">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1249">
-        <v>0.004082342076992642</v>
+        <v>0.003964228239768115</v>
       </c>
       <c r="H1249">
-        <v>0.004086439651756521</v>
+        <v>0.004008244502228761</v>
       </c>
       <c r="I1249">
-        <v>0.04409757476387921</v>
+        <v>0.03598373753935369</v>
       </c>
       <c r="J1249">
         <v>0.4016262460646597</v>
       </c>
       <c r="K1249">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="L1249">
-        <v>3.01</v>
+        <v>2.92</v>
       </c>
       <c r="M1249">
-        <v>2.73</v>
+        <v>2.61</v>
       </c>
       <c r="N1249">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="O1249">
         <v>1</v>
@@ -64323,13 +64326,13 @@
     </row>
     <row r="1250" spans="1:16">
       <c r="A1250" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1250" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C1250">
-        <v>1.943560348243479</v>
+        <v>1.937657923007359</v>
       </c>
       <c r="D1250" t="s">
         <v>195</v>
@@ -64341,22 +64344,22 @@
         <v>-1</v>
       </c>
       <c r="G1250">
-        <v>0.004136439651756521</v>
+        <v>0.004082342076992642</v>
       </c>
       <c r="H1250">
         <v>0.004086439651756521</v>
       </c>
       <c r="I1250">
-        <v>0.04999999999999982</v>
+        <v>0.04409757476387921</v>
       </c>
       <c r="J1250">
         <v>0.4016262460646597</v>
       </c>
       <c r="K1250">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="L1250">
-        <v>3.04</v>
+        <v>3.01</v>
       </c>
       <c r="M1250">
         <v>2.73</v>
@@ -64373,96 +64376,96 @@
     </row>
     <row r="1251" spans="1:16">
       <c r="A1251" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B1251" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C1251">
-        <v>1.88677507248715</v>
+        <v>1.943560348243479</v>
       </c>
       <c r="D1251" t="s">
-        <v>339</v>
+        <v>195</v>
       </c>
       <c r="E1251">
-        <v>1.85357846761942</v>
+        <v>1.893560348243479</v>
       </c>
       <c r="F1251">
         <v>-1</v>
       </c>
       <c r="G1251">
-        <v>0.00411322492751285</v>
+        <v>0.004136439651756521</v>
       </c>
       <c r="H1251">
-        <v>0.004046421532380581</v>
+        <v>0.004086439651756521</v>
       </c>
       <c r="I1251">
-        <v>0.03319660486773035</v>
+        <v>0.04999999999999982</v>
       </c>
       <c r="J1251">
-        <v>0.4200848783067358</v>
+        <v>0.4016262460646597</v>
       </c>
       <c r="K1251">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="L1251">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="M1251">
-        <v>2.61</v>
+        <v>2.73</v>
       </c>
       <c r="N1251">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="O1251">
         <v>1</v>
       </c>
       <c r="P1251" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="1252" spans="1:16">
       <c r="A1252" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1252" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="C1252">
-        <v>1.815176770053285</v>
+        <v>1.88677507248715</v>
       </c>
       <c r="D1252" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E1252">
-        <v>1.859377618836352</v>
+        <v>1.85357846761942</v>
       </c>
       <c r="F1252">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1252">
-        <v>0.004024823229946716</v>
+        <v>0.00411322492751285</v>
       </c>
       <c r="H1252">
-        <v>0.004060622381163647</v>
+        <v>0.004046421532380581</v>
       </c>
       <c r="I1252">
-        <v>0.0442008487830674</v>
+        <v>0.03319660486773035</v>
       </c>
       <c r="J1252">
         <v>0.4200848783067358</v>
       </c>
       <c r="K1252">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="L1252">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="M1252">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="N1252">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="O1252">
         <v>1</v>
@@ -64473,13 +64476,13 @@
     </row>
     <row r="1253" spans="1:16">
       <c r="A1253" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1253" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="C1253">
-        <v>1.831980165185554</v>
+        <v>1.815176770053285</v>
       </c>
       <c r="D1253" t="s">
         <v>341</v>
@@ -64491,19 +64494,19 @@
         <v>1</v>
       </c>
       <c r="G1253">
-        <v>0.004008019834814446</v>
+        <v>0.004024823229946716</v>
       </c>
       <c r="H1253">
         <v>0.004060622381163647</v>
       </c>
       <c r="I1253">
-        <v>0.02739745365079793</v>
+        <v>0.0442008487830674</v>
       </c>
       <c r="J1253">
         <v>0.4200848783067358</v>
       </c>
       <c r="K1253">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="L1253">
         <v>2.92</v>
@@ -64523,13 +64526,13 @@
     </row>
     <row r="1254" spans="1:16">
       <c r="A1254" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1254" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C1254">
-        <v>1.829377618836352</v>
+        <v>1.831980165185554</v>
       </c>
       <c r="D1254" t="s">
         <v>341</v>
@@ -64541,22 +64544,22 @@
         <v>1</v>
       </c>
       <c r="G1254">
-        <v>0.004030622381163648</v>
+        <v>0.004008019834814446</v>
       </c>
       <c r="H1254">
         <v>0.004060622381163647</v>
       </c>
       <c r="I1254">
-        <v>0.0299999999999998</v>
+        <v>0.02739745365079793</v>
       </c>
       <c r="J1254">
         <v>0.4200848783067358</v>
       </c>
       <c r="K1254">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="L1254">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="M1254">
         <v>2.62</v>
@@ -64573,43 +64576,43 @@
     </row>
     <row r="1255" spans="1:16">
       <c r="A1255" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1255" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C1255">
-        <v>1.827779316402487</v>
+        <v>1.829377618836352</v>
       </c>
       <c r="D1255" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E1255">
-        <v>1.86357846761942</v>
+        <v>1.859377618836352</v>
       </c>
       <c r="F1255">
         <v>1</v>
       </c>
       <c r="G1255">
-        <v>0.004012220683597513</v>
+        <v>0.004030622381163648</v>
       </c>
       <c r="H1255">
-        <v>0.004056421532380581</v>
+        <v>0.004060622381163647</v>
       </c>
       <c r="I1255">
-        <v>0.03579915121693267</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="J1255">
         <v>0.4200848783067358</v>
       </c>
       <c r="K1255">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="L1255">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="M1255">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="N1255">
         <v>2.96</v>
@@ -64623,46 +64626,46 @@
     </row>
     <row r="1256" spans="1:16">
       <c r="A1256" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1256" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C1256">
-        <v>1.888373374921015</v>
+        <v>1.827779316402487</v>
       </c>
       <c r="D1256" t="s">
-        <v>195</v>
+        <v>340</v>
       </c>
       <c r="E1256">
-        <v>1.843168282222611</v>
+        <v>1.86357846761942</v>
       </c>
       <c r="F1256">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1256">
-        <v>0.004131626625078985</v>
+        <v>0.004012220683597513</v>
       </c>
       <c r="H1256">
-        <v>0.004136831717777388</v>
+        <v>0.004056421532380581</v>
       </c>
       <c r="I1256">
-        <v>0.04520509269840378</v>
+        <v>0.03579915121693267</v>
       </c>
       <c r="J1256">
         <v>0.4200848783067358</v>
       </c>
       <c r="K1256">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="L1256">
-        <v>3.01</v>
+        <v>2.92</v>
       </c>
       <c r="M1256">
-        <v>2.73</v>
+        <v>2.61</v>
       </c>
       <c r="N1256">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="O1256">
         <v>1</v>
@@ -64673,13 +64676,13 @@
     </row>
     <row r="1257" spans="1:16">
       <c r="A1257" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1257" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C1257">
-        <v>1.893168282222611</v>
+        <v>1.888373374921015</v>
       </c>
       <c r="D1257" t="s">
         <v>195</v>
@@ -64691,22 +64694,22 @@
         <v>-1</v>
       </c>
       <c r="G1257">
-        <v>0.004186831717777389</v>
+        <v>0.004131626625078985</v>
       </c>
       <c r="H1257">
         <v>0.004136831717777388</v>
       </c>
       <c r="I1257">
-        <v>0.04999999999999982</v>
+        <v>0.04520509269840378</v>
       </c>
       <c r="J1257">
         <v>0.4200848783067358</v>
       </c>
       <c r="K1257">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="L1257">
-        <v>3.04</v>
+        <v>3.01</v>
       </c>
       <c r="M1257">
         <v>2.73</v>
@@ -64723,96 +64726,96 @@
     </row>
     <row r="1258" spans="1:16">
       <c r="A1258" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B1258" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C1258">
-        <v>1.837587821290496</v>
+        <v>1.893168282222611</v>
       </c>
       <c r="D1258" t="s">
-        <v>339</v>
+        <v>195</v>
       </c>
       <c r="E1258">
-        <v>1.805133665497433</v>
+        <v>1.843168282222611</v>
       </c>
       <c r="F1258">
         <v>-1</v>
       </c>
       <c r="G1258">
-        <v>0.004162412178709504</v>
+        <v>0.004186831717777389</v>
       </c>
       <c r="H1258">
-        <v>0.004094866334502568</v>
+        <v>0.004136831717777388</v>
       </c>
       <c r="I1258">
-        <v>0.03245415579306377</v>
+        <v>0.04999999999999982</v>
       </c>
       <c r="J1258">
-        <v>0.4386461051733976</v>
+        <v>0.4200848783067358</v>
       </c>
       <c r="K1258">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="L1258">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="M1258">
-        <v>2.61</v>
+        <v>2.73</v>
       </c>
       <c r="N1258">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="O1258">
         <v>1</v>
       </c>
       <c r="P1258" t="s">
-        <v>474</v>
+        <v>338</v>
       </c>
     </row>
     <row r="1259" spans="1:16">
       <c r="A1259" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1259" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="C1259">
-        <v>1.766360743393964</v>
+        <v>1.837587821290496</v>
       </c>
       <c r="D1259" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E1259">
-        <v>1.810747204445698</v>
+        <v>1.805133665497433</v>
       </c>
       <c r="F1259">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1259">
-        <v>0.004073639256606036</v>
+        <v>0.004162412178709504</v>
       </c>
       <c r="H1259">
-        <v>0.004109252795554301</v>
+        <v>0.004094866334502568</v>
       </c>
       <c r="I1259">
-        <v>0.04438646105173394</v>
+        <v>0.03245415579306377</v>
       </c>
       <c r="J1259">
         <v>0.4386461051733976</v>
       </c>
       <c r="K1259">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="L1259">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="M1259">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="N1259">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="O1259">
         <v>1</v>
@@ -64823,13 +64826,13 @@
     </row>
     <row r="1260" spans="1:16">
       <c r="A1260" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1260" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="C1260">
-        <v>1.7839065876009</v>
+        <v>1.766360743393964</v>
       </c>
       <c r="D1260" t="s">
         <v>341</v>
@@ -64841,19 +64844,19 @@
         <v>1</v>
       </c>
       <c r="G1260">
-        <v>0.004056093412399099</v>
+        <v>0.004073639256606036</v>
       </c>
       <c r="H1260">
         <v>0.004109252795554301</v>
       </c>
       <c r="I1260">
-        <v>0.0268406168447981</v>
+        <v>0.04438646105173394</v>
       </c>
       <c r="J1260">
         <v>0.4386461051733976</v>
       </c>
       <c r="K1260">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="L1260">
         <v>2.92</v>
@@ -64873,13 +64876,13 @@
     </row>
     <row r="1261" spans="1:16">
       <c r="A1261" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1261" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C1261">
-        <v>1.780747204445698</v>
+        <v>1.7839065876009</v>
       </c>
       <c r="D1261" t="s">
         <v>341</v>
@@ -64891,22 +64894,22 @@
         <v>1</v>
       </c>
       <c r="G1261">
-        <v>0.004079252795554302</v>
+        <v>0.004056093412399099</v>
       </c>
       <c r="H1261">
         <v>0.004109252795554301</v>
       </c>
       <c r="I1261">
-        <v>0.0299999999999998</v>
+        <v>0.0268406168447981</v>
       </c>
       <c r="J1261">
         <v>0.4386461051733976</v>
       </c>
       <c r="K1261">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="L1261">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="M1261">
         <v>2.62</v>
@@ -64923,43 +64926,43 @@
     </row>
     <row r="1262" spans="1:16">
       <c r="A1262" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1262" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C1262">
-        <v>1.779520126549166</v>
+        <v>1.780747204445698</v>
       </c>
       <c r="D1262" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E1262">
-        <v>1.815133665497432</v>
+        <v>1.810747204445698</v>
       </c>
       <c r="F1262">
         <v>1</v>
       </c>
       <c r="G1262">
-        <v>0.004060479873450834</v>
+        <v>0.004079252795554302</v>
       </c>
       <c r="H1262">
-        <v>0.004104866334502568</v>
+        <v>0.004109252795554301</v>
       </c>
       <c r="I1262">
-        <v>0.03561353894826613</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="J1262">
         <v>0.4386461051733976</v>
       </c>
       <c r="K1262">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="L1262">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="M1262">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="N1262">
         <v>2.96</v>
@@ -64973,46 +64976,46 @@
     </row>
     <row r="1263" spans="1:16">
       <c r="A1263" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1263" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C1263">
-        <v>1.838814899187028</v>
+        <v>1.779520126549166</v>
       </c>
       <c r="D1263" t="s">
-        <v>195</v>
+        <v>340</v>
       </c>
       <c r="E1263">
-        <v>1.792496132876625</v>
+        <v>1.815133665497432</v>
       </c>
       <c r="F1263">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1263">
-        <v>0.004181185100812971</v>
+        <v>0.004060479873450834</v>
       </c>
       <c r="H1263">
-        <v>0.004187503867123375</v>
+        <v>0.004104866334502568</v>
       </c>
       <c r="I1263">
-        <v>0.04631876631040344</v>
+        <v>0.03561353894826613</v>
       </c>
       <c r="J1263">
         <v>0.4386461051733976</v>
       </c>
       <c r="K1263">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="L1263">
-        <v>3.01</v>
+        <v>2.92</v>
       </c>
       <c r="M1263">
-        <v>2.73</v>
+        <v>2.61</v>
       </c>
       <c r="N1263">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="O1263">
         <v>1</v>
@@ -65023,13 +65026,13 @@
     </row>
     <row r="1264" spans="1:16">
       <c r="A1264" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1264" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C1264">
-        <v>1.842496132876625</v>
+        <v>1.838814899187028</v>
       </c>
       <c r="D1264" t="s">
         <v>195</v>
@@ -65041,22 +65044,22 @@
         <v>-1</v>
       </c>
       <c r="G1264">
-        <v>0.004237503867123375</v>
+        <v>0.004181185100812971</v>
       </c>
       <c r="H1264">
         <v>0.004187503867123375</v>
       </c>
       <c r="I1264">
-        <v>0.04999999999999982</v>
+        <v>0.04631876631040344</v>
       </c>
       <c r="J1264">
         <v>0.4386461051733976</v>
       </c>
       <c r="K1264">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="L1264">
-        <v>3.04</v>
+        <v>3.01</v>
       </c>
       <c r="M1264">
         <v>2.73</v>
@@ -65073,96 +65076,96 @@
     </row>
     <row r="1265" spans="1:16">
       <c r="A1265" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B1265" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C1265">
-        <v>1.780823177477708</v>
+        <v>1.842496132876625</v>
       </c>
       <c r="D1265" t="s">
-        <v>339</v>
+        <v>195</v>
       </c>
       <c r="E1265">
-        <v>1.749225846496913</v>
+        <v>1.792496132876625</v>
       </c>
       <c r="F1265">
         <v>-1</v>
       </c>
       <c r="G1265">
-        <v>0.004219176822522292</v>
+        <v>0.004237503867123375</v>
       </c>
       <c r="H1265">
-        <v>0.004150774153503088</v>
+        <v>0.004187503867123375</v>
       </c>
       <c r="I1265">
-        <v>0.03159733098079531</v>
+        <v>0.04999999999999982</v>
       </c>
       <c r="J1265">
-        <v>0.4600667254801102</v>
+        <v>0.4386461051733976</v>
       </c>
       <c r="K1265">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="L1265">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="M1265">
-        <v>2.61</v>
+        <v>2.73</v>
       </c>
       <c r="N1265">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="O1265">
         <v>1</v>
       </c>
       <c r="P1265" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="1266" spans="1:16">
       <c r="A1266" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1266" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="C1266">
-        <v>1.71002451198731</v>
+        <v>1.780823177477708</v>
       </c>
       <c r="D1266" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E1266">
-        <v>1.754625179242111</v>
+        <v>1.749225846496913</v>
       </c>
       <c r="F1266">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1266">
-        <v>0.004129975488012689</v>
+        <v>0.004219176822522292</v>
       </c>
       <c r="H1266">
-        <v>0.004165374820757889</v>
+        <v>0.004150774153503088</v>
       </c>
       <c r="I1266">
-        <v>0.04460066725480094</v>
+        <v>0.03159733098079531</v>
       </c>
       <c r="J1266">
         <v>0.4600667254801102</v>
       </c>
       <c r="K1266">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="L1266">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="M1266">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="N1266">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="O1266">
         <v>1</v>
@@ -65173,13 +65176,13 @@
     </row>
     <row r="1267" spans="1:16">
       <c r="A1267" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1267" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="C1267">
-        <v>1.728427181006514</v>
+        <v>1.71002451198731</v>
       </c>
       <c r="D1267" t="s">
         <v>341</v>
@@ -65191,19 +65194,19 @@
         <v>1</v>
       </c>
       <c r="G1267">
-        <v>0.004111572818993485</v>
+        <v>0.004129975488012689</v>
       </c>
       <c r="H1267">
         <v>0.004165374820757889</v>
       </c>
       <c r="I1267">
-        <v>0.02619799823559665</v>
+        <v>0.04460066725480094</v>
       </c>
       <c r="J1267">
         <v>0.4600667254801102</v>
       </c>
       <c r="K1267">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="L1267">
         <v>2.92</v>
@@ -65223,13 +65226,13 @@
     </row>
     <row r="1268" spans="1:16">
       <c r="A1268" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1268" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C1268">
-        <v>1.724625179242111</v>
+        <v>1.728427181006514</v>
       </c>
       <c r="D1268" t="s">
         <v>341</v>
@@ -65241,22 +65244,22 @@
         <v>1</v>
       </c>
       <c r="G1268">
-        <v>0.004135374820757889</v>
+        <v>0.004111572818993485</v>
       </c>
       <c r="H1268">
         <v>0.004165374820757889</v>
       </c>
       <c r="I1268">
-        <v>0.0299999999999998</v>
+        <v>0.02619799823559665</v>
       </c>
       <c r="J1268">
         <v>0.4600667254801102</v>
       </c>
       <c r="K1268">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="L1268">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="M1268">
         <v>2.62</v>
@@ -65273,43 +65276,43 @@
     </row>
     <row r="1269" spans="1:16">
       <c r="A1269" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1269" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C1269">
-        <v>1.723826513751713</v>
+        <v>1.724625179242111</v>
       </c>
       <c r="D1269" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E1269">
-        <v>1.759225846496912</v>
+        <v>1.754625179242111</v>
       </c>
       <c r="F1269">
         <v>1</v>
       </c>
       <c r="G1269">
-        <v>0.004116173486248287</v>
+        <v>0.004135374820757889</v>
       </c>
       <c r="H1269">
-        <v>0.004160774153503088</v>
+        <v>0.004165374820757889</v>
       </c>
       <c r="I1269">
-        <v>0.03539933274519913</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="J1269">
         <v>0.4600667254801102</v>
       </c>
       <c r="K1269">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="L1269">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="M1269">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="N1269">
         <v>2.96</v>
@@ -65323,13 +65326,13 @@
     </row>
     <row r="1270" spans="1:16">
       <c r="A1270" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1270" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C1270">
-        <v>1.719225846496912</v>
+        <v>1.723826513751713</v>
       </c>
       <c r="D1270" t="s">
         <v>340</v>
@@ -65341,19 +65344,19 @@
         <v>1</v>
       </c>
       <c r="G1270">
-        <v>0.004120774153503088</v>
+        <v>0.004116173486248287</v>
       </c>
       <c r="H1270">
         <v>0.004160774153503088</v>
       </c>
       <c r="I1270">
-        <v>0.04000000000000004</v>
+        <v>0.03539933274519913</v>
       </c>
       <c r="J1270">
         <v>0.4600667254801102</v>
       </c>
       <c r="K1270">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="L1270">
         <v>2.92</v>
@@ -65373,46 +65376,46 @@
     </row>
     <row r="1271" spans="1:16">
       <c r="A1271" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1271" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C1271">
-        <v>1.781621842968105</v>
+        <v>1.719225846496912</v>
       </c>
       <c r="D1271" t="s">
-        <v>195</v>
+        <v>340</v>
       </c>
       <c r="E1271">
-        <v>1.734017839439299</v>
+        <v>1.759225846496912</v>
       </c>
       <c r="F1271">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1271">
-        <v>0.004238378157031895</v>
+        <v>0.004120774153503088</v>
       </c>
       <c r="H1271">
-        <v>0.004245982160560702</v>
+        <v>0.004160774153503088</v>
       </c>
       <c r="I1271">
-        <v>0.04760400352880612</v>
+        <v>0.04000000000000004</v>
       </c>
       <c r="J1271">
         <v>0.4600667254801102</v>
       </c>
       <c r="K1271">
-        <v>2.67</v>
+        <v>2.61</v>
       </c>
       <c r="L1271">
-        <v>3.01</v>
+        <v>2.92</v>
       </c>
       <c r="M1271">
-        <v>2.73</v>
+        <v>2.61</v>
       </c>
       <c r="N1271">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="O1271">
         <v>1</v>
@@ -65423,13 +65426,13 @@
     </row>
     <row r="1272" spans="1:16">
       <c r="A1272" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1272" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C1272">
-        <v>1.784017839439299</v>
+        <v>1.781621842968105</v>
       </c>
       <c r="D1272" t="s">
         <v>195</v>
@@ -65441,22 +65444,22 @@
         <v>-1</v>
       </c>
       <c r="G1272">
-        <v>0.004295982160560701</v>
+        <v>0.004238378157031895</v>
       </c>
       <c r="H1272">
         <v>0.004245982160560702</v>
       </c>
       <c r="I1272">
-        <v>0.04999999999999982</v>
+        <v>0.04760400352880612</v>
       </c>
       <c r="J1272">
         <v>0.4600667254801102</v>
       </c>
       <c r="K1272">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="L1272">
-        <v>3.04</v>
+        <v>3.01</v>
       </c>
       <c r="M1272">
         <v>2.73</v>
@@ -65473,46 +65476,46 @@
     </row>
     <row r="1273" spans="1:16">
       <c r="A1273" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1273" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C1273">
-        <v>1.7286185066941</v>
+        <v>1.784017839439299</v>
       </c>
       <c r="D1273" t="s">
-        <v>342</v>
+        <v>195</v>
       </c>
       <c r="E1273">
-        <v>1.744625179242111</v>
+        <v>1.734017839439299</v>
       </c>
       <c r="F1273">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1273">
-        <v>0.0042313814933059</v>
+        <v>0.004295982160560701</v>
       </c>
       <c r="H1273">
-        <v>0.004155374820757889</v>
+        <v>0.004245982160560702</v>
       </c>
       <c r="I1273">
-        <v>0.01600667254801125</v>
+        <v>0.04999999999999982</v>
       </c>
       <c r="J1273">
         <v>0.4600667254801102</v>
       </c>
       <c r="K1273">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="L1273">
-        <v>2.98</v>
+        <v>3.04</v>
       </c>
       <c r="M1273">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="N1273">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="O1273">
         <v>1</v>
@@ -65523,96 +65526,96 @@
     </row>
     <row r="1274" spans="1:16">
       <c r="A1274" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B1274" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C1274">
-        <v>1.738072100680357</v>
+        <v>1.7286185066941</v>
       </c>
       <c r="D1274" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="E1274">
-        <v>1.707120068971975</v>
+        <v>1.740823177477708</v>
       </c>
       <c r="F1274">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1274">
-        <v>0.004261927899319643</v>
+        <v>0.0042313814933059</v>
       </c>
       <c r="H1274">
-        <v>0.004192879931028026</v>
+        <v>0.004179176822522292</v>
       </c>
       <c r="I1274">
-        <v>0.03095203170838245</v>
+        <v>0.01220467078360787</v>
       </c>
       <c r="J1274">
-        <v>0.4761992072904313</v>
+        <v>0.4600667254801102</v>
       </c>
       <c r="K1274">
+        <v>2.72</v>
+      </c>
+      <c r="L1274">
+        <v>2.98</v>
+      </c>
+      <c r="M1274">
         <v>2.65</v>
       </c>
-      <c r="L1274">
-        <v>3</v>
-      </c>
-      <c r="M1274">
-        <v>2.61</v>
-      </c>
       <c r="N1274">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="O1274">
         <v>1</v>
       </c>
       <c r="P1274" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="1275" spans="1:16">
       <c r="A1275" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1275" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="C1275">
-        <v>1.667596084826166</v>
+        <v>1.738072100680357</v>
       </c>
       <c r="D1275" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E1275">
-        <v>1.71235807689907</v>
+        <v>1.707120068971975</v>
       </c>
       <c r="F1275">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1275">
-        <v>0.004172403915173835</v>
+        <v>0.004261927899319643</v>
       </c>
       <c r="H1275">
-        <v>0.00420764192310093</v>
+        <v>0.004192879931028026</v>
       </c>
       <c r="I1275">
-        <v>0.0447619920729041</v>
+        <v>0.03095203170838245</v>
       </c>
       <c r="J1275">
         <v>0.4761992072904313</v>
       </c>
       <c r="K1275">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="L1275">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="M1275">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="N1275">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="O1275">
         <v>1</v>
@@ -65623,13 +65626,13 @@
     </row>
     <row r="1276" spans="1:16">
       <c r="A1276" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1276" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C1276">
-        <v>1.68235807689907</v>
+        <v>1.667596084826166</v>
       </c>
       <c r="D1276" t="s">
         <v>341</v>
@@ -65641,22 +65644,22 @@
         <v>1</v>
       </c>
       <c r="G1276">
-        <v>0.00417764192310093</v>
+        <v>0.004172403915173835</v>
       </c>
       <c r="H1276">
         <v>0.00420764192310093</v>
       </c>
       <c r="I1276">
-        <v>0.0299999999999998</v>
+        <v>0.0447619920729041</v>
       </c>
       <c r="J1276">
         <v>0.4761992072904313</v>
       </c>
       <c r="K1276">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="L1276">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="M1276">
         <v>2.62</v>
@@ -65673,43 +65676,43 @@
     </row>
     <row r="1277" spans="1:16">
       <c r="A1277" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1277" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C1277">
-        <v>1.681882061044879</v>
+        <v>1.68235807689907</v>
       </c>
       <c r="D1277" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E1277">
-        <v>1.717120068971974</v>
+        <v>1.71235807689907</v>
       </c>
       <c r="F1277">
         <v>1</v>
       </c>
       <c r="G1277">
-        <v>0.004158117938955121</v>
+        <v>0.00417764192310093</v>
       </c>
       <c r="H1277">
-        <v>0.004202879931028026</v>
+        <v>0.00420764192310093</v>
       </c>
       <c r="I1277">
-        <v>0.03523800792709575</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="J1277">
         <v>0.4761992072904313</v>
       </c>
       <c r="K1277">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="L1277">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="M1277">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="N1277">
         <v>2.96</v>
@@ -65723,13 +65726,13 @@
     </row>
     <row r="1278" spans="1:16">
       <c r="A1278" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1278" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C1278">
-        <v>1.677120068971974</v>
+        <v>1.681882061044879</v>
       </c>
       <c r="D1278" t="s">
         <v>340</v>
@@ -65741,19 +65744,19 @@
         <v>1</v>
       </c>
       <c r="G1278">
-        <v>0.004162879931028026</v>
+        <v>0.004158117938955121</v>
       </c>
       <c r="H1278">
         <v>0.004202879931028026</v>
       </c>
       <c r="I1278">
-        <v>0.04000000000000004</v>
+        <v>0.03523800792709575</v>
       </c>
       <c r="J1278">
         <v>0.4761992072904313</v>
       </c>
       <c r="K1278">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="L1278">
         <v>2.92</v>
@@ -65773,46 +65776,46 @@
     </row>
     <row r="1279" spans="1:16">
       <c r="A1279" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1279" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C1279">
-        <v>1.738548116534548</v>
+        <v>1.677120068971974</v>
       </c>
       <c r="D1279" t="s">
-        <v>195</v>
+        <v>340</v>
       </c>
       <c r="E1279">
-        <v>1.689976164097123</v>
+        <v>1.717120068971974</v>
       </c>
       <c r="F1279">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1279">
-        <v>0.004281451883465451</v>
+        <v>0.004162879931028026</v>
       </c>
       <c r="H1279">
-        <v>0.004290023835902878</v>
+        <v>0.004202879931028026</v>
       </c>
       <c r="I1279">
-        <v>0.04857195243742551</v>
+        <v>0.04000000000000004</v>
       </c>
       <c r="J1279">
         <v>0.4761992072904313</v>
       </c>
       <c r="K1279">
-        <v>2.67</v>
+        <v>2.61</v>
       </c>
       <c r="L1279">
-        <v>3.01</v>
+        <v>2.92</v>
       </c>
       <c r="M1279">
-        <v>2.73</v>
+        <v>2.61</v>
       </c>
       <c r="N1279">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="O1279">
         <v>1</v>
@@ -65823,13 +65826,13 @@
     </row>
     <row r="1280" spans="1:16">
       <c r="A1280" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1280" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C1280">
-        <v>1.739976164097123</v>
+        <v>1.738548116534548</v>
       </c>
       <c r="D1280" t="s">
         <v>195</v>
@@ -65841,22 +65844,22 @@
         <v>-1</v>
       </c>
       <c r="G1280">
-        <v>0.004340023835902878</v>
+        <v>0.004281451883465451</v>
       </c>
       <c r="H1280">
         <v>0.004290023835902878</v>
       </c>
       <c r="I1280">
-        <v>0.04999999999999982</v>
+        <v>0.04857195243742551</v>
       </c>
       <c r="J1280">
         <v>0.4761992072904313</v>
       </c>
       <c r="K1280">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="L1280">
-        <v>3.04</v>
+        <v>3.01</v>
       </c>
       <c r="M1280">
         <v>2.73</v>
@@ -65873,46 +65876,46 @@
     </row>
     <row r="1281" spans="1:16">
       <c r="A1281" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1281" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C1281">
-        <v>1.684738156170027</v>
+        <v>1.739976164097123</v>
       </c>
       <c r="D1281" t="s">
-        <v>342</v>
+        <v>195</v>
       </c>
       <c r="E1281">
-        <v>1.70235807689907</v>
+        <v>1.689976164097123</v>
       </c>
       <c r="F1281">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1281">
-        <v>0.004275261843829974</v>
+        <v>0.004340023835902878</v>
       </c>
       <c r="H1281">
-        <v>0.00419764192310093</v>
+        <v>0.004290023835902878</v>
       </c>
       <c r="I1281">
-        <v>0.01761992072904328</v>
+        <v>0.04999999999999982</v>
       </c>
       <c r="J1281">
         <v>0.4761992072904313</v>
       </c>
       <c r="K1281">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="L1281">
-        <v>2.98</v>
+        <v>3.04</v>
       </c>
       <c r="M1281">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="N1281">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="O1281">
         <v>1</v>
@@ -65923,43 +65926,43 @@
     </row>
     <row r="1282" spans="1:16">
       <c r="A1282" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B1282" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="C1282">
-        <v>1.631109064123743</v>
+        <v>1.684738156170027</v>
       </c>
       <c r="D1282" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E1282">
-        <v>1.676009790115668</v>
+        <v>1.698072100680357</v>
       </c>
       <c r="F1282">
         <v>1</v>
       </c>
       <c r="G1282">
-        <v>0.004208890935876257</v>
+        <v>0.004275261843829974</v>
       </c>
       <c r="H1282">
-        <v>0.004243990209884333</v>
+        <v>0.004221927899319643</v>
       </c>
       <c r="I1282">
-        <v>0.04490072599192496</v>
+        <v>0.01333394451033021</v>
       </c>
       <c r="J1282">
-        <v>0.4900725991924931</v>
+        <v>0.4761992072904313</v>
       </c>
       <c r="K1282">
-        <v>2.63</v>
+        <v>2.72</v>
       </c>
       <c r="L1282">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="M1282">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="N1282">
         <v>2.96</v>
@@ -65968,18 +65971,18 @@
         <v>1</v>
       </c>
       <c r="P1282" t="s">
-        <v>188</v>
+        <v>476</v>
       </c>
     </row>
     <row r="1283" spans="1:16">
       <c r="A1283" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1283" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C1283">
-        <v>1.646009790115668</v>
+        <v>1.631109064123743</v>
       </c>
       <c r="D1283" t="s">
         <v>341</v>
@@ -65991,22 +65994,22 @@
         <v>1</v>
       </c>
       <c r="G1283">
-        <v>0.004213990209884332</v>
+        <v>0.004208890935876257</v>
       </c>
       <c r="H1283">
         <v>0.004243990209884333</v>
       </c>
       <c r="I1283">
-        <v>0.0299999999999998</v>
+        <v>0.04490072599192496</v>
       </c>
       <c r="J1283">
         <v>0.4900725991924931</v>
       </c>
       <c r="K1283">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="L1283">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="M1283">
         <v>2.62</v>
@@ -66023,43 +66026,43 @@
     </row>
     <row r="1284" spans="1:16">
       <c r="A1284" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1284" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C1284">
-        <v>1.645811242099518</v>
+        <v>1.646009790115668</v>
       </c>
       <c r="D1284" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E1284">
-        <v>1.680910516107593</v>
+        <v>1.676009790115668</v>
       </c>
       <c r="F1284">
         <v>1</v>
       </c>
       <c r="G1284">
-        <v>0.004194188757900483</v>
+        <v>0.004213990209884332</v>
       </c>
       <c r="H1284">
-        <v>0.004239089483892407</v>
+        <v>0.004243990209884333</v>
       </c>
       <c r="I1284">
-        <v>0.03509927400807511</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="J1284">
         <v>0.4900725991924931</v>
       </c>
       <c r="K1284">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="L1284">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="M1284">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="N1284">
         <v>2.96</v>
@@ -66073,13 +66076,13 @@
     </row>
     <row r="1285" spans="1:16">
       <c r="A1285" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1285" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C1285">
-        <v>1.640910516107593</v>
+        <v>1.645811242099518</v>
       </c>
       <c r="D1285" t="s">
         <v>340</v>
@@ -66091,19 +66094,19 @@
         <v>1</v>
       </c>
       <c r="G1285">
-        <v>0.004199089483892407</v>
+        <v>0.004194188757900483</v>
       </c>
       <c r="H1285">
         <v>0.004239089483892407</v>
       </c>
       <c r="I1285">
-        <v>0.04000000000000004</v>
+        <v>0.03509927400807511</v>
       </c>
       <c r="J1285">
         <v>0.4900725991924931</v>
       </c>
       <c r="K1285">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="L1285">
         <v>2.92</v>
@@ -66123,46 +66126,46 @@
     </row>
     <row r="1286" spans="1:16">
       <c r="A1286" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1286" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C1286">
-        <v>1.701506160156043</v>
+        <v>1.640910516107593</v>
       </c>
       <c r="D1286" t="s">
-        <v>195</v>
+        <v>340</v>
       </c>
       <c r="E1286">
-        <v>1.652101804204494</v>
+        <v>1.680910516107593</v>
       </c>
       <c r="F1286">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1286">
-        <v>0.004318493839843956</v>
+        <v>0.004199089483892407</v>
       </c>
       <c r="H1286">
-        <v>0.004327898195795507</v>
+        <v>0.004239089483892407</v>
       </c>
       <c r="I1286">
-        <v>0.04940435595154913</v>
+        <v>0.04000000000000004</v>
       </c>
       <c r="J1286">
         <v>0.4900725991924931</v>
       </c>
       <c r="K1286">
-        <v>2.67</v>
+        <v>2.61</v>
       </c>
       <c r="L1286">
-        <v>3.01</v>
+        <v>2.92</v>
       </c>
       <c r="M1286">
-        <v>2.73</v>
+        <v>2.61</v>
       </c>
       <c r="N1286">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="O1286">
         <v>1</v>
@@ -66173,13 +66176,13 @@
     </row>
     <row r="1287" spans="1:16">
       <c r="A1287" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1287" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C1287">
-        <v>1.702101804204494</v>
+        <v>1.701506160156043</v>
       </c>
       <c r="D1287" t="s">
         <v>195</v>
@@ -66191,22 +66194,22 @@
         <v>-1</v>
       </c>
       <c r="G1287">
-        <v>0.004377898195795506</v>
+        <v>0.004318493839843956</v>
       </c>
       <c r="H1287">
         <v>0.004327898195795507</v>
       </c>
       <c r="I1287">
-        <v>0.04999999999999982</v>
+        <v>0.04940435595154913</v>
       </c>
       <c r="J1287">
         <v>0.4900725991924931</v>
       </c>
       <c r="K1287">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="L1287">
-        <v>3.04</v>
+        <v>3.01</v>
       </c>
       <c r="M1287">
         <v>2.73</v>
@@ -66223,46 +66226,46 @@
     </row>
     <row r="1288" spans="1:16">
       <c r="A1288" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1288" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C1288">
-        <v>1.647002530196419</v>
+        <v>1.702101804204494</v>
       </c>
       <c r="D1288" t="s">
-        <v>342</v>
+        <v>195</v>
       </c>
       <c r="E1288">
-        <v>1.666009790115668</v>
+        <v>1.652101804204494</v>
       </c>
       <c r="F1288">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1288">
-        <v>0.004312997469803581</v>
+        <v>0.004377898195795506</v>
       </c>
       <c r="H1288">
-        <v>0.004233990209884333</v>
+        <v>0.004327898195795507</v>
       </c>
       <c r="I1288">
-        <v>0.01900725991924967</v>
+        <v>0.04999999999999982</v>
       </c>
       <c r="J1288">
         <v>0.4900725991924931</v>
       </c>
       <c r="K1288">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="L1288">
-        <v>2.98</v>
+        <v>3.04</v>
       </c>
       <c r="M1288">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="N1288">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="O1288">
         <v>1</v>
@@ -66273,43 +66276,43 @@
     </row>
     <row r="1289" spans="1:16">
       <c r="A1289" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B1289" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="C1289">
-        <v>1.596583044051827</v>
+        <v>1.647002530196419</v>
       </c>
       <c r="D1289" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E1289">
-        <v>1.641615047686611</v>
+        <v>1.661307612139893</v>
       </c>
       <c r="F1289">
         <v>1</v>
       </c>
       <c r="G1289">
-        <v>0.004243416955948173</v>
+        <v>0.004312997469803581</v>
       </c>
       <c r="H1289">
-        <v>0.004278384952313389</v>
+        <v>0.004258692387860107</v>
       </c>
       <c r="I1289">
-        <v>0.04503200363478399</v>
+        <v>0.01430508194347468</v>
       </c>
       <c r="J1289">
-        <v>0.5032003634783927</v>
+        <v>0.4900725991924931</v>
       </c>
       <c r="K1289">
-        <v>2.63</v>
+        <v>2.72</v>
       </c>
       <c r="L1289">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="M1289">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="N1289">
         <v>2.96</v>
@@ -66318,18 +66321,18 @@
         <v>1</v>
       </c>
       <c r="P1289" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
     </row>
     <row r="1290" spans="1:16">
       <c r="A1290" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1290" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C1290">
-        <v>1.611615047686611</v>
+        <v>1.596583044051827</v>
       </c>
       <c r="D1290" t="s">
         <v>341</v>
@@ -66341,22 +66344,22 @@
         <v>1</v>
       </c>
       <c r="G1290">
-        <v>0.004248384952313389</v>
+        <v>0.004243416955948173</v>
       </c>
       <c r="H1290">
         <v>0.004278384952313389</v>
       </c>
       <c r="I1290">
-        <v>0.0299999999999998</v>
+        <v>0.04503200363478399</v>
       </c>
       <c r="J1290">
         <v>0.5032003634783927</v>
       </c>
       <c r="K1290">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="L1290">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="M1290">
         <v>2.62</v>
@@ -66373,43 +66376,43 @@
     </row>
     <row r="1291" spans="1:16">
       <c r="A1291" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1291" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C1291">
-        <v>1.611679054956179</v>
+        <v>1.611615047686611</v>
       </c>
       <c r="D1291" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E1291">
-        <v>1.646647051321395</v>
+        <v>1.641615047686611</v>
       </c>
       <c r="F1291">
         <v>1</v>
       </c>
       <c r="G1291">
-        <v>0.004228320945043821</v>
+        <v>0.004248384952313389</v>
       </c>
       <c r="H1291">
-        <v>0.004273352948678606</v>
+        <v>0.004278384952313389</v>
       </c>
       <c r="I1291">
-        <v>0.0349679963652163</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="J1291">
         <v>0.5032003634783927</v>
       </c>
       <c r="K1291">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="L1291">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="M1291">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="N1291">
         <v>2.96</v>
@@ -66423,13 +66426,13 @@
     </row>
     <row r="1292" spans="1:16">
       <c r="A1292" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1292" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C1292">
-        <v>1.606647051321395</v>
+        <v>1.611679054956179</v>
       </c>
       <c r="D1292" t="s">
         <v>340</v>
@@ -66441,19 +66444,19 @@
         <v>1</v>
       </c>
       <c r="G1292">
-        <v>0.004233352948678605</v>
+        <v>0.004228320945043821</v>
       </c>
       <c r="H1292">
         <v>0.004273352948678606</v>
       </c>
       <c r="I1292">
-        <v>0.04000000000000004</v>
+        <v>0.0349679963652163</v>
       </c>
       <c r="J1292">
         <v>0.5032003634783927</v>
       </c>
       <c r="K1292">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="L1292">
         <v>2.92</v>
@@ -66473,46 +66476,46 @@
     </row>
     <row r="1293" spans="1:16">
       <c r="A1293" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1293" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C1293">
-        <v>1.666455029512691</v>
+        <v>1.606647051321395</v>
       </c>
       <c r="D1293" t="s">
-        <v>195</v>
+        <v>340</v>
       </c>
       <c r="E1293">
-        <v>1.616263007703988</v>
+        <v>1.646647051321395</v>
       </c>
       <c r="F1293">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1293">
-        <v>0.004353544970487308</v>
+        <v>0.004233352948678605</v>
       </c>
       <c r="H1293">
-        <v>0.004363736992296012</v>
+        <v>0.004273352948678606</v>
       </c>
       <c r="I1293">
-        <v>0.0501920218087033</v>
+        <v>0.04000000000000004</v>
       </c>
       <c r="J1293">
         <v>0.5032003634783927</v>
       </c>
       <c r="K1293">
-        <v>2.67</v>
+        <v>2.61</v>
       </c>
       <c r="L1293">
-        <v>3.01</v>
+        <v>2.92</v>
       </c>
       <c r="M1293">
-        <v>2.73</v>
+        <v>2.61</v>
       </c>
       <c r="N1293">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="O1293">
         <v>1</v>
@@ -66523,13 +66526,13 @@
     </row>
     <row r="1294" spans="1:16">
       <c r="A1294" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1294" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C1294">
-        <v>1.666263007703988</v>
+        <v>1.666455029512691</v>
       </c>
       <c r="D1294" t="s">
         <v>195</v>
@@ -66541,22 +66544,22 @@
         <v>-1</v>
       </c>
       <c r="G1294">
-        <v>0.004413736992296012</v>
+        <v>0.004353544970487308</v>
       </c>
       <c r="H1294">
         <v>0.004363736992296012</v>
       </c>
       <c r="I1294">
-        <v>0.04999999999999982</v>
+        <v>0.0501920218087033</v>
       </c>
       <c r="J1294">
         <v>0.5032003634783927</v>
       </c>
       <c r="K1294">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="L1294">
-        <v>3.04</v>
+        <v>3.01</v>
       </c>
       <c r="M1294">
         <v>2.73</v>
@@ -66573,46 +66576,46 @@
     </row>
     <row r="1295" spans="1:16">
       <c r="A1295" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1295" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C1295">
-        <v>1.611295011338772</v>
+        <v>1.666263007703988</v>
       </c>
       <c r="D1295" t="s">
-        <v>342</v>
+        <v>195</v>
       </c>
       <c r="E1295">
-        <v>1.631615047686611</v>
+        <v>1.616263007703988</v>
       </c>
       <c r="F1295">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1295">
-        <v>0.004348704988661229</v>
+        <v>0.004413736992296012</v>
       </c>
       <c r="H1295">
-        <v>0.00426838495231339</v>
+        <v>0.004363736992296012</v>
       </c>
       <c r="I1295">
-        <v>0.02032003634783952</v>
+        <v>0.04999999999999982</v>
       </c>
       <c r="J1295">
         <v>0.5032003634783927</v>
       </c>
       <c r="K1295">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="L1295">
-        <v>2.98</v>
+        <v>3.04</v>
       </c>
       <c r="M1295">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="N1295">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="O1295">
         <v>1</v>
@@ -66623,43 +66626,43 @@
     </row>
     <row r="1296" spans="1:16">
       <c r="A1296" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B1296" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="C1296">
-        <v>1.575343698422129</v>
+        <v>1.611295011338772</v>
       </c>
       <c r="D1296" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E1296">
-        <v>1.620456460025087</v>
+        <v>1.626519036782259</v>
       </c>
       <c r="F1296">
         <v>1</v>
       </c>
       <c r="G1296">
-        <v>0.004264656301577871</v>
+        <v>0.004348704988661229</v>
       </c>
       <c r="H1296">
-        <v>0.004299543539974913</v>
+        <v>0.004293480963217741</v>
       </c>
       <c r="I1296">
-        <v>0.04511276160295763</v>
+        <v>0.01522402544348744</v>
       </c>
       <c r="J1296">
-        <v>0.5112761602957683</v>
+        <v>0.5032003634783927</v>
       </c>
       <c r="K1296">
-        <v>2.63</v>
+        <v>2.72</v>
       </c>
       <c r="L1296">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="M1296">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="N1296">
         <v>2.96</v>
@@ -66668,18 +66671,18 @@
         <v>1</v>
       </c>
       <c r="P1296" t="s">
-        <v>477</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1297" spans="1:16">
       <c r="A1297" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1297" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C1297">
-        <v>1.590456460025087</v>
+        <v>1.575343698422129</v>
       </c>
       <c r="D1297" t="s">
         <v>341</v>
@@ -66691,22 +66694,22 @@
         <v>1</v>
       </c>
       <c r="G1297">
-        <v>0.004269543539974914</v>
+        <v>0.004264656301577871</v>
       </c>
       <c r="H1297">
         <v>0.004299543539974913</v>
       </c>
       <c r="I1297">
-        <v>0.0299999999999998</v>
+        <v>0.04511276160295763</v>
       </c>
       <c r="J1297">
         <v>0.5112761602957683</v>
       </c>
       <c r="K1297">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="L1297">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="M1297">
         <v>2.62</v>
@@ -66723,43 +66726,43 @@
     </row>
     <row r="1298" spans="1:16">
       <c r="A1298" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1298" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C1298">
-        <v>1.590681983231002</v>
+        <v>1.590456460025087</v>
       </c>
       <c r="D1298" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E1298">
-        <v>1.625569221628045</v>
+        <v>1.620456460025087</v>
       </c>
       <c r="F1298">
         <v>1</v>
       </c>
       <c r="G1298">
-        <v>0.004249318016768998</v>
+        <v>0.004269543539974914</v>
       </c>
       <c r="H1298">
-        <v>0.004294430778371956</v>
+        <v>0.004299543539974913</v>
       </c>
       <c r="I1298">
-        <v>0.03488723839704244</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="J1298">
         <v>0.5112761602957683</v>
       </c>
       <c r="K1298">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="L1298">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="M1298">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="N1298">
         <v>2.96</v>
@@ -66773,13 +66776,13 @@
     </row>
     <row r="1299" spans="1:16">
       <c r="A1299" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1299" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C1299">
-        <v>1.585569221628045</v>
+        <v>1.590681983231002</v>
       </c>
       <c r="D1299" t="s">
         <v>340</v>
@@ -66791,19 +66794,19 @@
         <v>1</v>
       </c>
       <c r="G1299">
-        <v>0.004254430778371955</v>
+        <v>0.004249318016768998</v>
       </c>
       <c r="H1299">
         <v>0.004294430778371956</v>
       </c>
       <c r="I1299">
-        <v>0.04000000000000004</v>
+        <v>0.03488723839704244</v>
       </c>
       <c r="J1299">
         <v>0.5112761602957683</v>
       </c>
       <c r="K1299">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="L1299">
         <v>2.92</v>
@@ -66823,46 +66826,46 @@
     </row>
     <row r="1300" spans="1:16">
       <c r="A1300" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1300" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C1300">
-        <v>1.644892652010298</v>
+        <v>1.585569221628045</v>
       </c>
       <c r="D1300" t="s">
-        <v>195</v>
+        <v>340</v>
       </c>
       <c r="E1300">
-        <v>1.594216082392553</v>
+        <v>1.625569221628045</v>
       </c>
       <c r="F1300">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1300">
-        <v>0.004375107347989701</v>
+        <v>0.004254430778371955</v>
       </c>
       <c r="H1300">
-        <v>0.004385783917607448</v>
+        <v>0.004294430778371956</v>
       </c>
       <c r="I1300">
-        <v>0.05067656961774558</v>
+        <v>0.04000000000000004</v>
       </c>
       <c r="J1300">
         <v>0.5112761602957683</v>
       </c>
       <c r="K1300">
-        <v>2.67</v>
+        <v>2.61</v>
       </c>
       <c r="L1300">
-        <v>3.01</v>
+        <v>2.92</v>
       </c>
       <c r="M1300">
-        <v>2.73</v>
+        <v>2.61</v>
       </c>
       <c r="N1300">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="O1300">
         <v>1</v>
@@ -66873,13 +66876,13 @@
     </row>
     <row r="1301" spans="1:16">
       <c r="A1301" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1301" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C1301">
-        <v>1.644216082392553</v>
+        <v>1.644892652010298</v>
       </c>
       <c r="D1301" t="s">
         <v>195</v>
@@ -66891,22 +66894,22 @@
         <v>-1</v>
       </c>
       <c r="G1301">
-        <v>0.004435783917607448</v>
+        <v>0.004375107347989701</v>
       </c>
       <c r="H1301">
         <v>0.004385783917607448</v>
       </c>
       <c r="I1301">
-        <v>0.04999999999999982</v>
+        <v>0.05067656961774558</v>
       </c>
       <c r="J1301">
         <v>0.5112761602957683</v>
       </c>
       <c r="K1301">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="L1301">
-        <v>3.04</v>
+        <v>3.01</v>
       </c>
       <c r="M1301">
         <v>2.73</v>
@@ -66923,46 +66926,46 @@
     </row>
     <row r="1302" spans="1:16">
       <c r="A1302" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1302" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C1302">
-        <v>1.58932884399551</v>
+        <v>1.644216082392553</v>
       </c>
       <c r="D1302" t="s">
-        <v>342</v>
+        <v>195</v>
       </c>
       <c r="E1302">
-        <v>1.610456460025087</v>
+        <v>1.594216082392553</v>
       </c>
       <c r="F1302">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1302">
-        <v>0.00437067115600449</v>
+        <v>0.004435783917607448</v>
       </c>
       <c r="H1302">
-        <v>0.004289543539974913</v>
+        <v>0.004385783917607448</v>
       </c>
       <c r="I1302">
-        <v>0.02112761602957702</v>
+        <v>0.04999999999999982</v>
       </c>
       <c r="J1302">
         <v>0.5112761602957683</v>
       </c>
       <c r="K1302">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="L1302">
-        <v>2.98</v>
+        <v>3.04</v>
       </c>
       <c r="M1302">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="N1302">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="O1302">
         <v>1</v>
@@ -66973,43 +66976,43 @@
     </row>
     <row r="1303" spans="1:16">
       <c r="A1303" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B1303" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="C1303">
-        <v>1.558285979436833</v>
+        <v>1.58932884399551</v>
       </c>
       <c r="D1303" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E1303">
-        <v>1.603463599286883</v>
+        <v>1.605118175216214</v>
       </c>
       <c r="F1303">
         <v>1</v>
       </c>
       <c r="G1303">
-        <v>0.004281714020563167</v>
+        <v>0.00437067115600449</v>
       </c>
       <c r="H1303">
-        <v>0.004316536400713117</v>
+        <v>0.004314881824783786</v>
       </c>
       <c r="I1303">
-        <v>0.04517761985004998</v>
+        <v>0.01578933122070381</v>
       </c>
       <c r="J1303">
-        <v>0.5177619850050065</v>
+        <v>0.5112761602957683</v>
       </c>
       <c r="K1303">
-        <v>2.63</v>
+        <v>2.72</v>
       </c>
       <c r="L1303">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="M1303">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="N1303">
         <v>2.96</v>
@@ -67018,18 +67021,18 @@
         <v>1</v>
       </c>
       <c r="P1303" t="s">
-        <v>182</v>
+        <v>477</v>
       </c>
     </row>
     <row r="1304" spans="1:16">
       <c r="A1304" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1304" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C1304">
-        <v>1.573463599286883</v>
+        <v>1.558285979436833</v>
       </c>
       <c r="D1304" t="s">
         <v>341</v>
@@ -67041,22 +67044,22 @@
         <v>1</v>
       </c>
       <c r="G1304">
-        <v>0.004286536400713118</v>
+        <v>0.004281714020563167</v>
       </c>
       <c r="H1304">
         <v>0.004316536400713117</v>
       </c>
       <c r="I1304">
-        <v>0.0299999999999998</v>
+        <v>0.04517761985004998</v>
       </c>
       <c r="J1304">
         <v>0.5177619850050065</v>
       </c>
       <c r="K1304">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="L1304">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="M1304">
         <v>2.62</v>
@@ -67073,43 +67076,43 @@
     </row>
     <row r="1305" spans="1:16">
       <c r="A1305" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1305" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C1305">
-        <v>1.573818838986983</v>
+        <v>1.573463599286883</v>
       </c>
       <c r="D1305" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E1305">
-        <v>1.608641219136933</v>
+        <v>1.603463599286883</v>
       </c>
       <c r="F1305">
         <v>1</v>
       </c>
       <c r="G1305">
-        <v>0.004266181161013017</v>
+        <v>0.004286536400713118</v>
       </c>
       <c r="H1305">
-        <v>0.004311358780863067</v>
+        <v>0.004316536400713117</v>
       </c>
       <c r="I1305">
-        <v>0.03482238014995009</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="J1305">
         <v>0.5177619850050065</v>
       </c>
       <c r="K1305">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="L1305">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="M1305">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="N1305">
         <v>2.96</v>
@@ -67123,13 +67126,13 @@
     </row>
     <row r="1306" spans="1:16">
       <c r="A1306" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1306" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C1306">
-        <v>1.568641219136933</v>
+        <v>1.573818838986983</v>
       </c>
       <c r="D1306" t="s">
         <v>340</v>
@@ -67141,19 +67144,19 @@
         <v>1</v>
       </c>
       <c r="G1306">
-        <v>0.004271358780863067</v>
+        <v>0.004266181161013017</v>
       </c>
       <c r="H1306">
         <v>0.004311358780863067</v>
       </c>
       <c r="I1306">
-        <v>0.04000000000000004</v>
+        <v>0.03482238014995009</v>
       </c>
       <c r="J1306">
         <v>0.5177619850050065</v>
       </c>
       <c r="K1306">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="L1306">
         <v>2.92</v>
@@ -67173,46 +67176,46 @@
     </row>
     <row r="1307" spans="1:16">
       <c r="A1307" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1307" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C1307">
-        <v>1.617930739736733</v>
+        <v>1.568641219136933</v>
       </c>
       <c r="D1307" t="s">
-        <v>195</v>
+        <v>340</v>
       </c>
       <c r="E1307">
-        <v>1.576509780936333</v>
+        <v>1.608641219136933</v>
       </c>
       <c r="F1307">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1307">
-        <v>0.004362069260263267</v>
+        <v>0.004271358780863067</v>
       </c>
       <c r="H1307">
-        <v>0.004403490219063669</v>
+        <v>0.004311358780863067</v>
       </c>
       <c r="I1307">
-        <v>0.04142095880040042</v>
+        <v>0.04000000000000004</v>
       </c>
       <c r="J1307">
         <v>0.5177619850050065</v>
       </c>
       <c r="K1307">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
       <c r="L1307">
-        <v>2.99</v>
+        <v>2.92</v>
       </c>
       <c r="M1307">
-        <v>2.73</v>
+        <v>2.61</v>
       </c>
       <c r="N1307">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="O1307">
         <v>1</v>
@@ -67223,13 +67226,13 @@
     </row>
     <row r="1308" spans="1:16">
       <c r="A1308" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1308" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="C1308">
-        <v>1.626509780936332</v>
+        <v>1.617930739736733</v>
       </c>
       <c r="D1308" t="s">
         <v>195</v>
@@ -67241,22 +67244,22 @@
         <v>-1</v>
       </c>
       <c r="G1308">
-        <v>0.004453490219063667</v>
+        <v>0.004362069260263267</v>
       </c>
       <c r="H1308">
         <v>0.004403490219063669</v>
       </c>
       <c r="I1308">
-        <v>0.04999999999999982</v>
+        <v>0.04142095880040042</v>
       </c>
       <c r="J1308">
         <v>0.5177619850050065</v>
       </c>
       <c r="K1308">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="L1308">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="M1308">
         <v>2.73</v>
@@ -67273,46 +67276,46 @@
     </row>
     <row r="1309" spans="1:16">
       <c r="A1309" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1309" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C1309">
-        <v>1.571687400786382</v>
+        <v>1.626509780936332</v>
       </c>
       <c r="D1309" t="s">
-        <v>342</v>
+        <v>195</v>
       </c>
       <c r="E1309">
-        <v>1.593463599286883</v>
+        <v>1.576509780936333</v>
       </c>
       <c r="F1309">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1309">
-        <v>0.004388312599213617</v>
+        <v>0.004453490219063667</v>
       </c>
       <c r="H1309">
-        <v>0.004306536400713118</v>
+        <v>0.004403490219063669</v>
       </c>
       <c r="I1309">
-        <v>0.02177619850050072</v>
+        <v>0.04999999999999982</v>
       </c>
       <c r="J1309">
         <v>0.5177619850050065</v>
       </c>
       <c r="K1309">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="L1309">
-        <v>2.98</v>
+        <v>3.04</v>
       </c>
       <c r="M1309">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="N1309">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="O1309">
         <v>1</v>
@@ -67323,43 +67326,43 @@
     </row>
     <row r="1310" spans="1:16">
       <c r="A1310" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B1310" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="C1310">
-        <v>1.540926184059721</v>
+        <v>1.571687400786382</v>
       </c>
       <c r="D1310" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E1310">
-        <v>1.5861698107363</v>
+        <v>1.587930739736733</v>
       </c>
       <c r="F1310">
         <v>1</v>
       </c>
       <c r="G1310">
-        <v>0.004299073815940278</v>
+        <v>0.004388312599213617</v>
       </c>
       <c r="H1310">
-        <v>0.0043338301892637</v>
+        <v>0.004332069260263268</v>
       </c>
       <c r="I1310">
-        <v>0.045243626676579</v>
+        <v>0.01624333895035046</v>
       </c>
       <c r="J1310">
-        <v>0.5243626676579006</v>
+        <v>0.5177619850050065</v>
       </c>
       <c r="K1310">
-        <v>2.63</v>
+        <v>2.72</v>
       </c>
       <c r="L1310">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="M1310">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="N1310">
         <v>2.96</v>
@@ -67368,18 +67371,18 @@
         <v>1</v>
       </c>
       <c r="P1310" t="s">
-        <v>478</v>
+        <v>182</v>
       </c>
     </row>
     <row r="1311" spans="1:16">
       <c r="A1311" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1311" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C1311">
-        <v>1.5561698107363</v>
+        <v>1.540926184059721</v>
       </c>
       <c r="D1311" t="s">
         <v>341</v>
@@ -67391,22 +67394,22 @@
         <v>1</v>
       </c>
       <c r="G1311">
-        <v>0.004303830189263699</v>
+        <v>0.004299073815940278</v>
       </c>
       <c r="H1311">
         <v>0.0043338301892637</v>
       </c>
       <c r="I1311">
-        <v>0.0299999999999998</v>
+        <v>0.045243626676579</v>
       </c>
       <c r="J1311">
         <v>0.5243626676579006</v>
       </c>
       <c r="K1311">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="L1311">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="M1311">
         <v>2.62</v>
@@ -67423,43 +67426,43 @@
     </row>
     <row r="1312" spans="1:16">
       <c r="A1312" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1312" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C1312">
-        <v>1.556657064089458</v>
+        <v>1.5561698107363</v>
       </c>
       <c r="D1312" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E1312">
-        <v>1.591413437412879</v>
+        <v>1.5861698107363</v>
       </c>
       <c r="F1312">
         <v>1</v>
       </c>
       <c r="G1312">
-        <v>0.004283342935910542</v>
+        <v>0.004303830189263699</v>
       </c>
       <c r="H1312">
-        <v>0.004328586562587121</v>
+        <v>0.0043338301892637</v>
       </c>
       <c r="I1312">
-        <v>0.0347563733234213</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="J1312">
         <v>0.5243626676579006</v>
       </c>
       <c r="K1312">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="L1312">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="M1312">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="N1312">
         <v>2.96</v>
@@ -67473,13 +67476,13 @@
     </row>
     <row r="1313" spans="1:16">
       <c r="A1313" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1313" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C1313">
-        <v>1.551413437412879</v>
+        <v>1.556657064089458</v>
       </c>
       <c r="D1313" t="s">
         <v>340</v>
@@ -67491,19 +67494,19 @@
         <v>1</v>
       </c>
       <c r="G1313">
-        <v>0.004288586562587121</v>
+        <v>0.004283342935910542</v>
       </c>
       <c r="H1313">
         <v>0.004328586562587121</v>
       </c>
       <c r="I1313">
-        <v>0.04000000000000004</v>
+        <v>0.0347563733234213</v>
       </c>
       <c r="J1313">
         <v>0.5243626676579006</v>
       </c>
       <c r="K1313">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="L1313">
         <v>2.92</v>
@@ -67523,46 +67526,46 @@
     </row>
     <row r="1314" spans="1:16">
       <c r="A1314" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1314" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C1314">
-        <v>1.600438930706564</v>
+        <v>1.551413437412879</v>
       </c>
       <c r="D1314" t="s">
-        <v>195</v>
+        <v>340</v>
       </c>
       <c r="E1314">
-        <v>1.558489917293931</v>
+        <v>1.591413437412879</v>
       </c>
       <c r="F1314">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1314">
-        <v>0.004379561069293437</v>
+        <v>0.004288586562587121</v>
       </c>
       <c r="H1314">
-        <v>0.004421510082706069</v>
+        <v>0.004328586562587121</v>
       </c>
       <c r="I1314">
-        <v>0.04194901341263213</v>
+        <v>0.04000000000000004</v>
       </c>
       <c r="J1314">
         <v>0.5243626676579006</v>
       </c>
       <c r="K1314">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
       <c r="L1314">
-        <v>2.99</v>
+        <v>2.92</v>
       </c>
       <c r="M1314">
-        <v>2.73</v>
+        <v>2.61</v>
       </c>
       <c r="N1314">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="O1314">
         <v>1</v>
@@ -67573,13 +67576,13 @@
     </row>
     <row r="1315" spans="1:16">
       <c r="A1315" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1315" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="C1315">
-        <v>1.608489917293931</v>
+        <v>1.600438930706564</v>
       </c>
       <c r="D1315" t="s">
         <v>195</v>
@@ -67591,22 +67594,22 @@
         <v>-1</v>
       </c>
       <c r="G1315">
-        <v>0.004471510082706069</v>
+        <v>0.004379561069293437</v>
       </c>
       <c r="H1315">
         <v>0.004421510082706069</v>
       </c>
       <c r="I1315">
-        <v>0.04999999999999982</v>
+        <v>0.04194901341263213</v>
       </c>
       <c r="J1315">
         <v>0.5243626676579006</v>
       </c>
       <c r="K1315">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="L1315">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="M1315">
         <v>2.73</v>
@@ -67623,63 +67626,63 @@
     </row>
     <row r="1316" spans="1:16">
       <c r="A1316" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B1316" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C1316">
-        <v>1.523625633709941</v>
+        <v>1.608489917293931</v>
       </c>
       <c r="D1316" t="s">
-        <v>341</v>
+        <v>195</v>
       </c>
       <c r="E1316">
-        <v>1.568935041946785</v>
+        <v>1.558489917293931</v>
       </c>
       <c r="F1316">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1316">
-        <v>0.004316374366290059</v>
+        <v>0.004471510082706069</v>
       </c>
       <c r="H1316">
-        <v>0.004351064958053216</v>
+        <v>0.004421510082706069</v>
       </c>
       <c r="I1316">
-        <v>0.04530940823684415</v>
+        <v>0.04999999999999982</v>
       </c>
       <c r="J1316">
-        <v>0.5309408236844333</v>
+        <v>0.5243626676579006</v>
       </c>
       <c r="K1316">
-        <v>2.63</v>
+        <v>2.73</v>
       </c>
       <c r="L1316">
-        <v>2.92</v>
+        <v>3.04</v>
       </c>
       <c r="M1316">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="N1316">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="O1316">
         <v>1</v>
       </c>
       <c r="P1316" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="1317" spans="1:16">
       <c r="A1317" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1317" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C1317">
-        <v>1.538935041946785</v>
+        <v>1.523625633709941</v>
       </c>
       <c r="D1317" t="s">
         <v>341</v>
@@ -67691,22 +67694,22 @@
         <v>1</v>
       </c>
       <c r="G1317">
-        <v>0.004321064958053215</v>
+        <v>0.004316374366290059</v>
       </c>
       <c r="H1317">
         <v>0.004351064958053216</v>
       </c>
       <c r="I1317">
-        <v>0.0299999999999998</v>
+        <v>0.04530940823684415</v>
       </c>
       <c r="J1317">
         <v>0.5309408236844333</v>
       </c>
       <c r="K1317">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="L1317">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="M1317">
         <v>2.62</v>
@@ -67723,43 +67726,43 @@
     </row>
     <row r="1318" spans="1:16">
       <c r="A1318" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1318" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C1318">
-        <v>1.539553858420473</v>
+        <v>1.538935041946785</v>
       </c>
       <c r="D1318" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E1318">
-        <v>1.574244450183629</v>
+        <v>1.568935041946785</v>
       </c>
       <c r="F1318">
         <v>1</v>
       </c>
       <c r="G1318">
-        <v>0.004300446141579527</v>
+        <v>0.004321064958053215</v>
       </c>
       <c r="H1318">
-        <v>0.004345755549816371</v>
+        <v>0.004351064958053216</v>
       </c>
       <c r="I1318">
-        <v>0.03469059176315592</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="J1318">
         <v>0.5309408236844333</v>
       </c>
       <c r="K1318">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="L1318">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="M1318">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="N1318">
         <v>2.96</v>
@@ -67773,13 +67776,13 @@
     </row>
     <row r="1319" spans="1:16">
       <c r="A1319" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1319" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C1319">
-        <v>1.534244450183629</v>
+        <v>1.539553858420473</v>
       </c>
       <c r="D1319" t="s">
         <v>340</v>
@@ -67791,19 +67794,19 @@
         <v>1</v>
       </c>
       <c r="G1319">
-        <v>0.004305755549816371</v>
+        <v>0.004300446141579527</v>
       </c>
       <c r="H1319">
         <v>0.004345755549816371</v>
       </c>
       <c r="I1319">
-        <v>0.04000000000000004</v>
+        <v>0.03469059176315592</v>
       </c>
       <c r="J1319">
         <v>0.5309408236844333</v>
       </c>
       <c r="K1319">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="L1319">
         <v>2.92</v>
@@ -67823,46 +67826,46 @@
     </row>
     <row r="1320" spans="1:16">
       <c r="A1320" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1320" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C1320">
-        <v>1.583006817236252</v>
+        <v>1.534244450183629</v>
       </c>
       <c r="D1320" t="s">
-        <v>195</v>
+        <v>340</v>
       </c>
       <c r="E1320">
-        <v>1.540531551341497</v>
+        <v>1.574244450183629</v>
       </c>
       <c r="F1320">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1320">
-        <v>0.004396993182763749</v>
+        <v>0.004305755549816371</v>
       </c>
       <c r="H1320">
-        <v>0.004439468448658503</v>
+        <v>0.004345755549816371</v>
       </c>
       <c r="I1320">
-        <v>0.0424752658947547</v>
+        <v>0.04000000000000004</v>
       </c>
       <c r="J1320">
         <v>0.5309408236844333</v>
       </c>
       <c r="K1320">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
       <c r="L1320">
-        <v>2.99</v>
+        <v>2.92</v>
       </c>
       <c r="M1320">
-        <v>2.73</v>
+        <v>2.61</v>
       </c>
       <c r="N1320">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="O1320">
         <v>1</v>
@@ -67873,13 +67876,13 @@
     </row>
     <row r="1321" spans="1:16">
       <c r="A1321" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1321" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="C1321">
-        <v>1.590531551341497</v>
+        <v>1.583006817236252</v>
       </c>
       <c r="D1321" t="s">
         <v>195</v>
@@ -67891,22 +67894,22 @@
         <v>-1</v>
       </c>
       <c r="G1321">
-        <v>0.004489468448658503</v>
+        <v>0.004396993182763749</v>
       </c>
       <c r="H1321">
         <v>0.004439468448658503</v>
       </c>
       <c r="I1321">
-        <v>0.04999999999999982</v>
+        <v>0.0424752658947547</v>
       </c>
       <c r="J1321">
         <v>0.5309408236844333</v>
       </c>
       <c r="K1321">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="L1321">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="M1321">
         <v>2.73</v>
@@ -67923,63 +67926,63 @@
     </row>
     <row r="1322" spans="1:16">
       <c r="A1322" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B1322" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C1322">
-        <v>1.508109076568332</v>
+        <v>1.590531551341497</v>
       </c>
       <c r="D1322" t="s">
-        <v>341</v>
+        <v>195</v>
       </c>
       <c r="E1322">
-        <v>1.553477483121304</v>
+        <v>1.540531551341497</v>
       </c>
       <c r="F1322">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1322">
-        <v>0.004331890923431669</v>
+        <v>0.004489468448658503</v>
       </c>
       <c r="H1322">
-        <v>0.004366522516878696</v>
+        <v>0.004439468448658503</v>
       </c>
       <c r="I1322">
-        <v>0.04536840655297203</v>
+        <v>0.04999999999999982</v>
       </c>
       <c r="J1322">
-        <v>0.5368406552972123</v>
+        <v>0.5309408236844333</v>
       </c>
       <c r="K1322">
-        <v>2.63</v>
+        <v>2.73</v>
       </c>
       <c r="L1322">
-        <v>2.92</v>
+        <v>3.04</v>
       </c>
       <c r="M1322">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="N1322">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="O1322">
         <v>1</v>
       </c>
       <c r="P1322" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="1323" spans="1:16">
       <c r="A1323" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1323" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C1323">
-        <v>1.523477483121304</v>
+        <v>1.508109076568332</v>
       </c>
       <c r="D1323" t="s">
         <v>341</v>
@@ -67991,22 +67994,22 @@
         <v>1</v>
       </c>
       <c r="G1323">
-        <v>0.004336522516878697</v>
+        <v>0.004331890923431669</v>
       </c>
       <c r="H1323">
         <v>0.004366522516878696</v>
       </c>
       <c r="I1323">
-        <v>0.0299999999999998</v>
+        <v>0.04536840655297203</v>
       </c>
       <c r="J1323">
         <v>0.5368406552972123</v>
       </c>
       <c r="K1323">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="L1323">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="M1323">
         <v>2.62</v>
@@ -68023,46 +68026,46 @@
     </row>
     <row r="1324" spans="1:16">
       <c r="A1324" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1324" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="C1324">
-        <v>1.56958270278022</v>
+        <v>1.523477483121304</v>
       </c>
       <c r="D1324" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E1324">
-        <v>1.534214296227248</v>
+        <v>1.553477483121304</v>
       </c>
       <c r="F1324">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1324">
-        <v>0.00435041729721978</v>
+        <v>0.004336522516878697</v>
       </c>
       <c r="H1324">
-        <v>0.004325785703772752</v>
+        <v>0.004366522516878696</v>
       </c>
       <c r="I1324">
-        <v>0.03536840655297202</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="J1324">
         <v>0.5368406552972123</v>
       </c>
       <c r="K1324">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="L1324">
+        <v>2.93</v>
+      </c>
+      <c r="M1324">
+        <v>2.62</v>
+      </c>
+      <c r="N1324">
         <v>2.96</v>
-      </c>
-      <c r="M1324">
-        <v>2.6</v>
-      </c>
-      <c r="N1324">
-        <v>2.93</v>
       </c>
       <c r="O1324">
         <v>1</v>
@@ -68073,46 +68076,46 @@
     </row>
     <row r="1325" spans="1:16">
       <c r="A1325" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1325" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="C1325">
-        <v>1.524214296227248</v>
+        <v>1.56958270278022</v>
       </c>
       <c r="D1325" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="E1325">
-        <v>1.558845889674276</v>
+        <v>1.534214296227248</v>
       </c>
       <c r="F1325">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1325">
-        <v>0.004315785703772752</v>
+        <v>0.00435041729721978</v>
       </c>
       <c r="H1325">
-        <v>0.004361154110325724</v>
+        <v>0.004325785703772752</v>
       </c>
       <c r="I1325">
-        <v>0.03463159344702804</v>
+        <v>0.03536840655297202</v>
       </c>
       <c r="J1325">
         <v>0.5368406552972123</v>
       </c>
       <c r="K1325">
+        <v>2.59</v>
+      </c>
+      <c r="L1325">
+        <v>2.96</v>
+      </c>
+      <c r="M1325">
         <v>2.6</v>
       </c>
-      <c r="L1325">
-        <v>2.92</v>
-      </c>
-      <c r="M1325">
-        <v>2.61</v>
-      </c>
       <c r="N1325">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="O1325">
         <v>1</v>
@@ -68123,13 +68126,13 @@
     </row>
     <row r="1326" spans="1:16">
       <c r="A1326" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1326" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C1326">
-        <v>1.518845889674276</v>
+        <v>1.524214296227248</v>
       </c>
       <c r="D1326" t="s">
         <v>340</v>
@@ -68141,19 +68144,19 @@
         <v>1</v>
       </c>
       <c r="G1326">
-        <v>0.004321154110325724</v>
+        <v>0.004315785703772752</v>
       </c>
       <c r="H1326">
         <v>0.004361154110325724</v>
       </c>
       <c r="I1326">
-        <v>0.04000000000000004</v>
+        <v>0.03463159344702804</v>
       </c>
       <c r="J1326">
         <v>0.5368406552972123</v>
       </c>
       <c r="K1326">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="L1326">
         <v>2.92</v>
@@ -68173,46 +68176,46 @@
     </row>
     <row r="1327" spans="1:16">
       <c r="A1327" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1327" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C1327">
-        <v>1.567372263462388</v>
+        <v>1.518845889674276</v>
       </c>
       <c r="D1327" t="s">
-        <v>195</v>
+        <v>340</v>
       </c>
       <c r="E1327">
-        <v>1.524425011038611</v>
+        <v>1.558845889674276</v>
       </c>
       <c r="F1327">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1327">
-        <v>0.004412627736537613</v>
+        <v>0.004321154110325724</v>
       </c>
       <c r="H1327">
-        <v>0.00445557498896139</v>
+        <v>0.004361154110325724</v>
       </c>
       <c r="I1327">
-        <v>0.04294725242377706</v>
+        <v>0.04000000000000004</v>
       </c>
       <c r="J1327">
         <v>0.5368406552972123</v>
       </c>
       <c r="K1327">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
       <c r="L1327">
-        <v>2.99</v>
+        <v>2.92</v>
       </c>
       <c r="M1327">
-        <v>2.73</v>
+        <v>2.61</v>
       </c>
       <c r="N1327">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="O1327">
         <v>1</v>
@@ -68223,13 +68226,13 @@
     </row>
     <row r="1328" spans="1:16">
       <c r="A1328" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1328" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="C1328">
-        <v>1.574425011038611</v>
+        <v>1.567372263462388</v>
       </c>
       <c r="D1328" t="s">
         <v>195</v>
@@ -68241,22 +68244,22 @@
         <v>-1</v>
       </c>
       <c r="G1328">
-        <v>0.004505574988961389</v>
+        <v>0.004412627736537613</v>
       </c>
       <c r="H1328">
         <v>0.00445557498896139</v>
       </c>
       <c r="I1328">
-        <v>0.04999999999999982</v>
+        <v>0.04294725242377706</v>
       </c>
       <c r="J1328">
         <v>0.5368406552972123</v>
       </c>
       <c r="K1328">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="L1328">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="M1328">
         <v>2.73</v>
@@ -68273,63 +68276,63 @@
     </row>
     <row r="1329" spans="1:16">
       <c r="A1329" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B1329" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C1329">
-        <v>1.492010522817169</v>
+        <v>1.574425011038611</v>
       </c>
       <c r="D1329" t="s">
-        <v>341</v>
+        <v>195</v>
       </c>
       <c r="E1329">
-        <v>1.537440140601135</v>
+        <v>1.524425011038611</v>
       </c>
       <c r="F1329">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1329">
-        <v>0.004347989477182831</v>
+        <v>0.004505574988961389</v>
       </c>
       <c r="H1329">
-        <v>0.004382559859398866</v>
+        <v>0.00445557498896139</v>
       </c>
       <c r="I1329">
-        <v>0.04542961778396526</v>
+        <v>0.04999999999999982</v>
       </c>
       <c r="J1329">
-        <v>0.5429617783965135</v>
+        <v>0.5368406552972123</v>
       </c>
       <c r="K1329">
-        <v>2.63</v>
+        <v>2.73</v>
       </c>
       <c r="L1329">
-        <v>2.92</v>
+        <v>3.04</v>
       </c>
       <c r="M1329">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="N1329">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="O1329">
         <v>1</v>
       </c>
       <c r="P1329" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="1330" spans="1:16">
       <c r="A1330" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1330" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C1330">
-        <v>1.507440140601135</v>
+        <v>1.492010522817169</v>
       </c>
       <c r="D1330" t="s">
         <v>341</v>
@@ -68341,22 +68344,22 @@
         <v>1</v>
       </c>
       <c r="G1330">
-        <v>0.004352559859398865</v>
+        <v>0.004347989477182831</v>
       </c>
       <c r="H1330">
         <v>0.004382559859398866</v>
       </c>
       <c r="I1330">
-        <v>0.0299999999999998</v>
+        <v>0.04542961778396526</v>
       </c>
       <c r="J1330">
         <v>0.5429617783965135</v>
       </c>
       <c r="K1330">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="L1330">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="M1330">
         <v>2.62</v>
@@ -68373,46 +68376,46 @@
     </row>
     <row r="1331" spans="1:16">
       <c r="A1331" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1331" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="C1331">
-        <v>1.55372899395303</v>
+        <v>1.507440140601135</v>
       </c>
       <c r="D1331" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E1331">
-        <v>1.518299376169065</v>
+        <v>1.537440140601135</v>
       </c>
       <c r="F1331">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1331">
-        <v>0.004366271006046971</v>
+        <v>0.004352559859398865</v>
       </c>
       <c r="H1331">
-        <v>0.004341700623830935</v>
+        <v>0.004382559859398866</v>
       </c>
       <c r="I1331">
-        <v>0.03542961778396503</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="J1331">
         <v>0.5429617783965135</v>
       </c>
       <c r="K1331">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="L1331">
+        <v>2.93</v>
+      </c>
+      <c r="M1331">
+        <v>2.62</v>
+      </c>
+      <c r="N1331">
         <v>2.96</v>
-      </c>
-      <c r="M1331">
-        <v>2.6</v>
-      </c>
-      <c r="N1331">
-        <v>2.93</v>
       </c>
       <c r="O1331">
         <v>1</v>
@@ -68423,46 +68426,46 @@
     </row>
     <row r="1332" spans="1:16">
       <c r="A1332" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1332" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="C1332">
-        <v>1.508299376169065</v>
+        <v>1.55372899395303</v>
       </c>
       <c r="D1332" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="E1332">
-        <v>1.5428697583851</v>
+        <v>1.518299376169065</v>
       </c>
       <c r="F1332">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1332">
-        <v>0.004331700623830935</v>
+        <v>0.004366271006046971</v>
       </c>
       <c r="H1332">
-        <v>0.0043771302416149</v>
+        <v>0.004341700623830935</v>
       </c>
       <c r="I1332">
-        <v>0.03457038221603503</v>
+        <v>0.03542961778396503</v>
       </c>
       <c r="J1332">
         <v>0.5429617783965135</v>
       </c>
       <c r="K1332">
+        <v>2.59</v>
+      </c>
+      <c r="L1332">
+        <v>2.96</v>
+      </c>
+      <c r="M1332">
         <v>2.6</v>
       </c>
-      <c r="L1332">
-        <v>2.92</v>
-      </c>
-      <c r="M1332">
-        <v>2.61</v>
-      </c>
       <c r="N1332">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="O1332">
         <v>1</v>
@@ -68473,13 +68476,13 @@
     </row>
     <row r="1333" spans="1:16">
       <c r="A1333" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1333" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C1333">
-        <v>1.5028697583851</v>
+        <v>1.508299376169065</v>
       </c>
       <c r="D1333" t="s">
         <v>340</v>
@@ -68491,19 +68494,19 @@
         <v>1</v>
       </c>
       <c r="G1333">
-        <v>0.0043371302416149</v>
+        <v>0.004331700623830935</v>
       </c>
       <c r="H1333">
         <v>0.0043771302416149</v>
       </c>
       <c r="I1333">
-        <v>0.04000000000000004</v>
+        <v>0.03457038221603503</v>
       </c>
       <c r="J1333">
         <v>0.5429617783965135</v>
       </c>
       <c r="K1333">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="L1333">
         <v>2.92</v>
@@ -68523,46 +68526,46 @@
     </row>
     <row r="1334" spans="1:16">
       <c r="A1334" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1334" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C1334">
-        <v>1.551151287249239</v>
+        <v>1.5028697583851</v>
       </c>
       <c r="D1334" t="s">
-        <v>195</v>
+        <v>340</v>
       </c>
       <c r="E1334">
-        <v>1.507714344977518</v>
+        <v>1.5428697583851</v>
       </c>
       <c r="F1334">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1334">
-        <v>0.004428848712750761</v>
+        <v>0.0043371302416149</v>
       </c>
       <c r="H1334">
-        <v>0.004472285655022482</v>
+        <v>0.0043771302416149</v>
       </c>
       <c r="I1334">
-        <v>0.04343694227172112</v>
+        <v>0.04000000000000004</v>
       </c>
       <c r="J1334">
         <v>0.5429617783965135</v>
       </c>
       <c r="K1334">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
       <c r="L1334">
-        <v>2.99</v>
+        <v>2.92</v>
       </c>
       <c r="M1334">
-        <v>2.73</v>
+        <v>2.61</v>
       </c>
       <c r="N1334">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="O1334">
         <v>1</v>
@@ -68573,13 +68576,13 @@
     </row>
     <row r="1335" spans="1:16">
       <c r="A1335" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1335" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="C1335">
-        <v>1.557714344977518</v>
+        <v>1.551151287249239</v>
       </c>
       <c r="D1335" t="s">
         <v>195</v>
@@ -68591,22 +68594,22 @@
         <v>-1</v>
       </c>
       <c r="G1335">
-        <v>0.004522285655022482</v>
+        <v>0.004428848712750761</v>
       </c>
       <c r="H1335">
         <v>0.004472285655022482</v>
       </c>
       <c r="I1335">
-        <v>0.04999999999999982</v>
+        <v>0.04343694227172112</v>
       </c>
       <c r="J1335">
         <v>0.5429617783965135</v>
       </c>
       <c r="K1335">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="L1335">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="M1335">
         <v>2.73</v>
@@ -68623,63 +68626,63 @@
     </row>
     <row r="1336" spans="1:16">
       <c r="A1336" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B1336" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C1336">
-        <v>1.472263189489777</v>
+        <v>1.557714344977518</v>
       </c>
       <c r="D1336" t="s">
-        <v>341</v>
+        <v>195</v>
       </c>
       <c r="E1336">
-        <v>1.517767892191336</v>
+        <v>1.507714344977518</v>
       </c>
       <c r="F1336">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1336">
-        <v>0.004367736810510224</v>
+        <v>0.004522285655022482</v>
       </c>
       <c r="H1336">
-        <v>0.004402232107808663</v>
+        <v>0.004472285655022482</v>
       </c>
       <c r="I1336">
-        <v>0.0455047027015596</v>
+        <v>0.04999999999999982</v>
       </c>
       <c r="J1336">
-        <v>0.5504702701559784</v>
+        <v>0.5429617783965135</v>
       </c>
       <c r="K1336">
-        <v>2.63</v>
+        <v>2.73</v>
       </c>
       <c r="L1336">
-        <v>2.92</v>
+        <v>3.04</v>
       </c>
       <c r="M1336">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="N1336">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="O1336">
         <v>1</v>
       </c>
       <c r="P1336" t="s">
-        <v>339</v>
+        <v>481</v>
       </c>
     </row>
     <row r="1337" spans="1:16">
       <c r="A1337" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1337" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C1337">
-        <v>1.487767892191337</v>
+        <v>1.472263189489777</v>
       </c>
       <c r="D1337" t="s">
         <v>341</v>
@@ -68691,22 +68694,22 @@
         <v>1</v>
       </c>
       <c r="G1337">
-        <v>0.004372232107808664</v>
+        <v>0.004367736810510224</v>
       </c>
       <c r="H1337">
         <v>0.004402232107808663</v>
       </c>
       <c r="I1337">
-        <v>0.0299999999999998</v>
+        <v>0.0455047027015596</v>
       </c>
       <c r="J1337">
         <v>0.5504702701559784</v>
       </c>
       <c r="K1337">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="L1337">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="M1337">
         <v>2.62</v>
@@ -68723,46 +68726,46 @@
     </row>
     <row r="1338" spans="1:16">
       <c r="A1338" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1338" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="C1338">
-        <v>1.534282000296016</v>
+        <v>1.487767892191337</v>
       </c>
       <c r="D1338" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E1338">
-        <v>1.498777297594456</v>
+        <v>1.517767892191336</v>
       </c>
       <c r="F1338">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1338">
-        <v>0.004385717999703984</v>
+        <v>0.004372232107808664</v>
       </c>
       <c r="H1338">
-        <v>0.004361222702405544</v>
+        <v>0.004402232107808663</v>
       </c>
       <c r="I1338">
-        <v>0.03550470270155981</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="J1338">
         <v>0.5504702701559784</v>
       </c>
       <c r="K1338">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="L1338">
+        <v>2.93</v>
+      </c>
+      <c r="M1338">
+        <v>2.62</v>
+      </c>
+      <c r="N1338">
         <v>2.96</v>
-      </c>
-      <c r="M1338">
-        <v>2.6</v>
-      </c>
-      <c r="N1338">
-        <v>2.93</v>
       </c>
       <c r="O1338">
         <v>1</v>
@@ -68773,46 +68776,46 @@
     </row>
     <row r="1339" spans="1:16">
       <c r="A1339" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1339" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="C1339">
-        <v>1.488777297594456</v>
+        <v>1.534282000296016</v>
       </c>
       <c r="D1339" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="E1339">
-        <v>1.523272594892896</v>
+        <v>1.498777297594456</v>
       </c>
       <c r="F1339">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1339">
-        <v>0.004351222702405544</v>
+        <v>0.004385717999703984</v>
       </c>
       <c r="H1339">
-        <v>0.004396727405107104</v>
+        <v>0.004361222702405544</v>
       </c>
       <c r="I1339">
-        <v>0.03449529729844047</v>
+        <v>0.03550470270155981</v>
       </c>
       <c r="J1339">
         <v>0.5504702701559784</v>
       </c>
       <c r="K1339">
+        <v>2.59</v>
+      </c>
+      <c r="L1339">
+        <v>2.96</v>
+      </c>
+      <c r="M1339">
         <v>2.6</v>
       </c>
-      <c r="L1339">
-        <v>2.92</v>
-      </c>
-      <c r="M1339">
-        <v>2.61</v>
-      </c>
       <c r="N1339">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="O1339">
         <v>1</v>
@@ -68823,13 +68826,13 @@
     </row>
     <row r="1340" spans="1:16">
       <c r="A1340" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1340" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C1340">
-        <v>1.483272594892896</v>
+        <v>1.488777297594456</v>
       </c>
       <c r="D1340" t="s">
         <v>340</v>
@@ -68841,19 +68844,19 @@
         <v>1</v>
       </c>
       <c r="G1340">
-        <v>0.004356727405107104</v>
+        <v>0.004351222702405544</v>
       </c>
       <c r="H1340">
         <v>0.004396727405107104</v>
       </c>
       <c r="I1340">
-        <v>0.04000000000000004</v>
+        <v>0.03449529729844047</v>
       </c>
       <c r="J1340">
         <v>0.5504702701559784</v>
       </c>
       <c r="K1340">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="L1340">
         <v>2.92</v>
@@ -68873,46 +68876,46 @@
     </row>
     <row r="1341" spans="1:16">
       <c r="A1341" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1341" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C1341">
-        <v>1.531253784086658</v>
+        <v>1.483272594892896</v>
       </c>
       <c r="D1341" t="s">
-        <v>195</v>
+        <v>340</v>
       </c>
       <c r="E1341">
-        <v>1.487216162474179</v>
+        <v>1.523272594892896</v>
       </c>
       <c r="F1341">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1341">
-        <v>0.004448746215913344</v>
+        <v>0.004356727405107104</v>
       </c>
       <c r="H1341">
-        <v>0.004492783837525821</v>
+        <v>0.004396727405107104</v>
       </c>
       <c r="I1341">
-        <v>0.04403762161247826</v>
+        <v>0.04000000000000004</v>
       </c>
       <c r="J1341">
         <v>0.5504702701559784</v>
       </c>
       <c r="K1341">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
       <c r="L1341">
-        <v>2.99</v>
+        <v>2.92</v>
       </c>
       <c r="M1341">
-        <v>2.73</v>
+        <v>2.61</v>
       </c>
       <c r="N1341">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="O1341">
         <v>1</v>
@@ -68923,13 +68926,13 @@
     </row>
     <row r="1342" spans="1:16">
       <c r="A1342" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1342" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="C1342">
-        <v>1.537216162474179</v>
+        <v>1.531253784086658</v>
       </c>
       <c r="D1342" t="s">
         <v>195</v>
@@ -68941,22 +68944,22 @@
         <v>-1</v>
       </c>
       <c r="G1342">
-        <v>0.004542783837525821</v>
+        <v>0.004448746215913344</v>
       </c>
       <c r="H1342">
         <v>0.004492783837525821</v>
       </c>
       <c r="I1342">
-        <v>0.04999999999999982</v>
+        <v>0.04403762161247826</v>
       </c>
       <c r="J1342">
         <v>0.5504702701559784</v>
       </c>
       <c r="K1342">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="L1342">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="M1342">
         <v>2.73</v>
@@ -68973,63 +68976,63 @@
     </row>
     <row r="1343" spans="1:16">
       <c r="A1343" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B1343" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C1343">
-        <v>1.448840538429687</v>
+        <v>1.537216162474179</v>
       </c>
       <c r="D1343" t="s">
-        <v>341</v>
+        <v>195</v>
       </c>
       <c r="E1343">
-        <v>1.49443430064098</v>
+        <v>1.487216162474179</v>
       </c>
       <c r="F1343">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1343">
-        <v>0.004391159461570314</v>
+        <v>0.004542783837525821</v>
       </c>
       <c r="H1343">
-        <v>0.00442556569935902</v>
+        <v>0.004492783837525821</v>
       </c>
       <c r="I1343">
-        <v>0.04559376221129385</v>
+        <v>0.04999999999999982</v>
       </c>
       <c r="J1343">
-        <v>0.5593762211293968</v>
+        <v>0.5504702701559784</v>
       </c>
       <c r="K1343">
-        <v>2.63</v>
+        <v>2.73</v>
       </c>
       <c r="L1343">
-        <v>2.92</v>
+        <v>3.04</v>
       </c>
       <c r="M1343">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="N1343">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="O1343">
         <v>1</v>
       </c>
       <c r="P1343" t="s">
-        <v>482</v>
+        <v>339</v>
       </c>
     </row>
     <row r="1344" spans="1:16">
       <c r="A1344" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1344" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C1344">
-        <v>1.464434300640981</v>
+        <v>1.448840538429687</v>
       </c>
       <c r="D1344" t="s">
         <v>341</v>
@@ -69041,22 +69044,22 @@
         <v>1</v>
       </c>
       <c r="G1344">
-        <v>0.00439556569935902</v>
+        <v>0.004391159461570314</v>
       </c>
       <c r="H1344">
         <v>0.00442556569935902</v>
       </c>
       <c r="I1344">
-        <v>0.0299999999999998</v>
+        <v>0.04559376221129385</v>
       </c>
       <c r="J1344">
         <v>0.5593762211293968</v>
       </c>
       <c r="K1344">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="L1344">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="M1344">
         <v>2.62</v>
@@ -69073,46 +69076,46 @@
     </row>
     <row r="1345" spans="1:16">
       <c r="A1345" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1345" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="C1345">
-        <v>1.511215587274862</v>
+        <v>1.464434300640981</v>
       </c>
       <c r="D1345" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E1345">
-        <v>1.475621825063568</v>
+        <v>1.49443430064098</v>
       </c>
       <c r="F1345">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1345">
-        <v>0.004408784412725138</v>
+        <v>0.00439556569935902</v>
       </c>
       <c r="H1345">
-        <v>0.004384378174936431</v>
+        <v>0.00442556569935902</v>
       </c>
       <c r="I1345">
-        <v>0.03559376221129407</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="J1345">
         <v>0.5593762211293968</v>
       </c>
       <c r="K1345">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="L1345">
+        <v>2.93</v>
+      </c>
+      <c r="M1345">
+        <v>2.62</v>
+      </c>
+      <c r="N1345">
         <v>2.96</v>
-      </c>
-      <c r="M1345">
-        <v>2.6</v>
-      </c>
-      <c r="N1345">
-        <v>2.93</v>
       </c>
       <c r="O1345">
         <v>1</v>
@@ -69123,46 +69126,46 @@
     </row>
     <row r="1346" spans="1:16">
       <c r="A1346" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1346" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="C1346">
-        <v>1.465621825063568</v>
+        <v>1.511215587274862</v>
       </c>
       <c r="D1346" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="E1346">
-        <v>1.500028062852274</v>
+        <v>1.475621825063568</v>
       </c>
       <c r="F1346">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1346">
-        <v>0.004374378174936432</v>
+        <v>0.004408784412725138</v>
       </c>
       <c r="H1346">
-        <v>0.004419971937147725</v>
+        <v>0.004384378174936431</v>
       </c>
       <c r="I1346">
-        <v>0.03440623778870622</v>
+        <v>0.03559376221129407</v>
       </c>
       <c r="J1346">
         <v>0.5593762211293968</v>
       </c>
       <c r="K1346">
+        <v>2.59</v>
+      </c>
+      <c r="L1346">
+        <v>2.96</v>
+      </c>
+      <c r="M1346">
         <v>2.6</v>
       </c>
-      <c r="L1346">
-        <v>2.92</v>
-      </c>
-      <c r="M1346">
-        <v>2.61</v>
-      </c>
       <c r="N1346">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="O1346">
         <v>1</v>
@@ -69173,13 +69176,13 @@
     </row>
     <row r="1347" spans="1:16">
       <c r="A1347" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1347" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C1347">
-        <v>1.460028062852274</v>
+        <v>1.465621825063568</v>
       </c>
       <c r="D1347" t="s">
         <v>340</v>
@@ -69191,19 +69194,19 @@
         <v>1</v>
       </c>
       <c r="G1347">
-        <v>0.004379971937147726</v>
+        <v>0.004374378174936432</v>
       </c>
       <c r="H1347">
         <v>0.004419971937147725</v>
       </c>
       <c r="I1347">
-        <v>0.04000000000000004</v>
+        <v>0.03440623778870622</v>
       </c>
       <c r="J1347">
         <v>0.5593762211293968</v>
       </c>
       <c r="K1347">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="L1347">
         <v>2.92</v>
@@ -69223,46 +69226,46 @@
     </row>
     <row r="1348" spans="1:16">
       <c r="A1348" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1348" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C1348">
-        <v>1.507653014007099</v>
+        <v>1.460028062852274</v>
       </c>
       <c r="D1348" t="s">
-        <v>195</v>
+        <v>340</v>
       </c>
       <c r="E1348">
-        <v>1.462902916316747</v>
+        <v>1.500028062852274</v>
       </c>
       <c r="F1348">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1348">
-        <v>0.004472346985992901</v>
+        <v>0.004379971937147726</v>
       </c>
       <c r="H1348">
-        <v>0.004517097083683254</v>
+        <v>0.004419971937147725</v>
       </c>
       <c r="I1348">
-        <v>0.04475009769035165</v>
+        <v>0.04000000000000004</v>
       </c>
       <c r="J1348">
         <v>0.5593762211293968</v>
       </c>
       <c r="K1348">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
       <c r="L1348">
-        <v>2.99</v>
+        <v>2.92</v>
       </c>
       <c r="M1348">
-        <v>2.73</v>
+        <v>2.61</v>
       </c>
       <c r="N1348">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="O1348">
         <v>1</v>
@@ -69273,13 +69276,13 @@
     </row>
     <row r="1349" spans="1:16">
       <c r="A1349" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1349" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="C1349">
-        <v>1.512902916316747</v>
+        <v>1.507653014007099</v>
       </c>
       <c r="D1349" t="s">
         <v>195</v>
@@ -69291,22 +69294,22 @@
         <v>-1</v>
       </c>
       <c r="G1349">
-        <v>0.004567097083683253</v>
+        <v>0.004472346985992901</v>
       </c>
       <c r="H1349">
         <v>0.004517097083683254</v>
       </c>
       <c r="I1349">
-        <v>0.04999999999999982</v>
+        <v>0.04475009769035165</v>
       </c>
       <c r="J1349">
         <v>0.5593762211293968</v>
       </c>
       <c r="K1349">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="L1349">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="M1349">
         <v>2.73</v>
@@ -69323,63 +69326,63 @@
     </row>
     <row r="1350" spans="1:16">
       <c r="A1350" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B1350" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C1350">
-        <v>1.42590638267437</v>
+        <v>1.512902916316747</v>
       </c>
       <c r="D1350" t="s">
-        <v>341</v>
+        <v>195</v>
       </c>
       <c r="E1350">
-        <v>1.471587346998802</v>
+        <v>1.462902916316747</v>
       </c>
       <c r="F1350">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1350">
-        <v>0.00441409361732563</v>
+        <v>0.004567097083683253</v>
       </c>
       <c r="H1350">
-        <v>0.004448412653001197</v>
+        <v>0.004517097083683254</v>
       </c>
       <c r="I1350">
-        <v>0.04568096432443203</v>
+        <v>0.04999999999999982</v>
       </c>
       <c r="J1350">
-        <v>0.5680964324432053</v>
+        <v>0.5593762211293968</v>
       </c>
       <c r="K1350">
-        <v>2.63</v>
+        <v>2.73</v>
       </c>
       <c r="L1350">
-        <v>2.92</v>
+        <v>3.04</v>
       </c>
       <c r="M1350">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="N1350">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="O1350">
         <v>1</v>
       </c>
       <c r="P1350" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="1351" spans="1:16">
       <c r="A1351" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1351" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="C1351">
-        <v>1.439992168620962</v>
+        <v>1.42590638267437</v>
       </c>
       <c r="D1351" t="s">
         <v>341</v>
@@ -69391,22 +69394,22 @@
         <v>1</v>
       </c>
       <c r="G1351">
-        <v>0.004360007831379038</v>
+        <v>0.00441409361732563</v>
       </c>
       <c r="H1351">
         <v>0.004448412653001197</v>
       </c>
       <c r="I1351">
-        <v>0.03159517837783965</v>
+        <v>0.04568096432443203</v>
       </c>
       <c r="J1351">
         <v>0.5680964324432053</v>
       </c>
       <c r="K1351">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="L1351">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="M1351">
         <v>2.62</v>
@@ -69423,13 +69426,13 @@
     </row>
     <row r="1352" spans="1:16">
       <c r="A1352" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1352" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="C1352">
-        <v>1.441587346998802</v>
+        <v>1.439992168620962</v>
       </c>
       <c r="D1352" t="s">
         <v>341</v>
@@ -69441,22 +69444,22 @@
         <v>1</v>
       </c>
       <c r="G1352">
-        <v>0.004418412653001198</v>
+        <v>0.004360007831379038</v>
       </c>
       <c r="H1352">
         <v>0.004448412653001197</v>
       </c>
       <c r="I1352">
-        <v>0.0299999999999998</v>
+        <v>0.03159517837783965</v>
       </c>
       <c r="J1352">
         <v>0.5680964324432053</v>
       </c>
       <c r="K1352">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="L1352">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="M1352">
         <v>2.62</v>
@@ -69473,46 +69476,46 @@
     </row>
     <row r="1353" spans="1:16">
       <c r="A1353" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1353" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="C1353">
-        <v>1.488630239972098</v>
+        <v>1.441587346998802</v>
       </c>
       <c r="D1353" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E1353">
-        <v>1.452949275647666</v>
+        <v>1.471587346998802</v>
       </c>
       <c r="F1353">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1353">
-        <v>0.004431369760027902</v>
+        <v>0.004418412653001198</v>
       </c>
       <c r="H1353">
-        <v>0.004407050724352334</v>
+        <v>0.004448412653001197</v>
       </c>
       <c r="I1353">
-        <v>0.03568096432443202</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="J1353">
         <v>0.5680964324432053</v>
       </c>
       <c r="K1353">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="L1353">
+        <v>2.93</v>
+      </c>
+      <c r="M1353">
+        <v>2.62</v>
+      </c>
+      <c r="N1353">
         <v>2.96</v>
-      </c>
-      <c r="M1353">
-        <v>2.6</v>
-      </c>
-      <c r="N1353">
-        <v>2.93</v>
       </c>
       <c r="O1353">
         <v>1</v>
@@ -69523,46 +69526,46 @@
     </row>
     <row r="1354" spans="1:16">
       <c r="A1354" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1354" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C1354">
-        <v>1.437268311323234</v>
+        <v>1.488630239972098</v>
       </c>
       <c r="D1354" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="E1354">
-        <v>1.477268311323234</v>
+        <v>1.452949275647666</v>
       </c>
       <c r="F1354">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1354">
-        <v>0.004402731688676766</v>
+        <v>0.004431369760027902</v>
       </c>
       <c r="H1354">
-        <v>0.004442731688676766</v>
+        <v>0.004407050724352334</v>
       </c>
       <c r="I1354">
-        <v>0.04000000000000004</v>
+        <v>0.03568096432443202</v>
       </c>
       <c r="J1354">
         <v>0.5680964324432053</v>
       </c>
       <c r="K1354">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="L1354">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="M1354">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="N1354">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="O1354">
         <v>1</v>
@@ -69573,46 +69576,46 @@
     </row>
     <row r="1355" spans="1:16">
       <c r="A1355" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1355" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C1355">
-        <v>1.484544454025506</v>
+        <v>1.437268311323234</v>
       </c>
       <c r="D1355" t="s">
-        <v>195</v>
+        <v>340</v>
       </c>
       <c r="E1355">
-        <v>1.43909673943005</v>
+        <v>1.477268311323234</v>
       </c>
       <c r="F1355">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1355">
-        <v>0.004495455545974494</v>
+        <v>0.004402731688676766</v>
       </c>
       <c r="H1355">
-        <v>0.004540903260569951</v>
+        <v>0.004442731688676766</v>
       </c>
       <c r="I1355">
-        <v>0.04544771459545638</v>
+        <v>0.04000000000000004</v>
       </c>
       <c r="J1355">
         <v>0.5680964324432053</v>
       </c>
       <c r="K1355">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
       <c r="L1355">
-        <v>2.99</v>
+        <v>2.92</v>
       </c>
       <c r="M1355">
-        <v>2.73</v>
+        <v>2.61</v>
       </c>
       <c r="N1355">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="O1355">
         <v>1</v>
@@ -69623,13 +69626,13 @@
     </row>
     <row r="1356" spans="1:16">
       <c r="A1356" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1356" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="C1356">
-        <v>1.48909673943005</v>
+        <v>1.484544454025506</v>
       </c>
       <c r="D1356" t="s">
         <v>195</v>
@@ -69641,22 +69644,22 @@
         <v>-1</v>
       </c>
       <c r="G1356">
-        <v>0.004590903260569951</v>
+        <v>0.004495455545974494</v>
       </c>
       <c r="H1356">
         <v>0.004540903260569951</v>
       </c>
       <c r="I1356">
-        <v>0.04999999999999982</v>
+        <v>0.04544771459545638</v>
       </c>
       <c r="J1356">
         <v>0.5680964324432053</v>
       </c>
       <c r="K1356">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="L1356">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="M1356">
         <v>2.73</v>
@@ -69673,63 +69676,63 @@
     </row>
     <row r="1357" spans="1:16">
       <c r="A1357" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B1357" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="C1357">
-        <v>1.411951954121605</v>
+        <v>1.48909673943005</v>
       </c>
       <c r="D1357" t="s">
-        <v>341</v>
+        <v>195</v>
       </c>
       <c r="E1357">
-        <v>1.443001603034477</v>
+        <v>1.43909673943005</v>
       </c>
       <c r="F1357">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1357">
-        <v>0.004388048045878395</v>
+        <v>0.004590903260569951</v>
       </c>
       <c r="H1357">
-        <v>0.004476998396965523</v>
+        <v>0.004540903260569951</v>
       </c>
       <c r="I1357">
-        <v>0.03104964891287176</v>
+        <v>0.04999999999999982</v>
       </c>
       <c r="J1357">
-        <v>0.579007021742566</v>
+        <v>0.5680964324432053</v>
       </c>
       <c r="K1357">
-        <v>2.57</v>
+        <v>2.73</v>
       </c>
       <c r="L1357">
-        <v>2.9</v>
+        <v>3.04</v>
       </c>
       <c r="M1357">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="N1357">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="O1357">
         <v>1</v>
       </c>
       <c r="P1357" t="s">
-        <v>183</v>
+        <v>483</v>
       </c>
     </row>
     <row r="1358" spans="1:16">
       <c r="A1358" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1358" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="C1358">
-        <v>1.413001603034477</v>
+        <v>1.411951954121605</v>
       </c>
       <c r="D1358" t="s">
         <v>341</v>
@@ -69741,22 +69744,22 @@
         <v>1</v>
       </c>
       <c r="G1358">
-        <v>0.004446998396965524</v>
+        <v>0.004388048045878395</v>
       </c>
       <c r="H1358">
         <v>0.004476998396965523</v>
       </c>
       <c r="I1358">
-        <v>0.0299999999999998</v>
+        <v>0.03104964891287176</v>
       </c>
       <c r="J1358">
         <v>0.579007021742566</v>
       </c>
       <c r="K1358">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="L1358">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="M1358">
         <v>2.62</v>
@@ -69773,46 +69776,46 @@
     </row>
     <row r="1359" spans="1:16">
       <c r="A1359" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1359" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="C1359">
-        <v>1.460371813686754</v>
+        <v>1.413001603034477</v>
       </c>
       <c r="D1359" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E1359">
-        <v>1.424581743469328</v>
+        <v>1.443001603034477</v>
       </c>
       <c r="F1359">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1359">
-        <v>0.004459628186313246</v>
+        <v>0.004446998396965524</v>
       </c>
       <c r="H1359">
-        <v>0.004435418256530672</v>
+        <v>0.004476998396965523</v>
       </c>
       <c r="I1359">
-        <v>0.03579007021742564</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="J1359">
         <v>0.579007021742566</v>
       </c>
       <c r="K1359">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="L1359">
+        <v>2.93</v>
+      </c>
+      <c r="M1359">
+        <v>2.62</v>
+      </c>
+      <c r="N1359">
         <v>2.96</v>
-      </c>
-      <c r="M1359">
-        <v>2.6</v>
-      </c>
-      <c r="N1359">
-        <v>2.93</v>
       </c>
       <c r="O1359">
         <v>1</v>
@@ -69823,46 +69826,46 @@
     </row>
     <row r="1360" spans="1:16">
       <c r="A1360" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1360" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C1360">
-        <v>1.408791673251903</v>
+        <v>1.460371813686754</v>
       </c>
       <c r="D1360" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="E1360">
-        <v>1.448791673251903</v>
+        <v>1.424581743469328</v>
       </c>
       <c r="F1360">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1360">
-        <v>0.004431208326748097</v>
+        <v>0.004459628186313246</v>
       </c>
       <c r="H1360">
-        <v>0.004471208326748097</v>
+        <v>0.004435418256530672</v>
       </c>
       <c r="I1360">
-        <v>0.04000000000000004</v>
+        <v>0.03579007021742564</v>
       </c>
       <c r="J1360">
         <v>0.579007021742566</v>
       </c>
       <c r="K1360">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="L1360">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="M1360">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="N1360">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="O1360">
         <v>1</v>
@@ -69873,46 +69876,46 @@
     </row>
     <row r="1361" spans="1:16">
       <c r="A1361" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1361" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C1361">
-        <v>1.4556313923822</v>
+        <v>1.408791673251903</v>
       </c>
       <c r="D1361" t="s">
-        <v>195</v>
+        <v>340</v>
       </c>
       <c r="E1361">
-        <v>1.409310830642795</v>
+        <v>1.448791673251903</v>
       </c>
       <c r="F1361">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1361">
-        <v>0.004524368607617801</v>
+        <v>0.004431208326748097</v>
       </c>
       <c r="H1361">
-        <v>0.004570689169357206</v>
+        <v>0.004471208326748097</v>
       </c>
       <c r="I1361">
-        <v>0.04632056173940535</v>
+        <v>0.04000000000000004</v>
       </c>
       <c r="J1361">
         <v>0.579007021742566</v>
       </c>
       <c r="K1361">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
       <c r="L1361">
-        <v>2.99</v>
+        <v>2.92</v>
       </c>
       <c r="M1361">
-        <v>2.73</v>
+        <v>2.61</v>
       </c>
       <c r="N1361">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="O1361">
         <v>1</v>
@@ -69923,13 +69926,13 @@
     </row>
     <row r="1362" spans="1:16">
       <c r="A1362" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1362" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="C1362">
-        <v>1.459310830642795</v>
+        <v>1.4556313923822</v>
       </c>
       <c r="D1362" t="s">
         <v>195</v>
@@ -69941,22 +69944,22 @@
         <v>-1</v>
       </c>
       <c r="G1362">
-        <v>0.004620689169357205</v>
+        <v>0.004524368607617801</v>
       </c>
       <c r="H1362">
         <v>0.004570689169357206</v>
       </c>
       <c r="I1362">
-        <v>0.04999999999999982</v>
+        <v>0.04632056173940535</v>
       </c>
       <c r="J1362">
         <v>0.579007021742566</v>
       </c>
       <c r="K1362">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="L1362">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="M1362">
         <v>2.73</v>
@@ -69973,96 +69976,96 @@
     </row>
     <row r="1363" spans="1:16">
       <c r="A1363" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B1363" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C1363">
-        <v>1.394785989820947</v>
+        <v>1.459310830642795</v>
       </c>
       <c r="D1363" t="s">
-        <v>341</v>
+        <v>195</v>
       </c>
       <c r="E1363">
-        <v>1.424785989820947</v>
+        <v>1.409310830642795</v>
       </c>
       <c r="F1363">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1363">
-        <v>0.004465214010179054</v>
+        <v>0.004620689169357205</v>
       </c>
       <c r="H1363">
-        <v>0.004495214010179053</v>
+        <v>0.004570689169357206</v>
       </c>
       <c r="I1363">
-        <v>0.0299999999999998</v>
+        <v>0.04999999999999982</v>
       </c>
       <c r="J1363">
-        <v>0.5859595458698675</v>
+        <v>0.579007021742566</v>
       </c>
       <c r="K1363">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="L1363">
-        <v>2.93</v>
+        <v>3.04</v>
       </c>
       <c r="M1363">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="N1363">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="O1363">
         <v>1</v>
       </c>
       <c r="P1363" t="s">
-        <v>484</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1364" spans="1:16">
       <c r="A1364" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1364" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="C1364">
-        <v>1.442364776197043</v>
+        <v>1.394785989820947</v>
       </c>
       <c r="D1364" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E1364">
-        <v>1.406505180738344</v>
+        <v>1.424785989820947</v>
       </c>
       <c r="F1364">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1364">
-        <v>0.004477635223802957</v>
+        <v>0.004465214010179054</v>
       </c>
       <c r="H1364">
-        <v>0.004453494819261656</v>
+        <v>0.004495214010179053</v>
       </c>
       <c r="I1364">
-        <v>0.03585959545869866</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="J1364">
         <v>0.5859595458698675</v>
       </c>
       <c r="K1364">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="L1364">
+        <v>2.93</v>
+      </c>
+      <c r="M1364">
+        <v>2.62</v>
+      </c>
+      <c r="N1364">
         <v>2.96</v>
-      </c>
-      <c r="M1364">
-        <v>2.6</v>
-      </c>
-      <c r="N1364">
-        <v>2.93</v>
       </c>
       <c r="O1364">
         <v>1</v>
@@ -70073,46 +70076,46 @@
     </row>
     <row r="1365" spans="1:16">
       <c r="A1365" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1365" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="C1365">
-        <v>1.396505180738344</v>
+        <v>1.442364776197043</v>
       </c>
       <c r="D1365" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="E1365">
-        <v>1.430645585279646</v>
+        <v>1.406505180738344</v>
       </c>
       <c r="F1365">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1365">
-        <v>0.004443494819261655</v>
+        <v>0.004477635223802957</v>
       </c>
       <c r="H1365">
-        <v>0.004489354414720354</v>
+        <v>0.004453494819261656</v>
       </c>
       <c r="I1365">
-        <v>0.03414040454130163</v>
+        <v>0.03585959545869866</v>
       </c>
       <c r="J1365">
         <v>0.5859595458698675</v>
       </c>
       <c r="K1365">
+        <v>2.59</v>
+      </c>
+      <c r="L1365">
+        <v>2.96</v>
+      </c>
+      <c r="M1365">
         <v>2.6</v>
       </c>
-      <c r="L1365">
-        <v>2.92</v>
-      </c>
-      <c r="M1365">
-        <v>2.61</v>
-      </c>
       <c r="N1365">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="O1365">
         <v>1</v>
@@ -70123,13 +70126,13 @@
     </row>
     <row r="1366" spans="1:16">
       <c r="A1366" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1366" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C1366">
-        <v>1.390645585279646</v>
+        <v>1.396505180738344</v>
       </c>
       <c r="D1366" t="s">
         <v>340</v>
@@ -70141,19 +70144,19 @@
         <v>1</v>
       </c>
       <c r="G1366">
-        <v>0.004449354414720354</v>
+        <v>0.004443494819261655</v>
       </c>
       <c r="H1366">
         <v>0.004489354414720354</v>
       </c>
       <c r="I1366">
-        <v>0.04000000000000004</v>
+        <v>0.03414040454130163</v>
       </c>
       <c r="J1366">
         <v>0.5859595458698675</v>
       </c>
       <c r="K1366">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="L1366">
         <v>2.92</v>
@@ -70173,46 +70176,46 @@
     </row>
     <row r="1367" spans="1:16">
       <c r="A1367" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1367" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C1367">
-        <v>1.437207203444851</v>
+        <v>1.390645585279646</v>
       </c>
       <c r="D1367" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="E1367">
-        <v>1.412751653399166</v>
+        <v>1.430645585279646</v>
       </c>
       <c r="F1367">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1367">
-        <v>0.004542792796555149</v>
+        <v>0.004449354414720354</v>
       </c>
       <c r="H1367">
-        <v>0.004647248346600834</v>
+        <v>0.004489354414720354</v>
       </c>
       <c r="I1367">
-        <v>0.02445555004568578</v>
+        <v>0.04000000000000004</v>
       </c>
       <c r="J1367">
         <v>0.5859595458698675</v>
       </c>
       <c r="K1367">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
       <c r="L1367">
-        <v>2.99</v>
+        <v>2.92</v>
       </c>
       <c r="M1367">
-        <v>2.76</v>
+        <v>2.61</v>
       </c>
       <c r="N1367">
-        <v>3.03</v>
+        <v>2.96</v>
       </c>
       <c r="O1367">
         <v>1</v>
@@ -70223,7 +70226,7 @@
     </row>
     <row r="1368" spans="1:16">
       <c r="A1368" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1368" t="s">
         <v>186</v>
@@ -70273,7 +70276,7 @@
     </row>
     <row r="1369" spans="1:16">
       <c r="A1369" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1369" t="s">
         <v>195</v>
@@ -70282,7 +70285,7 @@
         <v>1.390330439775262</v>
       </c>
       <c r="D1369" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E1369">
         <v>1.416505180738344</v>
@@ -70632,7 +70635,7 @@
         <v>1.370324650979806</v>
       </c>
       <c r="D1376" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E1376">
         <v>1.397452048552196</v>
@@ -70982,7 +70985,7 @@
         <v>1.348468159244095</v>
       </c>
       <c r="D1383" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E1383">
         <v>1.376636342137233</v>
@@ -71332,7 +71335,7 @@
         <v>1.33228122264937</v>
       </c>
       <c r="D1390" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E1390">
         <v>1.361220212047018</v>
@@ -71682,7 +71685,7 @@
         <v>1.317322248903738</v>
       </c>
       <c r="D1397" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E1397">
         <v>1.346973570384512</v>
@@ -72032,7 +72035,7 @@
         <v>1.305222122267559</v>
       </c>
       <c r="D1404" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E1404">
         <v>1.335449640254817</v>
@@ -72382,7 +72385,7 @@
         <v>1.295424450030335</v>
       </c>
       <c r="D1411" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E1411">
         <v>1.326118523838414</v>
@@ -72732,7 +72735,7 @@
         <v>1.28564566418373</v>
       </c>
       <c r="D1418" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E1418">
         <v>1.316805394460695</v>
@@ -73032,7 +73035,7 @@
         <v>1.275332342027732</v>
       </c>
       <c r="D1424" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E1424">
         <v>1.306983182883554</v>
@@ -73332,7 +73335,7 @@
         <v>1.264402492668623</v>
       </c>
       <c r="D1430" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E1430">
         <v>1.296573802541546</v>
@@ -73632,7 +73635,7 @@
         <v>1.254506730079175</v>
       </c>
       <c r="D1436" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E1436">
         <v>1.287149266742071</v>
@@ -73932,7 +73935,7 @@
         <v>1.248027450569951</v>
       </c>
       <c r="D1442" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E1442">
         <v>1.280978524352334</v>
@@ -74132,7 +74135,7 @@
         <v>1.240169547762036</v>
       </c>
       <c r="D1446" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E1446">
         <v>1.273494807392415</v>
@@ -74332,7 +74335,7 @@
         <v>1.233364943562871</v>
       </c>
       <c r="D1450" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E1450">
         <v>1.267014231964639</v>
@@ -74426,10 +74429,10 @@
         <v>1</v>
       </c>
       <c r="B1452" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="C1452">
-        <v>1.274920145077063</v>
+        <v>1.273144149456747</v>
       </c>
       <c r="D1452" t="s">
         <v>344</v>
@@ -74441,22 +74444,22 @@
         <v>-1</v>
       </c>
       <c r="G1452">
-        <v>0.004705079854922937</v>
+        <v>0.004806855850543253</v>
       </c>
       <c r="H1452">
         <v>0.004816271848900871</v>
       </c>
       <c r="I1452">
-        <v>0.03119199397793371</v>
+        <v>0.02941599835761832</v>
       </c>
       <c r="J1452">
         <v>0.6471999452539388</v>
       </c>
       <c r="K1452">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="L1452">
-        <v>2.99</v>
+        <v>3.04</v>
       </c>
       <c r="M1452">
         <v>2.76</v>
@@ -74476,28 +74479,28 @@
         <v>2</v>
       </c>
       <c r="B1453" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="C1453">
-        <v>1.273144149456747</v>
+        <v>1.223144149456747</v>
       </c>
       <c r="D1453" t="s">
-        <v>344</v>
+        <v>197</v>
       </c>
       <c r="E1453">
-        <v>1.243728151099129</v>
+        <v>1.257280142339759</v>
       </c>
       <c r="F1453">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1453">
-        <v>0.004806855850543253</v>
+        <v>0.004756855850543254</v>
       </c>
       <c r="H1453">
-        <v>0.004816271848900871</v>
+        <v>0.004622719857660241</v>
       </c>
       <c r="I1453">
-        <v>0.02941599835761832</v>
+        <v>0.03413599288301161</v>
       </c>
       <c r="J1453">
         <v>0.6471999452539388</v>
@@ -74506,13 +74509,13 @@
         <v>2.73</v>
       </c>
       <c r="L1453">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="M1453">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="N1453">
-        <v>3.03</v>
+        <v>2.94</v>
       </c>
       <c r="O1453">
         <v>1</v>
@@ -74523,96 +74526,96 @@
     </row>
     <row r="1454" spans="1:16">
       <c r="A1454" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1454" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="C1454">
-        <v>1.223144149456747</v>
+        <v>1.223972981196628</v>
       </c>
       <c r="D1454" t="s">
-        <v>198</v>
+        <v>340</v>
       </c>
       <c r="E1454">
-        <v>1.257280142339759</v>
+        <v>1.263972981196628</v>
       </c>
       <c r="F1454">
         <v>1</v>
       </c>
       <c r="G1454">
-        <v>0.004756855850543254</v>
+        <v>0.004616027018803372</v>
       </c>
       <c r="H1454">
-        <v>0.004622719857660241</v>
+        <v>0.004656027018803371</v>
       </c>
       <c r="I1454">
-        <v>0.03413599288301161</v>
+        <v>0.04000000000000004</v>
       </c>
       <c r="J1454">
-        <v>0.6471999452539388</v>
+        <v>0.6498187811507171</v>
       </c>
       <c r="K1454">
-        <v>2.73</v>
+        <v>2.61</v>
       </c>
       <c r="L1454">
-        <v>2.99</v>
+        <v>2.92</v>
       </c>
       <c r="M1454">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="N1454">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="O1454">
         <v>1</v>
       </c>
       <c r="P1454" t="s">
-        <v>493</v>
+        <v>343</v>
       </c>
     </row>
     <row r="1455" spans="1:16">
       <c r="A1455" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1455" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C1455">
-        <v>1.223972981196628</v>
+        <v>1.265994727458542</v>
       </c>
       <c r="D1455" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="E1455">
-        <v>1.263972981196628</v>
+        <v>1.236500164024021</v>
       </c>
       <c r="F1455">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1455">
-        <v>0.004616027018803372</v>
+        <v>0.004814005272541458</v>
       </c>
       <c r="H1455">
-        <v>0.004656027018803371</v>
+        <v>0.00482349983597598</v>
       </c>
       <c r="I1455">
-        <v>0.04000000000000004</v>
+        <v>0.02949456343452161</v>
       </c>
       <c r="J1455">
         <v>0.6498187811507171</v>
       </c>
       <c r="K1455">
-        <v>2.61</v>
+        <v>2.73</v>
       </c>
       <c r="L1455">
-        <v>2.92</v>
+        <v>3.04</v>
       </c>
       <c r="M1455">
-        <v>2.61</v>
+        <v>2.76</v>
       </c>
       <c r="N1455">
-        <v>2.96</v>
+        <v>3.03</v>
       </c>
       <c r="O1455">
         <v>1</v>
@@ -74623,46 +74626,46 @@
     </row>
     <row r="1456" spans="1:16">
       <c r="A1456" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1456" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C1456">
-        <v>1.2679802299506</v>
+        <v>1.215994727458543</v>
       </c>
       <c r="D1456" t="s">
-        <v>344</v>
+        <v>197</v>
       </c>
       <c r="E1456">
-        <v>1.236500164024021</v>
+        <v>1.250471169008135</v>
       </c>
       <c r="F1456">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1456">
-        <v>0.0047120197700494</v>
+        <v>0.004764005272541458</v>
       </c>
       <c r="H1456">
-        <v>0.00482349983597598</v>
+        <v>0.004629528830991865</v>
       </c>
       <c r="I1456">
-        <v>0.03148006592657926</v>
+        <v>0.03447644154959284</v>
       </c>
       <c r="J1456">
         <v>0.6498187811507171</v>
       </c>
       <c r="K1456">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="L1456">
         <v>2.99</v>
       </c>
       <c r="M1456">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="N1456">
-        <v>3.03</v>
+        <v>2.94</v>
       </c>
       <c r="O1456">
         <v>1</v>
@@ -74673,146 +74676,146 @@
     </row>
     <row r="1457" spans="1:16">
       <c r="A1457" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1457" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C1457">
-        <v>1.265994727458542</v>
+        <v>1.213361651402694</v>
       </c>
       <c r="D1457" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="E1457">
-        <v>1.236500164024021</v>
+        <v>1.253361651402694</v>
       </c>
       <c r="F1457">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1457">
-        <v>0.004814005272541458</v>
+        <v>0.004626638348597305</v>
       </c>
       <c r="H1457">
-        <v>0.00482349983597598</v>
+        <v>0.004666638348597305</v>
       </c>
       <c r="I1457">
-        <v>0.02949456343452161</v>
+        <v>0.04000000000000004</v>
       </c>
       <c r="J1457">
-        <v>0.6498187811507171</v>
+        <v>0.6538844247499256</v>
       </c>
       <c r="K1457">
-        <v>2.73</v>
+        <v>2.61</v>
       </c>
       <c r="L1457">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="M1457">
-        <v>2.76</v>
+        <v>2.61</v>
       </c>
       <c r="N1457">
-        <v>3.03</v>
+        <v>2.96</v>
       </c>
       <c r="O1457">
         <v>1</v>
       </c>
       <c r="P1457" t="s">
-        <v>343</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1458" spans="1:16">
       <c r="A1458" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1458" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C1458">
-        <v>1.215994727458543</v>
+        <v>1.257206274412697</v>
       </c>
       <c r="D1458" t="s">
-        <v>198</v>
+        <v>344</v>
       </c>
       <c r="E1458">
-        <v>1.250471169008135</v>
+        <v>1.225278987690205</v>
       </c>
       <c r="F1458">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1458">
-        <v>0.004764005272541458</v>
+        <v>0.004722793725587303</v>
       </c>
       <c r="H1458">
-        <v>0.004629528830991865</v>
+        <v>0.004834721012309794</v>
       </c>
       <c r="I1458">
-        <v>0.03447644154959284</v>
+        <v>0.03192728672249223</v>
       </c>
       <c r="J1458">
-        <v>0.6498187811507171</v>
+        <v>0.6538844247499256</v>
       </c>
       <c r="K1458">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="L1458">
         <v>2.99</v>
       </c>
       <c r="M1458">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="N1458">
-        <v>2.94</v>
+        <v>3.03</v>
       </c>
       <c r="O1458">
         <v>1</v>
       </c>
       <c r="P1458" t="s">
-        <v>343</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1459" spans="1:16">
       <c r="A1459" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1459" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C1459">
-        <v>1.213361651402694</v>
+        <v>1.254895520432703</v>
       </c>
       <c r="D1459" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="E1459">
-        <v>1.253361651402694</v>
+        <v>1.225278987690205</v>
       </c>
       <c r="F1459">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1459">
-        <v>0.004626638348597305</v>
+        <v>0.004825104479567297</v>
       </c>
       <c r="H1459">
-        <v>0.004666638348597305</v>
+        <v>0.004834721012309794</v>
       </c>
       <c r="I1459">
-        <v>0.04000000000000004</v>
+        <v>0.02961653274249798</v>
       </c>
       <c r="J1459">
         <v>0.6538844247499256</v>
       </c>
       <c r="K1459">
-        <v>2.61</v>
+        <v>2.73</v>
       </c>
       <c r="L1459">
-        <v>2.92</v>
+        <v>3.04</v>
       </c>
       <c r="M1459">
-        <v>2.61</v>
+        <v>2.76</v>
       </c>
       <c r="N1459">
-        <v>2.96</v>
+        <v>3.03</v>
       </c>
       <c r="O1459">
         <v>1</v>
@@ -74823,46 +74826,46 @@
     </row>
     <row r="1460" spans="1:16">
       <c r="A1460" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1460" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C1460">
-        <v>1.257206274412697</v>
+        <v>1.204895520432703</v>
       </c>
       <c r="D1460" t="s">
-        <v>344</v>
+        <v>197</v>
       </c>
       <c r="E1460">
-        <v>1.225278987690205</v>
+        <v>1.239900495650193</v>
       </c>
       <c r="F1460">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1460">
-        <v>0.004722793725587303</v>
+        <v>0.004775104479567297</v>
       </c>
       <c r="H1460">
-        <v>0.004834721012309794</v>
+        <v>0.004640099504349807</v>
       </c>
       <c r="I1460">
-        <v>0.03192728672249223</v>
+        <v>0.03500497521748991</v>
       </c>
       <c r="J1460">
         <v>0.6538844247499256</v>
       </c>
       <c r="K1460">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="L1460">
         <v>2.99</v>
       </c>
       <c r="M1460">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="N1460">
-        <v>3.03</v>
+        <v>2.94</v>
       </c>
       <c r="O1460">
         <v>1</v>
@@ -74873,146 +74876,146 @@
     </row>
     <row r="1461" spans="1:16">
       <c r="A1461" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1461" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C1461">
-        <v>1.254895520432703</v>
+        <v>1.205165186955779</v>
       </c>
       <c r="D1461" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="E1461">
-        <v>1.225278987690205</v>
+        <v>1.245165186955779</v>
       </c>
       <c r="F1461">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1461">
-        <v>0.004825104479567297</v>
+        <v>0.00463483481304422</v>
       </c>
       <c r="H1461">
-        <v>0.004834721012309794</v>
+        <v>0.004674834813044221</v>
       </c>
       <c r="I1461">
-        <v>0.02961653274249798</v>
+        <v>0.04000000000000004</v>
       </c>
       <c r="J1461">
-        <v>0.6538844247499256</v>
+        <v>0.6570248325839926</v>
       </c>
       <c r="K1461">
-        <v>2.73</v>
+        <v>2.61</v>
       </c>
       <c r="L1461">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="M1461">
-        <v>2.76</v>
+        <v>2.61</v>
       </c>
       <c r="N1461">
-        <v>3.03</v>
+        <v>2.96</v>
       </c>
       <c r="O1461">
         <v>1</v>
       </c>
       <c r="P1461" t="s">
-        <v>185</v>
+        <v>494</v>
       </c>
     </row>
     <row r="1462" spans="1:16">
       <c r="A1462" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1462" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C1462">
-        <v>1.204895520432703</v>
+        <v>1.24888419365242</v>
       </c>
       <c r="D1462" t="s">
-        <v>198</v>
+        <v>344</v>
       </c>
       <c r="E1462">
-        <v>1.239900495650193</v>
+        <v>1.21661146206818</v>
       </c>
       <c r="F1462">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1462">
-        <v>0.004775104479567297</v>
+        <v>0.004731115806347581</v>
       </c>
       <c r="H1462">
-        <v>0.004640099504349807</v>
+        <v>0.004843388537931819</v>
       </c>
       <c r="I1462">
-        <v>0.03500497521748991</v>
+        <v>0.03227273158423949</v>
       </c>
       <c r="J1462">
-        <v>0.6538844247499256</v>
+        <v>0.6570248325839926</v>
       </c>
       <c r="K1462">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="L1462">
         <v>2.99</v>
       </c>
       <c r="M1462">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="N1462">
-        <v>2.94</v>
+        <v>3.03</v>
       </c>
       <c r="O1462">
         <v>1</v>
       </c>
       <c r="P1462" t="s">
-        <v>185</v>
+        <v>494</v>
       </c>
     </row>
     <row r="1463" spans="1:16">
       <c r="A1463" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1463" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C1463">
-        <v>1.205165186955779</v>
+        <v>1.2463222070457</v>
       </c>
       <c r="D1463" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="E1463">
-        <v>1.245165186955779</v>
+        <v>1.21661146206818</v>
       </c>
       <c r="F1463">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1463">
-        <v>0.00463483481304422</v>
+        <v>0.004833677792954299</v>
       </c>
       <c r="H1463">
-        <v>0.004674834813044221</v>
+        <v>0.004843388537931819</v>
       </c>
       <c r="I1463">
-        <v>0.04000000000000004</v>
+        <v>0.0297107449775198</v>
       </c>
       <c r="J1463">
         <v>0.6570248325839926</v>
       </c>
       <c r="K1463">
-        <v>2.61</v>
+        <v>2.73</v>
       </c>
       <c r="L1463">
-        <v>2.92</v>
+        <v>3.04</v>
       </c>
       <c r="M1463">
-        <v>2.61</v>
+        <v>2.76</v>
       </c>
       <c r="N1463">
-        <v>2.96</v>
+        <v>3.03</v>
       </c>
       <c r="O1463">
         <v>1</v>
@@ -75023,46 +75026,46 @@
     </row>
     <row r="1464" spans="1:16">
       <c r="A1464" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1464" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C1464">
-        <v>1.24888419365242</v>
+        <v>1.1963222070457</v>
       </c>
       <c r="D1464" t="s">
-        <v>344</v>
+        <v>197</v>
       </c>
       <c r="E1464">
-        <v>1.21661146206818</v>
+        <v>1.231735435281619</v>
       </c>
       <c r="F1464">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1464">
-        <v>0.004731115806347581</v>
+        <v>0.0047836777929543</v>
       </c>
       <c r="H1464">
-        <v>0.004843388537931819</v>
+        <v>0.004648264564718381</v>
       </c>
       <c r="I1464">
-        <v>0.03227273158423949</v>
+        <v>0.03541322823591875</v>
       </c>
       <c r="J1464">
         <v>0.6570248325839926</v>
       </c>
       <c r="K1464">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="L1464">
         <v>2.99</v>
       </c>
       <c r="M1464">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="N1464">
-        <v>3.03</v>
+        <v>2.94</v>
       </c>
       <c r="O1464">
         <v>1</v>
@@ -75073,40 +75076,40 @@
     </row>
     <row r="1465" spans="1:16">
       <c r="A1465" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1465" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C1465">
-        <v>1.25289245537154</v>
+        <v>1.241877668106339</v>
       </c>
       <c r="D1465" t="s">
         <v>344</v>
       </c>
       <c r="E1465">
-        <v>1.21661146206818</v>
+        <v>1.20931409961264</v>
       </c>
       <c r="F1465">
         <v>-1</v>
       </c>
       <c r="G1465">
-        <v>0.004827107544628459</v>
+        <v>0.004738122331893661</v>
       </c>
       <c r="H1465">
-        <v>0.004843388537931819</v>
+        <v>0.00485068590038736</v>
       </c>
       <c r="I1465">
-        <v>0.03628099330335965</v>
+        <v>0.03256356849369957</v>
       </c>
       <c r="J1465">
-        <v>0.6570248325839926</v>
+        <v>0.6596688044881739</v>
       </c>
       <c r="K1465">
-        <v>2.72</v>
+        <v>2.65</v>
       </c>
       <c r="L1465">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="M1465">
         <v>2.76</v>
@@ -75118,101 +75121,101 @@
         <v>1</v>
       </c>
       <c r="P1465" t="s">
-        <v>494</v>
+        <v>190</v>
       </c>
     </row>
     <row r="1466" spans="1:16">
       <c r="A1466" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1466" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C1466">
-        <v>1.1963222070457</v>
+        <v>1.245700851792167</v>
       </c>
       <c r="D1466" t="s">
-        <v>198</v>
+        <v>344</v>
       </c>
       <c r="E1466">
-        <v>1.231735435281619</v>
+        <v>1.20931409961264</v>
       </c>
       <c r="F1466">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1466">
-        <v>0.0047836777929543</v>
+        <v>0.004834299148207833</v>
       </c>
       <c r="H1466">
-        <v>0.004648264564718381</v>
+        <v>0.00485068590038736</v>
       </c>
       <c r="I1466">
-        <v>0.03541322823591875</v>
+        <v>0.03638675217952692</v>
       </c>
       <c r="J1466">
-        <v>0.6570248325839926</v>
+        <v>0.6596688044881739</v>
       </c>
       <c r="K1466">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="L1466">
-        <v>2.99</v>
+        <v>3.04</v>
       </c>
       <c r="M1466">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="N1466">
-        <v>2.94</v>
+        <v>3.03</v>
       </c>
       <c r="O1466">
         <v>1</v>
       </c>
       <c r="P1466" t="s">
-        <v>494</v>
+        <v>190</v>
       </c>
     </row>
     <row r="1467" spans="1:16">
       <c r="A1467" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1467" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C1467">
-        <v>1.241877668106339</v>
+        <v>1.189104163747285</v>
       </c>
       <c r="D1467" t="s">
-        <v>344</v>
+        <v>197</v>
       </c>
       <c r="E1467">
-        <v>1.20931409961264</v>
+        <v>1.224861108330748</v>
       </c>
       <c r="F1467">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1467">
-        <v>0.004738122331893661</v>
+        <v>0.004790895836252715</v>
       </c>
       <c r="H1467">
-        <v>0.00485068590038736</v>
+        <v>0.004655138891669252</v>
       </c>
       <c r="I1467">
-        <v>0.03256356849369957</v>
+        <v>0.03575694458346224</v>
       </c>
       <c r="J1467">
         <v>0.6596688044881739</v>
       </c>
       <c r="K1467">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="L1467">
         <v>2.99</v>
       </c>
       <c r="M1467">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="N1467">
-        <v>3.03</v>
+        <v>2.94</v>
       </c>
       <c r="O1467">
         <v>1</v>
@@ -75223,40 +75226,40 @@
     </row>
     <row r="1468" spans="1:16">
       <c r="A1468" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1468" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C1468">
-        <v>1.245700851792167</v>
+        <v>1.236863587030822</v>
       </c>
       <c r="D1468" t="s">
         <v>344</v>
       </c>
       <c r="E1468">
-        <v>1.20931409961264</v>
+        <v>1.204091886869838</v>
       </c>
       <c r="F1468">
         <v>-1</v>
       </c>
       <c r="G1468">
-        <v>0.004834299148207833</v>
+        <v>0.004743136412969178</v>
       </c>
       <c r="H1468">
-        <v>0.00485068590038736</v>
+        <v>0.004855908113130162</v>
       </c>
       <c r="I1468">
-        <v>0.03638675217952692</v>
+        <v>0.03277170016098485</v>
       </c>
       <c r="J1468">
-        <v>0.6596688044881739</v>
+        <v>0.6615609105544067</v>
       </c>
       <c r="K1468">
-        <v>2.72</v>
+        <v>2.65</v>
       </c>
       <c r="L1468">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="M1468">
         <v>2.76</v>
@@ -75268,101 +75271,101 @@
         <v>1</v>
       </c>
       <c r="P1468" t="s">
-        <v>190</v>
+        <v>340</v>
       </c>
     </row>
     <row r="1469" spans="1:16">
       <c r="A1469" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1469" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C1469">
-        <v>1.189104163747285</v>
+        <v>1.240554323292014</v>
       </c>
       <c r="D1469" t="s">
-        <v>198</v>
+        <v>344</v>
       </c>
       <c r="E1469">
-        <v>1.224861108330748</v>
+        <v>1.204091886869838</v>
       </c>
       <c r="F1469">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1469">
-        <v>0.004790895836252715</v>
+        <v>0.004839445676707986</v>
       </c>
       <c r="H1469">
-        <v>0.004655138891669252</v>
+        <v>0.004855908113130162</v>
       </c>
       <c r="I1469">
-        <v>0.03575694458346224</v>
+        <v>0.03646243642217617</v>
       </c>
       <c r="J1469">
-        <v>0.6596688044881739</v>
+        <v>0.6615609105544067</v>
       </c>
       <c r="K1469">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="L1469">
-        <v>2.99</v>
+        <v>3.04</v>
       </c>
       <c r="M1469">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="N1469">
-        <v>2.94</v>
+        <v>3.03</v>
       </c>
       <c r="O1469">
         <v>1</v>
       </c>
       <c r="P1469" t="s">
-        <v>190</v>
+        <v>340</v>
       </c>
     </row>
     <row r="1470" spans="1:16">
       <c r="A1470" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1470" t="s">
+        <v>195</v>
+      </c>
+      <c r="C1470">
+        <v>1.18393871418647</v>
+      </c>
+      <c r="D1470" t="s">
         <v>197</v>
       </c>
-      <c r="C1470">
-        <v>1.240094805241911</v>
-      </c>
-      <c r="D1470" t="s">
-        <v>344</v>
-      </c>
       <c r="E1470">
-        <v>1.204091886869838</v>
+        <v>1.219941632558543</v>
       </c>
       <c r="F1470">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1470">
-        <v>0.00471990519475809</v>
+        <v>0.004796061285813531</v>
       </c>
       <c r="H1470">
-        <v>0.004855908113130162</v>
+        <v>0.004660058367441457</v>
       </c>
       <c r="I1470">
-        <v>0.03600291837207292</v>
+        <v>0.0360029183720727</v>
       </c>
       <c r="J1470">
         <v>0.6615609105544067</v>
       </c>
       <c r="K1470">
-        <v>2.63</v>
+        <v>2.73</v>
       </c>
       <c r="L1470">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="M1470">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="N1470">
-        <v>3.03</v>
+        <v>2.94</v>
       </c>
       <c r="O1470">
         <v>1</v>
@@ -75373,34 +75376,34 @@
     </row>
     <row r="1471" spans="1:16">
       <c r="A1471" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1471" t="s">
         <v>196</v>
       </c>
       <c r="C1471">
-        <v>1.240554323292014</v>
+        <v>1.238510606702118</v>
       </c>
       <c r="D1471" t="s">
         <v>344</v>
       </c>
       <c r="E1471">
-        <v>1.204091886869838</v>
+        <v>1.202018115624208</v>
       </c>
       <c r="F1471">
         <v>-1</v>
       </c>
       <c r="G1471">
-        <v>0.004839445676707986</v>
+        <v>0.004841489393297882</v>
       </c>
       <c r="H1471">
-        <v>0.004855908113130162</v>
+        <v>0.004857981884375791</v>
       </c>
       <c r="I1471">
-        <v>0.03646243642217617</v>
+        <v>0.03649249107790986</v>
       </c>
       <c r="J1471">
-        <v>0.6615609105544067</v>
+        <v>0.6623122769477506</v>
       </c>
       <c r="K1471">
         <v>2.72</v>
@@ -75418,39 +75421,39 @@
         <v>1</v>
       </c>
       <c r="P1471" t="s">
-        <v>340</v>
+        <v>192</v>
       </c>
     </row>
     <row r="1472" spans="1:16">
       <c r="A1472" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1472" t="s">
         <v>195</v>
       </c>
       <c r="C1472">
-        <v>1.18393871418647</v>
+        <v>1.181887483932641</v>
       </c>
       <c r="D1472" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E1472">
-        <v>1.219941632558543</v>
+        <v>1.217988079935848</v>
       </c>
       <c r="F1472">
         <v>1</v>
       </c>
       <c r="G1472">
-        <v>0.004796061285813531</v>
+        <v>0.004798112516067359</v>
       </c>
       <c r="H1472">
-        <v>0.004660058367441457</v>
+        <v>0.004662011920064151</v>
       </c>
       <c r="I1472">
-        <v>0.0360029183720727</v>
+        <v>0.03610059600320725</v>
       </c>
       <c r="J1472">
-        <v>0.6615609105544067</v>
+        <v>0.6623122769477506</v>
       </c>
       <c r="K1472">
         <v>2.73</v>
@@ -75468,7 +75471,7 @@
         <v>1</v>
       </c>
       <c r="P1472" t="s">
-        <v>340</v>
+        <v>192</v>
       </c>
     </row>
     <row r="1473" spans="1:16">
@@ -75476,34 +75479,34 @@
         <v>0</v>
       </c>
       <c r="B1473" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="C1473">
-        <v>1.238510606702118</v>
+        <v>1.234042325901743</v>
       </c>
       <c r="D1473" t="s">
         <v>344</v>
       </c>
       <c r="E1473">
-        <v>1.202018115624208</v>
+        <v>1.204196637175389</v>
       </c>
       <c r="F1473">
         <v>-1</v>
       </c>
       <c r="G1473">
-        <v>0.004841489393297882</v>
+        <v>0.004845957674098257</v>
       </c>
       <c r="H1473">
-        <v>0.004857981884375791</v>
+        <v>0.004855803362824611</v>
       </c>
       <c r="I1473">
-        <v>0.03649249107790986</v>
+        <v>0.02984568872635451</v>
       </c>
       <c r="J1473">
-        <v>0.6623122769477506</v>
+        <v>0.661522957545149</v>
       </c>
       <c r="K1473">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="L1473">
         <v>3.04</v>
@@ -75518,7 +75521,7 @@
         <v>1</v>
       </c>
       <c r="P1473" t="s">
-        <v>192</v>
+        <v>495</v>
       </c>
     </row>
     <row r="1474" spans="1:16">
@@ -75529,28 +75532,28 @@
         <v>195</v>
       </c>
       <c r="C1474">
-        <v>1.181887483932641</v>
+        <v>1.184042325901743</v>
       </c>
       <c r="D1474" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E1474">
-        <v>1.217988079935848</v>
+        <v>1.220040310382613</v>
       </c>
       <c r="F1474">
         <v>1</v>
       </c>
       <c r="G1474">
-        <v>0.004798112516067359</v>
+        <v>0.004795957674098257</v>
       </c>
       <c r="H1474">
-        <v>0.004662011920064151</v>
+        <v>0.004659959689617388</v>
       </c>
       <c r="I1474">
-        <v>0.03610059600320725</v>
+        <v>0.03599798448086911</v>
       </c>
       <c r="J1474">
-        <v>0.6623122769477506</v>
+        <v>0.661522957545149</v>
       </c>
       <c r="K1474">
         <v>2.73</v>
@@ -75568,7 +75571,7 @@
         <v>1</v>
       </c>
       <c r="P1474" t="s">
-        <v>192</v>
+        <v>495</v>
       </c>
     </row>
     <row r="1475" spans="1:16">
@@ -75576,34 +75579,34 @@
         <v>0</v>
       </c>
       <c r="B1475" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="C1475">
-        <v>1.240657555477195</v>
+        <v>1.234778933877341</v>
       </c>
       <c r="D1475" t="s">
         <v>344</v>
       </c>
       <c r="E1475">
-        <v>1.204196637175389</v>
+        <v>1.204941339744125</v>
       </c>
       <c r="F1475">
         <v>-1</v>
       </c>
       <c r="G1475">
-        <v>0.004839342444522806</v>
+        <v>0.004845221066122659</v>
       </c>
       <c r="H1475">
-        <v>0.004855803362824611</v>
+        <v>0.004855058660255875</v>
       </c>
       <c r="I1475">
-        <v>0.03646091830180587</v>
+        <v>0.02983759413321607</v>
       </c>
       <c r="J1475">
-        <v>0.661522957545149</v>
+        <v>0.6612531377738676</v>
       </c>
       <c r="K1475">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="L1475">
         <v>3.04</v>
@@ -75618,7 +75621,7 @@
         <v>1</v>
       </c>
       <c r="P1475" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
     </row>
     <row r="1476" spans="1:16">
@@ -75629,28 +75632,28 @@
         <v>195</v>
       </c>
       <c r="C1476">
-        <v>1.184042325901743</v>
+        <v>1.184778933877342</v>
       </c>
       <c r="D1476" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E1476">
-        <v>1.220040310382613</v>
+        <v>1.220741841787944</v>
       </c>
       <c r="F1476">
         <v>1</v>
       </c>
       <c r="G1476">
-        <v>0.004795957674098257</v>
+        <v>0.004795221066122659</v>
       </c>
       <c r="H1476">
-        <v>0.004659959689617388</v>
+        <v>0.004659258158212057</v>
       </c>
       <c r="I1476">
-        <v>0.03599798448086911</v>
+        <v>0.03596290791060253</v>
       </c>
       <c r="J1476">
-        <v>0.661522957545149</v>
+        <v>0.6612531377738676</v>
       </c>
       <c r="K1476">
         <v>2.73</v>
@@ -75668,7 +75671,7 @@
         <v>1</v>
       </c>
       <c r="P1476" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
     </row>
     <row r="1477" spans="1:16">
@@ -75679,28 +75682,28 @@
         <v>186</v>
       </c>
       <c r="C1477">
-        <v>1.234778933877341</v>
+        <v>1.234040024035716</v>
       </c>
       <c r="D1477" t="s">
         <v>344</v>
       </c>
       <c r="E1477">
-        <v>1.204941339744125</v>
+        <v>1.204194310014131</v>
       </c>
       <c r="F1477">
         <v>-1</v>
       </c>
       <c r="G1477">
-        <v>0.004845221066122659</v>
+        <v>0.004845959975964285</v>
       </c>
       <c r="H1477">
-        <v>0.004855058660255875</v>
+        <v>0.004855805689985869</v>
       </c>
       <c r="I1477">
-        <v>0.02983759413321607</v>
+        <v>0.02984571402158576</v>
       </c>
       <c r="J1477">
-        <v>0.6612531377738676</v>
+        <v>0.6615238007195179</v>
       </c>
       <c r="K1477">
         <v>2.73</v>
@@ -75718,7 +75721,7 @@
         <v>1</v>
       </c>
       <c r="P1477" t="s">
-        <v>187</v>
+        <v>496</v>
       </c>
     </row>
     <row r="1478" spans="1:16">
@@ -75729,28 +75732,28 @@
         <v>195</v>
       </c>
       <c r="C1478">
-        <v>1.184778933877342</v>
+        <v>1.184040024035717</v>
       </c>
       <c r="D1478" t="s">
-        <v>198</v>
+        <v>345</v>
       </c>
       <c r="E1478">
-        <v>1.220741841787944</v>
+        <v>1.213577166100473</v>
       </c>
       <c r="F1478">
         <v>1</v>
       </c>
       <c r="G1478">
-        <v>0.004795221066122659</v>
+        <v>0.004795959975964283</v>
       </c>
       <c r="H1478">
-        <v>0.004659258158212057</v>
+        <v>0.004706422833899528</v>
       </c>
       <c r="I1478">
-        <v>0.03596290791060253</v>
+        <v>0.02953714206475611</v>
       </c>
       <c r="J1478">
-        <v>0.6612531377738676</v>
+        <v>0.6615238007195179</v>
       </c>
       <c r="K1478">
         <v>2.73</v>
@@ -75759,16 +75762,16 @@
         <v>2.99</v>
       </c>
       <c r="M1478">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="N1478">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="O1478">
         <v>1</v>
       </c>
       <c r="P1478" t="s">
-        <v>187</v>
+        <v>496</v>
       </c>
     </row>
     <row r="1479" spans="1:16">
@@ -75779,28 +75782,28 @@
         <v>186</v>
       </c>
       <c r="C1479">
-        <v>1.234040024035716</v>
+        <v>1.232747240570372</v>
       </c>
       <c r="D1479" t="s">
         <v>344</v>
       </c>
       <c r="E1479">
-        <v>1.204194310014131</v>
+        <v>1.202887320137079</v>
       </c>
       <c r="F1479">
         <v>-1</v>
       </c>
       <c r="G1479">
-        <v>0.004845959975964285</v>
+        <v>0.004847252759429628</v>
       </c>
       <c r="H1479">
-        <v>0.004855805689985869</v>
+        <v>0.004857112679862921</v>
       </c>
       <c r="I1479">
-        <v>0.02984571402158576</v>
+        <v>0.02985992043329277</v>
       </c>
       <c r="J1479">
-        <v>0.6615238007195179</v>
+        <v>0.6619973477764205</v>
       </c>
       <c r="K1479">
         <v>2.73</v>
@@ -75818,7 +75821,7 @@
         <v>1</v>
       </c>
       <c r="P1479" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="1480" spans="1:16">
@@ -75829,28 +75832,28 @@
         <v>195</v>
       </c>
       <c r="C1480">
-        <v>1.184040024035717</v>
+        <v>1.182747240570372</v>
       </c>
       <c r="D1480" t="s">
         <v>345</v>
       </c>
       <c r="E1480">
-        <v>1.213577166100473</v>
+        <v>1.21232700187025</v>
       </c>
       <c r="F1480">
         <v>1</v>
       </c>
       <c r="G1480">
-        <v>0.004795959975964283</v>
+        <v>0.004797252759429628</v>
       </c>
       <c r="H1480">
-        <v>0.004706422833899528</v>
+        <v>0.00470767299812975</v>
       </c>
       <c r="I1480">
-        <v>0.02953714206475611</v>
+        <v>0.02957976129987738</v>
       </c>
       <c r="J1480">
-        <v>0.6615238007195179</v>
+        <v>0.6619973477764205</v>
       </c>
       <c r="K1480">
         <v>2.73</v>
@@ -75868,7 +75871,7 @@
         <v>1</v>
       </c>
       <c r="P1480" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="1481" spans="1:16">
@@ -75876,81 +75879,81 @@
         <v>0</v>
       </c>
       <c r="B1481" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="C1481">
-        <v>1.232747240570372</v>
+        <v>1.180535576787292</v>
       </c>
       <c r="D1481" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E1481">
-        <v>1.202887320137079</v>
+        <v>1.210188250080019</v>
       </c>
       <c r="F1481">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1481">
-        <v>0.004847252759429628</v>
+        <v>0.004799464423212708</v>
       </c>
       <c r="H1481">
-        <v>0.004857112679862921</v>
+        <v>0.004709811749919982</v>
       </c>
       <c r="I1481">
-        <v>0.02985992043329277</v>
+        <v>0.02965267329272625</v>
       </c>
       <c r="J1481">
-        <v>0.6619973477764205</v>
+        <v>0.6628074810302959</v>
       </c>
       <c r="K1481">
         <v>2.73</v>
       </c>
       <c r="L1481">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="M1481">
-        <v>2.76</v>
+        <v>2.64</v>
       </c>
       <c r="N1481">
-        <v>3.03</v>
+        <v>2.96</v>
       </c>
       <c r="O1481">
         <v>1</v>
       </c>
       <c r="P1481" t="s">
-        <v>496</v>
+        <v>186</v>
       </c>
     </row>
     <row r="1482" spans="1:16">
       <c r="A1482" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1482" t="s">
         <v>195</v>
       </c>
       <c r="C1482">
-        <v>1.182747240570372</v>
+        <v>1.178582922039017</v>
       </c>
       <c r="D1482" t="s">
         <v>345</v>
       </c>
       <c r="E1482">
-        <v>1.21232700187025</v>
+        <v>1.208299968565203</v>
       </c>
       <c r="F1482">
         <v>1</v>
       </c>
       <c r="G1482">
-        <v>0.004797252759429628</v>
+        <v>0.004801417077960984</v>
       </c>
       <c r="H1482">
-        <v>0.00470767299812975</v>
+        <v>0.004711700031434798</v>
       </c>
       <c r="I1482">
-        <v>0.02957976129987738</v>
+        <v>0.02971704652618579</v>
       </c>
       <c r="J1482">
-        <v>0.6619973477764205</v>
+        <v>0.6635227391798474</v>
       </c>
       <c r="K1482">
         <v>2.73</v>
@@ -75968,7 +75971,7 @@
         <v>1</v>
       </c>
       <c r="P1482" t="s">
-        <v>496</v>
+        <v>196</v>
       </c>
     </row>
     <row r="1483" spans="1:16">
@@ -75979,28 +75982,28 @@
         <v>195</v>
       </c>
       <c r="C1483">
-        <v>1.180535576787292</v>
+        <v>1.177578181481615</v>
       </c>
       <c r="D1483" t="s">
         <v>345</v>
       </c>
       <c r="E1483">
-        <v>1.210188250080019</v>
+        <v>1.20732835132288</v>
       </c>
       <c r="F1483">
         <v>1</v>
       </c>
       <c r="G1483">
-        <v>0.004799464423212708</v>
+        <v>0.004802421818518386</v>
       </c>
       <c r="H1483">
-        <v>0.004709811749919982</v>
+        <v>0.004712671648677121</v>
       </c>
       <c r="I1483">
-        <v>0.02965267329272625</v>
+        <v>0.02975016984126522</v>
       </c>
       <c r="J1483">
-        <v>0.6628074810302959</v>
+        <v>0.6638907760140607</v>
       </c>
       <c r="K1483">
         <v>2.73</v>
@@ -76018,48 +76021,48 @@
         <v>1</v>
       </c>
       <c r="P1483" t="s">
-        <v>186</v>
+        <v>498</v>
       </c>
     </row>
     <row r="1484" spans="1:16">
       <c r="A1484" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1484" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C1484">
-        <v>1.178582922039017</v>
+        <v>1.213883982363442</v>
       </c>
       <c r="D1484" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="E1484">
-        <v>1.208299968565203</v>
+        <v>1.200689443562739</v>
       </c>
       <c r="F1484">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1484">
-        <v>0.004801417077960984</v>
+        <v>0.004666116017636558</v>
       </c>
       <c r="H1484">
-        <v>0.004711700031434798</v>
+        <v>0.004719310556437261</v>
       </c>
       <c r="I1484">
-        <v>0.02971704652618579</v>
+        <v>0.01319453880070287</v>
       </c>
       <c r="J1484">
-        <v>0.6635227391798474</v>
+        <v>0.6638907760140607</v>
       </c>
       <c r="K1484">
-        <v>2.73</v>
+        <v>2.6</v>
       </c>
       <c r="L1484">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="M1484">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="N1484">
         <v>2.96</v>
@@ -76068,7 +76071,7 @@
         <v>1</v>
       </c>
       <c r="P1484" t="s">
-        <v>196</v>
+        <v>498</v>
       </c>
     </row>
     <row r="1485" spans="1:16">
@@ -76076,40 +76079,40 @@
         <v>0</v>
       </c>
       <c r="B1485" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C1485">
-        <v>1.177578181481615</v>
+        <v>1.211087090327073</v>
       </c>
       <c r="D1485" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="E1485">
-        <v>1.20732835132288</v>
+        <v>1.197838765141055</v>
       </c>
       <c r="F1485">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1485">
-        <v>0.004802421818518386</v>
+        <v>0.004668912909672928</v>
       </c>
       <c r="H1485">
-        <v>0.004712671648677121</v>
+        <v>0.004722161234858946</v>
       </c>
       <c r="I1485">
-        <v>0.02975016984126522</v>
+        <v>0.01324832518601782</v>
       </c>
       <c r="J1485">
-        <v>0.6638907760140607</v>
+        <v>0.6649665037203567</v>
       </c>
       <c r="K1485">
-        <v>2.73</v>
+        <v>2.6</v>
       </c>
       <c r="L1485">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="M1485">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="N1485">
         <v>2.96</v>
@@ -76118,7 +76121,7 @@
         <v>1</v>
       </c>
       <c r="P1485" t="s">
-        <v>497</v>
+        <v>344</v>
       </c>
     </row>
     <row r="1486" spans="1:16">
@@ -76129,46 +76132,46 @@
         <v>198</v>
       </c>
       <c r="C1486">
-        <v>1.213883982363442</v>
+        <v>1.207787760252665</v>
       </c>
       <c r="D1486" t="s">
         <v>342</v>
       </c>
       <c r="E1486">
-        <v>1.210606166843161</v>
+        <v>1.197838765141055</v>
       </c>
       <c r="F1486">
         <v>-1</v>
       </c>
       <c r="G1486">
-        <v>0.004666116017636558</v>
+        <v>0.004692212239747334</v>
       </c>
       <c r="H1486">
-        <v>0.00468939383315684</v>
+        <v>0.004722161234858946</v>
       </c>
       <c r="I1486">
-        <v>0.003277815520281058</v>
+        <v>0.009948995111610737</v>
       </c>
       <c r="J1486">
-        <v>0.6638907760140607</v>
+        <v>0.6649665037203567</v>
       </c>
       <c r="K1486">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="L1486">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="M1486">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="N1486">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="O1486">
         <v>1</v>
       </c>
       <c r="P1486" t="s">
-        <v>497</v>
+        <v>344</v>
       </c>
     </row>
     <row r="1487" spans="1:16">
@@ -76176,31 +76179,31 @@
         <v>0</v>
       </c>
       <c r="B1487" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C1487">
-        <v>1.211087090327073</v>
+        <v>1.208549663553548</v>
       </c>
       <c r="D1487" t="s">
         <v>342</v>
       </c>
       <c r="E1487">
-        <v>1.207787760252665</v>
+        <v>1.195252541698808</v>
       </c>
       <c r="F1487">
         <v>-1</v>
       </c>
       <c r="G1487">
-        <v>0.004668912909672928</v>
+        <v>0.004671450336446452</v>
       </c>
       <c r="H1487">
-        <v>0.004692212239747334</v>
+        <v>0.004724747458301192</v>
       </c>
       <c r="I1487">
-        <v>0.003299330074407081</v>
+        <v>0.0132971218547393</v>
       </c>
       <c r="J1487">
-        <v>0.6649665037203567</v>
+        <v>0.6659424370947893</v>
       </c>
       <c r="K1487">
         <v>2.6</v>
@@ -76209,60 +76212,60 @@
         <v>2.94</v>
       </c>
       <c r="M1487">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="N1487">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="O1487">
         <v>1</v>
       </c>
       <c r="P1487" t="s">
-        <v>344</v>
+        <v>195</v>
       </c>
     </row>
     <row r="1488" spans="1:16">
       <c r="A1488" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1488" t="s">
         <v>198</v>
       </c>
       <c r="C1488">
-        <v>1.208549663553548</v>
+        <v>1.205230814811652</v>
       </c>
       <c r="D1488" t="s">
         <v>342</v>
       </c>
       <c r="E1488">
-        <v>1.205230814811652</v>
+        <v>1.195252541698808</v>
       </c>
       <c r="F1488">
         <v>-1</v>
       </c>
       <c r="G1488">
-        <v>0.004671450336446452</v>
+        <v>0.004694769185188349</v>
       </c>
       <c r="H1488">
-        <v>0.004694769185188349</v>
+        <v>0.004724747458301192</v>
       </c>
       <c r="I1488">
-        <v>0.003318848741895586</v>
+        <v>0.009978273112843716</v>
       </c>
       <c r="J1488">
         <v>0.6659424370947893</v>
       </c>
       <c r="K1488">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="L1488">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="M1488">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="N1488">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="O1488">
         <v>1</v>
@@ -76276,7 +76279,7 @@
         <v>0</v>
       </c>
       <c r="B1489" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C1489">
         <v>1.204222079642759</v>
@@ -76285,7 +76288,7 @@
         <v>342</v>
       </c>
       <c r="E1489">
-        <v>1.200869941793857</v>
+        <v>1.190841735020504</v>
       </c>
       <c r="F1489">
         <v>-1</v>
@@ -76294,10 +76297,10 @@
         <v>0.004675777920357241</v>
       </c>
       <c r="H1489">
-        <v>0.004699130058206143</v>
+        <v>0.004729158264979496</v>
       </c>
       <c r="I1489">
-        <v>0.003352137848901648</v>
+        <v>0.01338034462225446</v>
       </c>
       <c r="J1489">
         <v>0.6676068924450927</v>
@@ -76309,10 +76312,10 @@
         <v>2.94</v>
       </c>
       <c r="M1489">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="N1489">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="O1489">
         <v>1</v>
@@ -76326,7 +76329,7 @@
         <v>0</v>
       </c>
       <c r="B1490" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C1490">
         <v>1.198607937501674</v>
@@ -76335,7 +76338,7 @@
         <v>342</v>
       </c>
       <c r="E1490">
-        <v>1.195212613943995</v>
+        <v>1.185119628607475</v>
       </c>
       <c r="F1490">
         <v>-1</v>
@@ -76344,10 +76347,10 @@
         <v>0.004681392062498326</v>
       </c>
       <c r="H1490">
-        <v>0.004704787386056006</v>
+        <v>0.004734880371392525</v>
       </c>
       <c r="I1490">
-        <v>0.003395323557679131</v>
+        <v>0.01348830889419839</v>
       </c>
       <c r="J1490">
         <v>0.6697661778839715</v>
@@ -76359,16 +76362,16 @@
         <v>2.94</v>
       </c>
       <c r="M1490">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="N1490">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="O1490">
         <v>1</v>
       </c>
       <c r="P1490" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="1491" spans="1:16">
@@ -76376,7 +76379,7 @@
         <v>0</v>
       </c>
       <c r="B1491" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C1491">
         <v>1.192721796924865</v>
@@ -76418,7 +76421,7 @@
         <v>1</v>
       </c>
       <c r="P1491" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01288-601288.xlsx
+++ b/s60_signal/position-01288-601288.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5070" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5073" uniqueCount="541">
   <si>
     <t>trade_time</t>
   </si>
@@ -649,13 +649,13 @@
     <t>2021-11-29</t>
   </si>
   <si>
+    <t>2021-12-03</t>
+  </si>
+  <si>
     <t>2021-11-11</t>
   </si>
   <si>
     <t>2021-11-23</t>
-  </si>
-  <si>
-    <t>2021-12-03</t>
   </si>
   <si>
     <t>2017-05-12</t>
@@ -1156,7 +1156,7 @@
     <t>2021-12-02</t>
   </si>
   <si>
-    <t>2021-12-06</t>
+    <t>2021-12-07</t>
   </si>
   <si>
     <t>2017-04-07</t>
@@ -1994,7 +1994,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1686"/>
+  <dimension ref="A1:P1687"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -70755,7 +70755,7 @@
         <v>1.326506970680973</v>
       </c>
       <c r="D1376" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E1376">
         <v>1.352584593554729</v>
@@ -70805,7 +70805,7 @@
         <v>1.336506970680972</v>
       </c>
       <c r="D1377" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E1377">
         <v>1.352584593554729</v>
@@ -70855,7 +70855,7 @@
         <v>1.322519907826599</v>
       </c>
       <c r="D1378" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E1378">
         <v>1.352584593554729</v>
@@ -70905,7 +70905,7 @@
         <v>1.324545782117851</v>
       </c>
       <c r="D1379" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E1379">
         <v>1.352584593554729</v>
@@ -70955,7 +70955,7 @@
         <v>1.332584593554729</v>
       </c>
       <c r="D1380" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E1380">
         <v>1.352584593554729</v>
@@ -73355,7 +73355,7 @@
         <v>1.229935202898527</v>
       </c>
       <c r="D1428" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E1428">
         <v>1.261720793922718</v>
@@ -73405,7 +73405,7 @@
         <v>1.239006557513042</v>
       </c>
       <c r="D1429" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E1429">
         <v>1.261720793922718</v>
@@ -73455,7 +73455,7 @@
         <v>1.232649439308204</v>
       </c>
       <c r="D1430" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E1430">
         <v>1.261720793922718</v>
@@ -73505,7 +73505,7 @@
         <v>1.232649439308204</v>
       </c>
       <c r="D1431" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E1431">
         <v>1.261720793922718</v>
@@ -75405,7 +75405,7 @@
         <v>1.17260320034906</v>
       </c>
       <c r="D1469" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E1469">
         <v>1.205454441978259</v>
@@ -75455,7 +75455,7 @@
         <v>1.17574369700074</v>
       </c>
       <c r="D1470" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E1470">
         <v>1.205454441978259</v>
@@ -75505,7 +75505,7 @@
         <v>1.17574369700074</v>
       </c>
       <c r="D1471" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E1471">
         <v>1.205454441978259</v>
@@ -75855,7 +75855,7 @@
         <v>1.168684292016576</v>
       </c>
       <c r="D1478" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E1478">
         <v>1.198474356151221</v>
@@ -76155,7 +76155,7 @@
         <v>1.163632368819734</v>
       </c>
       <c r="D1484" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E1484">
         <v>1.193479196136366</v>
@@ -76455,7 +76455,7 @@
         <v>1.161626220549506</v>
       </c>
       <c r="D1490" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E1490">
         <v>1.191495588857938</v>
@@ -76755,7 +76755,7 @@
         <v>1.163733703354452</v>
       </c>
       <c r="D1496" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E1496">
         <v>1.193579392080806</v>
@@ -77055,7 +77055,7 @@
         <v>1.164454122143774</v>
       </c>
       <c r="D1502" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E1502">
         <v>1.194291716276989</v>
@@ -77305,7 +77305,7 @@
         <v>1.163731452078888</v>
       </c>
       <c r="D1507" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E1507">
         <v>1.193577166100473</v>
@@ -77605,7 +77605,7 @@
         <v>1.162467081436958</v>
       </c>
       <c r="D1513" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E1513">
         <v>1.19232700187025</v>
@@ -77805,10 +77805,10 @@
         <v>1.157047876028504</v>
       </c>
       <c r="D1517" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="E1517">
-        <v>1.190072474510928</v>
+        <v>1.183560175269716</v>
       </c>
       <c r="F1517">
         <v>1</v>
@@ -77817,10 +77817,10 @@
         <v>0.004722952123971495</v>
       </c>
       <c r="H1517">
-        <v>0.004649927525489071</v>
+        <v>0.004696439824730284</v>
       </c>
       <c r="I1517">
-        <v>0.03302459848242378</v>
+        <v>0.0265122992412119</v>
       </c>
       <c r="J1517">
         <v>0.6628074810302959</v>
@@ -77832,10 +77832,10 @@
         <v>2.94</v>
       </c>
       <c r="M1517">
-        <v>2.61</v>
+        <v>2.65</v>
       </c>
       <c r="N1517">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="O1517">
         <v>1</v>
@@ -77905,10 +77905,10 @@
         <v>1.16030402564911</v>
       </c>
       <c r="D1519" t="s">
-        <v>212</v>
+        <v>375</v>
       </c>
       <c r="E1519">
-        <v>1.190188250080019</v>
+        <v>1.183560175269716</v>
       </c>
       <c r="F1519">
         <v>1</v>
@@ -77917,10 +77917,10 @@
         <v>0.00469969597435089</v>
       </c>
       <c r="H1519">
-        <v>0.004689811749919981</v>
+        <v>0.004696439824730284</v>
       </c>
       <c r="I1519">
-        <v>0.02988422443090855</v>
+        <v>0.02325614962060585</v>
       </c>
       <c r="J1519">
         <v>0.6628074810302959</v>
@@ -77932,7 +77932,7 @@
         <v>2.93</v>
       </c>
       <c r="M1519">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="N1519">
         <v>2.94</v>
@@ -80549,10 +80549,10 @@
         <v>4</v>
       </c>
       <c r="B1572" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C1572">
-        <v>1.171297561499397</v>
+        <v>1.161001424084992</v>
       </c>
       <c r="D1572" t="s">
         <v>379</v>
@@ -80564,22 +80564,22 @@
         <v>-1</v>
       </c>
       <c r="G1572">
-        <v>0.004648702438500603</v>
+        <v>0.004678998575915008</v>
       </c>
       <c r="H1572">
         <v>0.004736356229881951</v>
       </c>
       <c r="I1572">
-        <v>0.04765379138134662</v>
+        <v>0.03735765396694224</v>
       </c>
       <c r="J1572">
         <v>0.6765379138134644</v>
       </c>
       <c r="K1572">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="L1572">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="M1572">
         <v>2.67</v>
@@ -81899,43 +81899,43 @@
         <v>1</v>
       </c>
       <c r="B1599" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="C1599">
+        <v>1.124376915605622</v>
+      </c>
+      <c r="D1599" t="s">
+        <v>379</v>
+      </c>
+      <c r="E1599">
         <v>1.08603321717962</v>
       </c>
-      <c r="D1599" t="s">
-        <v>367</v>
-      </c>
-      <c r="E1599">
-        <v>1.117470672973336</v>
-      </c>
       <c r="F1599">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1599">
+        <v>0.004715623084394377</v>
+      </c>
+      <c r="H1599">
         <v>0.004773966782820381</v>
       </c>
-      <c r="H1599">
-        <v>0.004722529327026663</v>
-      </c>
       <c r="I1599">
-        <v>0.03143745579371604</v>
+        <v>0.03834369842600216</v>
       </c>
       <c r="J1599">
         <v>0.6906242632286068</v>
       </c>
       <c r="K1599">
+        <v>2.6</v>
+      </c>
+      <c r="L1599">
+        <v>2.92</v>
+      </c>
+      <c r="M1599">
         <v>2.67</v>
       </c>
-      <c r="L1599">
+      <c r="N1599">
         <v>2.93</v>
-      </c>
-      <c r="M1599">
-        <v>2.61</v>
-      </c>
-      <c r="N1599">
-        <v>2.92</v>
       </c>
       <c r="O1599">
         <v>1</v>
@@ -81949,40 +81949,40 @@
         <v>2</v>
       </c>
       <c r="B1600" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="C1600">
-        <v>1.08603321717962</v>
+        <v>1.079126974547334</v>
       </c>
       <c r="D1600" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="E1600">
-        <v>1.109845702444192</v>
+        <v>1.089126974547334</v>
       </c>
       <c r="F1600">
         <v>1</v>
       </c>
       <c r="G1600">
-        <v>0.004773966782820381</v>
+        <v>0.004780873025452667</v>
       </c>
       <c r="H1600">
-        <v>0.004770154297555809</v>
+        <v>0.004790873025452666</v>
       </c>
       <c r="I1600">
-        <v>0.0238124852645718</v>
+        <v>0.009999999999999787</v>
       </c>
       <c r="J1600">
         <v>0.6906242632286068</v>
       </c>
       <c r="K1600">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="L1600">
         <v>2.93</v>
       </c>
       <c r="M1600">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="N1600">
         <v>2.94</v>
@@ -81996,34 +81996,34 @@
     </row>
     <row r="1601" spans="1:16">
       <c r="A1601" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1601" t="s">
         <v>210</v>
       </c>
       <c r="C1601">
-        <v>1.124376915605622</v>
+        <v>1.122317021928619</v>
       </c>
       <c r="D1601" t="s">
         <v>379</v>
       </c>
       <c r="E1601">
-        <v>1.08603321717962</v>
+        <v>1.083917864826698</v>
       </c>
       <c r="F1601">
         <v>-1</v>
       </c>
       <c r="G1601">
-        <v>0.004715623084394377</v>
+        <v>0.004717682978071382</v>
       </c>
       <c r="H1601">
-        <v>0.004773966782820381</v>
+        <v>0.004776082135173302</v>
       </c>
       <c r="I1601">
-        <v>0.03834369842600216</v>
+        <v>0.03839915710192132</v>
       </c>
       <c r="J1601">
-        <v>0.6906242632286068</v>
+        <v>0.6914165300274542</v>
       </c>
       <c r="K1601">
         <v>2.6</v>
@@ -82041,48 +82041,48 @@
         <v>1</v>
       </c>
       <c r="P1601" t="s">
-        <v>205</v>
+        <v>539</v>
       </c>
     </row>
     <row r="1602" spans="1:16">
       <c r="A1602" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1602" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="C1602">
-        <v>1.083917864826698</v>
+        <v>1.077003699526423</v>
       </c>
       <c r="D1602" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="E1602">
-        <v>1.107746195427247</v>
+        <v>1.087003699526423</v>
       </c>
       <c r="F1602">
         <v>1</v>
       </c>
       <c r="G1602">
-        <v>0.004776082135173302</v>
+        <v>0.004782996300473578</v>
       </c>
       <c r="H1602">
-        <v>0.004772253804572754</v>
+        <v>0.004792996300473577</v>
       </c>
       <c r="I1602">
-        <v>0.0238283306005489</v>
+        <v>0.009999999999999787</v>
       </c>
       <c r="J1602">
         <v>0.6914165300274542</v>
       </c>
       <c r="K1602">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="L1602">
         <v>2.93</v>
       </c>
       <c r="M1602">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="N1602">
         <v>2.94</v>
@@ -82096,43 +82096,43 @@
     </row>
     <row r="1603" spans="1:16">
       <c r="A1603" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1603" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C1603">
-        <v>1.122317021928619</v>
+        <v>1.112310701019539</v>
       </c>
       <c r="D1603" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="E1603">
-        <v>1.083917864826698</v>
+        <v>1.095387635493099</v>
       </c>
       <c r="F1603">
         <v>-1</v>
       </c>
       <c r="G1603">
-        <v>0.004717682978071382</v>
+        <v>0.00476768929898046</v>
       </c>
       <c r="H1603">
-        <v>0.004776082135173302</v>
+        <v>0.004764612364506902</v>
       </c>
       <c r="I1603">
-        <v>0.03839915710192132</v>
+        <v>0.01692306552644074</v>
       </c>
       <c r="J1603">
-        <v>0.6914165300274542</v>
+        <v>0.6923065526441138</v>
       </c>
       <c r="K1603">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="L1603">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="M1603">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="N1603">
         <v>2.93</v>
@@ -82141,24 +82141,24 @@
         <v>1</v>
       </c>
       <c r="P1603" t="s">
-        <v>539</v>
+        <v>378</v>
       </c>
     </row>
     <row r="1604" spans="1:16">
       <c r="A1604" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1604" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C1604">
         <v>1.112310701019539</v>
       </c>
       <c r="D1604" t="s">
-        <v>371</v>
+        <v>204</v>
       </c>
       <c r="E1604">
-        <v>1.095387635493099</v>
+        <v>1.078464569966657</v>
       </c>
       <c r="F1604">
         <v>-1</v>
@@ -82167,10 +82167,10 @@
         <v>0.00476768929898046</v>
       </c>
       <c r="H1604">
-        <v>0.004764612364506902</v>
+        <v>0.004761535430033343</v>
       </c>
       <c r="I1604">
-        <v>0.01692306552644074</v>
+        <v>0.03384613105288237</v>
       </c>
       <c r="J1604">
         <v>0.6923065526441138</v>
@@ -82182,10 +82182,10 @@
         <v>2.94</v>
       </c>
       <c r="M1604">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="N1604">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="O1604">
         <v>1</v>
@@ -82196,46 +82196,46 @@
     </row>
     <row r="1605" spans="1:16">
       <c r="A1605" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1605" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="C1605">
+        <v>1.120002963125304</v>
+      </c>
+      <c r="D1605" t="s">
+        <v>379</v>
+      </c>
+      <c r="E1605">
         <v>1.081541504440216</v>
       </c>
-      <c r="D1605" t="s">
-        <v>375</v>
-      </c>
-      <c r="E1605">
-        <v>1.105387635493098</v>
-      </c>
       <c r="F1605">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1605">
+        <v>0.004719997036874695</v>
+      </c>
+      <c r="H1605">
         <v>0.004778458495559784</v>
       </c>
-      <c r="H1605">
-        <v>0.004774612364506901</v>
-      </c>
       <c r="I1605">
-        <v>0.02384613105288214</v>
+        <v>0.03846145868508777</v>
       </c>
       <c r="J1605">
         <v>0.6923065526441138</v>
       </c>
       <c r="K1605">
+        <v>2.6</v>
+      </c>
+      <c r="L1605">
+        <v>2.92</v>
+      </c>
+      <c r="M1605">
         <v>2.67</v>
       </c>
-      <c r="L1605">
+      <c r="N1605">
         <v>2.93</v>
-      </c>
-      <c r="M1605">
-        <v>2.65</v>
-      </c>
-      <c r="N1605">
-        <v>2.94</v>
       </c>
       <c r="O1605">
         <v>1</v>
@@ -82246,46 +82246,46 @@
     </row>
     <row r="1606" spans="1:16">
       <c r="A1606" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1606" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C1606">
-        <v>1.112310701019539</v>
+        <v>1.074618438913775</v>
       </c>
       <c r="D1606" t="s">
-        <v>204</v>
+        <v>380</v>
       </c>
       <c r="E1606">
-        <v>1.078464569966657</v>
+        <v>1.084618438913775</v>
       </c>
       <c r="F1606">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1606">
-        <v>0.00476768929898046</v>
+        <v>0.004785381561086226</v>
       </c>
       <c r="H1606">
-        <v>0.004761535430033343</v>
+        <v>0.004795381561086226</v>
       </c>
       <c r="I1606">
-        <v>0.03384613105288237</v>
+        <v>0.009999999999999787</v>
       </c>
       <c r="J1606">
         <v>0.6923065526441138</v>
       </c>
       <c r="K1606">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="L1606">
+        <v>2.93</v>
+      </c>
+      <c r="M1606">
+        <v>2.68</v>
+      </c>
+      <c r="N1606">
         <v>2.94</v>
-      </c>
-      <c r="M1606">
-        <v>2.66</v>
-      </c>
-      <c r="N1606">
-        <v>2.92</v>
       </c>
       <c r="O1606">
         <v>1</v>
@@ -82296,43 +82296,43 @@
     </row>
     <row r="1607" spans="1:16">
       <c r="A1607" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1607" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C1607">
-        <v>1.120002963125304</v>
+        <v>1.10751365441215</v>
       </c>
       <c r="D1607" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="E1607">
-        <v>1.081541504440216</v>
+        <v>1.090572418254621</v>
       </c>
       <c r="F1607">
         <v>-1</v>
       </c>
       <c r="G1607">
-        <v>0.004719997036874695</v>
+        <v>0.004772486345587849</v>
       </c>
       <c r="H1607">
-        <v>0.004778458495559784</v>
+        <v>0.004769427581745379</v>
       </c>
       <c r="I1607">
-        <v>0.03846145868508777</v>
+        <v>0.0169412361575294</v>
       </c>
       <c r="J1607">
-        <v>0.6923065526441138</v>
+        <v>0.6941236157529733</v>
       </c>
       <c r="K1607">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="L1607">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="M1607">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="N1607">
         <v>2.93</v>
@@ -82341,24 +82341,24 @@
         <v>1</v>
       </c>
       <c r="P1607" t="s">
-        <v>378</v>
+        <v>540</v>
       </c>
     </row>
     <row r="1608" spans="1:16">
       <c r="A1608" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1608" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C1608">
         <v>1.10751365441215</v>
       </c>
       <c r="D1608" t="s">
-        <v>371</v>
+        <v>204</v>
       </c>
       <c r="E1608">
-        <v>1.090572418254621</v>
+        <v>1.073631182097091</v>
       </c>
       <c r="F1608">
         <v>-1</v>
@@ -82367,10 +82367,10 @@
         <v>0.004772486345587849</v>
       </c>
       <c r="H1608">
-        <v>0.004769427581745379</v>
+        <v>0.004766368817902909</v>
       </c>
       <c r="I1608">
-        <v>0.0169412361575294</v>
+        <v>0.03388247231505948</v>
       </c>
       <c r="J1608">
         <v>0.6941236157529733</v>
@@ -82382,10 +82382,10 @@
         <v>2.94</v>
       </c>
       <c r="M1608">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="N1608">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="O1608">
         <v>1</v>
@@ -82396,46 +82396,46 @@
     </row>
     <row r="1609" spans="1:16">
       <c r="A1609" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1609" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="C1609">
+        <v>1.115278599042269</v>
+      </c>
+      <c r="D1609" t="s">
+        <v>379</v>
+      </c>
+      <c r="E1609">
         <v>1.076689945939561</v>
       </c>
-      <c r="D1609" t="s">
-        <v>375</v>
-      </c>
-      <c r="E1609">
-        <v>1.100572418254621</v>
-      </c>
       <c r="F1609">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1609">
+        <v>0.004724721400957731</v>
+      </c>
+      <c r="H1609">
         <v>0.004783310054060439</v>
       </c>
-      <c r="H1609">
-        <v>0.004779427581745379</v>
-      </c>
       <c r="I1609">
-        <v>0.02388247231505924</v>
+        <v>0.03858865310270798</v>
       </c>
       <c r="J1609">
         <v>0.6941236157529733</v>
       </c>
       <c r="K1609">
+        <v>2.6</v>
+      </c>
+      <c r="L1609">
+        <v>2.92</v>
+      </c>
+      <c r="M1609">
         <v>2.67</v>
       </c>
-      <c r="L1609">
+      <c r="N1609">
         <v>2.93</v>
-      </c>
-      <c r="M1609">
-        <v>2.65</v>
-      </c>
-      <c r="N1609">
-        <v>2.94</v>
       </c>
       <c r="O1609">
         <v>1</v>
@@ -82446,46 +82446,46 @@
     </row>
     <row r="1610" spans="1:16">
       <c r="A1610" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1610" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C1610">
-        <v>1.10751365441215</v>
+        <v>1.069748709782032</v>
       </c>
       <c r="D1610" t="s">
-        <v>204</v>
+        <v>380</v>
       </c>
       <c r="E1610">
-        <v>1.073631182097091</v>
+        <v>1.079748709782031</v>
       </c>
       <c r="F1610">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1610">
-        <v>0.004772486345587849</v>
+        <v>0.004790251290217968</v>
       </c>
       <c r="H1610">
-        <v>0.004766368817902909</v>
+        <v>0.004800251290217968</v>
       </c>
       <c r="I1610">
-        <v>0.03388247231505948</v>
+        <v>0.009999999999999787</v>
       </c>
       <c r="J1610">
         <v>0.6941236157529733</v>
       </c>
       <c r="K1610">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="L1610">
+        <v>2.93</v>
+      </c>
+      <c r="M1610">
+        <v>2.68</v>
+      </c>
+      <c r="N1610">
         <v>2.94</v>
-      </c>
-      <c r="M1610">
-        <v>2.66</v>
-      </c>
-      <c r="N1610">
-        <v>2.92</v>
       </c>
       <c r="O1610">
         <v>1</v>
@@ -82496,43 +82496,43 @@
     </row>
     <row r="1611" spans="1:16">
       <c r="A1611" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1611" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C1611">
-        <v>1.115278599042269</v>
+        <v>1.104207216649199</v>
       </c>
       <c r="D1611" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="E1611">
-        <v>1.076689945939561</v>
+        <v>1.087253456106204</v>
       </c>
       <c r="F1611">
         <v>-1</v>
       </c>
       <c r="G1611">
-        <v>0.004724721400957731</v>
+        <v>0.004775792783350801</v>
       </c>
       <c r="H1611">
-        <v>0.004783310054060439</v>
+        <v>0.004772746543893797</v>
       </c>
       <c r="I1611">
-        <v>0.03858865310270798</v>
+        <v>0.01695376054299502</v>
       </c>
       <c r="J1611">
-        <v>0.6941236157529733</v>
+        <v>0.6953760542995459</v>
       </c>
       <c r="K1611">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="L1611">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="M1611">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="N1611">
         <v>2.93</v>
@@ -82541,24 +82541,24 @@
         <v>1</v>
       </c>
       <c r="P1611" t="s">
-        <v>540</v>
+        <v>192</v>
       </c>
     </row>
     <row r="1612" spans="1:16">
       <c r="A1612" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1612" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C1612">
         <v>1.104207216649199</v>
       </c>
       <c r="D1612" t="s">
-        <v>371</v>
+        <v>204</v>
       </c>
       <c r="E1612">
-        <v>1.087253456106204</v>
+        <v>1.070299695563208</v>
       </c>
       <c r="F1612">
         <v>-1</v>
@@ -82567,10 +82567,10 @@
         <v>0.004775792783350801</v>
       </c>
       <c r="H1612">
-        <v>0.004772746543893797</v>
+        <v>0.004769700304436793</v>
       </c>
       <c r="I1612">
-        <v>0.01695376054299502</v>
+        <v>0.03390752108599093</v>
       </c>
       <c r="J1612">
         <v>0.6953760542995459</v>
@@ -82582,10 +82582,10 @@
         <v>2.94</v>
       </c>
       <c r="M1612">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="N1612">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="O1612">
         <v>1</v>
@@ -82596,46 +82596,46 @@
     </row>
     <row r="1613" spans="1:16">
       <c r="A1613" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1613" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C1613">
-        <v>1.104207216649199</v>
+        <v>1.112022258821181</v>
       </c>
       <c r="D1613" t="s">
-        <v>204</v>
+        <v>379</v>
       </c>
       <c r="E1613">
-        <v>1.070299695563208</v>
+        <v>1.073345935020213</v>
       </c>
       <c r="F1613">
         <v>-1</v>
       </c>
       <c r="G1613">
-        <v>0.004775792783350801</v>
+        <v>0.004727977741178819</v>
       </c>
       <c r="H1613">
-        <v>0.004769700304436793</v>
+        <v>0.004786654064979788</v>
       </c>
       <c r="I1613">
-        <v>0.03390752108599093</v>
+        <v>0.03867632380096775</v>
       </c>
       <c r="J1613">
         <v>0.6953760542995459</v>
       </c>
       <c r="K1613">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="L1613">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="M1613">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="N1613">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="O1613">
         <v>1</v>
@@ -82646,46 +82646,46 @@
     </row>
     <row r="1614" spans="1:16">
       <c r="A1614" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1614" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C1614">
-        <v>1.112022258821181</v>
+        <v>1.066392174477217</v>
       </c>
       <c r="D1614" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E1614">
-        <v>1.073345935020213</v>
+        <v>1.076392174477217</v>
       </c>
       <c r="F1614">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1614">
-        <v>0.004727977741178819</v>
+        <v>0.004793607825522783</v>
       </c>
       <c r="H1614">
-        <v>0.004786654064979788</v>
+        <v>0.004803607825522783</v>
       </c>
       <c r="I1614">
-        <v>0.03867632380096775</v>
+        <v>0.009999999999999787</v>
       </c>
       <c r="J1614">
         <v>0.6953760542995459</v>
       </c>
       <c r="K1614">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="L1614">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="M1614">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="N1614">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="O1614">
         <v>1</v>
@@ -82696,43 +82696,43 @@
     </row>
     <row r="1615" spans="1:16">
       <c r="A1615" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1615" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C1615">
-        <v>1.066392174477217</v>
+        <v>1.099749151215716</v>
       </c>
       <c r="D1615" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="E1615">
-        <v>1.066392174477217</v>
+        <v>1.082778504061231</v>
       </c>
       <c r="F1615">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1615">
-        <v>0.004793607825522783</v>
+        <v>0.004780250848784283</v>
       </c>
       <c r="H1615">
-        <v>0.004793607825522783</v>
+        <v>0.004777221495938769</v>
       </c>
       <c r="I1615">
-        <v>0</v>
+        <v>0.01697064715448549</v>
       </c>
       <c r="J1615">
-        <v>0.6953760542995459</v>
+        <v>0.6970647154485922</v>
       </c>
       <c r="K1615">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="L1615">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="M1615">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="N1615">
         <v>2.93</v>
@@ -82741,24 +82741,24 @@
         <v>1</v>
       </c>
       <c r="P1615" t="s">
-        <v>192</v>
+        <v>358</v>
       </c>
     </row>
     <row r="1616" spans="1:16">
       <c r="A1616" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1616" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C1616">
         <v>1.099749151215716</v>
       </c>
       <c r="D1616" t="s">
-        <v>371</v>
+        <v>204</v>
       </c>
       <c r="E1616">
-        <v>1.082778504061231</v>
+        <v>1.065807856906745</v>
       </c>
       <c r="F1616">
         <v>-1</v>
@@ -82767,10 +82767,10 @@
         <v>0.004780250848784283</v>
       </c>
       <c r="H1616">
-        <v>0.004777221495938769</v>
+        <v>0.004774192143093256</v>
       </c>
       <c r="I1616">
-        <v>0.01697064715448549</v>
+        <v>0.03394129430897186</v>
       </c>
       <c r="J1616">
         <v>0.6970647154485922</v>
@@ -82782,10 +82782,10 @@
         <v>2.94</v>
       </c>
       <c r="M1616">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="N1616">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="O1616">
         <v>1</v>
@@ -82796,46 +82796,46 @@
     </row>
     <row r="1617" spans="1:16">
       <c r="A1617" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1617" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="C1617">
+        <v>1.10763173983366</v>
+      </c>
+      <c r="D1617" t="s">
+        <v>379</v>
+      </c>
+      <c r="E1617">
         <v>1.068837209752259</v>
       </c>
-      <c r="D1617" t="s">
-        <v>375</v>
-      </c>
-      <c r="E1617">
-        <v>1.092778504061231</v>
-      </c>
       <c r="F1617">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1617">
+        <v>0.00473236826016634</v>
+      </c>
+      <c r="H1617">
         <v>0.004791162790247741</v>
       </c>
-      <c r="H1617">
-        <v>0.004787221495938769</v>
-      </c>
       <c r="I1617">
-        <v>0.02394129430897163</v>
+        <v>0.03879453008140099</v>
       </c>
       <c r="J1617">
         <v>0.6970647154485922</v>
       </c>
       <c r="K1617">
+        <v>2.6</v>
+      </c>
+      <c r="L1617">
+        <v>2.92</v>
+      </c>
+      <c r="M1617">
         <v>2.67</v>
       </c>
-      <c r="L1617">
+      <c r="N1617">
         <v>2.93</v>
-      </c>
-      <c r="M1617">
-        <v>2.65</v>
-      </c>
-      <c r="N1617">
-        <v>2.94</v>
       </c>
       <c r="O1617">
         <v>1</v>
@@ -82846,46 +82846,46 @@
     </row>
     <row r="1618" spans="1:16">
       <c r="A1618" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1618" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C1618">
-        <v>1.099749151215716</v>
+        <v>1.061866562597773</v>
       </c>
       <c r="D1618" t="s">
-        <v>204</v>
+        <v>380</v>
       </c>
       <c r="E1618">
-        <v>1.065807856906745</v>
+        <v>1.071866562597773</v>
       </c>
       <c r="F1618">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1618">
-        <v>0.004780250848784283</v>
+        <v>0.004798133437402228</v>
       </c>
       <c r="H1618">
-        <v>0.004774192143093256</v>
+        <v>0.004808133437402227</v>
       </c>
       <c r="I1618">
-        <v>0.03394129430897186</v>
+        <v>0.009999999999999787</v>
       </c>
       <c r="J1618">
         <v>0.6970647154485922</v>
       </c>
       <c r="K1618">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="L1618">
+        <v>2.93</v>
+      </c>
+      <c r="M1618">
+        <v>2.68</v>
+      </c>
+      <c r="N1618">
         <v>2.94</v>
-      </c>
-      <c r="M1618">
-        <v>2.66</v>
-      </c>
-      <c r="N1618">
-        <v>2.92</v>
       </c>
       <c r="O1618">
         <v>1</v>
@@ -82896,43 +82896,43 @@
     </row>
     <row r="1619" spans="1:16">
       <c r="A1619" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1619" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C1619">
-        <v>1.10763173983366</v>
+        <v>1.095364733551475</v>
       </c>
       <c r="D1619" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="E1619">
-        <v>1.068837209752259</v>
+        <v>1.078377478754322</v>
       </c>
       <c r="F1619">
         <v>-1</v>
       </c>
       <c r="G1619">
-        <v>0.00473236826016634</v>
+        <v>0.004784635266448525</v>
       </c>
       <c r="H1619">
-        <v>0.004791162790247741</v>
+        <v>0.004781622521245679</v>
       </c>
       <c r="I1619">
-        <v>0.03879453008140099</v>
+        <v>0.01698725479715302</v>
       </c>
       <c r="J1619">
-        <v>0.6970647154485922</v>
+        <v>0.6987254797153503</v>
       </c>
       <c r="K1619">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="L1619">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="M1619">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="N1619">
         <v>2.93</v>
@@ -82941,51 +82941,51 @@
         <v>1</v>
       </c>
       <c r="P1619" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="1620" spans="1:16">
       <c r="A1620" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1620" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="C1620">
-        <v>1.095364733551475</v>
+        <v>1.064402969160015</v>
       </c>
       <c r="D1620" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="E1620">
-        <v>1.078377478754322</v>
+        <v>1.088377478754322</v>
       </c>
       <c r="F1620">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1620">
-        <v>0.004784635266448525</v>
+        <v>0.004795597030839985</v>
       </c>
       <c r="H1620">
-        <v>0.004781622521245679</v>
+        <v>0.004791622521245678</v>
       </c>
       <c r="I1620">
-        <v>0.01698725479715302</v>
+        <v>0.02397450959430691</v>
       </c>
       <c r="J1620">
         <v>0.6987254797153503</v>
       </c>
       <c r="K1620">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="L1620">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="M1620">
         <v>2.65</v>
       </c>
       <c r="N1620">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="O1620">
         <v>1</v>
@@ -82996,46 +82996,46 @@
     </row>
     <row r="1621" spans="1:16">
       <c r="A1621" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1621" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="C1621">
-        <v>1.064402969160015</v>
+        <v>1.095364733551475</v>
       </c>
       <c r="D1621" t="s">
-        <v>375</v>
+        <v>204</v>
       </c>
       <c r="E1621">
-        <v>1.088377478754322</v>
+        <v>1.061390223957168</v>
       </c>
       <c r="F1621">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1621">
-        <v>0.004795597030839985</v>
+        <v>0.004784635266448525</v>
       </c>
       <c r="H1621">
-        <v>0.004791622521245678</v>
+        <v>0.004778609776042831</v>
       </c>
       <c r="I1621">
-        <v>0.02397450959430691</v>
+        <v>0.03397450959430692</v>
       </c>
       <c r="J1621">
         <v>0.6987254797153503</v>
       </c>
       <c r="K1621">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="L1621">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="M1621">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="N1621">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="O1621">
         <v>1</v>
@@ -83046,46 +83046,46 @@
     </row>
     <row r="1622" spans="1:16">
       <c r="A1622" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1622" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C1622">
-        <v>1.095364733551475</v>
+        <v>1.103313752740089</v>
       </c>
       <c r="D1622" t="s">
-        <v>204</v>
+        <v>379</v>
       </c>
       <c r="E1622">
-        <v>1.061390223957168</v>
+        <v>1.064402969160015</v>
       </c>
       <c r="F1622">
         <v>-1</v>
       </c>
       <c r="G1622">
-        <v>0.004784635266448525</v>
+        <v>0.004736686247259911</v>
       </c>
       <c r="H1622">
-        <v>0.004778609776042831</v>
+        <v>0.004795597030839985</v>
       </c>
       <c r="I1622">
-        <v>0.03397450959430692</v>
+        <v>0.03891078358007416</v>
       </c>
       <c r="J1622">
         <v>0.6987254797153503</v>
       </c>
       <c r="K1622">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="L1622">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="M1622">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="N1622">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="O1622">
         <v>1</v>
@@ -83096,43 +83096,43 @@
     </row>
     <row r="1623" spans="1:16">
       <c r="A1623" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1623" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C1623">
-        <v>1.103313752740089</v>
+        <v>1.092196505092984</v>
       </c>
       <c r="D1623" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="E1623">
-        <v>1.064402969160015</v>
+        <v>1.075197249430458</v>
       </c>
       <c r="F1623">
         <v>-1</v>
       </c>
       <c r="G1623">
-        <v>0.004736686247259911</v>
+        <v>0.004787803494907016</v>
       </c>
       <c r="H1623">
-        <v>0.004795597030839985</v>
+        <v>0.004784802750569543</v>
       </c>
       <c r="I1623">
-        <v>0.03891078358007416</v>
+        <v>0.01699925566252625</v>
       </c>
       <c r="J1623">
-        <v>0.6987254797153503</v>
+        <v>0.6999255662526576</v>
       </c>
       <c r="K1623">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="L1623">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="M1623">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="N1623">
         <v>2.93</v>
@@ -83141,51 +83141,51 @@
         <v>1</v>
       </c>
       <c r="P1623" t="s">
-        <v>359</v>
+        <v>195</v>
       </c>
     </row>
     <row r="1624" spans="1:16">
       <c r="A1624" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1624" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="C1624">
-        <v>1.092196505092984</v>
+        <v>1.061198738105404</v>
       </c>
       <c r="D1624" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="E1624">
-        <v>1.075197249430458</v>
+        <v>1.085197249430457</v>
       </c>
       <c r="F1624">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1624">
-        <v>0.004787803494907016</v>
+        <v>0.004798801261894596</v>
       </c>
       <c r="H1624">
-        <v>0.004784802750569543</v>
+        <v>0.004794802750569542</v>
       </c>
       <c r="I1624">
-        <v>0.01699925566252625</v>
+        <v>0.02399851132505293</v>
       </c>
       <c r="J1624">
         <v>0.6999255662526576</v>
       </c>
       <c r="K1624">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="L1624">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="M1624">
         <v>2.65</v>
       </c>
       <c r="N1624">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="O1624">
         <v>1</v>
@@ -83196,46 +83196,46 @@
     </row>
     <row r="1625" spans="1:16">
       <c r="A1625" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1625" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="C1625">
-        <v>1.061198738105404</v>
+        <v>1.092196505092984</v>
       </c>
       <c r="D1625" t="s">
-        <v>375</v>
+        <v>204</v>
       </c>
       <c r="E1625">
-        <v>1.085197249430457</v>
+        <v>1.058197993767931</v>
       </c>
       <c r="F1625">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1625">
-        <v>0.004798801261894596</v>
+        <v>0.004787803494907016</v>
       </c>
       <c r="H1625">
-        <v>0.004794802750569542</v>
+        <v>0.004781802006232069</v>
       </c>
       <c r="I1625">
-        <v>0.02399851132505293</v>
+        <v>0.03399851132505316</v>
       </c>
       <c r="J1625">
         <v>0.6999255662526576</v>
       </c>
       <c r="K1625">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="L1625">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="M1625">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="N1625">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="O1625">
         <v>1</v>
@@ -83246,46 +83246,46 @@
     </row>
     <row r="1626" spans="1:16">
       <c r="A1626" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1626" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C1626">
-        <v>1.092196505092984</v>
+        <v>1.10019352774309</v>
       </c>
       <c r="D1626" t="s">
-        <v>204</v>
+        <v>379</v>
       </c>
       <c r="E1626">
-        <v>1.058197993767931</v>
+        <v>1.061198738105404</v>
       </c>
       <c r="F1626">
         <v>-1</v>
       </c>
       <c r="G1626">
-        <v>0.004787803494907016</v>
+        <v>0.00473980647225691</v>
       </c>
       <c r="H1626">
-        <v>0.004781802006232069</v>
+        <v>0.004798801261894596</v>
       </c>
       <c r="I1626">
-        <v>0.03399851132505316</v>
+        <v>0.03899478963768588</v>
       </c>
       <c r="J1626">
         <v>0.6999255662526576</v>
       </c>
       <c r="K1626">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="L1626">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="M1626">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="N1626">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="O1626">
         <v>1</v>
@@ -83296,43 +83296,43 @@
     </row>
     <row r="1627" spans="1:16">
       <c r="A1627" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1627" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C1627">
-        <v>1.10019352774309</v>
+        <v>1.087054780595984</v>
       </c>
       <c r="D1627" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="E1627">
-        <v>1.061198738105404</v>
+        <v>1.070036048704302</v>
       </c>
       <c r="F1627">
         <v>-1</v>
       </c>
       <c r="G1627">
-        <v>0.00473980647225691</v>
+        <v>0.004792945219404017</v>
       </c>
       <c r="H1627">
-        <v>0.004798801261894596</v>
+        <v>0.004789963951295699</v>
       </c>
       <c r="I1627">
-        <v>0.03899478963768588</v>
+        <v>0.01701873189168146</v>
       </c>
       <c r="J1627">
-        <v>0.6999255662526576</v>
+        <v>0.701873189168188</v>
       </c>
       <c r="K1627">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="L1627">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="M1627">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="N1627">
         <v>2.93</v>
@@ -83341,24 +83341,24 @@
         <v>1</v>
       </c>
       <c r="P1627" t="s">
-        <v>195</v>
+        <v>360</v>
       </c>
     </row>
     <row r="1628" spans="1:16">
       <c r="A1628" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1628" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C1628">
         <v>1.087054780595984</v>
       </c>
       <c r="D1628" t="s">
-        <v>371</v>
+        <v>204</v>
       </c>
       <c r="E1628">
-        <v>1.070036048704302</v>
+        <v>1.05301731681262</v>
       </c>
       <c r="F1628">
         <v>-1</v>
@@ -83367,10 +83367,10 @@
         <v>0.004792945219404017</v>
       </c>
       <c r="H1628">
-        <v>0.004789963951295699</v>
+        <v>0.00478698268318738</v>
       </c>
       <c r="I1628">
-        <v>0.01701873189168146</v>
+        <v>0.03403746378336381</v>
       </c>
       <c r="J1628">
         <v>0.701873189168188</v>
@@ -83382,10 +83382,10 @@
         <v>2.94</v>
       </c>
       <c r="M1628">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="N1628">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="O1628">
         <v>1</v>
@@ -83396,46 +83396,46 @@
     </row>
     <row r="1629" spans="1:16">
       <c r="A1629" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1629" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="C1629">
+        <v>1.095129708162711</v>
+      </c>
+      <c r="D1629" t="s">
+        <v>379</v>
+      </c>
+      <c r="E1629">
         <v>1.055998584920938</v>
       </c>
-      <c r="D1629" t="s">
-        <v>375</v>
-      </c>
-      <c r="E1629">
-        <v>1.080036048704302</v>
-      </c>
       <c r="F1629">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1629">
+        <v>0.00474487029183729</v>
+      </c>
+      <c r="H1629">
         <v>0.004804001415079063</v>
       </c>
-      <c r="H1629">
-        <v>0.004799963951295698</v>
-      </c>
       <c r="I1629">
-        <v>0.02403746378336358</v>
+        <v>0.03913112324177281</v>
       </c>
       <c r="J1629">
         <v>0.701873189168188</v>
       </c>
       <c r="K1629">
+        <v>2.6</v>
+      </c>
+      <c r="L1629">
+        <v>2.92</v>
+      </c>
+      <c r="M1629">
         <v>2.67</v>
       </c>
-      <c r="L1629">
+      <c r="N1629">
         <v>2.93</v>
-      </c>
-      <c r="M1629">
-        <v>2.65</v>
-      </c>
-      <c r="N1629">
-        <v>2.94</v>
       </c>
       <c r="O1629">
         <v>1</v>
@@ -83446,46 +83446,46 @@
     </row>
     <row r="1630" spans="1:16">
       <c r="A1630" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1630" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C1630">
-        <v>1.087054780595984</v>
+        <v>1.048979853029256</v>
       </c>
       <c r="D1630" t="s">
-        <v>204</v>
+        <v>380</v>
       </c>
       <c r="E1630">
-        <v>1.05301731681262</v>
+        <v>1.058979853029256</v>
       </c>
       <c r="F1630">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1630">
-        <v>0.004792945219404017</v>
+        <v>0.004811020146970744</v>
       </c>
       <c r="H1630">
-        <v>0.00478698268318738</v>
+        <v>0.004821020146970744</v>
       </c>
       <c r="I1630">
-        <v>0.03403746378336381</v>
+        <v>0.009999999999999787</v>
       </c>
       <c r="J1630">
         <v>0.701873189168188</v>
       </c>
       <c r="K1630">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="L1630">
+        <v>2.93</v>
+      </c>
+      <c r="M1630">
+        <v>2.68</v>
+      </c>
+      <c r="N1630">
         <v>2.94</v>
-      </c>
-      <c r="M1630">
-        <v>2.66</v>
-      </c>
-      <c r="N1630">
-        <v>2.92</v>
       </c>
       <c r="O1630">
         <v>1</v>
@@ -83496,43 +83496,43 @@
     </row>
     <row r="1631" spans="1:16">
       <c r="A1631" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1631" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C1631">
-        <v>1.095129708162711</v>
+        <v>1.081706268086576</v>
       </c>
       <c r="D1631" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="E1631">
-        <v>1.055998584920938</v>
+        <v>1.064667276677814</v>
       </c>
       <c r="F1631">
         <v>-1</v>
       </c>
       <c r="G1631">
-        <v>0.00474487029183729</v>
+        <v>0.004798293731913423</v>
       </c>
       <c r="H1631">
-        <v>0.004804001415079063</v>
+        <v>0.004795332723322186</v>
       </c>
       <c r="I1631">
-        <v>0.03913112324177281</v>
+        <v>0.01703899140876253</v>
       </c>
       <c r="J1631">
-        <v>0.701873189168188</v>
+        <v>0.7038991408762968</v>
       </c>
       <c r="K1631">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="L1631">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="M1631">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="N1631">
         <v>2.93</v>
@@ -83541,24 +83541,24 @@
         <v>1</v>
       </c>
       <c r="P1631" t="s">
-        <v>360</v>
+        <v>197</v>
       </c>
     </row>
     <row r="1632" spans="1:16">
       <c r="A1632" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1632" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C1632">
         <v>1.081706268086576</v>
       </c>
       <c r="D1632" t="s">
-        <v>371</v>
+        <v>204</v>
       </c>
       <c r="E1632">
-        <v>1.064667276677814</v>
+        <v>1.04762828526905</v>
       </c>
       <c r="F1632">
         <v>-1</v>
@@ -83567,10 +83567,10 @@
         <v>0.004798293731913423</v>
       </c>
       <c r="H1632">
-        <v>0.004795332723322186</v>
+        <v>0.004792371714730949</v>
       </c>
       <c r="I1632">
-        <v>0.01703899140876253</v>
+        <v>0.03407798281752594</v>
       </c>
       <c r="J1632">
         <v>0.7038991408762968</v>
@@ -83582,10 +83582,10 @@
         <v>2.94</v>
       </c>
       <c r="M1632">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="N1632">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="O1632">
         <v>1</v>
@@ -83596,46 +83596,46 @@
     </row>
     <row r="1633" spans="1:16">
       <c r="A1633" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1633" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C1633">
-        <v>1.081706268086576</v>
+        <v>1.089862233721628</v>
       </c>
       <c r="D1633" t="s">
-        <v>204</v>
+        <v>379</v>
       </c>
       <c r="E1633">
-        <v>1.04762828526905</v>
+        <v>1.050589293860288</v>
       </c>
       <c r="F1633">
         <v>-1</v>
       </c>
       <c r="G1633">
-        <v>0.004798293731913423</v>
+        <v>0.004750137766278372</v>
       </c>
       <c r="H1633">
-        <v>0.004792371714730949</v>
+        <v>0.004809410706139713</v>
       </c>
       <c r="I1633">
-        <v>0.03407798281752594</v>
+        <v>0.03927293986134028</v>
       </c>
       <c r="J1633">
         <v>0.7038991408762968</v>
       </c>
       <c r="K1633">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="L1633">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="M1633">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="N1633">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="O1633">
         <v>1</v>
@@ -83646,46 +83646,46 @@
     </row>
     <row r="1634" spans="1:16">
       <c r="A1634" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1634" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C1634">
-        <v>1.089862233721628</v>
+        <v>1.043550302451525</v>
       </c>
       <c r="D1634" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E1634">
-        <v>1.050589293860288</v>
+        <v>1.053550302451524</v>
       </c>
       <c r="F1634">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1634">
-        <v>0.004750137766278372</v>
+        <v>0.004816449697548475</v>
       </c>
       <c r="H1634">
-        <v>0.004809410706139713</v>
+        <v>0.004826449697548476</v>
       </c>
       <c r="I1634">
-        <v>0.03927293986134028</v>
+        <v>0.009999999999999787</v>
       </c>
       <c r="J1634">
         <v>0.7038991408762968</v>
       </c>
       <c r="K1634">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="L1634">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="M1634">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="N1634">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="O1634">
         <v>1</v>
@@ -83696,43 +83696,43 @@
     </row>
     <row r="1635" spans="1:16">
       <c r="A1635" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1635" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C1635">
-        <v>1.043550302451525</v>
+        <v>1.07524398177382</v>
       </c>
       <c r="D1635" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="E1635">
-        <v>1.043550302451525</v>
+        <v>1.058180512007812</v>
       </c>
       <c r="F1635">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1635">
-        <v>0.004816449697548475</v>
+        <v>0.00480475601822618</v>
       </c>
       <c r="H1635">
-        <v>0.004816449697548475</v>
+        <v>0.004801819487992188</v>
       </c>
       <c r="I1635">
-        <v>0</v>
+        <v>0.0170634697660077</v>
       </c>
       <c r="J1635">
-        <v>0.7038991408762968</v>
+        <v>0.7063469766008257</v>
       </c>
       <c r="K1635">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="L1635">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="M1635">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="N1635">
         <v>2.93</v>
@@ -83741,51 +83741,51 @@
         <v>1</v>
       </c>
       <c r="P1635" t="s">
-        <v>197</v>
+        <v>362</v>
       </c>
     </row>
     <row r="1636" spans="1:16">
       <c r="A1636" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1636" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="C1636">
-        <v>1.07524398177382</v>
+        <v>1.044053572475796</v>
       </c>
       <c r="D1636" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="E1636">
-        <v>1.058180512007812</v>
+        <v>1.068180512007812</v>
       </c>
       <c r="F1636">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1636">
-        <v>0.00480475601822618</v>
+        <v>0.004815946427524205</v>
       </c>
       <c r="H1636">
-        <v>0.004801819487992188</v>
+        <v>0.004811819487992188</v>
       </c>
       <c r="I1636">
-        <v>0.0170634697660077</v>
+        <v>0.0241269395320165</v>
       </c>
       <c r="J1636">
         <v>0.7063469766008257</v>
       </c>
       <c r="K1636">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="L1636">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="M1636">
         <v>2.65</v>
       </c>
       <c r="N1636">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="O1636">
         <v>1</v>
@@ -83796,46 +83796,46 @@
     </row>
     <row r="1637" spans="1:16">
       <c r="A1637" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1637" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="C1637">
-        <v>1.044053572475796</v>
+        <v>1.07524398177382</v>
       </c>
       <c r="D1637" t="s">
-        <v>375</v>
+        <v>204</v>
       </c>
       <c r="E1637">
-        <v>1.068180512007812</v>
+        <v>1.041117042241803</v>
       </c>
       <c r="F1637">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1637">
-        <v>0.004815946427524205</v>
+        <v>0.00480475601822618</v>
       </c>
       <c r="H1637">
-        <v>0.004811819487992188</v>
+        <v>0.004798882957758197</v>
       </c>
       <c r="I1637">
-        <v>0.0241269395320165</v>
+        <v>0.03412693953201651</v>
       </c>
       <c r="J1637">
         <v>0.7063469766008257</v>
       </c>
       <c r="K1637">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="L1637">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="M1637">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="N1637">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="O1637">
         <v>1</v>
@@ -83846,46 +83846,46 @@
     </row>
     <row r="1638" spans="1:16">
       <c r="A1638" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1638" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C1638">
-        <v>1.07524398177382</v>
+        <v>1.083497860837853</v>
       </c>
       <c r="D1638" t="s">
-        <v>204</v>
+        <v>379</v>
       </c>
       <c r="E1638">
-        <v>1.041117042241803</v>
+        <v>1.044053572475796</v>
       </c>
       <c r="F1638">
         <v>-1</v>
       </c>
       <c r="G1638">
-        <v>0.00480475601822618</v>
+        <v>0.004756502139162147</v>
       </c>
       <c r="H1638">
-        <v>0.004798882957758197</v>
+        <v>0.004815946427524205</v>
       </c>
       <c r="I1638">
-        <v>0.03412693953201651</v>
+        <v>0.0394442883620576</v>
       </c>
       <c r="J1638">
         <v>0.7063469766008257</v>
       </c>
       <c r="K1638">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="L1638">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="M1638">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="N1638">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="O1638">
         <v>1</v>
@@ -83896,43 +83896,43 @@
     </row>
     <row r="1639" spans="1:16">
       <c r="A1639" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1639" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C1639">
-        <v>1.083497860837853</v>
+        <v>1.069820290373149</v>
       </c>
       <c r="D1639" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="E1639">
-        <v>1.044053572475796</v>
+        <v>1.052736276321532</v>
       </c>
       <c r="F1639">
         <v>-1</v>
       </c>
       <c r="G1639">
-        <v>0.004756502139162147</v>
+        <v>0.004810179709626852</v>
       </c>
       <c r="H1639">
-        <v>0.004815946427524205</v>
+        <v>0.004807263723678468</v>
       </c>
       <c r="I1639">
-        <v>0.0394442883620576</v>
+        <v>0.01708401405161664</v>
       </c>
       <c r="J1639">
-        <v>0.7063469766008257</v>
+        <v>0.7084014051616859</v>
       </c>
       <c r="K1639">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="L1639">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="M1639">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="N1639">
         <v>2.93</v>
@@ -83941,24 +83941,24 @@
         <v>1</v>
       </c>
       <c r="P1639" t="s">
-        <v>362</v>
+        <v>202</v>
       </c>
     </row>
     <row r="1640" spans="1:16">
       <c r="A1640" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1640" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C1640">
         <v>1.038568248218299</v>
       </c>
       <c r="D1640" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="E1640">
-        <v>1.071072332528</v>
+        <v>1.062736276321532</v>
       </c>
       <c r="F1640">
         <v>1</v>
@@ -83967,10 +83967,10 @@
         <v>0.004821431751781701</v>
       </c>
       <c r="H1640">
-        <v>0.004768927667472</v>
+        <v>0.004817263723678468</v>
       </c>
       <c r="I1640">
-        <v>0.03250408430970109</v>
+        <v>0.02416802810323349</v>
       </c>
       <c r="J1640">
         <v>0.7084014051616859</v>
@@ -83982,10 +83982,10 @@
         <v>2.93</v>
       </c>
       <c r="M1640">
-        <v>2.61</v>
+        <v>2.65</v>
       </c>
       <c r="N1640">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="O1640">
         <v>1</v>
@@ -83996,46 +83996,46 @@
     </row>
     <row r="1641" spans="1:16">
       <c r="A1641" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1641" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="C1641">
-        <v>1.038568248218299</v>
+        <v>1.069820290373149</v>
       </c>
       <c r="D1641" t="s">
-        <v>375</v>
+        <v>204</v>
       </c>
       <c r="E1641">
-        <v>1.062736276321532</v>
+        <v>1.035652262269915</v>
       </c>
       <c r="F1641">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1641">
-        <v>0.004821431751781701</v>
+        <v>0.004810179709626852</v>
       </c>
       <c r="H1641">
-        <v>0.004817263723678468</v>
+        <v>0.004804347737730085</v>
       </c>
       <c r="I1641">
-        <v>0.02416802810323349</v>
+        <v>0.03416802810323372</v>
       </c>
       <c r="J1641">
         <v>0.7084014051616859</v>
       </c>
       <c r="K1641">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="L1641">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="M1641">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="N1641">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="O1641">
         <v>1</v>
@@ -84046,7 +84046,7 @@
     </row>
     <row r="1642" spans="1:16">
       <c r="A1642" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1642" t="s">
         <v>210</v>
@@ -84399,43 +84399,43 @@
         <v>0</v>
       </c>
       <c r="B1649" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="C1649">
+        <v>1.055969001014216</v>
+      </c>
+      <c r="D1649" t="s">
+        <v>379</v>
+      </c>
+      <c r="E1649">
         <v>1.015783551041523</v>
       </c>
-      <c r="D1649" t="s">
-        <v>375</v>
-      </c>
-      <c r="E1649">
-        <v>1.040122251033721</v>
-      </c>
       <c r="F1649">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1649">
+        <v>0.004784030998985784</v>
+      </c>
+      <c r="H1649">
         <v>0.004844216448958478</v>
       </c>
-      <c r="H1649">
-        <v>0.004839877748966279</v>
-      </c>
       <c r="I1649">
-        <v>0.02433869999219795</v>
+        <v>0.04018544997269369</v>
       </c>
       <c r="J1649">
         <v>0.7169349996099167</v>
       </c>
       <c r="K1649">
+        <v>2.6</v>
+      </c>
+      <c r="L1649">
+        <v>2.92</v>
+      </c>
+      <c r="M1649">
         <v>2.67</v>
       </c>
-      <c r="L1649">
+      <c r="N1649">
         <v>2.93</v>
-      </c>
-      <c r="M1649">
-        <v>2.65</v>
-      </c>
-      <c r="N1649">
-        <v>2.94</v>
       </c>
       <c r="O1649">
         <v>1</v>
@@ -84449,43 +84449,43 @@
         <v>1</v>
       </c>
       <c r="B1650" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C1650">
-        <v>1.055969001014216</v>
+        <v>1.008614201045423</v>
       </c>
       <c r="D1650" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E1650">
-        <v>1.015783551041523</v>
+        <v>1.018614201045423</v>
       </c>
       <c r="F1650">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1650">
-        <v>0.004784030998985784</v>
+        <v>0.004851385798954577</v>
       </c>
       <c r="H1650">
-        <v>0.004844216448958478</v>
+        <v>0.004861385798954576</v>
       </c>
       <c r="I1650">
-        <v>0.04018544997269369</v>
+        <v>0.009999999999999787</v>
       </c>
       <c r="J1650">
         <v>0.7169349996099167</v>
       </c>
       <c r="K1650">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="L1650">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="M1650">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="N1650">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="O1650">
         <v>1</v>
@@ -84999,43 +84999,43 @@
         <v>0</v>
       </c>
       <c r="B1661" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="C1661">
+        <v>1.018383137919799</v>
+      </c>
+      <c r="D1661" t="s">
+        <v>379</v>
+      </c>
+      <c r="E1661">
         <v>0.9771857608637942</v>
       </c>
-      <c r="D1661" t="s">
-        <v>375</v>
-      </c>
-      <c r="E1661">
-        <v>1.001813582879795</v>
-      </c>
       <c r="F1661">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1661">
+        <v>0.004821616862080201</v>
+      </c>
+      <c r="H1661">
         <v>0.004882814239136206</v>
       </c>
-      <c r="H1661">
-        <v>0.004878186417120204</v>
-      </c>
       <c r="I1661">
-        <v>0.02462782201600122</v>
+        <v>0.04119737705600501</v>
       </c>
       <c r="J1661">
         <v>0.7313911008000772</v>
       </c>
       <c r="K1661">
+        <v>2.6</v>
+      </c>
+      <c r="L1661">
+        <v>2.92</v>
+      </c>
+      <c r="M1661">
         <v>2.67</v>
       </c>
-      <c r="L1661">
+      <c r="N1661">
         <v>2.93</v>
-      </c>
-      <c r="M1661">
-        <v>2.65</v>
-      </c>
-      <c r="N1661">
-        <v>2.94</v>
       </c>
       <c r="O1661">
         <v>1</v>
@@ -85049,43 +85049,43 @@
         <v>1</v>
       </c>
       <c r="B1662" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C1662">
-        <v>1.018383137919799</v>
+        <v>0.9698718498557932</v>
       </c>
       <c r="D1662" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E1662">
-        <v>0.9771857608637942</v>
+        <v>0.979871849855793</v>
       </c>
       <c r="F1662">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1662">
-        <v>0.004821616862080201</v>
+        <v>0.004890128150144207</v>
       </c>
       <c r="H1662">
-        <v>0.004882814239136206</v>
+        <v>0.004900128150144207</v>
       </c>
       <c r="I1662">
-        <v>0.04119737705600501</v>
+        <v>0.009999999999999787</v>
       </c>
       <c r="J1662">
         <v>0.7313911008000772</v>
       </c>
       <c r="K1662">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="L1662">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="M1662">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="N1662">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="O1662">
         <v>1</v>
@@ -85141,7 +85141,7 @@
         <v>1</v>
       </c>
       <c r="P1663" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="1664" spans="1:16">
@@ -85149,7 +85149,7 @@
         <v>1</v>
       </c>
       <c r="B1664" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C1664">
         <v>0.9661410111521622</v>
@@ -85158,7 +85158,7 @@
         <v>380</v>
       </c>
       <c r="E1664">
-        <v>0.9661410111521622</v>
+        <v>0.976141011152162</v>
       </c>
       <c r="F1664">
         <v>1</v>
@@ -85167,10 +85167,10 @@
         <v>0.004893858988847838</v>
       </c>
       <c r="H1664">
-        <v>0.004893858988847838</v>
+        <v>0.004903858988847838</v>
       </c>
       <c r="I1664">
-        <v>0</v>
+        <v>0.009999999999999787</v>
       </c>
       <c r="J1664">
         <v>0.7327832047939693</v>
@@ -85185,13 +85185,13 @@
         <v>2.68</v>
       </c>
       <c r="N1664">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="O1664">
         <v>1</v>
       </c>
       <c r="P1664" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="1665" spans="1:16">
@@ -85249,7 +85249,7 @@
         <v>1</v>
       </c>
       <c r="B1666" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C1666">
         <v>0.9629392428960224</v>
@@ -85258,7 +85258,7 @@
         <v>380</v>
       </c>
       <c r="E1666">
-        <v>0.9629392428960224</v>
+        <v>0.9729392428960222</v>
       </c>
       <c r="F1666">
         <v>1</v>
@@ -85267,10 +85267,10 @@
         <v>0.004897060757103978</v>
       </c>
       <c r="H1666">
-        <v>0.004897060757103978</v>
+        <v>0.004907060757103977</v>
       </c>
       <c r="I1666">
-        <v>0</v>
+        <v>0.009999999999999787</v>
       </c>
       <c r="J1666">
         <v>0.7339778944417827</v>
@@ -85285,7 +85285,7 @@
         <v>2.68</v>
       </c>
       <c r="N1666">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="O1666">
         <v>1</v>
@@ -85349,7 +85349,7 @@
         <v>1</v>
       </c>
       <c r="B1668" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C1668">
         <v>0.9586817713155449</v>
@@ -85358,7 +85358,7 @@
         <v>380</v>
       </c>
       <c r="E1668">
-        <v>0.9586817713155449</v>
+        <v>0.9686817713155447</v>
       </c>
       <c r="F1668">
         <v>1</v>
@@ -85367,10 +85367,10 @@
         <v>0.004901318228684455</v>
       </c>
       <c r="H1668">
-        <v>0.004901318228684455</v>
+        <v>0.004911318228684456</v>
       </c>
       <c r="I1668">
-        <v>0</v>
+        <v>0.009999999999999787</v>
       </c>
       <c r="J1668">
         <v>0.7355665032404684</v>
@@ -85385,7 +85385,7 @@
         <v>2.68</v>
       </c>
       <c r="N1668">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="O1668">
         <v>1</v>
@@ -85449,7 +85449,7 @@
         <v>1</v>
       </c>
       <c r="B1670" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C1670">
         <v>0.9542230332364481</v>
@@ -85458,7 +85458,7 @@
         <v>380</v>
       </c>
       <c r="E1670">
-        <v>0.9542230332364481</v>
+        <v>0.9642230332364479</v>
       </c>
       <c r="F1670">
         <v>1</v>
@@ -85467,10 +85467,10 @@
         <v>0.004905776966763553</v>
       </c>
       <c r="H1670">
-        <v>0.004905776966763553</v>
+        <v>0.004915776966763552</v>
       </c>
       <c r="I1670">
-        <v>0</v>
+        <v>0.009999999999999787</v>
       </c>
       <c r="J1670">
         <v>0.7372302114789373</v>
@@ -85485,7 +85485,7 @@
         <v>2.68</v>
       </c>
       <c r="N1670">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="O1670">
         <v>1</v>
@@ -85549,7 +85549,7 @@
         <v>1</v>
       </c>
       <c r="B1672" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C1672">
         <v>0.9493037659229</v>
@@ -85558,7 +85558,7 @@
         <v>380</v>
       </c>
       <c r="E1672">
-        <v>0.9493037659229</v>
+        <v>0.9593037659228998</v>
       </c>
       <c r="F1672">
         <v>1</v>
@@ -85567,10 +85567,10 @@
         <v>0.004910696234077101</v>
       </c>
       <c r="H1672">
-        <v>0.004910696234077101</v>
+        <v>0.0049206962340771</v>
       </c>
       <c r="I1672">
-        <v>0</v>
+        <v>0.009999999999999787</v>
       </c>
       <c r="J1672">
         <v>0.7390657589839925</v>
@@ -85585,7 +85585,7 @@
         <v>2.68</v>
       </c>
       <c r="N1672">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="O1672">
         <v>1</v>
@@ -85649,7 +85649,7 @@
         <v>1</v>
       </c>
       <c r="B1674" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C1674">
         <v>0.9442677785678253</v>
@@ -85658,7 +85658,7 @@
         <v>380</v>
       </c>
       <c r="E1674">
-        <v>0.9442677785678253</v>
+        <v>0.9542677785678251</v>
       </c>
       <c r="F1674">
         <v>1</v>
@@ -85667,10 +85667,10 @@
         <v>0.004915732221432175</v>
       </c>
       <c r="H1674">
-        <v>0.004915732221432175</v>
+        <v>0.004925732221432175</v>
       </c>
       <c r="I1674">
-        <v>0</v>
+        <v>0.009999999999999787</v>
       </c>
       <c r="J1674">
         <v>0.7409448587433488</v>
@@ -85685,7 +85685,7 @@
         <v>2.68</v>
       </c>
       <c r="N1674">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="O1674">
         <v>1</v>
@@ -85746,52 +85746,52 @@
     </row>
     <row r="1676" spans="1:16">
       <c r="A1676" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1676" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C1676">
-        <v>0.9832048923380561</v>
+        <v>0.9387358316549501</v>
       </c>
       <c r="D1676" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E1676">
-        <v>0.9410604086702348</v>
+        <v>0.9487358316549499</v>
       </c>
       <c r="F1676">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1676">
-        <v>0.004856795107661943</v>
+        <v>0.00492126416834505</v>
       </c>
       <c r="H1676">
-        <v>0.004918939591329765</v>
+        <v>0.004931264168345051</v>
       </c>
       <c r="I1676">
-        <v>0.04214448366782131</v>
+        <v>0.009999999999999787</v>
       </c>
       <c r="J1676">
-        <v>0.7449211952545938</v>
+        <v>0.7430090180391977</v>
       </c>
       <c r="K1676">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="L1676">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="M1676">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="N1676">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="O1676">
         <v>1</v>
       </c>
       <c r="P1676" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="1677" spans="1:16">
@@ -85799,37 +85799,37 @@
         <v>0</v>
       </c>
       <c r="B1677" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C1677">
-        <v>0.9908270810578887</v>
+        <v>0.9832048923380561</v>
       </c>
       <c r="D1677" t="s">
         <v>379</v>
       </c>
       <c r="E1677">
-        <v>0.9361510919939933</v>
+        <v>0.9410604086702348</v>
       </c>
       <c r="F1677">
         <v>-1</v>
       </c>
       <c r="G1677">
-        <v>0.004829172918942111</v>
+        <v>0.004856795107661943</v>
       </c>
       <c r="H1677">
-        <v>0.004923848908006007</v>
+        <v>0.004918939591329765</v>
       </c>
       <c r="I1677">
-        <v>0.05467598906389548</v>
+        <v>0.04214448366782131</v>
       </c>
       <c r="J1677">
-        <v>0.7467598906389539</v>
+        <v>0.7449211952545938</v>
       </c>
       <c r="K1677">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="L1677">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="M1677">
         <v>2.67</v>
@@ -85841,7 +85841,7 @@
         <v>1</v>
       </c>
       <c r="P1677" t="s">
-        <v>212</v>
+        <v>375</v>
       </c>
     </row>
     <row r="1678" spans="1:16">
@@ -85849,31 +85849,31 @@
         <v>1</v>
       </c>
       <c r="B1678" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C1678">
-        <v>0.9286834930876036</v>
+        <v>0.9336111967176888</v>
       </c>
       <c r="D1678" t="s">
         <v>380</v>
       </c>
       <c r="E1678">
-        <v>0.9286834930876036</v>
+        <v>0.9436111967176886</v>
       </c>
       <c r="F1678">
         <v>1</v>
       </c>
       <c r="G1678">
-        <v>0.004931316506912397</v>
+        <v>0.004926388803282312</v>
       </c>
       <c r="H1678">
-        <v>0.004931316506912397</v>
+        <v>0.004936388803282311</v>
       </c>
       <c r="I1678">
-        <v>0</v>
+        <v>0.009999999999999787</v>
       </c>
       <c r="J1678">
-        <v>0.7467598906389539</v>
+        <v>0.7449211952545938</v>
       </c>
       <c r="K1678">
         <v>2.68</v>
@@ -85885,13 +85885,13 @@
         <v>2.68</v>
       </c>
       <c r="N1678">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="O1678">
         <v>1</v>
       </c>
       <c r="P1678" t="s">
-        <v>212</v>
+        <v>375</v>
       </c>
     </row>
     <row r="1679" spans="1:16">
@@ -85899,37 +85899,37 @@
         <v>0</v>
       </c>
       <c r="B1679" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C1679">
-        <v>0.9883073024579261</v>
+        <v>0.9784242843387199</v>
       </c>
       <c r="D1679" t="s">
         <v>379</v>
       </c>
       <c r="E1679">
-        <v>0.9335332675341099</v>
+        <v>0.9361510919939933</v>
       </c>
       <c r="F1679">
         <v>-1</v>
       </c>
       <c r="G1679">
-        <v>0.004831692697542075</v>
+        <v>0.00486157571566128</v>
       </c>
       <c r="H1679">
-        <v>0.00492646673246589</v>
+        <v>0.004923848908006007</v>
       </c>
       <c r="I1679">
-        <v>0.05477403492381616</v>
+        <v>0.0422731923447266</v>
       </c>
       <c r="J1679">
-        <v>0.7477403492381611</v>
+        <v>0.7467598906389539</v>
       </c>
       <c r="K1679">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="L1679">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="M1679">
         <v>2.67</v>
@@ -85941,7 +85941,7 @@
         <v>1</v>
       </c>
       <c r="P1679" t="s">
-        <v>376</v>
+        <v>213</v>
       </c>
     </row>
     <row r="1680" spans="1:16">
@@ -85949,31 +85949,31 @@
         <v>1</v>
       </c>
       <c r="B1680" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C1680">
-        <v>0.9260558640417282</v>
+        <v>0.9286834930876036</v>
       </c>
       <c r="D1680" t="s">
         <v>380</v>
       </c>
       <c r="E1680">
-        <v>0.9260558640417282</v>
+        <v>0.9386834930876033</v>
       </c>
       <c r="F1680">
         <v>1</v>
       </c>
       <c r="G1680">
-        <v>0.004933944135958272</v>
+        <v>0.004931316506912397</v>
       </c>
       <c r="H1680">
-        <v>0.004933944135958272</v>
+        <v>0.004941316506912397</v>
       </c>
       <c r="I1680">
-        <v>0</v>
+        <v>0.009999999999999787</v>
       </c>
       <c r="J1680">
-        <v>0.7477403492381611</v>
+        <v>0.7467598906389539</v>
       </c>
       <c r="K1680">
         <v>2.68</v>
@@ -85985,13 +85985,13 @@
         <v>2.68</v>
       </c>
       <c r="N1680">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="O1680">
         <v>1</v>
       </c>
       <c r="P1680" t="s">
-        <v>376</v>
+        <v>213</v>
       </c>
     </row>
     <row r="1681" spans="1:16">
@@ -86002,28 +86002,28 @@
         <v>210</v>
       </c>
       <c r="C1681">
-        <v>0.9750565593028233</v>
+        <v>0.975875091980781</v>
       </c>
       <c r="D1681" t="s">
         <v>379</v>
       </c>
       <c r="E1681">
-        <v>0.9326926974378997</v>
+        <v>0.9335332675341099</v>
       </c>
       <c r="F1681">
         <v>-1</v>
       </c>
       <c r="G1681">
-        <v>0.004864943440697177</v>
+        <v>0.00486412490801922</v>
       </c>
       <c r="H1681">
-        <v>0.004927307302562101</v>
+        <v>0.00492646673246589</v>
       </c>
       <c r="I1681">
-        <v>0.04236386186492358</v>
+        <v>0.04234182444667112</v>
       </c>
       <c r="J1681">
-        <v>0.748055169498914</v>
+        <v>0.7477403492381611</v>
       </c>
       <c r="K1681">
         <v>2.6</v>
@@ -86041,7 +86041,7 @@
         <v>1</v>
       </c>
       <c r="P1681" t="s">
-        <v>204</v>
+        <v>376</v>
       </c>
     </row>
     <row r="1682" spans="1:16">
@@ -86049,31 +86049,31 @@
         <v>1</v>
       </c>
       <c r="B1682" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C1682">
-        <v>0.9252121457429103</v>
+        <v>0.9260558640417282</v>
       </c>
       <c r="D1682" t="s">
         <v>380</v>
       </c>
       <c r="E1682">
-        <v>0.9252121457429103</v>
+        <v>0.936055864041728</v>
       </c>
       <c r="F1682">
         <v>1</v>
       </c>
       <c r="G1682">
-        <v>0.00493478785425709</v>
+        <v>0.004933944135958272</v>
       </c>
       <c r="H1682">
-        <v>0.00493478785425709</v>
+        <v>0.004943944135958272</v>
       </c>
       <c r="I1682">
-        <v>0</v>
+        <v>0.009999999999999787</v>
       </c>
       <c r="J1682">
-        <v>0.748055169498914</v>
+        <v>0.7477403492381611</v>
       </c>
       <c r="K1682">
         <v>2.68</v>
@@ -86085,13 +86085,13 @@
         <v>2.68</v>
       </c>
       <c r="N1682">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="O1682">
         <v>1</v>
       </c>
       <c r="P1682" t="s">
-        <v>204</v>
+        <v>376</v>
       </c>
     </row>
     <row r="1683" spans="1:16">
@@ -86099,37 +86099,37 @@
         <v>0</v>
       </c>
       <c r="B1683" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C1683">
-        <v>0.9851098914066783</v>
+        <v>0.9750565593028233</v>
       </c>
       <c r="D1683" t="s">
         <v>379</v>
       </c>
       <c r="E1683">
-        <v>0.9302114436014906</v>
+        <v>0.9326926974378997</v>
       </c>
       <c r="F1683">
         <v>-1</v>
       </c>
       <c r="G1683">
-        <v>0.004834890108593322</v>
+        <v>0.004864943440697177</v>
       </c>
       <c r="H1683">
-        <v>0.00492978855639851</v>
+        <v>0.004927307302562101</v>
       </c>
       <c r="I1683">
-        <v>0.05489844780518771</v>
+        <v>0.04236386186492358</v>
       </c>
       <c r="J1683">
-        <v>0.7489844780518763</v>
+        <v>0.748055169498914</v>
       </c>
       <c r="K1683">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="L1683">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="M1683">
         <v>2.67</v>
@@ -86141,7 +86141,7 @@
         <v>1</v>
       </c>
       <c r="P1683" t="s">
-        <v>377</v>
+        <v>204</v>
       </c>
     </row>
     <row r="1684" spans="1:16">
@@ -86149,31 +86149,31 @@
         <v>1</v>
       </c>
       <c r="B1684" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C1684">
-        <v>0.9227215988209716</v>
+        <v>0.9252121457429103</v>
       </c>
       <c r="D1684" t="s">
         <v>380</v>
       </c>
       <c r="E1684">
-        <v>0.9227215988209716</v>
+        <v>0.9352121457429101</v>
       </c>
       <c r="F1684">
         <v>1</v>
       </c>
       <c r="G1684">
-        <v>0.004937278401179029</v>
+        <v>0.00493478785425709</v>
       </c>
       <c r="H1684">
-        <v>0.004937278401179029</v>
+        <v>0.00494478785425709</v>
       </c>
       <c r="I1684">
-        <v>0</v>
+        <v>0.009999999999999787</v>
       </c>
       <c r="J1684">
-        <v>0.7489844780518763</v>
+        <v>0.748055169498914</v>
       </c>
       <c r="K1684">
         <v>2.68</v>
@@ -86185,13 +86185,13 @@
         <v>2.68</v>
       </c>
       <c r="N1684">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="O1684">
         <v>1</v>
       </c>
       <c r="P1684" t="s">
-        <v>377</v>
+        <v>204</v>
       </c>
     </row>
     <row r="1685" spans="1:16">
@@ -86199,37 +86199,37 @@
         <v>0</v>
       </c>
       <c r="B1685" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C1685">
-        <v>0.9848413094675537</v>
+        <v>0.9726403570651214</v>
       </c>
       <c r="D1685" t="s">
         <v>379</v>
       </c>
       <c r="E1685">
-        <v>0.9299324110032559</v>
+        <v>0.9302114436014906</v>
       </c>
       <c r="F1685">
         <v>-1</v>
       </c>
       <c r="G1685">
-        <v>0.004835158690532447</v>
+        <v>0.004867359642934878</v>
       </c>
       <c r="H1685">
-        <v>0.004930067588996744</v>
+        <v>0.00492978855639851</v>
       </c>
       <c r="I1685">
-        <v>0.05490889846429781</v>
+        <v>0.04242891346363087</v>
       </c>
       <c r="J1685">
-        <v>0.7490889846429754</v>
+        <v>0.7489844780518763</v>
       </c>
       <c r="K1685">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="L1685">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="M1685">
         <v>2.67</v>
@@ -86241,7 +86241,7 @@
         <v>1</v>
       </c>
       <c r="P1685" t="s">
-        <v>210</v>
+        <v>377</v>
       </c>
     </row>
     <row r="1686" spans="1:16">
@@ -86249,31 +86249,31 @@
         <v>1</v>
       </c>
       <c r="B1686" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C1686">
-        <v>0.9224415211568262</v>
+        <v>0.9227215988209716</v>
       </c>
       <c r="D1686" t="s">
         <v>380</v>
       </c>
       <c r="E1686">
-        <v>0.9224415211568262</v>
+        <v>0.9327215988209714</v>
       </c>
       <c r="F1686">
         <v>1</v>
       </c>
       <c r="G1686">
-        <v>0.004937558478843174</v>
+        <v>0.004937278401179029</v>
       </c>
       <c r="H1686">
-        <v>0.004937558478843174</v>
+        <v>0.004947278401179029</v>
       </c>
       <c r="I1686">
-        <v>0</v>
+        <v>0.009999999999999787</v>
       </c>
       <c r="J1686">
-        <v>0.7490889846429754</v>
+        <v>0.7489844780518763</v>
       </c>
       <c r="K1686">
         <v>2.68</v>
@@ -86285,12 +86285,62 @@
         <v>2.68</v>
       </c>
       <c r="N1686">
+        <v>2.94</v>
+      </c>
+      <c r="O1686">
+        <v>1</v>
+      </c>
+      <c r="P1686" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="1687" spans="1:16">
+      <c r="A1687" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1687" t="s">
+        <v>211</v>
+      </c>
+      <c r="C1687">
+        <v>0.9224415211568262</v>
+      </c>
+      <c r="D1687" t="s">
+        <v>380</v>
+      </c>
+      <c r="E1687">
+        <v>0.932441521156826</v>
+      </c>
+      <c r="F1687">
+        <v>1</v>
+      </c>
+      <c r="G1687">
+        <v>0.004937558478843174</v>
+      </c>
+      <c r="H1687">
+        <v>0.004947558478843174</v>
+      </c>
+      <c r="I1687">
+        <v>0.009999999999999787</v>
+      </c>
+      <c r="J1687">
+        <v>0.7490889846429754</v>
+      </c>
+      <c r="K1687">
+        <v>2.68</v>
+      </c>
+      <c r="L1687">
         <v>2.93</v>
       </c>
-      <c r="O1686">
-        <v>1</v>
-      </c>
-      <c r="P1686" t="s">
+      <c r="M1687">
+        <v>2.68</v>
+      </c>
+      <c r="N1687">
+        <v>2.94</v>
+      </c>
+      <c r="O1687">
+        <v>1</v>
+      </c>
+      <c r="P1687" t="s">
         <v>210</v>
       </c>
     </row>

--- a/s60_signal/position-01288-601288.xlsx
+++ b/s60_signal/position-01288-601288.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5073" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5070" uniqueCount="541">
   <si>
     <t>trade_time</t>
   </si>
@@ -1156,7 +1156,7 @@
     <t>2021-12-02</t>
   </si>
   <si>
-    <t>2021-12-07</t>
+    <t>2021-12-08</t>
   </si>
   <si>
     <t>2017-04-07</t>
@@ -1994,7 +1994,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1687"/>
+  <dimension ref="A1:P1686"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -77505,10 +77505,10 @@
         <v>1.159227134481429</v>
       </c>
       <c r="D1511" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="E1511">
-        <v>1.192186922303543</v>
+        <v>1.185707028392486</v>
       </c>
       <c r="F1511">
         <v>1</v>
@@ -77517,10 +77517,10 @@
         <v>0.004720772865518571</v>
       </c>
       <c r="H1511">
-        <v>0.004647813077696458</v>
+        <v>0.004694292971607514</v>
       </c>
       <c r="I1511">
-        <v>0.03295978782211373</v>
+        <v>0.02647989391105687</v>
       </c>
       <c r="J1511">
         <v>0.6619973477764205</v>
@@ -77532,10 +77532,10 @@
         <v>2.94</v>
       </c>
       <c r="M1511">
-        <v>2.61</v>
+        <v>2.65</v>
       </c>
       <c r="N1511">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="O1511">
         <v>1</v>
@@ -77605,10 +77605,10 @@
         <v>1.162467081436958</v>
       </c>
       <c r="D1513" t="s">
-        <v>213</v>
+        <v>375</v>
       </c>
       <c r="E1513">
-        <v>1.19232700187025</v>
+        <v>1.185707028392486</v>
       </c>
       <c r="F1513">
         <v>1</v>
@@ -77617,10 +77617,10 @@
         <v>0.004697532918563043</v>
       </c>
       <c r="H1513">
-        <v>0.00468767299812975</v>
+        <v>0.004694292971607514</v>
       </c>
       <c r="I1513">
-        <v>0.02985992043329211</v>
+        <v>0.02323994695552822</v>
       </c>
       <c r="J1513">
         <v>0.6619973477764205</v>
@@ -77632,7 +77632,7 @@
         <v>2.93</v>
       </c>
       <c r="M1513">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="N1513">
         <v>2.94</v>
@@ -81199,43 +81199,43 @@
         <v>2</v>
       </c>
       <c r="B1585" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="C1585">
+        <v>1.13951777516973</v>
+      </c>
+      <c r="D1585" t="s">
+        <v>379</v>
+      </c>
+      <c r="E1585">
         <v>1.101581715270453</v>
       </c>
-      <c r="D1585" t="s">
-        <v>367</v>
-      </c>
-      <c r="E1585">
-        <v>1.13266976661269</v>
-      </c>
       <c r="F1585">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1585">
+        <v>0.00470048222483027</v>
+      </c>
+      <c r="H1585">
         <v>0.004758418284729548</v>
       </c>
-      <c r="H1585">
-        <v>0.00470733023338731</v>
-      </c>
       <c r="I1585">
-        <v>0.03108805134223669</v>
+        <v>0.03793605989927618</v>
       </c>
       <c r="J1585">
         <v>0.6848008557039501</v>
       </c>
       <c r="K1585">
+        <v>2.6</v>
+      </c>
+      <c r="L1585">
+        <v>2.92</v>
+      </c>
+      <c r="M1585">
         <v>2.67</v>
       </c>
-      <c r="L1585">
+      <c r="N1585">
         <v>2.93</v>
-      </c>
-      <c r="M1585">
-        <v>2.61</v>
-      </c>
-      <c r="N1585">
-        <v>2.92</v>
       </c>
       <c r="O1585">
         <v>1</v>
@@ -81249,43 +81249,43 @@
         <v>3</v>
       </c>
       <c r="B1586" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="C1586">
+        <v>1.094733706713414</v>
+      </c>
+      <c r="D1586" t="s">
+        <v>380</v>
+      </c>
+      <c r="E1586">
         <v>1.101581715270453</v>
       </c>
-      <c r="D1586" t="s">
-        <v>375</v>
-      </c>
-      <c r="E1586">
-        <v>1.125277732384532</v>
-      </c>
       <c r="F1586">
         <v>1</v>
       </c>
       <c r="G1586">
+        <v>0.004765266293286587</v>
+      </c>
+      <c r="H1586">
         <v>0.004758418284729548</v>
       </c>
-      <c r="H1586">
-        <v>0.004754722267615467</v>
-      </c>
       <c r="I1586">
-        <v>0.02369601711407876</v>
+        <v>0.006848008557039709</v>
       </c>
       <c r="J1586">
         <v>0.6848008557039501</v>
       </c>
       <c r="K1586">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="L1586">
         <v>2.93</v>
       </c>
       <c r="M1586">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="N1586">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="O1586">
         <v>1</v>
@@ -81296,96 +81296,96 @@
     </row>
     <row r="1587" spans="1:16">
       <c r="A1587" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1587" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="C1587">
-        <v>1.13951777516973</v>
+        <v>1.1487656475318</v>
       </c>
       <c r="D1587" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E1587">
-        <v>1.101581715270453</v>
+        <v>1.101895370097217</v>
       </c>
       <c r="F1587">
         <v>-1</v>
       </c>
       <c r="G1587">
-        <v>0.00470048222483027</v>
+        <v>0.004831234352468201</v>
       </c>
       <c r="H1587">
-        <v>0.004758418284729548</v>
+        <v>0.004798104629902783</v>
       </c>
       <c r="I1587">
-        <v>0.03793605989927618</v>
+        <v>0.04687027743458283</v>
       </c>
       <c r="J1587">
-        <v>0.6848008557039501</v>
+        <v>0.6870277434582837</v>
       </c>
       <c r="K1587">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="L1587">
-        <v>2.92</v>
+        <v>2.99</v>
       </c>
       <c r="M1587">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="N1587">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="O1587">
         <v>1</v>
       </c>
       <c r="P1587" t="s">
-        <v>538</v>
+        <v>188</v>
       </c>
     </row>
     <row r="1588" spans="1:16">
       <c r="A1588" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1588" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="C1588">
-        <v>1.1487656475318</v>
+        <v>1.133727867008462</v>
       </c>
       <c r="D1588" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E1588">
-        <v>1.101895370097217</v>
+        <v>1.095635924966383</v>
       </c>
       <c r="F1588">
         <v>-1</v>
       </c>
       <c r="G1588">
-        <v>0.004831234352468201</v>
+        <v>0.004706272132991538</v>
       </c>
       <c r="H1588">
-        <v>0.004798104629902783</v>
+        <v>0.004764364075033617</v>
       </c>
       <c r="I1588">
-        <v>0.04687027743458283</v>
+        <v>0.03809194204207955</v>
       </c>
       <c r="J1588">
         <v>0.6870277434582837</v>
       </c>
       <c r="K1588">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="L1588">
-        <v>2.99</v>
+        <v>2.92</v>
       </c>
       <c r="M1588">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="N1588">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="O1588">
         <v>1</v>
@@ -81396,46 +81396,46 @@
     </row>
     <row r="1589" spans="1:16">
       <c r="A1589" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1589" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="C1589">
-        <v>1.091895370097217</v>
+        <v>1.0887656475318</v>
       </c>
       <c r="D1589" t="s">
-        <v>363</v>
+        <v>380</v>
       </c>
       <c r="E1589">
-        <v>1.119376479835548</v>
+        <v>1.095635924966383</v>
       </c>
       <c r="F1589">
         <v>1</v>
       </c>
       <c r="G1589">
-        <v>0.004788104629902783</v>
+        <v>0.004771234352468201</v>
       </c>
       <c r="H1589">
-        <v>0.004760623520164452</v>
+        <v>0.004764364075033617</v>
       </c>
       <c r="I1589">
-        <v>0.0274811097383314</v>
+        <v>0.006870277434582794</v>
       </c>
       <c r="J1589">
         <v>0.6870277434582837</v>
       </c>
       <c r="K1589">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="L1589">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="M1589">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="N1589">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="O1589">
         <v>1</v>
@@ -81446,140 +81446,140 @@
     </row>
     <row r="1590" spans="1:16">
       <c r="A1590" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1590" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="C1590">
-        <v>1.095635924966383</v>
+        <v>1.142929588258059</v>
       </c>
       <c r="D1590" t="s">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="E1590">
-        <v>1.12685758957388</v>
+        <v>1.096037534482903</v>
       </c>
       <c r="F1590">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1590">
-        <v>0.004764364075033617</v>
+        <v>0.004837070411741941</v>
       </c>
       <c r="H1590">
-        <v>0.00471314241042612</v>
+        <v>0.004803962465517097</v>
       </c>
       <c r="I1590">
-        <v>0.03122166460749698</v>
+        <v>0.04689205377515626</v>
       </c>
       <c r="J1590">
-        <v>0.6870277434582837</v>
+        <v>0.6892053775156495</v>
       </c>
       <c r="K1590">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="L1590">
-        <v>2.93</v>
+        <v>2.99</v>
       </c>
       <c r="M1590">
-        <v>2.61</v>
+        <v>2.69</v>
       </c>
       <c r="N1590">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="O1590">
         <v>1</v>
       </c>
       <c r="P1590" t="s">
-        <v>188</v>
+        <v>356</v>
       </c>
     </row>
     <row r="1591" spans="1:16">
       <c r="A1591" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1591" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="C1591">
-        <v>1.095635924966383</v>
+        <v>1.128066018459311</v>
       </c>
       <c r="D1591" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="E1591">
-        <v>1.119376479835548</v>
+        <v>1.089821642033216</v>
       </c>
       <c r="F1591">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1591">
-        <v>0.004764364075033617</v>
+        <v>0.004711933981540689</v>
       </c>
       <c r="H1591">
-        <v>0.004760623520164452</v>
+        <v>0.004770178357966785</v>
       </c>
       <c r="I1591">
-        <v>0.0237405548691656</v>
+        <v>0.03824437642609513</v>
       </c>
       <c r="J1591">
-        <v>0.6870277434582837</v>
+        <v>0.6892053775156495</v>
       </c>
       <c r="K1591">
+        <v>2.6</v>
+      </c>
+      <c r="L1591">
+        <v>2.92</v>
+      </c>
+      <c r="M1591">
         <v>2.67</v>
       </c>
-      <c r="L1591">
+      <c r="N1591">
         <v>2.93</v>
       </c>
-      <c r="M1591">
-        <v>2.65</v>
-      </c>
-      <c r="N1591">
-        <v>2.94</v>
-      </c>
       <c r="O1591">
         <v>1</v>
       </c>
       <c r="P1591" t="s">
-        <v>188</v>
+        <v>356</v>
       </c>
     </row>
     <row r="1592" spans="1:16">
       <c r="A1592" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B1592" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C1592">
-        <v>1.133727867008462</v>
+        <v>1.082929588258059</v>
       </c>
       <c r="D1592" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E1592">
-        <v>1.095635924966383</v>
+        <v>1.089821642033216</v>
       </c>
       <c r="F1592">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1592">
-        <v>0.004706272132991538</v>
+        <v>0.004777070411741941</v>
       </c>
       <c r="H1592">
-        <v>0.004764364075033617</v>
+        <v>0.004770178357966785</v>
       </c>
       <c r="I1592">
-        <v>0.03809194204207955</v>
+        <v>0.00689205377515667</v>
       </c>
       <c r="J1592">
-        <v>0.6870277434582837</v>
+        <v>0.6892053775156495</v>
       </c>
       <c r="K1592">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="L1592">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="M1592">
         <v>2.67</v>
@@ -81591,7 +81591,7 @@
         <v>1</v>
       </c>
       <c r="P1592" t="s">
-        <v>188</v>
+        <v>356</v>
       </c>
     </row>
     <row r="1593" spans="1:16">
@@ -81599,49 +81599,49 @@
         <v>0</v>
       </c>
       <c r="B1593" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="C1593">
-        <v>1.142929588258059</v>
+        <v>1.124376915605622</v>
       </c>
       <c r="D1593" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E1593">
-        <v>1.096037534482903</v>
+        <v>1.08603321717962</v>
       </c>
       <c r="F1593">
         <v>-1</v>
       </c>
       <c r="G1593">
-        <v>0.004837070411741941</v>
+        <v>0.004715623084394377</v>
       </c>
       <c r="H1593">
-        <v>0.004803962465517097</v>
+        <v>0.004773966782820381</v>
       </c>
       <c r="I1593">
-        <v>0.04689205377515626</v>
+        <v>0.03834369842600216</v>
       </c>
       <c r="J1593">
-        <v>0.6892053775156495</v>
+        <v>0.6906242632286068</v>
       </c>
       <c r="K1593">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="L1593">
-        <v>2.99</v>
+        <v>2.92</v>
       </c>
       <c r="M1593">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="N1593">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="O1593">
         <v>1</v>
       </c>
       <c r="P1593" t="s">
-        <v>356</v>
+        <v>205</v>
       </c>
     </row>
     <row r="1594" spans="1:16">
@@ -81649,181 +81649,181 @@
         <v>1</v>
       </c>
       <c r="B1594" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="C1594">
-        <v>1.086037534482903</v>
+        <v>1.079126974547334</v>
       </c>
       <c r="D1594" t="s">
-        <v>363</v>
+        <v>380</v>
       </c>
       <c r="E1594">
-        <v>1.113605749583529</v>
+        <v>1.08603321717962</v>
       </c>
       <c r="F1594">
         <v>1</v>
       </c>
       <c r="G1594">
-        <v>0.004793962465517098</v>
+        <v>0.004780873025452667</v>
       </c>
       <c r="H1594">
-        <v>0.004766394250416471</v>
+        <v>0.004773966782820381</v>
       </c>
       <c r="I1594">
-        <v>0.02756821510062601</v>
+        <v>0.006906242632286341</v>
       </c>
       <c r="J1594">
-        <v>0.6892053775156495</v>
+        <v>0.6906242632286068</v>
       </c>
       <c r="K1594">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="L1594">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="M1594">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="N1594">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="O1594">
         <v>1</v>
       </c>
       <c r="P1594" t="s">
-        <v>356</v>
+        <v>205</v>
       </c>
     </row>
     <row r="1595" spans="1:16">
       <c r="A1595" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1595" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="C1595">
-        <v>1.089821642033216</v>
+        <v>1.114660360727521</v>
       </c>
       <c r="D1595" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="E1595">
-        <v>1.121173964684155</v>
+        <v>1.097746195427247</v>
       </c>
       <c r="F1595">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1595">
-        <v>0.004770178357966785</v>
+        <v>0.004765339639272479</v>
       </c>
       <c r="H1595">
-        <v>0.004718826035315845</v>
+        <v>0.004762253804572754</v>
       </c>
       <c r="I1595">
-        <v>0.0313523226509389</v>
+        <v>0.01691416530027401</v>
       </c>
       <c r="J1595">
-        <v>0.6892053775156495</v>
+        <v>0.6914165300274542</v>
       </c>
       <c r="K1595">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="L1595">
+        <v>2.94</v>
+      </c>
+      <c r="M1595">
+        <v>2.65</v>
+      </c>
+      <c r="N1595">
         <v>2.93</v>
       </c>
-      <c r="M1595">
-        <v>2.61</v>
-      </c>
-      <c r="N1595">
-        <v>2.92</v>
-      </c>
       <c r="O1595">
         <v>1</v>
       </c>
       <c r="P1595" t="s">
-        <v>356</v>
+        <v>539</v>
       </c>
     </row>
     <row r="1596" spans="1:16">
       <c r="A1596" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1596" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="C1596">
-        <v>1.089821642033216</v>
+        <v>1.114660360727521</v>
       </c>
       <c r="D1596" t="s">
-        <v>375</v>
+        <v>204</v>
       </c>
       <c r="E1596">
-        <v>1.113605749583529</v>
+        <v>1.080832030126972</v>
       </c>
       <c r="F1596">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1596">
-        <v>0.004770178357966785</v>
+        <v>0.004765339639272479</v>
       </c>
       <c r="H1596">
-        <v>0.004766394250416471</v>
+        <v>0.004759167969873028</v>
       </c>
       <c r="I1596">
-        <v>0.02378410755031291</v>
+        <v>0.03382833060054891</v>
       </c>
       <c r="J1596">
-        <v>0.6892053775156495</v>
+        <v>0.6914165300274542</v>
       </c>
       <c r="K1596">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="L1596">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="M1596">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="N1596">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="O1596">
         <v>1</v>
       </c>
       <c r="P1596" t="s">
-        <v>356</v>
+        <v>539</v>
       </c>
     </row>
     <row r="1597" spans="1:16">
       <c r="A1597" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B1597" t="s">
         <v>210</v>
       </c>
       <c r="C1597">
-        <v>1.128066018459311</v>
+        <v>1.122317021928619</v>
       </c>
       <c r="D1597" t="s">
         <v>379</v>
       </c>
       <c r="E1597">
-        <v>1.089821642033216</v>
+        <v>1.083917864826698</v>
       </c>
       <c r="F1597">
         <v>-1</v>
       </c>
       <c r="G1597">
-        <v>0.004711933981540689</v>
+        <v>0.004717682978071382</v>
       </c>
       <c r="H1597">
-        <v>0.004770178357966785</v>
+        <v>0.004776082135173302</v>
       </c>
       <c r="I1597">
-        <v>0.03824437642609513</v>
+        <v>0.03839915710192132</v>
       </c>
       <c r="J1597">
-        <v>0.6892053775156495</v>
+        <v>0.6914165300274542</v>
       </c>
       <c r="K1597">
         <v>2.6</v>
@@ -81841,98 +81841,98 @@
         <v>1</v>
       </c>
       <c r="P1597" t="s">
-        <v>356</v>
+        <v>539</v>
       </c>
     </row>
     <row r="1598" spans="1:16">
       <c r="A1598" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1598" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="C1598">
-        <v>1.082220731915048</v>
+        <v>1.077003699526423</v>
       </c>
       <c r="D1598" t="s">
-        <v>363</v>
+        <v>380</v>
       </c>
       <c r="E1598">
-        <v>1.109845702444192</v>
+        <v>1.083917864826698</v>
       </c>
       <c r="F1598">
         <v>1</v>
       </c>
       <c r="G1598">
-        <v>0.004797779268084952</v>
+        <v>0.004782996300473578</v>
       </c>
       <c r="H1598">
-        <v>0.004770154297555809</v>
+        <v>0.004776082135173302</v>
       </c>
       <c r="I1598">
-        <v>0.02762497052914425</v>
+        <v>0.006914165300274666</v>
       </c>
       <c r="J1598">
-        <v>0.6906242632286068</v>
+        <v>0.6914165300274542</v>
       </c>
       <c r="K1598">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="L1598">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="M1598">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="N1598">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="O1598">
         <v>1</v>
       </c>
       <c r="P1598" t="s">
-        <v>205</v>
+        <v>539</v>
       </c>
     </row>
     <row r="1599" spans="1:16">
       <c r="A1599" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1599" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C1599">
-        <v>1.124376915605622</v>
+        <v>1.112310701019539</v>
       </c>
       <c r="D1599" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="E1599">
-        <v>1.08603321717962</v>
+        <v>1.095387635493099</v>
       </c>
       <c r="F1599">
         <v>-1</v>
       </c>
       <c r="G1599">
-        <v>0.004715623084394377</v>
+        <v>0.00476768929898046</v>
       </c>
       <c r="H1599">
-        <v>0.004773966782820381</v>
+        <v>0.004764612364506902</v>
       </c>
       <c r="I1599">
-        <v>0.03834369842600216</v>
+        <v>0.01692306552644074</v>
       </c>
       <c r="J1599">
-        <v>0.6906242632286068</v>
+        <v>0.6923065526441138</v>
       </c>
       <c r="K1599">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="L1599">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="M1599">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="N1599">
         <v>2.93</v>
@@ -81941,89 +81941,89 @@
         <v>1</v>
       </c>
       <c r="P1599" t="s">
-        <v>205</v>
+        <v>378</v>
       </c>
     </row>
     <row r="1600" spans="1:16">
       <c r="A1600" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1600" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C1600">
-        <v>1.079126974547334</v>
+        <v>1.112310701019539</v>
       </c>
       <c r="D1600" t="s">
-        <v>380</v>
+        <v>204</v>
       </c>
       <c r="E1600">
-        <v>1.089126974547334</v>
+        <v>1.078464569966657</v>
       </c>
       <c r="F1600">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1600">
-        <v>0.004780873025452667</v>
+        <v>0.00476768929898046</v>
       </c>
       <c r="H1600">
-        <v>0.004790873025452666</v>
+        <v>0.004761535430033343</v>
       </c>
       <c r="I1600">
-        <v>0.009999999999999787</v>
+        <v>0.03384613105288237</v>
       </c>
       <c r="J1600">
-        <v>0.6906242632286068</v>
+        <v>0.6923065526441138</v>
       </c>
       <c r="K1600">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="L1600">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="M1600">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="N1600">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="O1600">
         <v>1</v>
       </c>
       <c r="P1600" t="s">
-        <v>205</v>
+        <v>378</v>
       </c>
     </row>
     <row r="1601" spans="1:16">
       <c r="A1601" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1601" t="s">
         <v>210</v>
       </c>
       <c r="C1601">
-        <v>1.122317021928619</v>
+        <v>1.120002963125304</v>
       </c>
       <c r="D1601" t="s">
         <v>379</v>
       </c>
       <c r="E1601">
-        <v>1.083917864826698</v>
+        <v>1.081541504440216</v>
       </c>
       <c r="F1601">
         <v>-1</v>
       </c>
       <c r="G1601">
-        <v>0.004717682978071382</v>
+        <v>0.004719997036874695</v>
       </c>
       <c r="H1601">
-        <v>0.004776082135173302</v>
+        <v>0.004778458495559784</v>
       </c>
       <c r="I1601">
-        <v>0.03839915710192132</v>
+        <v>0.03846145868508777</v>
       </c>
       <c r="J1601">
-        <v>0.6914165300274542</v>
+        <v>0.6923065526441138</v>
       </c>
       <c r="K1601">
         <v>2.6</v>
@@ -82041,39 +82041,39 @@
         <v>1</v>
       </c>
       <c r="P1601" t="s">
-        <v>539</v>
+        <v>378</v>
       </c>
     </row>
     <row r="1602" spans="1:16">
       <c r="A1602" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1602" t="s">
         <v>211</v>
       </c>
       <c r="C1602">
-        <v>1.077003699526423</v>
+        <v>1.074618438913775</v>
       </c>
       <c r="D1602" t="s">
         <v>380</v>
       </c>
       <c r="E1602">
-        <v>1.087003699526423</v>
+        <v>1.081541504440216</v>
       </c>
       <c r="F1602">
         <v>1</v>
       </c>
       <c r="G1602">
-        <v>0.004782996300473578</v>
+        <v>0.004785381561086226</v>
       </c>
       <c r="H1602">
-        <v>0.004792996300473577</v>
+        <v>0.004778458495559784</v>
       </c>
       <c r="I1602">
-        <v>0.009999999999999787</v>
+        <v>0.006923065526441174</v>
       </c>
       <c r="J1602">
-        <v>0.6914165300274542</v>
+        <v>0.6923065526441138</v>
       </c>
       <c r="K1602">
         <v>2.68</v>
@@ -82082,16 +82082,16 @@
         <v>2.93</v>
       </c>
       <c r="M1602">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="N1602">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="O1602">
         <v>1</v>
       </c>
       <c r="P1602" t="s">
-        <v>539</v>
+        <v>378</v>
       </c>
     </row>
     <row r="1603" spans="1:16">
@@ -82102,28 +82102,28 @@
         <v>212</v>
       </c>
       <c r="C1603">
-        <v>1.112310701019539</v>
+        <v>1.10751365441215</v>
       </c>
       <c r="D1603" t="s">
         <v>371</v>
       </c>
       <c r="E1603">
-        <v>1.095387635493099</v>
+        <v>1.090572418254621</v>
       </c>
       <c r="F1603">
         <v>-1</v>
       </c>
       <c r="G1603">
-        <v>0.00476768929898046</v>
+        <v>0.004772486345587849</v>
       </c>
       <c r="H1603">
-        <v>0.004764612364506902</v>
+        <v>0.004769427581745379</v>
       </c>
       <c r="I1603">
-        <v>0.01692306552644074</v>
+        <v>0.0169412361575294</v>
       </c>
       <c r="J1603">
-        <v>0.6923065526441138</v>
+        <v>0.6941236157529733</v>
       </c>
       <c r="K1603">
         <v>2.64</v>
@@ -82141,7 +82141,7 @@
         <v>1</v>
       </c>
       <c r="P1603" t="s">
-        <v>378</v>
+        <v>540</v>
       </c>
     </row>
     <row r="1604" spans="1:16">
@@ -82152,28 +82152,28 @@
         <v>213</v>
       </c>
       <c r="C1604">
-        <v>1.112310701019539</v>
+        <v>1.10751365441215</v>
       </c>
       <c r="D1604" t="s">
         <v>204</v>
       </c>
       <c r="E1604">
-        <v>1.078464569966657</v>
+        <v>1.073631182097091</v>
       </c>
       <c r="F1604">
         <v>-1</v>
       </c>
       <c r="G1604">
-        <v>0.00476768929898046</v>
+        <v>0.004772486345587849</v>
       </c>
       <c r="H1604">
-        <v>0.004761535430033343</v>
+        <v>0.004766368817902909</v>
       </c>
       <c r="I1604">
-        <v>0.03384613105288237</v>
+        <v>0.03388247231505948</v>
       </c>
       <c r="J1604">
-        <v>0.6923065526441138</v>
+        <v>0.6941236157529733</v>
       </c>
       <c r="K1604">
         <v>2.64</v>
@@ -82191,7 +82191,7 @@
         <v>1</v>
       </c>
       <c r="P1604" t="s">
-        <v>378</v>
+        <v>540</v>
       </c>
     </row>
     <row r="1605" spans="1:16">
@@ -82202,28 +82202,28 @@
         <v>210</v>
       </c>
       <c r="C1605">
-        <v>1.120002963125304</v>
+        <v>1.115278599042269</v>
       </c>
       <c r="D1605" t="s">
         <v>379</v>
       </c>
       <c r="E1605">
-        <v>1.081541504440216</v>
+        <v>1.076689945939561</v>
       </c>
       <c r="F1605">
         <v>-1</v>
       </c>
       <c r="G1605">
-        <v>0.004719997036874695</v>
+        <v>0.004724721400957731</v>
       </c>
       <c r="H1605">
-        <v>0.004778458495559784</v>
+        <v>0.004783310054060439</v>
       </c>
       <c r="I1605">
-        <v>0.03846145868508777</v>
+        <v>0.03858865310270798</v>
       </c>
       <c r="J1605">
-        <v>0.6923065526441138</v>
+        <v>0.6941236157529733</v>
       </c>
       <c r="K1605">
         <v>2.6</v>
@@ -82241,7 +82241,7 @@
         <v>1</v>
       </c>
       <c r="P1605" t="s">
-        <v>378</v>
+        <v>540</v>
       </c>
     </row>
     <row r="1606" spans="1:16">
@@ -82252,28 +82252,28 @@
         <v>211</v>
       </c>
       <c r="C1606">
-        <v>1.074618438913775</v>
+        <v>1.069748709782032</v>
       </c>
       <c r="D1606" t="s">
         <v>380</v>
       </c>
       <c r="E1606">
-        <v>1.084618438913775</v>
+        <v>1.076689945939561</v>
       </c>
       <c r="F1606">
         <v>1</v>
       </c>
       <c r="G1606">
-        <v>0.004785381561086226</v>
+        <v>0.004790251290217968</v>
       </c>
       <c r="H1606">
-        <v>0.004795381561086226</v>
+        <v>0.004783310054060439</v>
       </c>
       <c r="I1606">
-        <v>0.009999999999999787</v>
+        <v>0.00694123615752984</v>
       </c>
       <c r="J1606">
-        <v>0.6923065526441138</v>
+        <v>0.6941236157529733</v>
       </c>
       <c r="K1606">
         <v>2.68</v>
@@ -82282,16 +82282,16 @@
         <v>2.93</v>
       </c>
       <c r="M1606">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="N1606">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="O1606">
         <v>1</v>
       </c>
       <c r="P1606" t="s">
-        <v>378</v>
+        <v>540</v>
       </c>
     </row>
     <row r="1607" spans="1:16">
@@ -82302,28 +82302,28 @@
         <v>212</v>
       </c>
       <c r="C1607">
-        <v>1.10751365441215</v>
+        <v>1.104207216649199</v>
       </c>
       <c r="D1607" t="s">
-        <v>371</v>
+        <v>201</v>
       </c>
       <c r="E1607">
-        <v>1.090572418254621</v>
+        <v>1.073345935020213</v>
       </c>
       <c r="F1607">
         <v>-1</v>
       </c>
       <c r="G1607">
-        <v>0.004772486345587849</v>
+        <v>0.004775792783350801</v>
       </c>
       <c r="H1607">
-        <v>0.004769427581745379</v>
+        <v>0.004786654064979788</v>
       </c>
       <c r="I1607">
-        <v>0.0169412361575294</v>
+        <v>0.03086128162898594</v>
       </c>
       <c r="J1607">
-        <v>0.6941236157529733</v>
+        <v>0.6953760542995459</v>
       </c>
       <c r="K1607">
         <v>2.64</v>
@@ -82332,7 +82332,7 @@
         <v>2.94</v>
       </c>
       <c r="M1607">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="N1607">
         <v>2.93</v>
@@ -82341,7 +82341,7 @@
         <v>1</v>
       </c>
       <c r="P1607" t="s">
-        <v>540</v>
+        <v>192</v>
       </c>
     </row>
     <row r="1608" spans="1:16">
@@ -82352,28 +82352,28 @@
         <v>213</v>
       </c>
       <c r="C1608">
-        <v>1.10751365441215</v>
+        <v>1.104207216649199</v>
       </c>
       <c r="D1608" t="s">
         <v>204</v>
       </c>
       <c r="E1608">
-        <v>1.073631182097091</v>
+        <v>1.070299695563208</v>
       </c>
       <c r="F1608">
         <v>-1</v>
       </c>
       <c r="G1608">
-        <v>0.004772486345587849</v>
+        <v>0.004775792783350801</v>
       </c>
       <c r="H1608">
-        <v>0.004766368817902909</v>
+        <v>0.004769700304436793</v>
       </c>
       <c r="I1608">
-        <v>0.03388247231505948</v>
+        <v>0.03390752108599093</v>
       </c>
       <c r="J1608">
-        <v>0.6941236157529733</v>
+        <v>0.6953760542995459</v>
       </c>
       <c r="K1608">
         <v>2.64</v>
@@ -82391,7 +82391,7 @@
         <v>1</v>
       </c>
       <c r="P1608" t="s">
-        <v>540</v>
+        <v>192</v>
       </c>
     </row>
     <row r="1609" spans="1:16">
@@ -82402,28 +82402,28 @@
         <v>210</v>
       </c>
       <c r="C1609">
-        <v>1.115278599042269</v>
+        <v>1.112022258821181</v>
       </c>
       <c r="D1609" t="s">
         <v>379</v>
       </c>
       <c r="E1609">
-        <v>1.076689945939561</v>
+        <v>1.073345935020213</v>
       </c>
       <c r="F1609">
         <v>-1</v>
       </c>
       <c r="G1609">
-        <v>0.004724721400957731</v>
+        <v>0.004727977741178819</v>
       </c>
       <c r="H1609">
-        <v>0.004783310054060439</v>
+        <v>0.004786654064979788</v>
       </c>
       <c r="I1609">
-        <v>0.03858865310270798</v>
+        <v>0.03867632380096775</v>
       </c>
       <c r="J1609">
-        <v>0.6941236157529733</v>
+        <v>0.6953760542995459</v>
       </c>
       <c r="K1609">
         <v>2.6</v>
@@ -82441,7 +82441,7 @@
         <v>1</v>
       </c>
       <c r="P1609" t="s">
-        <v>540</v>
+        <v>192</v>
       </c>
     </row>
     <row r="1610" spans="1:16">
@@ -82452,28 +82452,28 @@
         <v>211</v>
       </c>
       <c r="C1610">
-        <v>1.069748709782032</v>
+        <v>1.066392174477217</v>
       </c>
       <c r="D1610" t="s">
         <v>380</v>
       </c>
       <c r="E1610">
-        <v>1.079748709782031</v>
+        <v>1.073345935020213</v>
       </c>
       <c r="F1610">
         <v>1</v>
       </c>
       <c r="G1610">
-        <v>0.004790251290217968</v>
+        <v>0.004793607825522783</v>
       </c>
       <c r="H1610">
-        <v>0.004800251290217968</v>
+        <v>0.004786654064979788</v>
       </c>
       <c r="I1610">
-        <v>0.009999999999999787</v>
+        <v>0.006953760542995679</v>
       </c>
       <c r="J1610">
-        <v>0.6941236157529733</v>
+        <v>0.6953760542995459</v>
       </c>
       <c r="K1610">
         <v>2.68</v>
@@ -82482,16 +82482,16 @@
         <v>2.93</v>
       </c>
       <c r="M1610">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="N1610">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="O1610">
         <v>1</v>
       </c>
       <c r="P1610" t="s">
-        <v>540</v>
+        <v>192</v>
       </c>
     </row>
     <row r="1611" spans="1:16">
@@ -82502,28 +82502,28 @@
         <v>212</v>
       </c>
       <c r="C1611">
-        <v>1.104207216649199</v>
+        <v>1.099749151215716</v>
       </c>
       <c r="D1611" t="s">
         <v>371</v>
       </c>
       <c r="E1611">
-        <v>1.087253456106204</v>
+        <v>1.082778504061231</v>
       </c>
       <c r="F1611">
         <v>-1</v>
       </c>
       <c r="G1611">
-        <v>0.004775792783350801</v>
+        <v>0.004780250848784283</v>
       </c>
       <c r="H1611">
-        <v>0.004772746543893797</v>
+        <v>0.004777221495938769</v>
       </c>
       <c r="I1611">
-        <v>0.01695376054299502</v>
+        <v>0.01697064715448549</v>
       </c>
       <c r="J1611">
-        <v>0.6953760542995459</v>
+        <v>0.6970647154485922</v>
       </c>
       <c r="K1611">
         <v>2.64</v>
@@ -82541,7 +82541,7 @@
         <v>1</v>
       </c>
       <c r="P1611" t="s">
-        <v>192</v>
+        <v>358</v>
       </c>
     </row>
     <row r="1612" spans="1:16">
@@ -82552,28 +82552,28 @@
         <v>213</v>
       </c>
       <c r="C1612">
-        <v>1.104207216649199</v>
+        <v>1.099749151215716</v>
       </c>
       <c r="D1612" t="s">
         <v>204</v>
       </c>
       <c r="E1612">
-        <v>1.070299695563208</v>
+        <v>1.065807856906745</v>
       </c>
       <c r="F1612">
         <v>-1</v>
       </c>
       <c r="G1612">
-        <v>0.004775792783350801</v>
+        <v>0.004780250848784283</v>
       </c>
       <c r="H1612">
-        <v>0.004769700304436793</v>
+        <v>0.004774192143093256</v>
       </c>
       <c r="I1612">
-        <v>0.03390752108599093</v>
+        <v>0.03394129430897186</v>
       </c>
       <c r="J1612">
-        <v>0.6953760542995459</v>
+        <v>0.6970647154485922</v>
       </c>
       <c r="K1612">
         <v>2.64</v>
@@ -82591,7 +82591,7 @@
         <v>1</v>
       </c>
       <c r="P1612" t="s">
-        <v>192</v>
+        <v>358</v>
       </c>
     </row>
     <row r="1613" spans="1:16">
@@ -82602,28 +82602,28 @@
         <v>210</v>
       </c>
       <c r="C1613">
-        <v>1.112022258821181</v>
+        <v>1.10763173983366</v>
       </c>
       <c r="D1613" t="s">
         <v>379</v>
       </c>
       <c r="E1613">
-        <v>1.073345935020213</v>
+        <v>1.068837209752259</v>
       </c>
       <c r="F1613">
         <v>-1</v>
       </c>
       <c r="G1613">
-        <v>0.004727977741178819</v>
+        <v>0.00473236826016634</v>
       </c>
       <c r="H1613">
-        <v>0.004786654064979788</v>
+        <v>0.004791162790247741</v>
       </c>
       <c r="I1613">
-        <v>0.03867632380096775</v>
+        <v>0.03879453008140099</v>
       </c>
       <c r="J1613">
-        <v>0.6953760542995459</v>
+        <v>0.6970647154485922</v>
       </c>
       <c r="K1613">
         <v>2.6</v>
@@ -82641,7 +82641,7 @@
         <v>1</v>
       </c>
       <c r="P1613" t="s">
-        <v>192</v>
+        <v>358</v>
       </c>
     </row>
     <row r="1614" spans="1:16">
@@ -82652,28 +82652,28 @@
         <v>211</v>
       </c>
       <c r="C1614">
-        <v>1.066392174477217</v>
+        <v>1.061866562597773</v>
       </c>
       <c r="D1614" t="s">
         <v>380</v>
       </c>
       <c r="E1614">
-        <v>1.076392174477217</v>
+        <v>1.068837209752259</v>
       </c>
       <c r="F1614">
         <v>1</v>
       </c>
       <c r="G1614">
-        <v>0.004793607825522783</v>
+        <v>0.004798133437402228</v>
       </c>
       <c r="H1614">
-        <v>0.004803607825522783</v>
+        <v>0.004791162790247741</v>
       </c>
       <c r="I1614">
-        <v>0.009999999999999787</v>
+        <v>0.006970647154486143</v>
       </c>
       <c r="J1614">
-        <v>0.6953760542995459</v>
+        <v>0.6970647154485922</v>
       </c>
       <c r="K1614">
         <v>2.68</v>
@@ -82682,16 +82682,16 @@
         <v>2.93</v>
       </c>
       <c r="M1614">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="N1614">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="O1614">
         <v>1</v>
       </c>
       <c r="P1614" t="s">
-        <v>192</v>
+        <v>358</v>
       </c>
     </row>
     <row r="1615" spans="1:16">
@@ -82702,28 +82702,28 @@
         <v>212</v>
       </c>
       <c r="C1615">
-        <v>1.099749151215716</v>
+        <v>1.095364733551475</v>
       </c>
       <c r="D1615" t="s">
         <v>371</v>
       </c>
       <c r="E1615">
-        <v>1.082778504061231</v>
+        <v>1.078377478754322</v>
       </c>
       <c r="F1615">
         <v>-1</v>
       </c>
       <c r="G1615">
-        <v>0.004780250848784283</v>
+        <v>0.004784635266448525</v>
       </c>
       <c r="H1615">
-        <v>0.004777221495938769</v>
+        <v>0.004781622521245679</v>
       </c>
       <c r="I1615">
-        <v>0.01697064715448549</v>
+        <v>0.01698725479715302</v>
       </c>
       <c r="J1615">
-        <v>0.6970647154485922</v>
+        <v>0.6987254797153503</v>
       </c>
       <c r="K1615">
         <v>2.64</v>
@@ -82741,7 +82741,7 @@
         <v>1</v>
       </c>
       <c r="P1615" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="1616" spans="1:16">
@@ -82752,28 +82752,28 @@
         <v>213</v>
       </c>
       <c r="C1616">
-        <v>1.099749151215716</v>
+        <v>1.095364733551475</v>
       </c>
       <c r="D1616" t="s">
         <v>204</v>
       </c>
       <c r="E1616">
-        <v>1.065807856906745</v>
+        <v>1.061390223957168</v>
       </c>
       <c r="F1616">
         <v>-1</v>
       </c>
       <c r="G1616">
-        <v>0.004780250848784283</v>
+        <v>0.004784635266448525</v>
       </c>
       <c r="H1616">
-        <v>0.004774192143093256</v>
+        <v>0.004778609776042831</v>
       </c>
       <c r="I1616">
-        <v>0.03394129430897186</v>
+        <v>0.03397450959430692</v>
       </c>
       <c r="J1616">
-        <v>0.6970647154485922</v>
+        <v>0.6987254797153503</v>
       </c>
       <c r="K1616">
         <v>2.64</v>
@@ -82791,7 +82791,7 @@
         <v>1</v>
       </c>
       <c r="P1616" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="1617" spans="1:16">
@@ -82802,28 +82802,28 @@
         <v>210</v>
       </c>
       <c r="C1617">
-        <v>1.10763173983366</v>
+        <v>1.103313752740089</v>
       </c>
       <c r="D1617" t="s">
         <v>379</v>
       </c>
       <c r="E1617">
-        <v>1.068837209752259</v>
+        <v>1.064402969160015</v>
       </c>
       <c r="F1617">
         <v>-1</v>
       </c>
       <c r="G1617">
-        <v>0.00473236826016634</v>
+        <v>0.004736686247259911</v>
       </c>
       <c r="H1617">
-        <v>0.004791162790247741</v>
+        <v>0.004795597030839985</v>
       </c>
       <c r="I1617">
-        <v>0.03879453008140099</v>
+        <v>0.03891078358007416</v>
       </c>
       <c r="J1617">
-        <v>0.6970647154485922</v>
+        <v>0.6987254797153503</v>
       </c>
       <c r="K1617">
         <v>2.6</v>
@@ -82841,7 +82841,7 @@
         <v>1</v>
       </c>
       <c r="P1617" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="1618" spans="1:16">
@@ -82852,28 +82852,28 @@
         <v>211</v>
       </c>
       <c r="C1618">
-        <v>1.061866562597773</v>
+        <v>1.057415714362861</v>
       </c>
       <c r="D1618" t="s">
         <v>380</v>
       </c>
       <c r="E1618">
-        <v>1.071866562597773</v>
+        <v>1.064402969160015</v>
       </c>
       <c r="F1618">
         <v>1</v>
       </c>
       <c r="G1618">
-        <v>0.004798133437402228</v>
+        <v>0.004802584285637139</v>
       </c>
       <c r="H1618">
-        <v>0.004808133437402227</v>
+        <v>0.004795597030839985</v>
       </c>
       <c r="I1618">
-        <v>0.009999999999999787</v>
+        <v>0.006987254797153675</v>
       </c>
       <c r="J1618">
-        <v>0.6970647154485922</v>
+        <v>0.6987254797153503</v>
       </c>
       <c r="K1618">
         <v>2.68</v>
@@ -82882,16 +82882,16 @@
         <v>2.93</v>
       </c>
       <c r="M1618">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="N1618">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="O1618">
         <v>1</v>
       </c>
       <c r="P1618" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="1619" spans="1:16">
@@ -82902,28 +82902,28 @@
         <v>212</v>
       </c>
       <c r="C1619">
-        <v>1.095364733551475</v>
+        <v>1.092196505092984</v>
       </c>
       <c r="D1619" t="s">
         <v>371</v>
       </c>
       <c r="E1619">
-        <v>1.078377478754322</v>
+        <v>1.075197249430458</v>
       </c>
       <c r="F1619">
         <v>-1</v>
       </c>
       <c r="G1619">
-        <v>0.004784635266448525</v>
+        <v>0.004787803494907016</v>
       </c>
       <c r="H1619">
-        <v>0.004781622521245679</v>
+        <v>0.004784802750569543</v>
       </c>
       <c r="I1619">
-        <v>0.01698725479715302</v>
+        <v>0.01699925566252625</v>
       </c>
       <c r="J1619">
-        <v>0.6987254797153503</v>
+        <v>0.6999255662526576</v>
       </c>
       <c r="K1619">
         <v>2.64</v>
@@ -82941,7 +82941,7 @@
         <v>1</v>
       </c>
       <c r="P1619" t="s">
-        <v>359</v>
+        <v>195</v>
       </c>
     </row>
     <row r="1620" spans="1:16">
@@ -82949,49 +82949,49 @@
         <v>1</v>
       </c>
       <c r="B1620" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="C1620">
-        <v>1.064402969160015</v>
+        <v>1.092196505092984</v>
       </c>
       <c r="D1620" t="s">
-        <v>375</v>
+        <v>204</v>
       </c>
       <c r="E1620">
-        <v>1.088377478754322</v>
+        <v>1.058197993767931</v>
       </c>
       <c r="F1620">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1620">
-        <v>0.004795597030839985</v>
+        <v>0.004787803494907016</v>
       </c>
       <c r="H1620">
-        <v>0.004791622521245678</v>
+        <v>0.004781802006232069</v>
       </c>
       <c r="I1620">
-        <v>0.02397450959430691</v>
+        <v>0.03399851132505316</v>
       </c>
       <c r="J1620">
-        <v>0.6987254797153503</v>
+        <v>0.6999255662526576</v>
       </c>
       <c r="K1620">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="L1620">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="M1620">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="N1620">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="O1620">
         <v>1</v>
       </c>
       <c r="P1620" t="s">
-        <v>359</v>
+        <v>195</v>
       </c>
     </row>
     <row r="1621" spans="1:16">
@@ -82999,49 +82999,49 @@
         <v>2</v>
       </c>
       <c r="B1621" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C1621">
-        <v>1.095364733551475</v>
+        <v>1.10019352774309</v>
       </c>
       <c r="D1621" t="s">
-        <v>204</v>
+        <v>379</v>
       </c>
       <c r="E1621">
-        <v>1.061390223957168</v>
+        <v>1.061198738105404</v>
       </c>
       <c r="F1621">
         <v>-1</v>
       </c>
       <c r="G1621">
-        <v>0.004784635266448525</v>
+        <v>0.00473980647225691</v>
       </c>
       <c r="H1621">
-        <v>0.004778609776042831</v>
+        <v>0.004798801261894596</v>
       </c>
       <c r="I1621">
-        <v>0.03397450959430692</v>
+        <v>0.03899478963768588</v>
       </c>
       <c r="J1621">
-        <v>0.6987254797153503</v>
+        <v>0.6999255662526576</v>
       </c>
       <c r="K1621">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="L1621">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="M1621">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="N1621">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="O1621">
         <v>1</v>
       </c>
       <c r="P1621" t="s">
-        <v>359</v>
+        <v>195</v>
       </c>
     </row>
     <row r="1622" spans="1:16">
@@ -83049,37 +83049,37 @@
         <v>3</v>
       </c>
       <c r="B1622" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C1622">
-        <v>1.103313752740089</v>
+        <v>1.054199482442878</v>
       </c>
       <c r="D1622" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E1622">
-        <v>1.064402969160015</v>
+        <v>1.061198738105404</v>
       </c>
       <c r="F1622">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1622">
-        <v>0.004736686247259911</v>
+        <v>0.004805800517557122</v>
       </c>
       <c r="H1622">
-        <v>0.004795597030839985</v>
+        <v>0.004798801261894596</v>
       </c>
       <c r="I1622">
-        <v>0.03891078358007416</v>
+        <v>0.006999255662526682</v>
       </c>
       <c r="J1622">
-        <v>0.6987254797153503</v>
+        <v>0.6999255662526576</v>
       </c>
       <c r="K1622">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="L1622">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="M1622">
         <v>2.67</v>
@@ -83091,7 +83091,7 @@
         <v>1</v>
       </c>
       <c r="P1622" t="s">
-        <v>359</v>
+        <v>195</v>
       </c>
     </row>
     <row r="1623" spans="1:16">
@@ -83102,28 +83102,28 @@
         <v>212</v>
       </c>
       <c r="C1623">
-        <v>1.092196505092984</v>
+        <v>1.087054780595984</v>
       </c>
       <c r="D1623" t="s">
         <v>371</v>
       </c>
       <c r="E1623">
-        <v>1.075197249430458</v>
+        <v>1.070036048704302</v>
       </c>
       <c r="F1623">
         <v>-1</v>
       </c>
       <c r="G1623">
-        <v>0.004787803494907016</v>
+        <v>0.004792945219404017</v>
       </c>
       <c r="H1623">
-        <v>0.004784802750569543</v>
+        <v>0.004789963951295699</v>
       </c>
       <c r="I1623">
-        <v>0.01699925566252625</v>
+        <v>0.01701873189168146</v>
       </c>
       <c r="J1623">
-        <v>0.6999255662526576</v>
+        <v>0.701873189168188</v>
       </c>
       <c r="K1623">
         <v>2.64</v>
@@ -83141,7 +83141,7 @@
         <v>1</v>
       </c>
       <c r="P1623" t="s">
-        <v>195</v>
+        <v>360</v>
       </c>
     </row>
     <row r="1624" spans="1:16">
@@ -83149,49 +83149,49 @@
         <v>1</v>
       </c>
       <c r="B1624" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="C1624">
-        <v>1.061198738105404</v>
+        <v>1.087054780595984</v>
       </c>
       <c r="D1624" t="s">
-        <v>375</v>
+        <v>204</v>
       </c>
       <c r="E1624">
-        <v>1.085197249430457</v>
+        <v>1.05301731681262</v>
       </c>
       <c r="F1624">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1624">
-        <v>0.004798801261894596</v>
+        <v>0.004792945219404017</v>
       </c>
       <c r="H1624">
-        <v>0.004794802750569542</v>
+        <v>0.00478698268318738</v>
       </c>
       <c r="I1624">
-        <v>0.02399851132505293</v>
+        <v>0.03403746378336381</v>
       </c>
       <c r="J1624">
-        <v>0.6999255662526576</v>
+        <v>0.701873189168188</v>
       </c>
       <c r="K1624">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="L1624">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="M1624">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="N1624">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="O1624">
         <v>1</v>
       </c>
       <c r="P1624" t="s">
-        <v>195</v>
+        <v>360</v>
       </c>
     </row>
     <row r="1625" spans="1:16">
@@ -83199,49 +83199,49 @@
         <v>2</v>
       </c>
       <c r="B1625" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C1625">
-        <v>1.092196505092984</v>
+        <v>1.095129708162711</v>
       </c>
       <c r="D1625" t="s">
-        <v>204</v>
+        <v>379</v>
       </c>
       <c r="E1625">
-        <v>1.058197993767931</v>
+        <v>1.055998584920938</v>
       </c>
       <c r="F1625">
         <v>-1</v>
       </c>
       <c r="G1625">
-        <v>0.004787803494907016</v>
+        <v>0.00474487029183729</v>
       </c>
       <c r="H1625">
-        <v>0.004781802006232069</v>
+        <v>0.004804001415079063</v>
       </c>
       <c r="I1625">
-        <v>0.03399851132505316</v>
+        <v>0.03913112324177281</v>
       </c>
       <c r="J1625">
-        <v>0.6999255662526576</v>
+        <v>0.701873189168188</v>
       </c>
       <c r="K1625">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="L1625">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="M1625">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="N1625">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="O1625">
         <v>1</v>
       </c>
       <c r="P1625" t="s">
-        <v>195</v>
+        <v>360</v>
       </c>
     </row>
     <row r="1626" spans="1:16">
@@ -83249,37 +83249,37 @@
         <v>3</v>
       </c>
       <c r="B1626" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C1626">
-        <v>1.10019352774309</v>
+        <v>1.048979853029256</v>
       </c>
       <c r="D1626" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E1626">
-        <v>1.061198738105404</v>
+        <v>1.055998584920938</v>
       </c>
       <c r="F1626">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1626">
-        <v>0.00473980647225691</v>
+        <v>0.004811020146970744</v>
       </c>
       <c r="H1626">
-        <v>0.004798801261894596</v>
+        <v>0.004804001415079063</v>
       </c>
       <c r="I1626">
-        <v>0.03899478963768588</v>
+        <v>0.007018731891682117</v>
       </c>
       <c r="J1626">
-        <v>0.6999255662526576</v>
+        <v>0.701873189168188</v>
       </c>
       <c r="K1626">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="L1626">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="M1626">
         <v>2.67</v>
@@ -83291,7 +83291,7 @@
         <v>1</v>
       </c>
       <c r="P1626" t="s">
-        <v>195</v>
+        <v>360</v>
       </c>
     </row>
     <row r="1627" spans="1:16">
@@ -83302,28 +83302,28 @@
         <v>212</v>
       </c>
       <c r="C1627">
-        <v>1.087054780595984</v>
+        <v>1.081706268086576</v>
       </c>
       <c r="D1627" t="s">
         <v>371</v>
       </c>
       <c r="E1627">
-        <v>1.070036048704302</v>
+        <v>1.064667276677814</v>
       </c>
       <c r="F1627">
         <v>-1</v>
       </c>
       <c r="G1627">
-        <v>0.004792945219404017</v>
+        <v>0.004798293731913423</v>
       </c>
       <c r="H1627">
-        <v>0.004789963951295699</v>
+        <v>0.004795332723322186</v>
       </c>
       <c r="I1627">
-        <v>0.01701873189168146</v>
+        <v>0.01703899140876253</v>
       </c>
       <c r="J1627">
-        <v>0.701873189168188</v>
+        <v>0.7038991408762968</v>
       </c>
       <c r="K1627">
         <v>2.64</v>
@@ -83341,7 +83341,7 @@
         <v>1</v>
       </c>
       <c r="P1627" t="s">
-        <v>360</v>
+        <v>197</v>
       </c>
     </row>
     <row r="1628" spans="1:16">
@@ -83352,28 +83352,28 @@
         <v>213</v>
       </c>
       <c r="C1628">
-        <v>1.087054780595984</v>
+        <v>1.081706268086576</v>
       </c>
       <c r="D1628" t="s">
         <v>204</v>
       </c>
       <c r="E1628">
-        <v>1.05301731681262</v>
+        <v>1.04762828526905</v>
       </c>
       <c r="F1628">
         <v>-1</v>
       </c>
       <c r="G1628">
-        <v>0.004792945219404017</v>
+        <v>0.004798293731913423</v>
       </c>
       <c r="H1628">
-        <v>0.00478698268318738</v>
+        <v>0.004792371714730949</v>
       </c>
       <c r="I1628">
-        <v>0.03403746378336381</v>
+        <v>0.03407798281752594</v>
       </c>
       <c r="J1628">
-        <v>0.701873189168188</v>
+        <v>0.7038991408762968</v>
       </c>
       <c r="K1628">
         <v>2.64</v>
@@ -83391,7 +83391,7 @@
         <v>1</v>
       </c>
       <c r="P1628" t="s">
-        <v>360</v>
+        <v>197</v>
       </c>
     </row>
     <row r="1629" spans="1:16">
@@ -83402,28 +83402,28 @@
         <v>210</v>
       </c>
       <c r="C1629">
-        <v>1.095129708162711</v>
+        <v>1.089862233721628</v>
       </c>
       <c r="D1629" t="s">
         <v>379</v>
       </c>
       <c r="E1629">
-        <v>1.055998584920938</v>
+        <v>1.050589293860288</v>
       </c>
       <c r="F1629">
         <v>-1</v>
       </c>
       <c r="G1629">
-        <v>0.00474487029183729</v>
+        <v>0.004750137766278372</v>
       </c>
       <c r="H1629">
-        <v>0.004804001415079063</v>
+        <v>0.004809410706139713</v>
       </c>
       <c r="I1629">
-        <v>0.03913112324177281</v>
+        <v>0.03927293986134028</v>
       </c>
       <c r="J1629">
-        <v>0.701873189168188</v>
+        <v>0.7038991408762968</v>
       </c>
       <c r="K1629">
         <v>2.6</v>
@@ -83441,7 +83441,7 @@
         <v>1</v>
       </c>
       <c r="P1629" t="s">
-        <v>360</v>
+        <v>197</v>
       </c>
     </row>
     <row r="1630" spans="1:16">
@@ -83452,28 +83452,28 @@
         <v>211</v>
       </c>
       <c r="C1630">
-        <v>1.048979853029256</v>
+        <v>1.043550302451525</v>
       </c>
       <c r="D1630" t="s">
         <v>380</v>
       </c>
       <c r="E1630">
-        <v>1.058979853029256</v>
+        <v>1.050589293860288</v>
       </c>
       <c r="F1630">
         <v>1</v>
       </c>
       <c r="G1630">
-        <v>0.004811020146970744</v>
+        <v>0.004816449697548475</v>
       </c>
       <c r="H1630">
-        <v>0.004821020146970744</v>
+        <v>0.004809410706139713</v>
       </c>
       <c r="I1630">
-        <v>0.009999999999999787</v>
+        <v>0.007038991408763184</v>
       </c>
       <c r="J1630">
-        <v>0.701873189168188</v>
+        <v>0.7038991408762968</v>
       </c>
       <c r="K1630">
         <v>2.68</v>
@@ -83482,16 +83482,16 @@
         <v>2.93</v>
       </c>
       <c r="M1630">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="N1630">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="O1630">
         <v>1</v>
       </c>
       <c r="P1630" t="s">
-        <v>360</v>
+        <v>197</v>
       </c>
     </row>
     <row r="1631" spans="1:16">
@@ -83502,28 +83502,28 @@
         <v>212</v>
       </c>
       <c r="C1631">
-        <v>1.081706268086576</v>
+        <v>1.07524398177382</v>
       </c>
       <c r="D1631" t="s">
         <v>371</v>
       </c>
       <c r="E1631">
-        <v>1.064667276677814</v>
+        <v>1.058180512007812</v>
       </c>
       <c r="F1631">
         <v>-1</v>
       </c>
       <c r="G1631">
-        <v>0.004798293731913423</v>
+        <v>0.00480475601822618</v>
       </c>
       <c r="H1631">
-        <v>0.004795332723322186</v>
+        <v>0.004801819487992188</v>
       </c>
       <c r="I1631">
-        <v>0.01703899140876253</v>
+        <v>0.0170634697660077</v>
       </c>
       <c r="J1631">
-        <v>0.7038991408762968</v>
+        <v>0.7063469766008257</v>
       </c>
       <c r="K1631">
         <v>2.64</v>
@@ -83541,7 +83541,7 @@
         <v>1</v>
       </c>
       <c r="P1631" t="s">
-        <v>197</v>
+        <v>362</v>
       </c>
     </row>
     <row r="1632" spans="1:16">
@@ -83552,28 +83552,28 @@
         <v>213</v>
       </c>
       <c r="C1632">
-        <v>1.081706268086576</v>
+        <v>1.07524398177382</v>
       </c>
       <c r="D1632" t="s">
         <v>204</v>
       </c>
       <c r="E1632">
-        <v>1.04762828526905</v>
+        <v>1.041117042241803</v>
       </c>
       <c r="F1632">
         <v>-1</v>
       </c>
       <c r="G1632">
-        <v>0.004798293731913423</v>
+        <v>0.00480475601822618</v>
       </c>
       <c r="H1632">
-        <v>0.004792371714730949</v>
+        <v>0.004798882957758197</v>
       </c>
       <c r="I1632">
-        <v>0.03407798281752594</v>
+        <v>0.03412693953201651</v>
       </c>
       <c r="J1632">
-        <v>0.7038991408762968</v>
+        <v>0.7063469766008257</v>
       </c>
       <c r="K1632">
         <v>2.64</v>
@@ -83591,7 +83591,7 @@
         <v>1</v>
       </c>
       <c r="P1632" t="s">
-        <v>197</v>
+        <v>362</v>
       </c>
     </row>
     <row r="1633" spans="1:16">
@@ -83602,28 +83602,28 @@
         <v>210</v>
       </c>
       <c r="C1633">
-        <v>1.089862233721628</v>
+        <v>1.083497860837853</v>
       </c>
       <c r="D1633" t="s">
         <v>379</v>
       </c>
       <c r="E1633">
-        <v>1.050589293860288</v>
+        <v>1.044053572475796</v>
       </c>
       <c r="F1633">
         <v>-1</v>
       </c>
       <c r="G1633">
-        <v>0.004750137766278372</v>
+        <v>0.004756502139162147</v>
       </c>
       <c r="H1633">
-        <v>0.004809410706139713</v>
+        <v>0.004815946427524205</v>
       </c>
       <c r="I1633">
-        <v>0.03927293986134028</v>
+        <v>0.0394442883620576</v>
       </c>
       <c r="J1633">
-        <v>0.7038991408762968</v>
+        <v>0.7063469766008257</v>
       </c>
       <c r="K1633">
         <v>2.6</v>
@@ -83641,7 +83641,7 @@
         <v>1</v>
       </c>
       <c r="P1633" t="s">
-        <v>197</v>
+        <v>362</v>
       </c>
     </row>
     <row r="1634" spans="1:16">
@@ -83652,28 +83652,28 @@
         <v>211</v>
       </c>
       <c r="C1634">
-        <v>1.043550302451525</v>
+        <v>1.036990102709787</v>
       </c>
       <c r="D1634" t="s">
         <v>380</v>
       </c>
       <c r="E1634">
-        <v>1.053550302451524</v>
+        <v>1.044053572475796</v>
       </c>
       <c r="F1634">
         <v>1</v>
       </c>
       <c r="G1634">
-        <v>0.004816449697548475</v>
+        <v>0.004823009897290213</v>
       </c>
       <c r="H1634">
-        <v>0.004826449697548476</v>
+        <v>0.004815946427524205</v>
       </c>
       <c r="I1634">
-        <v>0.009999999999999787</v>
+        <v>0.007063469766008357</v>
       </c>
       <c r="J1634">
-        <v>0.7038991408762968</v>
+        <v>0.7063469766008257</v>
       </c>
       <c r="K1634">
         <v>2.68</v>
@@ -83682,16 +83682,16 @@
         <v>2.93</v>
       </c>
       <c r="M1634">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="N1634">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="O1634">
         <v>1</v>
       </c>
       <c r="P1634" t="s">
-        <v>197</v>
+        <v>362</v>
       </c>
     </row>
     <row r="1635" spans="1:16">
@@ -83702,28 +83702,28 @@
         <v>212</v>
       </c>
       <c r="C1635">
-        <v>1.07524398177382</v>
+        <v>1.069820290373149</v>
       </c>
       <c r="D1635" t="s">
         <v>371</v>
       </c>
       <c r="E1635">
-        <v>1.058180512007812</v>
+        <v>1.052736276321532</v>
       </c>
       <c r="F1635">
         <v>-1</v>
       </c>
       <c r="G1635">
-        <v>0.00480475601822618</v>
+        <v>0.004810179709626852</v>
       </c>
       <c r="H1635">
-        <v>0.004801819487992188</v>
+        <v>0.004807263723678468</v>
       </c>
       <c r="I1635">
-        <v>0.0170634697660077</v>
+        <v>0.01708401405161664</v>
       </c>
       <c r="J1635">
-        <v>0.7063469766008257</v>
+        <v>0.7084014051616859</v>
       </c>
       <c r="K1635">
         <v>2.64</v>
@@ -83741,7 +83741,7 @@
         <v>1</v>
       </c>
       <c r="P1635" t="s">
-        <v>362</v>
+        <v>202</v>
       </c>
     </row>
     <row r="1636" spans="1:16">
@@ -83749,49 +83749,49 @@
         <v>1</v>
       </c>
       <c r="B1636" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="C1636">
-        <v>1.044053572475796</v>
+        <v>1.069820290373149</v>
       </c>
       <c r="D1636" t="s">
-        <v>375</v>
+        <v>204</v>
       </c>
       <c r="E1636">
-        <v>1.068180512007812</v>
+        <v>1.035652262269915</v>
       </c>
       <c r="F1636">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1636">
-        <v>0.004815946427524205</v>
+        <v>0.004810179709626852</v>
       </c>
       <c r="H1636">
-        <v>0.004811819487992188</v>
+        <v>0.004804347737730085</v>
       </c>
       <c r="I1636">
-        <v>0.0241269395320165</v>
+        <v>0.03416802810323372</v>
       </c>
       <c r="J1636">
-        <v>0.7063469766008257</v>
+        <v>0.7084014051616859</v>
       </c>
       <c r="K1636">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="L1636">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="M1636">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="N1636">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="O1636">
         <v>1</v>
       </c>
       <c r="P1636" t="s">
-        <v>362</v>
+        <v>202</v>
       </c>
     </row>
     <row r="1637" spans="1:16">
@@ -83799,49 +83799,49 @@
         <v>2</v>
       </c>
       <c r="B1637" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C1637">
-        <v>1.07524398177382</v>
+        <v>1.078156346579616</v>
       </c>
       <c r="D1637" t="s">
-        <v>204</v>
+        <v>379</v>
       </c>
       <c r="E1637">
-        <v>1.041117042241803</v>
+        <v>1.038568248218299</v>
       </c>
       <c r="F1637">
         <v>-1</v>
       </c>
       <c r="G1637">
-        <v>0.00480475601822618</v>
+        <v>0.004761843653420384</v>
       </c>
       <c r="H1637">
-        <v>0.004798882957758197</v>
+        <v>0.004821431751781701</v>
       </c>
       <c r="I1637">
-        <v>0.03412693953201651</v>
+        <v>0.03958809836131771</v>
       </c>
       <c r="J1637">
-        <v>0.7063469766008257</v>
+        <v>0.7084014051616859</v>
       </c>
       <c r="K1637">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="L1637">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="M1637">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="N1637">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="O1637">
         <v>1</v>
       </c>
       <c r="P1637" t="s">
-        <v>362</v>
+        <v>202</v>
       </c>
     </row>
     <row r="1638" spans="1:16">
@@ -83849,37 +83849,37 @@
         <v>3</v>
       </c>
       <c r="B1638" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C1638">
-        <v>1.083497860837853</v>
+        <v>1.031484234166682</v>
       </c>
       <c r="D1638" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E1638">
-        <v>1.044053572475796</v>
+        <v>1.038568248218299</v>
       </c>
       <c r="F1638">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1638">
-        <v>0.004756502139162147</v>
+        <v>0.004828515765833319</v>
       </c>
       <c r="H1638">
-        <v>0.004815946427524205</v>
+        <v>0.004821431751781701</v>
       </c>
       <c r="I1638">
-        <v>0.0394442883620576</v>
+        <v>0.007084014051617071</v>
       </c>
       <c r="J1638">
-        <v>0.7063469766008257</v>
+        <v>0.7084014051616859</v>
       </c>
       <c r="K1638">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="L1638">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="M1638">
         <v>2.67</v>
@@ -83891,7 +83891,7 @@
         <v>1</v>
       </c>
       <c r="P1638" t="s">
-        <v>362</v>
+        <v>202</v>
       </c>
     </row>
     <row r="1639" spans="1:16">
@@ -83902,28 +83902,28 @@
         <v>212</v>
       </c>
       <c r="C1639">
-        <v>1.069820290373149</v>
+        <v>1.063184310995725</v>
       </c>
       <c r="D1639" t="s">
         <v>371</v>
       </c>
       <c r="E1639">
-        <v>1.052736276321532</v>
+        <v>1.046075160658587</v>
       </c>
       <c r="F1639">
         <v>-1</v>
       </c>
       <c r="G1639">
-        <v>0.004810179709626852</v>
+        <v>0.004816815689004275</v>
       </c>
       <c r="H1639">
-        <v>0.004807263723678468</v>
+        <v>0.004813924839341412</v>
       </c>
       <c r="I1639">
-        <v>0.01708401405161664</v>
+        <v>0.01710915033713722</v>
       </c>
       <c r="J1639">
-        <v>0.7084014051616859</v>
+        <v>0.7109150337137407</v>
       </c>
       <c r="K1639">
         <v>2.64</v>
@@ -83941,7 +83941,7 @@
         <v>1</v>
       </c>
       <c r="P1639" t="s">
-        <v>202</v>
+        <v>363</v>
       </c>
     </row>
     <row r="1640" spans="1:16">
@@ -83949,49 +83949,49 @@
         <v>1</v>
       </c>
       <c r="B1640" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="C1640">
-        <v>1.038568248218299</v>
+        <v>1.063184310995725</v>
       </c>
       <c r="D1640" t="s">
-        <v>375</v>
+        <v>204</v>
       </c>
       <c r="E1640">
-        <v>1.062736276321532</v>
+        <v>1.02896601032145</v>
       </c>
       <c r="F1640">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1640">
-        <v>0.004821431751781701</v>
+        <v>0.004816815689004275</v>
       </c>
       <c r="H1640">
-        <v>0.004817263723678468</v>
+        <v>0.00481103398967855</v>
       </c>
       <c r="I1640">
-        <v>0.02416802810323349</v>
+        <v>0.03421830067427489</v>
       </c>
       <c r="J1640">
-        <v>0.7084014051616859</v>
+        <v>0.7109150337137407</v>
       </c>
       <c r="K1640">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="L1640">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="M1640">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="N1640">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="O1640">
         <v>1</v>
       </c>
       <c r="P1640" t="s">
-        <v>202</v>
+        <v>363</v>
       </c>
     </row>
     <row r="1641" spans="1:16">
@@ -83999,49 +83999,49 @@
         <v>2</v>
       </c>
       <c r="B1641" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C1641">
-        <v>1.069820290373149</v>
+        <v>1.071620912344274</v>
       </c>
       <c r="D1641" t="s">
-        <v>204</v>
+        <v>379</v>
       </c>
       <c r="E1641">
-        <v>1.035652262269915</v>
+        <v>1.031856859984313</v>
       </c>
       <c r="F1641">
         <v>-1</v>
       </c>
       <c r="G1641">
-        <v>0.004810179709626852</v>
+        <v>0.004768379087655726</v>
       </c>
       <c r="H1641">
-        <v>0.004804347737730085</v>
+        <v>0.004828143140015688</v>
       </c>
       <c r="I1641">
-        <v>0.03416802810323372</v>
+        <v>0.03976405235996139</v>
       </c>
       <c r="J1641">
-        <v>0.7084014051616859</v>
+        <v>0.7109150337137407</v>
       </c>
       <c r="K1641">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="L1641">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="M1641">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="N1641">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="O1641">
         <v>1</v>
       </c>
       <c r="P1641" t="s">
-        <v>202</v>
+        <v>363</v>
       </c>
     </row>
     <row r="1642" spans="1:16">
@@ -84049,37 +84049,37 @@
         <v>3</v>
       </c>
       <c r="B1642" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C1642">
-        <v>1.078156346579616</v>
+        <v>1.024747709647175</v>
       </c>
       <c r="D1642" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E1642">
-        <v>1.038568248218299</v>
+        <v>1.031856859984313</v>
       </c>
       <c r="F1642">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1642">
-        <v>0.004761843653420384</v>
+        <v>0.004835252290352825</v>
       </c>
       <c r="H1642">
-        <v>0.004821431751781701</v>
+        <v>0.004828143140015688</v>
       </c>
       <c r="I1642">
-        <v>0.03958809836131771</v>
+        <v>0.00710915033713766</v>
       </c>
       <c r="J1642">
-        <v>0.7084014051616859</v>
+        <v>0.7109150337137407</v>
       </c>
       <c r="K1642">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="L1642">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="M1642">
         <v>2.67</v>
@@ -84091,7 +84091,7 @@
         <v>1</v>
       </c>
       <c r="P1642" t="s">
-        <v>202</v>
+        <v>363</v>
       </c>
     </row>
     <row r="1643" spans="1:16">
@@ -84099,49 +84099,49 @@
         <v>0</v>
       </c>
       <c r="B1643" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="C1643">
-        <v>1.031856859984313</v>
+        <v>1.055821077716637</v>
       </c>
       <c r="D1643" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="E1643">
-        <v>1.064511762007137</v>
+        <v>1.038684036344352</v>
       </c>
       <c r="F1643">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1643">
-        <v>0.004828143140015688</v>
+        <v>0.004824178922283364</v>
       </c>
       <c r="H1643">
-        <v>0.004775488237992863</v>
+        <v>0.004821315963655649</v>
       </c>
       <c r="I1643">
-        <v>0.03265490202282417</v>
+        <v>0.01713704137228511</v>
       </c>
       <c r="J1643">
-        <v>0.7109150337137407</v>
+        <v>0.7137041372285466</v>
       </c>
       <c r="K1643">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="L1643">
+        <v>2.94</v>
+      </c>
+      <c r="M1643">
+        <v>2.65</v>
+      </c>
+      <c r="N1643">
         <v>2.93</v>
       </c>
-      <c r="M1643">
-        <v>2.61</v>
-      </c>
-      <c r="N1643">
-        <v>2.92</v>
-      </c>
       <c r="O1643">
         <v>1</v>
       </c>
       <c r="P1643" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="1644" spans="1:16">
@@ -84149,49 +84149,49 @@
         <v>1</v>
       </c>
       <c r="B1644" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="C1644">
-        <v>1.031856859984313</v>
+        <v>1.055821077716637</v>
       </c>
       <c r="D1644" t="s">
-        <v>375</v>
+        <v>204</v>
       </c>
       <c r="E1644">
-        <v>1.056075160658587</v>
+        <v>1.021546994972066</v>
       </c>
       <c r="F1644">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1644">
-        <v>0.004828143140015688</v>
+        <v>0.004824178922283364</v>
       </c>
       <c r="H1644">
-        <v>0.004823924839341413</v>
+        <v>0.004818453005027934</v>
       </c>
       <c r="I1644">
-        <v>0.02421830067427444</v>
+        <v>0.03427408274457111</v>
       </c>
       <c r="J1644">
-        <v>0.7109150337137407</v>
+        <v>0.7137041372285466</v>
       </c>
       <c r="K1644">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="L1644">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="M1644">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="N1644">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="O1644">
         <v>1</v>
       </c>
       <c r="P1644" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="1645" spans="1:16">
@@ -84202,28 +84202,28 @@
         <v>210</v>
       </c>
       <c r="C1645">
-        <v>1.071620912344274</v>
+        <v>1.064369243205779</v>
       </c>
       <c r="D1645" t="s">
         <v>379</v>
       </c>
       <c r="E1645">
-        <v>1.031856859984313</v>
+        <v>1.024409953599781</v>
       </c>
       <c r="F1645">
         <v>-1</v>
       </c>
       <c r="G1645">
-        <v>0.004768379087655726</v>
+        <v>0.004775630756794221</v>
       </c>
       <c r="H1645">
-        <v>0.004828143140015688</v>
+        <v>0.004835590046400219</v>
       </c>
       <c r="I1645">
-        <v>0.03976405235996139</v>
+        <v>0.03995928960599793</v>
       </c>
       <c r="J1645">
-        <v>0.7109150337137407</v>
+        <v>0.7137041372285466</v>
       </c>
       <c r="K1645">
         <v>2.6</v>
@@ -84241,51 +84241,51 @@
         <v>1</v>
       </c>
       <c r="P1645" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="1646" spans="1:16">
       <c r="A1646" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1646" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="C1646">
+        <v>1.017272912227495</v>
+      </c>
+      <c r="D1646" t="s">
+        <v>380</v>
+      </c>
+      <c r="E1646">
         <v>1.024409953599781</v>
       </c>
-      <c r="D1646" t="s">
-        <v>367</v>
-      </c>
-      <c r="E1646">
-        <v>1.057232201833493</v>
-      </c>
       <c r="F1646">
         <v>1</v>
       </c>
       <c r="G1646">
+        <v>0.004842727087772506</v>
+      </c>
+      <c r="H1646">
         <v>0.004835590046400219</v>
       </c>
-      <c r="H1646">
-        <v>0.004782767798166507</v>
-      </c>
       <c r="I1646">
-        <v>0.0328222482337126</v>
+        <v>0.007137041372285546</v>
       </c>
       <c r="J1646">
         <v>0.7137041372285466</v>
       </c>
       <c r="K1646">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="L1646">
         <v>2.93</v>
       </c>
       <c r="M1646">
-        <v>2.61</v>
+        <v>2.67</v>
       </c>
       <c r="N1646">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="O1646">
         <v>1</v>
@@ -84296,107 +84296,107 @@
     </row>
     <row r="1647" spans="1:16">
       <c r="A1647" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1647" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="C1647">
-        <v>1.024409953599781</v>
+        <v>1.04729160102982</v>
       </c>
       <c r="D1647" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="E1647">
-        <v>1.048684036344351</v>
+        <v>1.030122251033721</v>
       </c>
       <c r="F1647">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1647">
-        <v>0.004835590046400219</v>
+        <v>0.00483270839897018</v>
       </c>
       <c r="H1647">
-        <v>0.004831315963655648</v>
+        <v>0.004829877748966279</v>
       </c>
       <c r="I1647">
-        <v>0.02427408274457088</v>
+        <v>0.01716934999609898</v>
       </c>
       <c r="J1647">
-        <v>0.7137041372285466</v>
+        <v>0.7169349996099167</v>
       </c>
       <c r="K1647">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="L1647">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="M1647">
         <v>2.65</v>
       </c>
       <c r="N1647">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="O1647">
         <v>1</v>
       </c>
       <c r="P1647" t="s">
-        <v>364</v>
+        <v>198</v>
       </c>
     </row>
     <row r="1648" spans="1:16">
       <c r="A1648" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1648" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C1648">
-        <v>1.064369243205779</v>
+        <v>1.04729160102982</v>
       </c>
       <c r="D1648" t="s">
-        <v>379</v>
+        <v>204</v>
       </c>
       <c r="E1648">
-        <v>1.024409953599781</v>
+        <v>1.012952901037621</v>
       </c>
       <c r="F1648">
         <v>-1</v>
       </c>
       <c r="G1648">
-        <v>0.004775630756794221</v>
+        <v>0.00483270839897018</v>
       </c>
       <c r="H1648">
-        <v>0.004835590046400219</v>
+        <v>0.004827047098962378</v>
       </c>
       <c r="I1648">
-        <v>0.03995928960599793</v>
+        <v>0.03433869999219841</v>
       </c>
       <c r="J1648">
-        <v>0.7137041372285466</v>
+        <v>0.7169349996099167</v>
       </c>
       <c r="K1648">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="L1648">
+        <v>2.94</v>
+      </c>
+      <c r="M1648">
+        <v>2.66</v>
+      </c>
+      <c r="N1648">
         <v>2.92</v>
       </c>
-      <c r="M1648">
-        <v>2.67</v>
-      </c>
-      <c r="N1648">
-        <v>2.93</v>
-      </c>
       <c r="O1648">
         <v>1</v>
       </c>
       <c r="P1648" t="s">
-        <v>364</v>
+        <v>198</v>
       </c>
     </row>
     <row r="1649" spans="1:16">
       <c r="A1649" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1649" t="s">
         <v>210</v>
@@ -84446,7 +84446,7 @@
     </row>
     <row r="1650" spans="1:16">
       <c r="A1650" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1650" t="s">
         <v>211</v>
@@ -84458,7 +84458,7 @@
         <v>380</v>
       </c>
       <c r="E1650">
-        <v>1.018614201045423</v>
+        <v>1.015783551041523</v>
       </c>
       <c r="F1650">
         <v>1</v>
@@ -84467,10 +84467,10 @@
         <v>0.004851385798954577</v>
       </c>
       <c r="H1650">
-        <v>0.004861385798954576</v>
+        <v>0.004844216448958478</v>
       </c>
       <c r="I1650">
-        <v>0.009999999999999787</v>
+        <v>0.007169349996099417</v>
       </c>
       <c r="J1650">
         <v>0.7169349996099167</v>
@@ -84482,10 +84482,10 @@
         <v>2.93</v>
       </c>
       <c r="M1650">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="N1650">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="O1650">
         <v>1</v>
@@ -84499,43 +84499,43 @@
         <v>0</v>
       </c>
       <c r="B1651" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="C1651">
+        <v>1.047123632216404</v>
+      </c>
+      <c r="D1651" t="s">
+        <v>379</v>
+      </c>
+      <c r="E1651">
         <v>1.006700037699154</v>
       </c>
-      <c r="D1651" t="s">
-        <v>375</v>
-      </c>
-      <c r="E1651">
-        <v>1.031106778989797</v>
-      </c>
       <c r="F1651">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1651">
+        <v>0.004792876367783595</v>
+      </c>
+      <c r="H1651">
         <v>0.004853299962300847</v>
       </c>
-      <c r="H1651">
-        <v>0.004848893221010203</v>
-      </c>
       <c r="I1651">
-        <v>0.0244067412906428</v>
+        <v>0.04042359451725019</v>
       </c>
       <c r="J1651">
         <v>0.7203370645321522</v>
       </c>
       <c r="K1651">
+        <v>2.6</v>
+      </c>
+      <c r="L1651">
+        <v>2.92</v>
+      </c>
+      <c r="M1651">
         <v>2.67</v>
       </c>
-      <c r="L1651">
+      <c r="N1651">
         <v>2.93</v>
-      </c>
-      <c r="M1651">
-        <v>2.65</v>
-      </c>
-      <c r="N1651">
-        <v>2.94</v>
       </c>
       <c r="O1651">
         <v>1</v>
@@ -84549,37 +84549,37 @@
         <v>1</v>
       </c>
       <c r="B1652" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C1652">
-        <v>1.047123632216404</v>
+        <v>0.9994966670538321</v>
       </c>
       <c r="D1652" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E1652">
         <v>1.006700037699154</v>
       </c>
       <c r="F1652">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1652">
-        <v>0.004792876367783595</v>
+        <v>0.004860503332946168</v>
       </c>
       <c r="H1652">
         <v>0.004853299962300847</v>
       </c>
       <c r="I1652">
-        <v>0.04042359451725019</v>
+        <v>0.007203370645321838</v>
       </c>
       <c r="J1652">
         <v>0.7203370645321522</v>
       </c>
       <c r="K1652">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="L1652">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="M1652">
         <v>2.67</v>
@@ -84899,43 +84899,43 @@
         <v>0</v>
       </c>
       <c r="B1659" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="C1659">
+        <v>1.021893262496982</v>
+      </c>
+      <c r="D1659" t="s">
+        <v>379</v>
+      </c>
+      <c r="E1659">
         <v>0.9807903887949778</v>
       </c>
-      <c r="D1659" t="s">
-        <v>375</v>
-      </c>
-      <c r="E1659">
-        <v>1.005391209852693</v>
-      </c>
       <c r="F1659">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1659">
+        <v>0.004818106737503018</v>
+      </c>
+      <c r="H1659">
         <v>0.004879209611205022</v>
       </c>
-      <c r="H1659">
-        <v>0.004874608790147307</v>
-      </c>
       <c r="I1659">
-        <v>0.02460082105771533</v>
+        <v>0.04110287370200405</v>
       </c>
       <c r="J1659">
         <v>0.7300410528857761</v>
       </c>
       <c r="K1659">
+        <v>2.6</v>
+      </c>
+      <c r="L1659">
+        <v>2.92</v>
+      </c>
+      <c r="M1659">
         <v>2.67</v>
       </c>
-      <c r="L1659">
+      <c r="N1659">
         <v>2.93</v>
-      </c>
-      <c r="M1659">
-        <v>2.65</v>
-      </c>
-      <c r="N1659">
-        <v>2.94</v>
       </c>
       <c r="O1659">
         <v>1</v>
@@ -84949,37 +84949,37 @@
         <v>1</v>
       </c>
       <c r="B1660" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C1660">
-        <v>1.021893262496982</v>
+        <v>0.9734899782661199</v>
       </c>
       <c r="D1660" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E1660">
         <v>0.9807903887949778</v>
       </c>
       <c r="F1660">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1660">
-        <v>0.004818106737503018</v>
+        <v>0.00488651002173388</v>
       </c>
       <c r="H1660">
         <v>0.004879209611205022</v>
       </c>
       <c r="I1660">
-        <v>0.04110287370200405</v>
+        <v>0.007300410528857881</v>
       </c>
       <c r="J1660">
         <v>0.7300410528857761</v>
       </c>
       <c r="K1660">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="L1660">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="M1660">
         <v>2.67</v>
@@ -85058,7 +85058,7 @@
         <v>380</v>
       </c>
       <c r="E1662">
-        <v>0.979871849855793</v>
+        <v>0.9771857608637942</v>
       </c>
       <c r="F1662">
         <v>1</v>
@@ -85067,10 +85067,10 @@
         <v>0.004890128150144207</v>
       </c>
       <c r="H1662">
-        <v>0.004900128150144207</v>
+        <v>0.004882814239136206</v>
       </c>
       <c r="I1662">
-        <v>0.009999999999999787</v>
+        <v>0.00731391100800094</v>
       </c>
       <c r="J1662">
         <v>0.7313911008000772</v>
@@ -85082,10 +85082,10 @@
         <v>2.93</v>
       </c>
       <c r="M1662">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="N1662">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="O1662">
         <v>1</v>
@@ -85158,7 +85158,7 @@
         <v>380</v>
       </c>
       <c r="E1664">
-        <v>0.976141011152162</v>
+        <v>0.9734688432001022</v>
       </c>
       <c r="F1664">
         <v>1</v>
@@ -85167,10 +85167,10 @@
         <v>0.004893858988847838</v>
       </c>
       <c r="H1664">
-        <v>0.004903858988847838</v>
+        <v>0.004886531156799898</v>
       </c>
       <c r="I1664">
-        <v>0.009999999999999787</v>
+        <v>0.007327832047939964</v>
       </c>
       <c r="J1664">
         <v>0.7327832047939693</v>
@@ -85182,10 +85182,10 @@
         <v>2.93</v>
       </c>
       <c r="M1664">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="N1664">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="O1664">
         <v>1</v>
@@ -85258,7 +85258,7 @@
         <v>380</v>
       </c>
       <c r="E1666">
-        <v>0.9729392428960222</v>
+        <v>0.9702790218404402</v>
       </c>
       <c r="F1666">
         <v>1</v>
@@ -85267,10 +85267,10 @@
         <v>0.004897060757103978</v>
       </c>
       <c r="H1666">
-        <v>0.004907060757103977</v>
+        <v>0.00488972097815956</v>
       </c>
       <c r="I1666">
-        <v>0.009999999999999787</v>
+        <v>0.007339778944417841</v>
       </c>
       <c r="J1666">
         <v>0.7339778944417827</v>
@@ -85282,10 +85282,10 @@
         <v>2.93</v>
       </c>
       <c r="M1666">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="N1666">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="O1666">
         <v>1</v>
@@ -85358,7 +85358,7 @@
         <v>380</v>
       </c>
       <c r="E1668">
-        <v>0.9686817713155447</v>
+        <v>0.9660374363479498</v>
       </c>
       <c r="F1668">
         <v>1</v>
@@ -85367,10 +85367,10 @@
         <v>0.004901318228684455</v>
       </c>
       <c r="H1668">
-        <v>0.004911318228684456</v>
+        <v>0.00489396256365205</v>
       </c>
       <c r="I1668">
-        <v>0.009999999999999787</v>
+        <v>0.007355665032404923</v>
       </c>
       <c r="J1668">
         <v>0.7355665032404684</v>
@@ -85382,10 +85382,10 @@
         <v>2.93</v>
       </c>
       <c r="M1668">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="N1668">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="O1668">
         <v>1</v>
@@ -85458,7 +85458,7 @@
         <v>380</v>
       </c>
       <c r="E1670">
-        <v>0.9642230332364479</v>
+        <v>0.9615953353512376</v>
       </c>
       <c r="F1670">
         <v>1</v>
@@ -85467,10 +85467,10 @@
         <v>0.004905776966763553</v>
       </c>
       <c r="H1670">
-        <v>0.004915776966763552</v>
+        <v>0.004898404664648763</v>
       </c>
       <c r="I1670">
-        <v>0.009999999999999787</v>
+        <v>0.007372302114789564</v>
       </c>
       <c r="J1670">
         <v>0.7372302114789373</v>
@@ -85482,10 +85482,10 @@
         <v>2.93</v>
       </c>
       <c r="M1670">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="N1670">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="O1670">
         <v>1</v>
@@ -85558,7 +85558,7 @@
         <v>380</v>
       </c>
       <c r="E1672">
-        <v>0.9593037659228998</v>
+        <v>0.9566944235127401</v>
       </c>
       <c r="F1672">
         <v>1</v>
@@ -85567,10 +85567,10 @@
         <v>0.004910696234077101</v>
       </c>
       <c r="H1672">
-        <v>0.0049206962340771</v>
+        <v>0.00490330557648726</v>
       </c>
       <c r="I1672">
-        <v>0.009999999999999787</v>
+        <v>0.007390657589840144</v>
       </c>
       <c r="J1672">
         <v>0.7390657589839925</v>
@@ -85582,10 +85582,10 @@
         <v>2.93</v>
       </c>
       <c r="M1672">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="N1672">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="O1672">
         <v>1</v>
@@ -85658,7 +85658,7 @@
         <v>380</v>
       </c>
       <c r="E1674">
-        <v>0.9542677785678251</v>
+        <v>0.9516772271552589</v>
       </c>
       <c r="F1674">
         <v>1</v>
@@ -85667,10 +85667,10 @@
         <v>0.004915732221432175</v>
       </c>
       <c r="H1674">
-        <v>0.004925732221432175</v>
+        <v>0.004908322772844741</v>
       </c>
       <c r="I1674">
-        <v>0.009999999999999787</v>
+        <v>0.007409448587433642</v>
       </c>
       <c r="J1674">
         <v>0.7409448587433488</v>
@@ -85682,10 +85682,10 @@
         <v>2.93</v>
       </c>
       <c r="M1674">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="N1674">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="O1674">
         <v>1</v>
@@ -85758,7 +85758,7 @@
         <v>380</v>
       </c>
       <c r="E1676">
-        <v>0.9487358316549499</v>
+        <v>0.9461659218353422</v>
       </c>
       <c r="F1676">
         <v>1</v>
@@ -85767,10 +85767,10 @@
         <v>0.00492126416834505</v>
       </c>
       <c r="H1676">
-        <v>0.004931264168345051</v>
+        <v>0.004913834078164659</v>
       </c>
       <c r="I1676">
-        <v>0.009999999999999787</v>
+        <v>0.00743009018039209</v>
       </c>
       <c r="J1676">
         <v>0.7430090180391977</v>
@@ -85782,10 +85782,10 @@
         <v>2.93</v>
       </c>
       <c r="M1676">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="N1676">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="O1676">
         <v>1</v>
@@ -85858,7 +85858,7 @@
         <v>380</v>
       </c>
       <c r="E1678">
-        <v>0.9436111967176886</v>
+        <v>0.9410604086702348</v>
       </c>
       <c r="F1678">
         <v>1</v>
@@ -85867,10 +85867,10 @@
         <v>0.004926388803282312</v>
       </c>
       <c r="H1678">
-        <v>0.004936388803282311</v>
+        <v>0.004918939591329765</v>
       </c>
       <c r="I1678">
-        <v>0.009999999999999787</v>
+        <v>0.007449211952545998</v>
       </c>
       <c r="J1678">
         <v>0.7449211952545938</v>
@@ -85882,10 +85882,10 @@
         <v>2.93</v>
       </c>
       <c r="M1678">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="N1678">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="O1678">
         <v>1</v>
@@ -85958,7 +85958,7 @@
         <v>380</v>
       </c>
       <c r="E1680">
-        <v>0.9386834930876033</v>
+        <v>0.9361510919939933</v>
       </c>
       <c r="F1680">
         <v>1</v>
@@ -85967,10 +85967,10 @@
         <v>0.004931316506912397</v>
       </c>
       <c r="H1680">
-        <v>0.004941316506912397</v>
+        <v>0.004923848908006007</v>
       </c>
       <c r="I1680">
-        <v>0.009999999999999787</v>
+        <v>0.007467598906389705</v>
       </c>
       <c r="J1680">
         <v>0.7467598906389539</v>
@@ -85982,10 +85982,10 @@
         <v>2.93</v>
       </c>
       <c r="M1680">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="N1680">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="O1680">
         <v>1</v>
@@ -86058,7 +86058,7 @@
         <v>380</v>
       </c>
       <c r="E1682">
-        <v>0.936055864041728</v>
+        <v>0.9335332675341099</v>
       </c>
       <c r="F1682">
         <v>1</v>
@@ -86067,10 +86067,10 @@
         <v>0.004933944135958272</v>
       </c>
       <c r="H1682">
-        <v>0.004943944135958272</v>
+        <v>0.00492646673246589</v>
       </c>
       <c r="I1682">
-        <v>0.009999999999999787</v>
+        <v>0.007477403492381685</v>
       </c>
       <c r="J1682">
         <v>0.7477403492381611</v>
@@ -86082,10 +86082,10 @@
         <v>2.93</v>
       </c>
       <c r="M1682">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="N1682">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="O1682">
         <v>1</v>
@@ -86158,7 +86158,7 @@
         <v>380</v>
       </c>
       <c r="E1684">
-        <v>0.9352121457429101</v>
+        <v>0.9326926974378997</v>
       </c>
       <c r="F1684">
         <v>1</v>
@@ -86167,10 +86167,10 @@
         <v>0.00493478785425709</v>
       </c>
       <c r="H1684">
-        <v>0.00494478785425709</v>
+        <v>0.004927307302562101</v>
       </c>
       <c r="I1684">
-        <v>0.009999999999999787</v>
+        <v>0.007480551694989401</v>
       </c>
       <c r="J1684">
         <v>0.748055169498914</v>
@@ -86182,10 +86182,10 @@
         <v>2.93</v>
       </c>
       <c r="M1684">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="N1684">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="O1684">
         <v>1</v>
@@ -86258,7 +86258,7 @@
         <v>380</v>
       </c>
       <c r="E1686">
-        <v>0.9327215988209714</v>
+        <v>0.9302114436014906</v>
       </c>
       <c r="F1686">
         <v>1</v>
@@ -86267,10 +86267,10 @@
         <v>0.004937278401179029</v>
       </c>
       <c r="H1686">
-        <v>0.004947278401179029</v>
+        <v>0.00492978855639851</v>
       </c>
       <c r="I1686">
-        <v>0.009999999999999787</v>
+        <v>0.007489844780518951</v>
       </c>
       <c r="J1686">
         <v>0.7489844780518763</v>
@@ -86282,66 +86282,16 @@
         <v>2.93</v>
       </c>
       <c r="M1686">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="N1686">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="O1686">
         <v>1</v>
       </c>
       <c r="P1686" t="s">
         <v>377</v>
-      </c>
-    </row>
-    <row r="1687" spans="1:16">
-      <c r="A1687" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1687" t="s">
-        <v>211</v>
-      </c>
-      <c r="C1687">
-        <v>0.9224415211568262</v>
-      </c>
-      <c r="D1687" t="s">
-        <v>380</v>
-      </c>
-      <c r="E1687">
-        <v>0.932441521156826</v>
-      </c>
-      <c r="F1687">
-        <v>1</v>
-      </c>
-      <c r="G1687">
-        <v>0.004937558478843174</v>
-      </c>
-      <c r="H1687">
-        <v>0.004947558478843174</v>
-      </c>
-      <c r="I1687">
-        <v>0.009999999999999787</v>
-      </c>
-      <c r="J1687">
-        <v>0.7490889846429754</v>
-      </c>
-      <c r="K1687">
-        <v>2.68</v>
-      </c>
-      <c r="L1687">
-        <v>2.93</v>
-      </c>
-      <c r="M1687">
-        <v>2.68</v>
-      </c>
-      <c r="N1687">
-        <v>2.94</v>
-      </c>
-      <c r="O1687">
-        <v>1</v>
-      </c>
-      <c r="P1687" t="s">
-        <v>210</v>
       </c>
     </row>
   </sheetData>
